--- a/data/SDET_SQA_DATA.xlsx
+++ b/data/SDET_SQA_DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WHSU\Desktop\Workspace\CycleView\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FF7224-6937-4EBA-B867-A935676821CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00A1364-E8D9-45F6-A83A-3350FC33E41F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4380" yWindow="1995" windowWidth="19260" windowHeight="13860" xr2:uid="{EB11FF79-EF06-B64E-AA6A-0CFF391A8BD1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{EB11FF79-EF06-B64E-AA6A-0CFF391A8BD1}"/>
   </bookViews>
   <sheets>
     <sheet name="TestAutomationProgress" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="103">
   <si>
     <t>TODO (P1)</t>
   </si>
@@ -99,21 +99,6 @@
   </si>
   <si>
     <t>To Do</t>
-  </si>
-  <si>
-    <t>v1.15</t>
-  </si>
-  <si>
-    <t>v1.16</t>
-  </si>
-  <si>
-    <t>v1.17</t>
-  </si>
-  <si>
-    <t>v1.18</t>
-  </si>
-  <si>
-    <t>v1.19</t>
   </si>
   <si>
     <t>v1.20</t>
@@ -346,6 +331,27 @@
   <si>
     <t>26W05</t>
   </si>
+  <si>
+    <t>v1.38</t>
+  </si>
+  <si>
+    <t>v1.39</t>
+  </si>
+  <si>
+    <t>y26w8</t>
+  </si>
+  <si>
+    <t>y26w10</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Candidate</t>
+  </si>
+  <si>
+    <t>26W06</t>
+  </si>
 </sst>
 </file>
 
@@ -533,6 +539,10 @@
   </cellStyles>
   <dxfs count="36">
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -708,33 +718,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -809,6 +792,13 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -833,13 +823,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -860,7 +843,33 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
@@ -892,9 +901,6 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1082,9 +1088,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$26</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>25W32</c:v>
                 </c:pt>
@@ -1159,16 +1165,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>26W05</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26W06</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$B$2:$B$26</c:f>
+              <c:f>TestAutomationProgress!$B$2:$B$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -1243,6 +1252,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>31</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1339,9 +1351,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$26</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>25W32</c:v>
                 </c:pt>
@@ -1416,16 +1428,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>26W05</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26W06</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$C$2:$C$26</c:f>
+              <c:f>TestAutomationProgress!$C$2:$C$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1500,6 +1515,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1596,9 +1614,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$26</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>25W32</c:v>
                 </c:pt>
@@ -1673,16 +1691,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>26W05</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26W06</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$D$2:$D$26</c:f>
+              <c:f>TestAutomationProgress!$D$2:$D$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>115</c:v>
                 </c:pt>
@@ -1756,6 +1777,9 @@
                   <c:v>162</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>161</c:v>
                 </c:pt>
               </c:numCache>
@@ -2133,9 +2157,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$17</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$18</c:f>
               <c:strCache>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2183,16 +2207,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>v1.37</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>v1.38</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$B$2:$B$17</c:f>
+              <c:f>'Humi-TestResult'!$B$2:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>421</c:v>
                 </c:pt>
@@ -2239,7 +2266,10 @@
                   <c:v>1642</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1204</c:v>
+                  <c:v>1350</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>388</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2276,9 +2306,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$17</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$18</c:f>
               <c:strCache>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2326,16 +2356,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>v1.37</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>v1.38</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$C$2:$C$17</c:f>
+              <c:f>'Humi-TestResult'!$C$2:$C$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2383,6 +2416,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2427,9 +2463,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$17</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$18</c:f>
               <c:strCache>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2477,16 +2513,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>v1.37</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>v1.38</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$D$2:$D$17</c:f>
+              <c:f>'Humi-TestResult'!$D$2:$D$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>12</c:v>
                 </c:pt>
@@ -2533,7 +2572,10 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>6</c:v>
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2624,9 +2666,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$17</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$18</c:f>
               <c:strCache>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2674,16 +2716,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>v1.37</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>v1.38</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$E$2:$E$17</c:f>
+              <c:f>'Humi-TestResult'!$E$2:$E$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -2731,6 +2776,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2767,9 +2815,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$17</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$18</c:f>
               <c:strCache>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2817,16 +2865,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>v1.37</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>v1.38</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$F$2:$F$17</c:f>
+              <c:f>'Humi-TestResult'!$F$2:$F$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -2874,6 +2925,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2912,9 +2966,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$17</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$18</c:f>
               <c:strCache>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2962,16 +3016,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>v1.37</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>v1.38</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$G$2:$G$17</c:f>
+              <c:f>'Humi-TestResult'!$G$2:$G$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3018,7 +3075,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>199</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>494</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3132,9 +3192,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$17</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$18</c:f>
               <c:strCache>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -3182,16 +3242,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>v1.37</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>v1.38</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$H$2:$H$17</c:f>
+              <c:f>'Humi-TestResult'!$H$2:$H$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>442</c:v>
                 </c:pt>
@@ -3238,7 +3301,10 @@
                   <c:v>1676</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1423</c:v>
+                  <c:v>1374</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>882</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3612,9 +3678,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$30</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -3701,16 +3767,19 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>26W04</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>26W06</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$B$2:$B$30</c:f>
+              <c:f>'SOVA-TestResult'!$B$2:$B$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>38</c:v>
                 </c:pt>
@@ -3772,7 +3841,10 @@
                   <c:v>636</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>336</c:v>
+                  <c:v>436</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3866,9 +3938,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$30</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -3955,16 +4027,19 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>26W04</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>26W06</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$C$2:$C$30</c:f>
+              <c:f>'SOVA-TestResult'!$C$2:$C$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4027,6 +4102,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4063,9 +4141,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$30</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4152,16 +4230,19 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>26W04</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>26W06</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$D$2:$D$30</c:f>
+              <c:f>'SOVA-TestResult'!$D$2:$D$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4224,6 +4305,9 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4260,9 +4344,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$30</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4349,16 +4433,19 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>26W04</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>26W06</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$E$2:$E$30</c:f>
+              <c:f>'SOVA-TestResult'!$E$2:$E$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
                 </c:pt>
@@ -4420,7 +4507,10 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>5</c:v>
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4531,9 +4621,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$30</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4620,16 +4710,19 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>26W04</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>26W06</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$F$2:$F$30</c:f>
+              <c:f>'SOVA-TestResult'!$F$2:$F$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>11</c:v>
                 </c:pt>
@@ -4691,7 +4784,10 @@
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>5</c:v>
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4731,9 +4827,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$30</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4820,16 +4916,19 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>26W04</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>26W06</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$G$2:$G$30</c:f>
+              <c:f>'SOVA-TestResult'!$G$2:$G$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4891,7 +4990,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>116</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>455</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4933,9 +5035,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$30</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -5022,16 +5124,19 @@
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>26W04</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>26W06</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$H$2:$H$30</c:f>
+              <c:f>'SOVA-TestResult'!$H$2:$H$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>54</c:v>
                 </c:pt>
@@ -5093,7 +5198,10 @@
                   <c:v>650</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>470</c:v>
+                  <c:v>464</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>639</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5463,155 +5571,137 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$24</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="23"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>v1.15</c:v>
+                  <c:v>v1.20</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>v1.16</c:v>
+                  <c:v>v1.21</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>v1.17</c:v>
+                  <c:v>v1.22</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>v1.18</c:v>
+                  <c:v>v1.23</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>v1.19</c:v>
+                  <c:v>v1.24</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>v1.20</c:v>
+                  <c:v>v1.25</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>v1.21</c:v>
+                  <c:v>v1.26</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>v1.22</c:v>
+                  <c:v>v1.27</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>v1.23</c:v>
+                  <c:v>v1.28</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>v1.24</c:v>
+                  <c:v>v1.29</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>v1.25</c:v>
+                  <c:v>v1.30</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>v1.26</c:v>
+                  <c:v>v1.31</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>v1.27</c:v>
+                  <c:v>v1.32</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>v1.28</c:v>
+                  <c:v>v1.33</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>v1.29</c:v>
+                  <c:v>v1.34</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>v1.30</c:v>
+                  <c:v>v1.35</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>v1.31</c:v>
+                  <c:v>v1.36</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>v1.32</c:v>
+                  <c:v>v1.37</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>v1.33</c:v>
+                  <c:v>v1.38</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>v1.34</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>v1.35</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>v1.36</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>v1.37</c:v>
+                  <c:v>v1.39</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$B$2:$B$24</c:f>
+              <c:f>'Humi-BugTrend'!$B$2:$B$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>8</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>30</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>14</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>15</c:v>
-                </c:pt>
                 <c:pt idx="6">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>7</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="17">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="15">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5651,87 +5741,78 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$24</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="23"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>v1.15</c:v>
+                  <c:v>v1.20</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>v1.16</c:v>
+                  <c:v>v1.21</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>v1.17</c:v>
+                  <c:v>v1.22</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>v1.18</c:v>
+                  <c:v>v1.23</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>v1.19</c:v>
+                  <c:v>v1.24</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>v1.20</c:v>
+                  <c:v>v1.25</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>v1.21</c:v>
+                  <c:v>v1.26</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>v1.22</c:v>
+                  <c:v>v1.27</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>v1.23</c:v>
+                  <c:v>v1.28</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>v1.24</c:v>
+                  <c:v>v1.29</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>v1.25</c:v>
+                  <c:v>v1.30</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>v1.26</c:v>
+                  <c:v>v1.31</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>v1.27</c:v>
+                  <c:v>v1.32</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>v1.28</c:v>
+                  <c:v>v1.33</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>v1.29</c:v>
+                  <c:v>v1.34</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>v1.30</c:v>
+                  <c:v>v1.35</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>v1.31</c:v>
+                  <c:v>v1.36</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>v1.32</c:v>
+                  <c:v>v1.37</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>v1.33</c:v>
+                  <c:v>v1.38</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>v1.34</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>v1.35</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>v1.36</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>v1.37</c:v>
+                  <c:v>v1.39</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$C$2:$C$24</c:f>
+              <c:f>'Humi-BugTrend'!$C$2:$C$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5757,7 +5838,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -5772,33 +5853,24 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
                 <c:pt idx="16">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5839,113 +5911,104 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$24</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="23"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>v1.15</c:v>
+                  <c:v>v1.20</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>v1.16</c:v>
+                  <c:v>v1.21</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>v1.17</c:v>
+                  <c:v>v1.22</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>v1.18</c:v>
+                  <c:v>v1.23</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>v1.19</c:v>
+                  <c:v>v1.24</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>v1.20</c:v>
+                  <c:v>v1.25</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>v1.21</c:v>
+                  <c:v>v1.26</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>v1.22</c:v>
+                  <c:v>v1.27</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>v1.23</c:v>
+                  <c:v>v1.28</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>v1.24</c:v>
+                  <c:v>v1.29</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>v1.25</c:v>
+                  <c:v>v1.30</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>v1.26</c:v>
+                  <c:v>v1.31</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>v1.27</c:v>
+                  <c:v>v1.32</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>v1.28</c:v>
+                  <c:v>v1.33</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>v1.29</c:v>
+                  <c:v>v1.34</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>v1.30</c:v>
+                  <c:v>v1.35</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>v1.31</c:v>
+                  <c:v>v1.36</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>v1.32</c:v>
+                  <c:v>v1.37</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>v1.33</c:v>
+                  <c:v>v1.38</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>v1.34</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>v1.35</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>v1.36</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>v1.37</c:v>
+                  <c:v>v1.39</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$D$2:$D$24</c:f>
+              <c:f>'Humi-BugTrend'!$D$2:$D$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -5972,22 +6035,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6024,87 +6078,78 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$24</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="23"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>v1.15</c:v>
+                  <c:v>v1.20</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>v1.16</c:v>
+                  <c:v>v1.21</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>v1.17</c:v>
+                  <c:v>v1.22</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>v1.18</c:v>
+                  <c:v>v1.23</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>v1.19</c:v>
+                  <c:v>v1.24</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>v1.20</c:v>
+                  <c:v>v1.25</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>v1.21</c:v>
+                  <c:v>v1.26</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>v1.22</c:v>
+                  <c:v>v1.27</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>v1.23</c:v>
+                  <c:v>v1.28</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>v1.24</c:v>
+                  <c:v>v1.29</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>v1.25</c:v>
+                  <c:v>v1.30</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>v1.26</c:v>
+                  <c:v>v1.31</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>v1.27</c:v>
+                  <c:v>v1.32</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>v1.28</c:v>
+                  <c:v>v1.33</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>v1.29</c:v>
+                  <c:v>v1.34</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>v1.30</c:v>
+                  <c:v>v1.35</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>v1.31</c:v>
+                  <c:v>v1.36</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>v1.32</c:v>
+                  <c:v>v1.37</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>v1.33</c:v>
+                  <c:v>v1.38</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>v1.34</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>v1.35</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>v1.36</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>v1.37</c:v>
+                  <c:v>v1.39</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$E$2:$E$24</c:f>
+              <c:f>'Humi-BugTrend'!$E$2:$E$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6163,15 +6208,6 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="22">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -6209,87 +6245,78 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$24</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="23"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>v1.15</c:v>
+                  <c:v>v1.20</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>v1.16</c:v>
+                  <c:v>v1.21</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>v1.17</c:v>
+                  <c:v>v1.22</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>v1.18</c:v>
+                  <c:v>v1.23</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>v1.19</c:v>
+                  <c:v>v1.24</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>v1.20</c:v>
+                  <c:v>v1.25</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>v1.21</c:v>
+                  <c:v>v1.26</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>v1.22</c:v>
+                  <c:v>v1.27</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>v1.23</c:v>
+                  <c:v>v1.28</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>v1.24</c:v>
+                  <c:v>v1.29</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>v1.25</c:v>
+                  <c:v>v1.30</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>v1.26</c:v>
+                  <c:v>v1.31</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>v1.27</c:v>
+                  <c:v>v1.32</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>v1.28</c:v>
+                  <c:v>v1.33</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>v1.29</c:v>
+                  <c:v>v1.34</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>v1.30</c:v>
+                  <c:v>v1.35</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>v1.31</c:v>
+                  <c:v>v1.36</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>v1.32</c:v>
+                  <c:v>v1.37</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>v1.33</c:v>
+                  <c:v>v1.38</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>v1.34</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>v1.35</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>v1.36</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>v1.37</c:v>
+                  <c:v>v1.39</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$F$2:$F$24</c:f>
+              <c:f>'Humi-BugTrend'!$F$2:$F$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6342,22 +6369,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6394,155 +6412,137 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$24</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="23"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>v1.15</c:v>
+                  <c:v>v1.20</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>v1.16</c:v>
+                  <c:v>v1.21</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>v1.17</c:v>
+                  <c:v>v1.22</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>v1.18</c:v>
+                  <c:v>v1.23</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>v1.19</c:v>
+                  <c:v>v1.24</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>v1.20</c:v>
+                  <c:v>v1.25</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>v1.21</c:v>
+                  <c:v>v1.26</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>v1.22</c:v>
+                  <c:v>v1.27</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>v1.23</c:v>
+                  <c:v>v1.28</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>v1.24</c:v>
+                  <c:v>v1.29</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>v1.25</c:v>
+                  <c:v>v1.30</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>v1.26</c:v>
+                  <c:v>v1.31</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>v1.27</c:v>
+                  <c:v>v1.32</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>v1.28</c:v>
+                  <c:v>v1.33</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>v1.29</c:v>
+                  <c:v>v1.34</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>v1.30</c:v>
+                  <c:v>v1.35</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>v1.31</c:v>
+                  <c:v>v1.36</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>v1.32</c:v>
+                  <c:v>v1.37</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>v1.33</c:v>
+                  <c:v>v1.38</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>v1.34</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>v1.35</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>v1.36</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>v1.37</c:v>
+                  <c:v>v1.39</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$G$2:$G$24</c:f>
+              <c:f>'Humi-BugTrend'!$G$2:$G$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>93</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>59</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>168</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>156</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>77</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>61</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>43</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>33</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>25</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>56</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>40</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>33</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>29</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>9</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>12</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>37</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>33</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6581,155 +6581,137 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$24</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="23"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>v1.15</c:v>
+                  <c:v>v1.20</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>v1.16</c:v>
+                  <c:v>v1.21</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>v1.17</c:v>
+                  <c:v>v1.22</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>v1.18</c:v>
+                  <c:v>v1.23</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>v1.19</c:v>
+                  <c:v>v1.24</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>v1.20</c:v>
+                  <c:v>v1.25</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>v1.21</c:v>
+                  <c:v>v1.26</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>v1.22</c:v>
+                  <c:v>v1.27</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>v1.23</c:v>
+                  <c:v>v1.28</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>v1.24</c:v>
+                  <c:v>v1.29</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>v1.25</c:v>
+                  <c:v>v1.30</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>v1.26</c:v>
+                  <c:v>v1.31</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>v1.27</c:v>
+                  <c:v>v1.32</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>v1.28</c:v>
+                  <c:v>v1.33</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>v1.29</c:v>
+                  <c:v>v1.34</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>v1.30</c:v>
+                  <c:v>v1.35</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>v1.31</c:v>
+                  <c:v>v1.36</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>v1.32</c:v>
+                  <c:v>v1.37</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>v1.33</c:v>
+                  <c:v>v1.38</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>v1.34</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>v1.35</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>v1.36</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>v1.37</c:v>
+                  <c:v>v1.39</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$H$2:$H$24</c:f>
+              <c:f>'Humi-BugTrend'!$H$2:$H$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>101</c:v>
+                  <c:v>77</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>66</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>193</c:v>
+                  <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>186</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>91</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>77</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>53</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>63</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>51</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>51</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>70</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>50</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>39</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>41</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>22</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>13</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>13</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>54</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>42</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>6</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7102,89 +7084,101 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
+                  <c:v>None</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Candidate</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>y25w16</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>y25w18</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>y25w20</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>y25w22</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>y25w24</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>y25w26</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>y25w28</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>y25w30</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>y25w32</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>y25w34</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>y25w36</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>y25w38</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>y25w40</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>y25w42</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>y25w44</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>y25w46</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>y25w48</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>y25w50</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>y25w52</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>y26w2</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>y26w4</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>y26w6</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>y26w8</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>y26w10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$B$2:$B$23</c:f>
+              <c:f>'SOVA-BugTrend'!$B$2:$B$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>158</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -7199,10 +7193,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>1</c:v>
@@ -7211,17 +7205,17 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
                 <c:pt idx="14">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7229,22 +7223,34 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="24">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="17">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>5</c:v>
+                <c:pt idx="25">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7338,84 +7344,96 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
+                  <c:v>None</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Candidate</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>y25w16</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>y25w18</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>y25w20</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>y25w22</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>y25w24</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>y25w26</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>y25w28</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>y25w30</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>y25w32</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>y25w34</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>y25w36</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>y25w38</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>y25w40</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>y25w42</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>y25w44</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>y25w46</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>y25w48</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>y25w50</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>y25w52</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>y26w2</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>y26w4</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>y26w6</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>y26w8</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>y26w10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$C$2:$C$23</c:f>
+              <c:f>'SOVA-BugTrend'!$C$2:$C$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7477,9 +7495,21 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -7574,86 +7604,98 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
+                  <c:v>None</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Candidate</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>y25w16</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>y25w18</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>y25w20</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>y25w22</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>y25w24</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>y25w26</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>y25w28</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>y25w30</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>y25w32</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>y25w34</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>y25w36</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>y25w38</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>y25w40</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>y25w42</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>y25w44</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>y25w46</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>y25w48</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>y25w50</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>y25w52</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>y26w2</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>y26w4</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>y26w6</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>y26w8</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>y26w10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$D$2:$D$23</c:f>
+              <c:f>'SOVA-BugTrend'!$D$2:$D$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -7713,9 +7755,21 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -7810,86 +7864,98 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
+                  <c:v>None</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Candidate</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>y25w16</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>y25w18</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>y25w20</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>y25w22</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>y25w24</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>y25w26</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>y25w28</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>y25w30</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>y25w32</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>y25w34</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>y25w36</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>y25w38</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>y25w40</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>y25w42</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>y25w44</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>y25w46</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>y25w48</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>y25w50</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>y25w52</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>y26w2</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>y26w4</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>y26w6</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>y26w8</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>y26w10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$E$2:$E$23</c:f>
+              <c:f>'SOVA-BugTrend'!$E$2:$E$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -7946,13 +8012,25 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="20">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1</c:v>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7989,84 +8067,96 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
+                  <c:v>None</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Candidate</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>y25w16</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>y25w18</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>y25w20</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>y25w22</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>y25w24</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>y25w26</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>y25w28</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>y25w30</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>y25w32</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>y25w34</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>y25w36</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>y25w38</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>y25w40</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>y25w42</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>y25w44</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>y25w46</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>y25w48</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>y25w50</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>y25w52</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>y26w2</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>y26w4</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>y26w6</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>y26w8</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>y26w10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$F$2:$F$23</c:f>
+              <c:f>'SOVA-BugTrend'!$F$2:$F$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8128,9 +8218,21 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -8222,148 +8324,172 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
+                  <c:v>None</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Candidate</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>y25w16</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>y25w18</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>y25w20</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>y25w22</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>y25w24</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>y25w26</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>y25w28</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>y25w30</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>y25w32</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>y25w34</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>y25w36</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>y25w38</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>y25w40</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>y25w42</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>y25w44</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>y25w46</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>y25w48</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>y25w50</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>y25w52</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>y26w2</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>y26w4</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>y26w6</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>y26w8</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>y26w10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$G$2:$G$23</c:f>
+              <c:f>'SOVA-BugTrend'!$G$2:$G$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>16</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>16</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>55</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>35</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>39</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>39</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>45</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>18</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>25</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>45</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>24</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>43</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>35</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>29</c:v>
                 </c:pt>
-                <c:pt idx="16">
-                  <c:v>38</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>30</c:v>
-                </c:pt>
                 <c:pt idx="18">
-                  <c:v>28</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>27</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>20</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="21">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -8403,129 +8529,141 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
+                  <c:v>None</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Candidate</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>y25w16</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>y25w18</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>y25w20</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>y25w22</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>y25w24</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>y25w26</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>y25w28</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>y25w30</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>y25w32</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>y25w34</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>y25w36</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>y25w38</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>y25w40</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>y25w42</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>y25w44</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>y25w46</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>y25w48</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>y25w50</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>y25w52</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>y26w2</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>y26w4</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>y26w6</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>y26w8</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>y26w10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$H$2:$H$23</c:f>
+              <c:f>'SOVA-BugTrend'!$H$2:$H$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
                 <c:pt idx="2">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>7</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8536,15 +8674,27 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -8584,149 +8734,173 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
+                  <c:v>None</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Candidate</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>y25w16</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>y25w18</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>y25w20</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>y25w22</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>y25w24</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>y25w26</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>y25w28</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>y25w30</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>y25w32</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>y25w34</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>y25w36</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>y25w38</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>y25w40</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>y25w42</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>y25w44</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>y25w46</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>y25w48</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>y25w50</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>y25w52</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>y26w2</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>y26w4</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>y26w6</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>y26w8</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>y26w10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$I$2:$I$23</c:f>
+              <c:f>'SOVA-BugTrend'!$I$2:$I$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
+                  <c:v>357</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>23</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>22</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>18</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>18</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>59</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>39</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>42</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>46</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>53</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>32</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>53</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>25</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>43</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>35</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>29</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>44</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>6</c:v>
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11658,13 +11832,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>171448</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>133348</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -11699,13 +11873,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1028700</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -11740,13 +11914,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>69662</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1057275</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>31562</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -11781,13 +11955,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>88899</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -11822,13 +11996,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -11858,8 +12032,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}" name="Table2" displayName="Table2" ref="A1:E26" totalsRowShown="0" headerRowDxfId="35">
-  <autoFilter ref="A1:E26" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}" name="Table2" displayName="Table2" ref="A1:E27" totalsRowShown="0" headerRowDxfId="35">
+  <autoFilter ref="A1:E27" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F25F0D34-0297-4771-8BBB-350BCDD85D46}" name="Week"/>
     <tableColumn id="2" xr3:uid="{39CFCD12-3130-47A8-A140-DBF602F1743D}" name="Done"/>
@@ -11874,8 +12048,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E42B6291-7056-475B-AE1E-CA59C524E5F1}" name="Table1" displayName="Table1" ref="A1:H17" totalsRowShown="0" headerRowDxfId="33">
-  <autoFilter ref="A1:H17" xr:uid="{E42B6291-7056-475B-AE1E-CA59C524E5F1}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E42B6291-7056-475B-AE1E-CA59C524E5F1}" name="Table1" displayName="Table1" ref="A1:H18" totalsRowShown="0" headerRowDxfId="33">
+  <autoFilter ref="A1:H18" xr:uid="{E42B6291-7056-475B-AE1E-CA59C524E5F1}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{9154D4F8-C83D-4DB9-9182-818F32FA7C26}" name="Versions"/>
     <tableColumn id="2" xr3:uid="{1FE19FA2-B8BE-47BC-9953-F802445DE79D}" name="Passed"/>
@@ -11884,7 +12058,7 @@
     <tableColumn id="5" xr3:uid="{DC0F99B4-F7A9-4F8A-BBA0-6D907EC37C98}" name="Failed"/>
     <tableColumn id="6" xr3:uid="{2F758004-8A07-4C9F-A1EF-D5DABF4F31F0}" name="Partially Failed"/>
     <tableColumn id="7" xr3:uid="{DA700F0A-CDCF-4F77-AE73-82D409134037}" name="Untested"/>
-    <tableColumn id="8" xr3:uid="{F186EC08-2AB3-485D-B982-BDBCE5ABE745}" name="Total" dataDxfId="32">
+    <tableColumn id="8" xr3:uid="{F186EC08-2AB3-485D-B982-BDBCE5ABE745}" name="Total" dataDxfId="0">
       <calculatedColumnFormula>SUM(Table1[[#This Row],[Passed]:[Untested]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11893,8 +12067,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}" name="Table3" displayName="Table3" ref="A1:H30" totalsRowShown="0" headerRowDxfId="31">
-  <autoFilter ref="A1:H30" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}" name="Table3" displayName="Table3" ref="A1:H31" totalsRowShown="0" headerRowDxfId="32">
+  <autoFilter ref="A1:H31" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{8103CDF3-74DC-4B31-821D-E20368EA5455}" name="Versions"/>
     <tableColumn id="2" xr3:uid="{6C3B261F-FA51-42D2-821A-F22633569372}" name="Passed"/>
@@ -11903,7 +12077,7 @@
     <tableColumn id="5" xr3:uid="{41B83D2F-6D51-4667-B2B2-F76F6482C1D1}" name="Failed"/>
     <tableColumn id="6" xr3:uid="{26F61733-CA12-4B2B-8922-ABF23FA1A0CF}" name="Partially Failed"/>
     <tableColumn id="7" xr3:uid="{D40FAE8C-0F59-4E72-8577-B404EAC3FBFC}" name="Untested"/>
-    <tableColumn id="8" xr3:uid="{9EDBB1BE-19AD-4F52-9FAF-1ED9F6FC2EBD}" name="Total" dataDxfId="30">
+    <tableColumn id="8" xr3:uid="{9EDBB1BE-19AD-4F52-9FAF-1ED9F6FC2EBD}" name="Total" dataDxfId="31">
       <calculatedColumnFormula>SUM(Table3[[#This Row],[Passed]:[Untested]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11912,17 +12086,17 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{E4AD0B7A-EC5B-4838-AC2B-8475A3B6644B}" name="Table7" displayName="Table7" ref="A1:H24" totalsRowShown="0" headerRowDxfId="29">
-  <autoFilter ref="A1:H24" xr:uid="{E4AD0B7A-EC5B-4838-AC2B-8475A3B6644B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{E4AD0B7A-EC5B-4838-AC2B-8475A3B6644B}" name="Table7" displayName="Table7" ref="A1:H21" totalsRowShown="0" headerRowDxfId="30">
+  <autoFilter ref="A1:H21" xr:uid="{E4AD0B7A-EC5B-4838-AC2B-8475A3B6644B}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{58F8A895-CEBE-41D2-B7BB-1681C0697C85}" name="Version"/>
-    <tableColumn id="2" xr3:uid="{CE08A48D-2419-484B-993C-54A546869B61}" name="To Do" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{FC519478-6B36-4D96-93F3-3AF4B1D70F3E}" name="In Progress" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{52258D92-71B9-4E63-A3AA-5ABE6B4F3D23}" name="In Review" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{C5EE39F3-E9DF-4F2E-9576-6DDB97E21DB3}" name="In QA" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{CC106112-C63E-4AA5-9AAA-D0A99983E0DD}" name="Internal Test" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{C69EECCF-E5E5-4372-B171-2B35FE10B60D}" name="Done" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{C7A900BC-8967-4049-AE22-7F9EDE21E913}" name="Total" dataDxfId="22" totalsRowDxfId="21">
+    <tableColumn id="2" xr3:uid="{CE08A48D-2419-484B-993C-54A546869B61}" name="To Do" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{FC519478-6B36-4D96-93F3-3AF4B1D70F3E}" name="In Progress" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{52258D92-71B9-4E63-A3AA-5ABE6B4F3D23}" name="In Review" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{C5EE39F3-E9DF-4F2E-9576-6DDB97E21DB3}" name="In QA" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{CC106112-C63E-4AA5-9AAA-D0A99983E0DD}" name="Internal Test" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{C69EECCF-E5E5-4372-B171-2B35FE10B60D}" name="Done" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{C7A900BC-8967-4049-AE22-7F9EDE21E913}" name="Total" dataDxfId="15" totalsRowDxfId="23">
       <calculatedColumnFormula>SUM(Table7[[#This Row],[To Do]:[Done]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11931,18 +12105,18 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}" name="Table5" displayName="Table5" ref="A1:I23" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17" totalsRowBorderDxfId="16" dataCellStyle="Hyperlink">
-  <autoFilter ref="A1:I23" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}" name="Table5" displayName="Table5" ref="A1:I27" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" headerRowBorderDxfId="11" tableBorderDxfId="12" totalsRowBorderDxfId="10" dataCellStyle="Hyperlink">
+  <autoFilter ref="A1:I27" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{5BE08AE0-E0B5-4B46-9423-456B88C2D9BC}" name="Sprint" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{030F9647-4FC0-4C7E-9B3A-AB099CC59EBA}" name="To Do (0%)" dataDxfId="6" dataCellStyle="Hyperlink"/>
-    <tableColumn id="3" xr3:uid="{7D2923F3-E2CF-4FD9-A7A5-68C36BB95591}" name="STARTING (10 ~ 40%)" dataDxfId="5" dataCellStyle="Hyperlink"/>
-    <tableColumn id="4" xr3:uid="{48FB5317-7F3B-4F74-B244-5A49C7749EBD}" name="In Progress (50 ~ 70%)" dataDxfId="4" dataCellStyle="Hyperlink"/>
-    <tableColumn id="5" xr3:uid="{86F5CCB5-C4C2-4C36-935A-657F085500B1}" name="IN REVIEW (80%)" dataDxfId="3" dataCellStyle="Hyperlink"/>
-    <tableColumn id="9" xr3:uid="{51D22AE3-424C-4604-9869-D672DED4301F}" name="READY FOR TESTING (90%)" dataDxfId="2" dataCellStyle="Hyperlink"/>
-    <tableColumn id="6" xr3:uid="{33C9BCE6-D9EB-4032-9B0A-DDD9A4051A2D}" name="Done (100%)" dataDxfId="1" dataCellStyle="Hyperlink"/>
-    <tableColumn id="8" xr3:uid="{D624FC89-A88E-45AC-9D22-66D66702B8C5}" name="WON'T DO (100%)" dataDxfId="0" dataCellStyle="Hyperlink"/>
-    <tableColumn id="7" xr3:uid="{EFEEB7EC-E2D1-40EA-B265-A558311E5D30}" name="Total" dataDxfId="14" dataCellStyle="Hyperlink">
+    <tableColumn id="1" xr3:uid="{5BE08AE0-E0B5-4B46-9423-456B88C2D9BC}" name="Sprint" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{030F9647-4FC0-4C7E-9B3A-AB099CC59EBA}" name="To Do (0%)" dataDxfId="8" dataCellStyle="Hyperlink"/>
+    <tableColumn id="3" xr3:uid="{7D2923F3-E2CF-4FD9-A7A5-68C36BB95591}" name="STARTING (10 ~ 40%)" dataDxfId="7" dataCellStyle="Hyperlink"/>
+    <tableColumn id="4" xr3:uid="{48FB5317-7F3B-4F74-B244-5A49C7749EBD}" name="In Progress (50 ~ 70%)" dataDxfId="6" dataCellStyle="Hyperlink"/>
+    <tableColumn id="5" xr3:uid="{86F5CCB5-C4C2-4C36-935A-657F085500B1}" name="IN REVIEW (80%)" dataDxfId="5" dataCellStyle="Hyperlink"/>
+    <tableColumn id="9" xr3:uid="{51D22AE3-424C-4604-9869-D672DED4301F}" name="READY FOR TESTING (90%)" dataDxfId="4" dataCellStyle="Hyperlink"/>
+    <tableColumn id="6" xr3:uid="{33C9BCE6-D9EB-4032-9B0A-DDD9A4051A2D}" name="Done (100%)" dataDxfId="3" dataCellStyle="Hyperlink"/>
+    <tableColumn id="8" xr3:uid="{D624FC89-A88E-45AC-9D22-66D66702B8C5}" name="WON'T DO (100%)" dataDxfId="2" dataCellStyle="Hyperlink"/>
+    <tableColumn id="7" xr3:uid="{EFEEB7EC-E2D1-40EA-B265-A558311E5D30}" name="Total" dataDxfId="1" dataCellStyle="Hyperlink">
       <calculatedColumnFormula>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11951,14 +12125,14 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}" name="Table25" displayName="Table25" ref="A1:E18" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="A1:E18" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}" name="Table25" displayName="Table25" ref="A1:E19" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+  <autoFilter ref="A1:E19" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7070D9F2-0ED1-4F39-8D72-28B37C8E98F2}" name="Week" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{1173F443-CC27-4C6E-A432-BF66DB2A740E}" name="Done" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{2EE10CB5-1AF1-4B50-9456-B3A666DD5338}" name="In Review/Progress" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{328D0A00-85F0-4BFF-81FE-C023998A3701}" name="TODO (P1)" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{E385808E-1FCD-451C-9807-DAF18A42B704}" name="Total" dataDxfId="7">
+    <tableColumn id="1" xr3:uid="{7070D9F2-0ED1-4F39-8D72-28B37C8E98F2}" name="Week" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{1173F443-CC27-4C6E-A432-BF66DB2A740E}" name="Done" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{2EE10CB5-1AF1-4B50-9456-B3A666DD5338}" name="In Review/Progress" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{328D0A00-85F0-4BFF-81FE-C023998A3701}" name="TODO (P1)" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{E385808E-1FCD-451C-9807-DAF18A42B704}" name="Total" dataDxfId="16">
       <calculatedColumnFormula>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12283,7 +12457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D733A42-966D-5F4E-B061-B304543CE88E}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.77734375" customWidth="1"/>
@@ -12294,7 +12468,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -12311,7 +12485,7 @@
     </row>
     <row r="2" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -12329,7 +12503,7 @@
     </row>
     <row r="3" spans="1:5" ht="21.95" customHeight="1">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -12347,7 +12521,7 @@
     </row>
     <row r="4" spans="1:5" ht="21.95" customHeight="1">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -12365,7 +12539,7 @@
     </row>
     <row r="5" spans="1:5" ht="21.95" customHeight="1">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -12383,7 +12557,7 @@
     </row>
     <row r="6" spans="1:5" ht="21.95" customHeight="1">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B6">
         <v>8</v>
@@ -12401,7 +12575,7 @@
     </row>
     <row r="7" spans="1:5" ht="21.95" customHeight="1">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B7">
         <v>10</v>
@@ -12419,7 +12593,7 @@
     </row>
     <row r="8" spans="1:5" ht="21.95" customHeight="1">
       <c r="A8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B8">
         <v>12</v>
@@ -12437,7 +12611,7 @@
     </row>
     <row r="9" spans="1:5" ht="21.95" customHeight="1">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B9">
         <v>15</v>
@@ -12455,7 +12629,7 @@
     </row>
     <row r="10" spans="1:5" ht="21.95" customHeight="1">
       <c r="A10" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B10">
         <v>15</v>
@@ -12473,7 +12647,7 @@
     </row>
     <row r="11" spans="1:5" ht="21.95" customHeight="1">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B11">
         <v>12</v>
@@ -12491,7 +12665,7 @@
     </row>
     <row r="12" spans="1:5" ht="21.95" customHeight="1">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B12">
         <v>13</v>
@@ -12509,7 +12683,7 @@
     </row>
     <row r="13" spans="1:5" ht="21.95" customHeight="1">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B13">
         <v>15</v>
@@ -12527,7 +12701,7 @@
     </row>
     <row r="14" spans="1:5" ht="21.95" customHeight="1">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B14">
         <v>18</v>
@@ -12545,7 +12719,7 @@
     </row>
     <row r="15" spans="1:5" ht="21.95" customHeight="1">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B15">
         <v>21</v>
@@ -12563,7 +12737,7 @@
     </row>
     <row r="16" spans="1:5" ht="21.95" customHeight="1">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B16">
         <v>22</v>
@@ -12581,7 +12755,7 @@
     </row>
     <row r="17" spans="1:5" ht="21.95" customHeight="1">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B17">
         <v>25</v>
@@ -12599,7 +12773,7 @@
     </row>
     <row r="18" spans="1:5" ht="21.95" customHeight="1">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B18">
         <v>28</v>
@@ -12617,7 +12791,7 @@
     </row>
     <row r="19" spans="1:5" ht="21.95" customHeight="1">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B19">
         <v>30</v>
@@ -12635,7 +12809,7 @@
     </row>
     <row r="20" spans="1:5" ht="21.95" customHeight="1">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B20">
         <v>32</v>
@@ -12653,7 +12827,7 @@
     </row>
     <row r="21" spans="1:5" ht="21.95" customHeight="1">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B21">
         <v>32</v>
@@ -12671,7 +12845,7 @@
     </row>
     <row r="22" spans="1:5" ht="21.95" customHeight="1">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B22">
         <v>32</v>
@@ -12689,7 +12863,7 @@
     </row>
     <row r="23" spans="1:5" ht="21.95" customHeight="1">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B23">
         <v>32</v>
@@ -12707,7 +12881,7 @@
     </row>
     <row r="24" spans="1:5" ht="21.95" customHeight="1">
       <c r="A24" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B24">
         <v>32</v>
@@ -12725,7 +12899,7 @@
     </row>
     <row r="25" spans="1:5" ht="21.95" customHeight="1">
       <c r="A25" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B25">
         <v>32</v>
@@ -12743,7 +12917,7 @@
     </row>
     <row r="26" spans="1:5" ht="21.95" customHeight="1">
       <c r="A26" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B26">
         <v>32</v>
@@ -12755,6 +12929,24 @@
         <v>161</v>
       </c>
       <c r="E26" s="12">
+        <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A27" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27">
+        <v>31</v>
+      </c>
+      <c r="C27">
+        <v>3</v>
+      </c>
+      <c r="D27">
+        <v>161</v>
+      </c>
+      <c r="E27" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
         <v>195</v>
       </c>
@@ -12771,7 +12963,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6429633B-8BD2-084C-8C0F-75969053522F}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.77734375" customWidth="1"/>
@@ -12781,7 +12973,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>11</v>
@@ -12996,7 +13188,7 @@
     </row>
     <row r="9" spans="1:8" ht="21.95" customHeight="1">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B9">
         <v>1399</v>
@@ -13023,7 +13215,7 @@
     </row>
     <row r="10" spans="1:8" ht="21.95" customHeight="1">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B10">
         <v>1271</v>
@@ -13050,7 +13242,7 @@
     </row>
     <row r="11" spans="1:8" ht="21.95" customHeight="1">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B11">
         <v>1333</v>
@@ -13077,7 +13269,7 @@
     </row>
     <row r="12" spans="1:8" ht="21.95" customHeight="1">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B12">
         <v>1475</v>
@@ -13104,7 +13296,7 @@
     </row>
     <row r="13" spans="1:8" ht="21.95" customHeight="1">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B13">
         <v>2031</v>
@@ -13131,7 +13323,7 @@
     </row>
     <row r="14" spans="1:8" ht="21.95" customHeight="1">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B14">
         <v>1755</v>
@@ -13158,7 +13350,7 @@
     </row>
     <row r="15" spans="1:8" ht="21.95" customHeight="1">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B15">
         <v>1892</v>
@@ -13185,7 +13377,7 @@
     </row>
     <row r="16" spans="1:8" ht="21.95" customHeight="1">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B16">
         <v>1642</v>
@@ -13212,16 +13404,16 @@
     </row>
     <row r="17" spans="1:8" ht="21.95" customHeight="1">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B17">
-        <v>1204</v>
+        <v>1350</v>
       </c>
       <c r="C17">
         <v>8</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -13230,11 +13422,38 @@
         <v>4</v>
       </c>
       <c r="G17">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="H17">
         <f>SUM(Table1[[#This Row],[Passed]:[Untested]])</f>
-        <v>1423</v>
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="21.95" customHeight="1">
+      <c r="A18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18">
+        <v>388</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>494</v>
+      </c>
+      <c r="H18">
+        <f>SUM(Table1[[#This Row],[Passed]:[Untested]])</f>
+        <v>882</v>
       </c>
     </row>
   </sheetData>
@@ -13249,7 +13468,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA6EDF6-834F-DA49-B3FC-BFE1673433AB}">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
@@ -13258,7 +13477,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>11</v>
@@ -13284,7 +13503,7 @@
     </row>
     <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B2">
         <v>38</v>
@@ -13311,12 +13530,12 @@
     </row>
     <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B4">
         <v>43</v>
@@ -13343,12 +13562,12 @@
     </row>
     <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B6">
         <v>58</v>
@@ -13375,12 +13594,12 @@
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B8">
         <v>76</v>
@@ -13407,12 +13626,12 @@
     </row>
     <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B10">
         <v>121</v>
@@ -13439,12 +13658,12 @@
     </row>
     <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B12">
         <v>148</v>
@@ -13471,12 +13690,12 @@
     </row>
     <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B14" s="10">
         <v>148</v>
@@ -13503,13 +13722,13 @@
     </row>
     <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H15" s="12"/>
     </row>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B16">
         <v>231</v>
@@ -13536,13 +13755,13 @@
     </row>
     <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H17" s="12"/>
     </row>
     <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B18">
         <v>249</v>
@@ -13569,7 +13788,7 @@
     </row>
     <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B19">
         <v>155</v>
@@ -13596,7 +13815,7 @@
     </row>
     <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B20">
         <v>225</v>
@@ -13623,7 +13842,7 @@
     </row>
     <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B21">
         <v>281</v>
@@ -13650,7 +13869,7 @@
     </row>
     <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B22">
         <v>291</v>
@@ -13677,7 +13896,7 @@
     </row>
     <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B23">
         <v>267</v>
@@ -13704,7 +13923,7 @@
     </row>
     <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B24">
         <v>343</v>
@@ -13731,7 +13950,7 @@
     </row>
     <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B25">
         <v>351</v>
@@ -13758,7 +13977,7 @@
     </row>
     <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B26">
         <v>142</v>
@@ -13785,7 +14004,7 @@
     </row>
     <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B27">
         <v>442</v>
@@ -13812,7 +14031,7 @@
     </row>
     <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B28">
         <v>518</v>
@@ -13839,7 +14058,7 @@
     </row>
     <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B29">
         <v>636</v>
@@ -13866,10 +14085,10 @@
     </row>
     <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B30">
-        <v>336</v>
+        <v>436</v>
       </c>
       <c r="C30">
         <v>4</v>
@@ -13878,17 +14097,44 @@
         <v>4</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G30">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="H30" s="12">
         <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
-        <v>470</v>
+        <v>464</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="A31" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31">
+        <v>171</v>
+      </c>
+      <c r="C31">
+        <v>6</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>6</v>
+      </c>
+      <c r="G31">
+        <v>455</v>
+      </c>
+      <c r="H31" s="12">
+        <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
+        <v>639</v>
       </c>
     </row>
   </sheetData>
@@ -13903,7 +14149,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7C79DB4-6EC1-E840-9DE9-46C117A6F960}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
@@ -13917,22 +14163,22 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>1</v>
@@ -13942,624 +14188,543 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B2">
-        <v>8</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
+      <c r="B2" s="3">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>93</v>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3">
+        <v>61</v>
       </c>
       <c r="H2">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>101</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="3">
         <v>7</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
         <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>59</v>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>46</v>
       </c>
       <c r="H3">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4">
-        <v>25</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>168</v>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>43</v>
       </c>
       <c r="H4">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>193</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5">
-        <v>30</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3">
+        <v>17</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>156</v>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>33</v>
       </c>
       <c r="H5">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>186</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
-        <v>14</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3">
+        <v>26</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
         <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>77</v>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>25</v>
       </c>
       <c r="H6">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>91</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
+      <c r="A7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3">
+        <v>14</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>61</v>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>56</v>
       </c>
       <c r="H7">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
+      <c r="A8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
         <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>46</v>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>40</v>
       </c>
       <c r="H8">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9">
-        <v>18</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>43</v>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>33</v>
       </c>
       <c r="H9">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>63</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10">
-        <v>17</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
+      <c r="A10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="3">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3">
         <v>1</v>
       </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>33</v>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>29</v>
       </c>
       <c r="H10">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11">
-        <v>26</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
+      <c r="A11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
         <v>0</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>25</v>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1</v>
       </c>
       <c r="H11">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>51</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12">
-        <v>14</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
+      <c r="A12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="3">
+        <v>13</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
         <v>0</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>56</v>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>9</v>
       </c>
       <c r="H12">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>70</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13">
-        <v>10</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
+      <c r="A13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
         <v>0</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>40</v>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>12</v>
       </c>
       <c r="H13">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>50</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" t="s">
+      <c r="A14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="3">
+        <v>4</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>9</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>33</v>
       </c>
       <c r="H14">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15">
-        <v>11</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
+      <c r="A15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="3">
+        <v>17</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
         <v>0</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>29</v>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>37</v>
       </c>
       <c r="H15">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16">
-        <v>2</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
+      <c r="A16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="3">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
         <v>0</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>37</v>
       </c>
       <c r="H16">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>3</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17">
-        <v>13</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
+      <c r="A17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="3">
+        <v>8</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3">
         <v>0</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>9</v>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>34</v>
       </c>
       <c r="H17">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
+      <c r="A18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="3">
+        <v>7</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3">
         <v>0</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>12</v>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>17</v>
       </c>
       <c r="H18">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19">
-        <v>4</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
+      <c r="A19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="3">
+        <v>2</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
+      <c r="F19" s="3">
+        <v>2</v>
+      </c>
+      <c r="G19" s="3">
         <v>8</v>
       </c>
       <c r="H19">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20">
-        <v>17</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
+      <c r="A20" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="3">
+        <v>2</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3">
         <v>0</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>37</v>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>4</v>
       </c>
       <c r="H20">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>54</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B21">
-        <v>6</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
+      <c r="A21" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="3">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3">
         <v>0</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>36</v>
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
       </c>
       <c r="H21">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22">
-        <v>9</v>
-      </c>
-      <c r="C22">
         <v>1</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>33</v>
-      </c>
-      <c r="H22">
-        <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" t="s">
-        <v>65</v>
-      </c>
-      <c r="B23">
-        <v>8</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>12</v>
-      </c>
-      <c r="H23">
-        <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" t="s">
-        <v>95</v>
-      </c>
-      <c r="B24">
-        <v>3</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -14574,10 +14739,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7487DEB-55FC-DC4E-A4B1-F7171B8F3237}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.21875" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" customWidth="1"/>
     <col min="2" max="2" width="18.44140625" customWidth="1"/>
     <col min="3" max="3" width="23.21875" customWidth="1"/>
     <col min="4" max="4" width="23.109375" customWidth="1"/>
@@ -14589,28 +14754,28 @@
   <sheetData>
     <row r="1" spans="1:9" ht="21" thickBot="1">
       <c r="A1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>32</v>
-      </c>
       <c r="D1" s="7" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I1" s="9" t="s">
         <v>3</v>
@@ -14618,40 +14783,40 @@
     </row>
     <row r="2" spans="1:9" ht="18" thickBot="1">
       <c r="A2" s="4" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="B2" s="5">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="C2" s="5">
         <v>0</v>
       </c>
       <c r="D2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2" s="5">
         <v>0</v>
       </c>
       <c r="G2" s="5">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="H2" s="5">
-        <v>3</v>
-      </c>
-      <c r="I2" s="5">
+        <v>74</v>
+      </c>
+      <c r="I2" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>23</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18" thickBot="1">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="B3" s="5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C3" s="5">
         <v>0</v>
@@ -14666,19 +14831,19 @@
         <v>0</v>
       </c>
       <c r="G3" s="5">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" thickBot="1">
       <c r="A4" s="4" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B4" s="5">
         <v>0</v>
@@ -14696,19 +14861,19 @@
         <v>0</v>
       </c>
       <c r="G4" s="5">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H4" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" thickBot="1">
       <c r="A5" s="4" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B5" s="5">
         <v>0</v>
@@ -14726,19 +14891,19 @@
         <v>0</v>
       </c>
       <c r="G5" s="5">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H5" s="5">
         <v>2</v>
       </c>
       <c r="I5" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="18" thickBot="1">
       <c r="A6" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B6" s="5">
         <v>0</v>
@@ -14756,19 +14921,19 @@
         <v>0</v>
       </c>
       <c r="G6" s="5">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="H6" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18" thickBot="1">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B7" s="5">
         <v>0</v>
@@ -14786,22 +14951,22 @@
         <v>0</v>
       </c>
       <c r="G7" s="5">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="H7" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I7" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="18" thickBot="1">
       <c r="A8" s="4" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="5">
         <v>0</v>
@@ -14816,22 +14981,22 @@
         <v>0</v>
       </c>
       <c r="G8" s="5">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="H8" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I8" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>42</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="18" thickBot="1">
       <c r="A9" s="4" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" s="5">
         <v>0</v>
@@ -14846,19 +15011,19 @@
         <v>0</v>
       </c>
       <c r="G9" s="5">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H9" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I9" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="18" thickBot="1">
       <c r="A10" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B10" s="5">
         <v>1</v>
@@ -14876,19 +15041,19 @@
         <v>0</v>
       </c>
       <c r="G10" s="5">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H10" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I10" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="18" thickBot="1">
       <c r="A11" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B11" s="5">
         <v>1</v>
@@ -14906,22 +15071,22 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="H11" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I11" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="18" thickBot="1">
       <c r="A12" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B12" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" s="5">
         <v>0</v>
@@ -14936,22 +15101,22 @@
         <v>0</v>
       </c>
       <c r="G12" s="5">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="H12" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I12" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>32</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18" thickBot="1">
       <c r="A13" s="4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B13" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" s="5">
         <v>0</v>
@@ -14966,22 +15131,22 @@
         <v>0</v>
       </c>
       <c r="G13" s="5">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H13" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I13" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18" thickBot="1">
       <c r="A14" s="4" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B14" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" s="5">
         <v>0</v>
@@ -14996,22 +15161,22 @@
         <v>0</v>
       </c>
       <c r="G14" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H14" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I14" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="18" thickBot="1">
       <c r="A15" s="4" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="B15" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C15" s="5">
         <v>0</v>
@@ -15026,19 +15191,19 @@
         <v>0</v>
       </c>
       <c r="G15" s="5">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H15" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I15" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="18" thickBot="1">
       <c r="A16" s="4" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="B16" s="5">
         <v>0</v>
@@ -15056,19 +15221,19 @@
         <v>0</v>
       </c>
       <c r="G16" s="5">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="H16" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="18" thickBot="1">
       <c r="A17" s="4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B17" s="5">
         <v>0</v>
@@ -15086,22 +15251,22 @@
         <v>0</v>
       </c>
       <c r="G17" s="5">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="H17" s="5">
         <v>0</v>
       </c>
       <c r="I17" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="18" thickBot="1">
       <c r="A18" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B18" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" s="5">
         <v>0</v>
@@ -15116,22 +15281,22 @@
         <v>0</v>
       </c>
       <c r="G18" s="5">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H18" s="5">
         <v>0</v>
       </c>
       <c r="I18" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="18" thickBot="1">
       <c r="A19" s="4" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B19" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C19" s="5">
         <v>0</v>
@@ -15146,22 +15311,22 @@
         <v>0</v>
       </c>
       <c r="G19" s="5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H19" s="5">
         <v>0</v>
       </c>
       <c r="I19" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="18" thickBot="1">
       <c r="A20" s="4" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B20" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C20" s="5">
         <v>0</v>
@@ -15176,22 +15341,22 @@
         <v>0</v>
       </c>
       <c r="G20" s="5">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H20" s="5">
-        <v>0</v>
-      </c>
-      <c r="I20" s="15">
+        <v>1</v>
+      </c>
+      <c r="I20" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="18" thickBot="1">
       <c r="A21" s="4" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B21" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" s="5">
         <v>0</v>
@@ -15200,43 +15365,43 @@
         <v>0</v>
       </c>
       <c r="E21" s="5">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5">
+        <v>31</v>
+      </c>
+      <c r="H21" s="5">
         <v>1</v>
-      </c>
-      <c r="F21" s="5">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5">
-        <v>27</v>
-      </c>
-      <c r="H21" s="5">
-        <v>0</v>
       </c>
       <c r="I21" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="18" thickBot="1">
       <c r="A22" s="4" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="B22" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C22" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E22" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F22" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G22" s="5">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H22" s="5">
         <v>1</v>
@@ -15248,10 +15413,10 @@
     </row>
     <row r="23" spans="1:9" ht="18" thickBot="1">
       <c r="A23" s="4" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="B23" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C23" s="5">
         <v>0</v>
@@ -15260,192 +15425,340 @@
         <v>0</v>
       </c>
       <c r="E23" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="5">
         <v>0</v>
       </c>
       <c r="G23" s="5">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H23" s="5">
         <v>0</v>
       </c>
       <c r="I23" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="18" thickBot="1">
+      <c r="A24" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="5">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>1</v>
+      </c>
+      <c r="D24" s="5">
+        <v>1</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5">
+        <v>2</v>
+      </c>
+      <c r="G24" s="5">
+        <v>26</v>
+      </c>
+      <c r="H24" s="5">
+        <v>2</v>
+      </c>
+      <c r="I24" s="15">
+        <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="18" thickBot="1">
+      <c r="A25" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" s="5">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>2</v>
+      </c>
+      <c r="D25" s="5">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5">
+        <v>1</v>
+      </c>
+      <c r="F25" s="5">
+        <v>5</v>
+      </c>
+      <c r="G25" s="5">
+        <v>4</v>
+      </c>
+      <c r="H25" s="5">
+        <v>3</v>
+      </c>
+      <c r="I25" s="15">
+        <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="18" thickBot="1">
+      <c r="A26" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="5">
         <v>6</v>
+      </c>
+      <c r="C26" s="5">
+        <v>1</v>
+      </c>
+      <c r="D26" s="5">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5">
+        <v>0</v>
+      </c>
+      <c r="I26" s="15">
+        <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="18" thickBot="1">
+      <c r="A27" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="5">
+        <v>1</v>
+      </c>
+      <c r="C27" s="5">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5">
+        <v>0</v>
+      </c>
+      <c r="I27" s="5">
+        <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A9F80F84-BA92-4A24-ABDC-ACC67BFE2E81}"/>
-    <hyperlink ref="D2" r:id="rId2" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{0C7998B5-B492-412F-819D-8A35630FA7B8}"/>
-    <hyperlink ref="G2" r:id="rId3" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{52EA4762-03C7-43BD-A628-570C351BAED9}"/>
-    <hyperlink ref="E2" r:id="rId4" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D88F2136-548D-461E-A07A-8C404D3C50A9}"/>
-    <hyperlink ref="H2" r:id="rId5" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{717973E6-4D24-4755-977E-2B6B33BD2776}"/>
-    <hyperlink ref="C2" r:id="rId6" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{418A2A32-3E41-4A82-8AE7-65C90C8C7D95}"/>
-    <hyperlink ref="F2" r:id="rId7" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{68B56113-D3FA-4341-8C3B-81B6266553DA}"/>
-    <hyperlink ref="B3" r:id="rId8" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{65304C31-947E-48F0-B2FB-937B69D3E20F}"/>
-    <hyperlink ref="D3" r:id="rId9" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{874EBB66-6B8A-45F9-A89F-CFB7E8A938E7}"/>
-    <hyperlink ref="G3" r:id="rId10" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{AB76801E-CAEC-4744-B1EA-94D21D0414D1}"/>
-    <hyperlink ref="E3" r:id="rId11" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{45D6D802-03A0-44DF-B75C-CCF6C06F3051}"/>
-    <hyperlink ref="H3" r:id="rId12" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{1A13DD52-C86B-4536-AA74-DE1E894DD3BA}"/>
-    <hyperlink ref="C3" r:id="rId13" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{9419882D-58DD-4ACC-91A9-9AC6886A54E3}"/>
-    <hyperlink ref="F3" r:id="rId14" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{74F5793A-AB3B-474A-9A40-BB9FB7C322FF}"/>
-    <hyperlink ref="B4" r:id="rId15" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{EF4D93C3-8274-4D55-89AF-8C33C627D37D}"/>
-    <hyperlink ref="D4" r:id="rId16" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{5E67226E-0B7F-4FAE-925E-1E2051F8874E}"/>
-    <hyperlink ref="G4" r:id="rId17" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F08EE343-FD8A-4E17-99E7-902A5D6D7A47}"/>
-    <hyperlink ref="E4" r:id="rId18" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{281704EA-318E-4FE4-9156-5C9F713AD975}"/>
-    <hyperlink ref="H4" r:id="rId19" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E6E9C93E-DA2D-4527-A751-F900A062C270}"/>
-    <hyperlink ref="C4" r:id="rId20" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{1F74AEDA-926F-4E6E-977B-BA6EFC9640A4}"/>
-    <hyperlink ref="F4" r:id="rId21" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{ABF632E0-8EAB-49B7-AC82-2608B9D545E4}"/>
-    <hyperlink ref="B5" r:id="rId22" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{37B81593-59F3-4D72-8B7A-56964DE37C12}"/>
-    <hyperlink ref="D5" r:id="rId23" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{53B606C9-68C4-4466-948B-21E7B823A0D4}"/>
-    <hyperlink ref="G5" r:id="rId24" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{6BDA6349-25BB-434E-9C1B-389ABC053E5E}"/>
-    <hyperlink ref="E5" r:id="rId25" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{96CEEA37-01EA-44CF-9B80-D2F36572F5D9}"/>
-    <hyperlink ref="H5" r:id="rId26" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{72D14AA7-7FF5-4CC9-8BF7-AD4B41080136}"/>
-    <hyperlink ref="C5" r:id="rId27" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{40AB41AE-6CA7-4B21-A35F-F64AD1AFBA0E}"/>
-    <hyperlink ref="F5" r:id="rId28" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C17C3EB9-4159-4D6B-8CE6-F6CF1CA87397}"/>
-    <hyperlink ref="B6" r:id="rId29" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A376F4F4-7BAC-4762-9284-C387FB31C69C}"/>
-    <hyperlink ref="D6" r:id="rId30" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{86E9AAB7-ECD7-417B-A1DC-AA2100E97BEA}"/>
-    <hyperlink ref="G6" r:id="rId31" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{30DB914F-4D85-4143-B4CB-B5DA9301920C}"/>
-    <hyperlink ref="E6" r:id="rId32" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{50945381-9778-4F97-9C94-E4408A1CFB06}"/>
-    <hyperlink ref="H6" r:id="rId33" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{1EB0AF17-30C1-4599-B124-1C9774EFB3C8}"/>
-    <hyperlink ref="C6" r:id="rId34" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{8BAAE8A8-2777-41B6-A527-8833652F1758}"/>
-    <hyperlink ref="F6" r:id="rId35" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F6B9FB7F-3725-4CB9-AB70-0C928A2E351F}"/>
-    <hyperlink ref="B7" r:id="rId36" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{FFECFC70-6FCD-4B97-AD4F-79D109F77E26}"/>
-    <hyperlink ref="D7" r:id="rId37" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{F1A4AA54-8234-410F-9481-3AC54C67B075}"/>
-    <hyperlink ref="G7" r:id="rId38" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{107C65F7-662D-4865-94DB-961872649DF7}"/>
-    <hyperlink ref="E7" r:id="rId39" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{C374BB7A-B5DB-4BBB-A5EB-D000789DA8C6}"/>
-    <hyperlink ref="H7" r:id="rId40" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5A4A8631-FF31-4E6F-A851-A0AA4E89608C}"/>
-    <hyperlink ref="C7" r:id="rId41" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{BB906A62-BF7C-491C-8E0B-377B9776ABD0}"/>
-    <hyperlink ref="F7" r:id="rId42" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{BB0A9381-882D-44CC-A601-6F03688FA737}"/>
-    <hyperlink ref="B8" r:id="rId43" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{7B99323B-B87B-4920-8901-7DE52E890FB7}"/>
-    <hyperlink ref="D8" r:id="rId44" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{60F6147B-730B-44E2-B948-A3CF47F1043E}"/>
-    <hyperlink ref="G8" r:id="rId45" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{2861CE91-573B-410C-9883-73A4D519183F}"/>
-    <hyperlink ref="E8" r:id="rId46" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{7C2B4010-E840-4240-991D-9094037CFD94}"/>
-    <hyperlink ref="H8" r:id="rId47" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{B3B2689B-AF04-416A-B2F4-634D24CBC4D9}"/>
-    <hyperlink ref="C8" r:id="rId48" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{D8EA6F8D-1560-4796-BAD2-700BA36A5FF6}"/>
-    <hyperlink ref="F8" r:id="rId49" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{4F3EE8FB-85B4-48C4-8E21-4DFD5222C647}"/>
-    <hyperlink ref="B9" r:id="rId50" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{9D556B0C-7B85-49F2-8C41-BD8C0FE411D3}"/>
-    <hyperlink ref="D9" r:id="rId51" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D34A086D-B10C-436C-B377-7B2D34D57B17}"/>
-    <hyperlink ref="G9" r:id="rId52" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{80D66145-C6DE-402C-B0B5-C767AE4E718E}"/>
-    <hyperlink ref="E9" r:id="rId53" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B8E8C0B9-01BC-494C-B66D-D36DF0E4E93E}"/>
-    <hyperlink ref="H9" r:id="rId54" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{67D8EDE0-6B09-429B-A523-5AD806609B35}"/>
-    <hyperlink ref="C9" r:id="rId55" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{24A566B3-D39E-46EF-9B63-04E4F58B840B}"/>
-    <hyperlink ref="F9" r:id="rId56" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{999E7F23-0525-4809-B85F-B8B9B98A4D1E}"/>
-    <hyperlink ref="B10" r:id="rId57" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{839DC036-FC98-4AF6-8272-917C9CF22947}"/>
-    <hyperlink ref="D10" r:id="rId58" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{44806174-C39A-403A-ADE7-5B514CD08A9A}"/>
-    <hyperlink ref="G10" r:id="rId59" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{04D0A8F9-FC7E-4B22-89BF-ACAA5435F0C1}"/>
-    <hyperlink ref="E10" r:id="rId60" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{4C5BA8FC-B8A4-4B06-B7DE-9E1BAD73332F}"/>
-    <hyperlink ref="H10" r:id="rId61" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{29C8C01A-8FDD-4764-BC90-EF02739BB4D2}"/>
-    <hyperlink ref="C10" r:id="rId62" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6E985BD8-F79A-44DF-BCD9-6A93386B6AE1}"/>
-    <hyperlink ref="F10" r:id="rId63" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{3A15E55D-FFF5-4426-A20D-4399B26B6DBB}"/>
-    <hyperlink ref="B11" r:id="rId64" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{59616EDA-C956-4D33-9859-7EAE9C8BCE6B}"/>
-    <hyperlink ref="D11" r:id="rId65" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{1786DDDD-AA48-46E7-B2FC-BC7FF11B9A6C}"/>
-    <hyperlink ref="G11" r:id="rId66" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{2483627D-6A50-4111-9988-D132BA907922}"/>
-    <hyperlink ref="E11" r:id="rId67" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{0584D67A-6878-4A73-B4AD-90B802D858B5}"/>
-    <hyperlink ref="H11" r:id="rId68" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E364DBF3-D50B-40DA-9635-3EDA5FA0C21C}"/>
-    <hyperlink ref="C11" r:id="rId69" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{37EBA7EA-201A-439F-B881-4015D55A3F6B}"/>
-    <hyperlink ref="F11" r:id="rId70" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{8391B261-1840-4C3E-A257-C9EB82EB0422}"/>
-    <hyperlink ref="B12" r:id="rId71" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{55303834-DEE3-45D8-BAA9-9BC176E0FC95}"/>
-    <hyperlink ref="D12" r:id="rId72" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{73A029BE-7ED5-44E6-9C21-1E60A9CE71B3}"/>
-    <hyperlink ref="G12" r:id="rId73" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F804D5B7-C7FB-4BCE-9E20-7980552CF8EE}"/>
-    <hyperlink ref="E12" r:id="rId74" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{47425AF4-F66A-4B45-A192-C342FD19656A}"/>
-    <hyperlink ref="H12" r:id="rId75" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{82E73120-DD00-47DC-A124-0AA04B6AD3D2}"/>
-    <hyperlink ref="C12" r:id="rId76" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{FF84701C-CBD4-46D1-AAD9-4B08E0BFB998}"/>
-    <hyperlink ref="F12" r:id="rId77" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C2DBA20F-6DAC-4B5B-BD36-DBF6878C2FB9}"/>
-    <hyperlink ref="B13" r:id="rId78" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{443B268A-5359-48F6-845B-540941E55C28}"/>
-    <hyperlink ref="D13" r:id="rId79" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{11D508E1-E3E0-4FCE-9E50-425C2F12C669}"/>
-    <hyperlink ref="G13" r:id="rId80" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{9F4EAACA-B876-4CFF-BD37-AA344628D4B7}"/>
-    <hyperlink ref="E13" r:id="rId81" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{33EFA38A-3136-4F27-89AB-89BE6C67911C}"/>
-    <hyperlink ref="H13" r:id="rId82" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E9B7BA55-0F29-4E17-B8C5-E25E6C267B42}"/>
-    <hyperlink ref="C13" r:id="rId83" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A8C17920-222D-406A-9B00-1A2F27A78F0E}"/>
-    <hyperlink ref="F13" r:id="rId84" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{AEB1948B-1159-429A-B34E-D65C622B431D}"/>
-    <hyperlink ref="B14" r:id="rId85" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{54D5FD02-7418-4D37-A752-511421CF432F}"/>
-    <hyperlink ref="D14" r:id="rId86" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{52DBE7C9-96FD-4AC8-968C-2750A8B8BC50}"/>
-    <hyperlink ref="G14" r:id="rId87" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{97763671-453B-44EC-A13C-961E2A0CFE3B}"/>
-    <hyperlink ref="E14" r:id="rId88" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{0A1134B6-87FA-4DFE-8F54-9584839E78E4}"/>
-    <hyperlink ref="H14" r:id="rId89" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{98569BB2-4036-4B5F-A7F3-A9E553008D4F}"/>
-    <hyperlink ref="C14" r:id="rId90" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{40700C2C-2E67-4CBD-A98A-266C772009B5}"/>
-    <hyperlink ref="F14" r:id="rId91" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{D21B01FC-318C-4BBD-9060-CA6EF261669A}"/>
-    <hyperlink ref="B15" r:id="rId92" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{576AE033-C6B4-43AA-9885-E1F0DF96E8B0}"/>
-    <hyperlink ref="D15" r:id="rId93" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{A2DA8F31-36DA-4E24-B004-DDAA638E7735}"/>
-    <hyperlink ref="G15" r:id="rId94" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{7AFE3DFA-600C-46B2-A1DD-C9E75DA5241E}"/>
-    <hyperlink ref="E15" r:id="rId95" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{DE32C529-DEEE-44A0-9BEB-6A176BE5F617}"/>
-    <hyperlink ref="H15" r:id="rId96" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{C9615AFA-A714-4A3F-A5FB-9103A4A5FC8E}"/>
-    <hyperlink ref="C15" r:id="rId97" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{F45920AA-EE33-4F95-9537-1569AC87C8D2}"/>
-    <hyperlink ref="F15" r:id="rId98" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A14712F4-D810-4CD8-980A-E6F0E3A8A092}"/>
-    <hyperlink ref="B16" r:id="rId99" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{55208663-A49E-4C1F-BD05-C126EA5BDD4E}"/>
-    <hyperlink ref="D16" r:id="rId100" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{1AD6DE03-DD0F-44D7-B8BD-4F367E236AC4}"/>
-    <hyperlink ref="G16" r:id="rId101" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{AEB4391F-1E66-4949-A3D8-2697BC86B9EF}"/>
-    <hyperlink ref="E16" r:id="rId102" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{75CDC6A6-9203-4608-A0AA-9FCA8F8B4ABE}"/>
-    <hyperlink ref="H16" r:id="rId103" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5D008DC6-F2C4-4F76-960C-2598B5BCE4F2}"/>
-    <hyperlink ref="C16" r:id="rId104" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{CCB3155D-8207-4B09-90DB-F4DAE66654DB}"/>
-    <hyperlink ref="F16" r:id="rId105" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{CD0D7ED7-7C92-4C0B-B9BD-8EC092327AA4}"/>
-    <hyperlink ref="B17" r:id="rId106" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{EEB43738-A759-40B2-A0D8-483FBC788839}"/>
-    <hyperlink ref="D17" r:id="rId107" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{E0841039-FC39-46EB-94B8-19C0C528A073}"/>
-    <hyperlink ref="G17" r:id="rId108" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{64E07241-46BA-4333-A3C7-E9278135D233}"/>
-    <hyperlink ref="E17" r:id="rId109" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{4FA6BA86-1BED-4AF4-9DF4-A499E0D28C58}"/>
-    <hyperlink ref="H17" r:id="rId110" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{11E5CB30-9514-49B0-916D-BB0CC4C1055A}"/>
-    <hyperlink ref="C17" r:id="rId111" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{787DA1A8-4154-4661-A44D-2DEE925A62D7}"/>
-    <hyperlink ref="F17" r:id="rId112" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{920866C1-CFD8-4C1A-B470-D658FCB9BAB9}"/>
-    <hyperlink ref="B18" r:id="rId113" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C2407B3D-57A9-4925-9C9D-E5D0B4A659A3}"/>
-    <hyperlink ref="D18" r:id="rId114" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D6A3A3E5-3834-47F8-B69B-E7BDB4C29187}"/>
-    <hyperlink ref="G18" r:id="rId115" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{BDA08CD9-5B7F-4B34-80FB-F053945111B8}"/>
-    <hyperlink ref="E18" r:id="rId116" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{92C66EEC-6CCA-4759-AFF0-504402840498}"/>
-    <hyperlink ref="H18" r:id="rId117" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{87AF4DD3-0CC0-42E2-B76B-DDBD75CEB6CD}"/>
-    <hyperlink ref="C18" r:id="rId118" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6031BD54-7FB9-471F-8226-8B541AC22CC9}"/>
-    <hyperlink ref="F18" r:id="rId119" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{0DBA619E-7D5F-40A4-8BD6-A4EF16DC15B0}"/>
-    <hyperlink ref="B19" r:id="rId120" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{3C395B88-97F3-43B3-B811-ABD3A503861A}"/>
-    <hyperlink ref="D19" r:id="rId121" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{5C13D2BD-D8C9-4A76-84D2-BDF083DF8659}"/>
-    <hyperlink ref="G19" r:id="rId122" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F46ACC26-FC73-408A-8F04-886090F3551B}"/>
-    <hyperlink ref="E19" r:id="rId123" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{48324850-6E94-4D30-BA9A-844CF673E7AD}"/>
-    <hyperlink ref="H19" r:id="rId124" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{39F83DA0-4FC2-4054-BB96-FEC14CA18104}"/>
-    <hyperlink ref="C19" r:id="rId125" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{CD33FCC0-4CB0-4A17-924C-5A887854FB70}"/>
-    <hyperlink ref="F19" r:id="rId126" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{162E7D95-F029-4396-A06C-9AC3373B99B5}"/>
-    <hyperlink ref="B20" r:id="rId127" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{2146DEB2-82F5-463B-A907-78E60F611B10}"/>
-    <hyperlink ref="D20" r:id="rId128" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{28EDEA46-B9C0-4FB5-88E2-64E298363C6A}"/>
-    <hyperlink ref="G20" r:id="rId129" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{AB479AEF-532D-41DC-B6BA-C646438B4554}"/>
-    <hyperlink ref="E20" r:id="rId130" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{484CFDA8-ACF0-4047-A8D0-35BFD01830A7}"/>
-    <hyperlink ref="H20" r:id="rId131" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{691834E0-AA86-48CA-B36E-805AD4182FCF}"/>
-    <hyperlink ref="C20" r:id="rId132" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{57E9EC80-F17D-4D6F-8CCC-5EAB357D3CE7}"/>
-    <hyperlink ref="F20" r:id="rId133" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{AE54FC2F-BE1E-47A2-9EC9-C2478A3F4924}"/>
-    <hyperlink ref="B21" r:id="rId134" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{7AF1F010-B910-41D4-88C2-B58DECB008A0}"/>
-    <hyperlink ref="D21" r:id="rId135" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{65E2DB36-FBB8-4B1C-A112-5D7D1CD4B721}"/>
-    <hyperlink ref="G21" r:id="rId136" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{53EB6C88-3B82-4073-82D0-D5EC74522FC9}"/>
-    <hyperlink ref="E21" r:id="rId137" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{5CBE353D-0F3E-4DD5-BCBE-EE7A742E7E7B}"/>
-    <hyperlink ref="H21" r:id="rId138" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{BA44829C-1004-440E-9EB3-368D7108CEC4}"/>
-    <hyperlink ref="C21" r:id="rId139" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{CE757053-DEC7-47B7-B77E-A0BD8D4536B0}"/>
-    <hyperlink ref="F21" r:id="rId140" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A2C391C7-7F81-44F3-A6BD-18ED8CFE0758}"/>
-    <hyperlink ref="B22" r:id="rId141" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{00BFF074-DA26-4277-9EBB-50D7F62C57BB}"/>
-    <hyperlink ref="D22" r:id="rId142" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D2A160A1-B705-4496-B386-9EE0212DEC9B}"/>
-    <hyperlink ref="G22" r:id="rId143" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{1872EC94-A686-4EAF-8F58-754A4EA1F0C9}"/>
-    <hyperlink ref="E22" r:id="rId144" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{78805724-7A3C-4002-AFDA-35FF302E690C}"/>
-    <hyperlink ref="H22" r:id="rId145" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{04D67F69-CEEB-43D1-AFBF-F2E57494CD8E}"/>
-    <hyperlink ref="C22" r:id="rId146" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{FDC852EF-23F8-4ADC-AE37-1CAD2F6BB5B3}"/>
-    <hyperlink ref="F22" r:id="rId147" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{68277F90-5E23-4937-8744-4C0F212100F8}"/>
-    <hyperlink ref="B23" r:id="rId148" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{8DB3278E-5306-4E20-9090-8ED957478E22}"/>
-    <hyperlink ref="D23" r:id="rId149" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{4017127B-2DAF-498D-A012-223614915BA9}"/>
-    <hyperlink ref="G23" r:id="rId150" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{0D1298D2-A3E5-4A8A-83A1-A1B4652BD371}"/>
-    <hyperlink ref="E23" r:id="rId151" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{1E6D8F7B-09FC-4730-BD3F-B1708E0FF90D}"/>
-    <hyperlink ref="H23" r:id="rId152" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{DD689B40-4361-4F83-890D-B8016B7DC3AC}"/>
-    <hyperlink ref="C23" r:id="rId153" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{460E475D-C429-4507-AEF0-EA9330067868}"/>
-    <hyperlink ref="F23" r:id="rId154" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A9B2B81E-B917-4BB8-A894-6955A9F8B48A}"/>
+    <hyperlink ref="B4" r:id="rId1" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{809911B9-76F9-4F05-BF2D-6BBC76E4F9A4}"/>
+    <hyperlink ref="D4" r:id="rId2" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{6B099EA0-04DA-43D1-8F27-EB9428CB8EF8}"/>
+    <hyperlink ref="G4" r:id="rId3" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{53437BDB-B9CF-4A77-8F51-0EC19C84E287}"/>
+    <hyperlink ref="E4" r:id="rId4" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{4A483F77-3DFE-4943-883F-066FD629EC60}"/>
+    <hyperlink ref="H4" r:id="rId5" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{4432C5CA-1687-45C6-A1FC-ACAE6248977B}"/>
+    <hyperlink ref="C4" r:id="rId6" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{CA463E28-82E9-4EC4-9F5C-36811632F5FB}"/>
+    <hyperlink ref="F4" r:id="rId7" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{8BCCA4C3-1A13-4861-8312-700629419ABB}"/>
+    <hyperlink ref="B5" r:id="rId8" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{43008575-D248-4C37-B84B-B58F31C9E710}"/>
+    <hyperlink ref="D5" r:id="rId9" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{1653F765-3F3B-4B2E-9D36-538466BF23A6}"/>
+    <hyperlink ref="G5" r:id="rId10" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{7070D2B0-7E6D-4074-A27C-E36E1E8AE2A5}"/>
+    <hyperlink ref="E5" r:id="rId11" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A76495A5-96A4-4290-8219-6C5408113A6F}"/>
+    <hyperlink ref="H5" r:id="rId12" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{C97C35D6-A179-4245-AA36-94D184175927}"/>
+    <hyperlink ref="C5" r:id="rId13" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{523C3F12-61CD-463C-A5FF-92656933318E}"/>
+    <hyperlink ref="F5" r:id="rId14" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E5410F34-7F6C-4F8C-B0AD-9230565A782A}"/>
+    <hyperlink ref="B6" r:id="rId15" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{AE9F9892-18D8-4BA4-97EA-2CBE8E8C303E}"/>
+    <hyperlink ref="D6" r:id="rId16" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{CB4D0C42-DB0E-4D72-B16C-151732989921}"/>
+    <hyperlink ref="G6" r:id="rId17" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{67892A8E-723C-4B5E-B1F9-DB1BB20C8917}"/>
+    <hyperlink ref="E6" r:id="rId18" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{336B88ED-F758-4271-8635-3A8D1D1D556A}"/>
+    <hyperlink ref="H6" r:id="rId19" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{2F756263-1270-43F6-950C-92BD3164EBBB}"/>
+    <hyperlink ref="C6" r:id="rId20" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{ACF67BC0-89FE-4D5A-B97B-812F44746C6D}"/>
+    <hyperlink ref="F6" r:id="rId21" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{9F1F05CA-A99B-4163-9466-5FF138BFBF50}"/>
+    <hyperlink ref="B7" r:id="rId22" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{FA4C0BF9-A9A1-4B46-9050-76DD68287419}"/>
+    <hyperlink ref="D7" r:id="rId23" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{22FE5682-848C-4093-AB72-5C6137AD99CE}"/>
+    <hyperlink ref="G7" r:id="rId24" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{DB9974B9-7BAC-40B7-BD0C-B06113AFB915}"/>
+    <hyperlink ref="E7" r:id="rId25" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{72130AC9-2DFB-417B-9555-D30217DEFFED}"/>
+    <hyperlink ref="H7" r:id="rId26" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{F680F49E-77A1-4803-8990-F1267B8509E7}"/>
+    <hyperlink ref="C7" r:id="rId27" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A107A0E4-D25D-4B5C-A287-2BA40D3A6CE1}"/>
+    <hyperlink ref="F7" r:id="rId28" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{71ABECD1-D053-4327-BA34-1AE3EFC5E005}"/>
+    <hyperlink ref="B8" r:id="rId29" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C2A15436-EB0D-41A7-BA99-74AC0265F40C}"/>
+    <hyperlink ref="D8" r:id="rId30" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{BE5C5B59-D82A-44B8-A178-0635264600AC}"/>
+    <hyperlink ref="G8" r:id="rId31" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{8CBB9692-A79C-44A2-A7A8-0FF31F3EE08A}"/>
+    <hyperlink ref="E8" r:id="rId32" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A45B00C8-CA31-4639-A512-D2CB8C9CC5E8}"/>
+    <hyperlink ref="H8" r:id="rId33" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{440016F2-D63E-4478-B81F-448FD1ECB262}"/>
+    <hyperlink ref="C8" r:id="rId34" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{EDE311DC-E60C-483B-BC39-7648489A0E99}"/>
+    <hyperlink ref="F8" r:id="rId35" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{8921717D-4DD0-415F-8786-1A949A18110F}"/>
+    <hyperlink ref="B9" r:id="rId36" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{5FF5D9F2-3D2C-415F-8402-AAD3FF701320}"/>
+    <hyperlink ref="D9" r:id="rId37" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D005BEE4-355C-4621-9CEF-3B254C7E0267}"/>
+    <hyperlink ref="G9" r:id="rId38" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{85757C4C-E150-4401-83A1-A24FA0FBD79B}"/>
+    <hyperlink ref="E9" r:id="rId39" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{78AFBF1B-52DE-4CDC-8CFC-C164967D0753}"/>
+    <hyperlink ref="H9" r:id="rId40" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{DCD465D9-29F4-4B28-BDFC-E5E9884A5FE8}"/>
+    <hyperlink ref="C9" r:id="rId41" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{0CCF4C5A-035E-4648-A9FF-3756DB75E273}"/>
+    <hyperlink ref="F9" r:id="rId42" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C2A2B8CD-FB8E-4535-8062-810B0CF2288A}"/>
+    <hyperlink ref="B10" r:id="rId43" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{CBC4FA39-776C-4DE2-93BB-37E2E644BA0D}"/>
+    <hyperlink ref="D10" r:id="rId44" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{AC65ED6C-148F-4532-A62A-FD801B17E639}"/>
+    <hyperlink ref="G10" r:id="rId45" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{AEB89E02-CD1F-421B-A29E-19CC77E06704}"/>
+    <hyperlink ref="E10" r:id="rId46" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F6B12E1B-1989-4478-9816-516133A06C54}"/>
+    <hyperlink ref="H10" r:id="rId47" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{8D3B67BF-765B-45B9-A673-1E5BA756D87E}"/>
+    <hyperlink ref="C10" r:id="rId48" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{268C54F3-9625-489E-AE1A-FE1C1FB23F04}"/>
+    <hyperlink ref="F10" r:id="rId49" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{BA5625FF-62E4-47D4-BDB9-CA6D7F76F92C}"/>
+    <hyperlink ref="B11" r:id="rId50" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A49E1934-7EFC-455B-A85C-337EC77B1B65}"/>
+    <hyperlink ref="D11" r:id="rId51" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{5C38973C-96E9-408E-B8CD-65DB985B2A99}"/>
+    <hyperlink ref="G11" r:id="rId52" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{BA200205-AA70-480C-AF68-32217E59167A}"/>
+    <hyperlink ref="E11" r:id="rId53" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{C054038C-7AD9-415D-BCC9-5A8C143768BD}"/>
+    <hyperlink ref="H11" r:id="rId54" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E5E35CC8-29BF-474E-9761-62C45C4172A8}"/>
+    <hyperlink ref="C11" r:id="rId55" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{3A5D8691-EA28-4A7D-B37C-0D93C59035D5}"/>
+    <hyperlink ref="F11" r:id="rId56" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{4BFFD283-E2FE-4C13-AD26-2210AA94B599}"/>
+    <hyperlink ref="B12" r:id="rId57" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{F8593ACE-636B-403A-A712-EF8DDC49A22E}"/>
+    <hyperlink ref="D12" r:id="rId58" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D725BBD2-653C-40D9-945F-BE91C8EB9733}"/>
+    <hyperlink ref="G12" r:id="rId59" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F95614A1-E6C4-4633-967B-FE665C115ED5}"/>
+    <hyperlink ref="E12" r:id="rId60" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E9EB2556-D891-4D22-8D3B-99640293CFEA}"/>
+    <hyperlink ref="H12" r:id="rId61" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{C77D8C36-5F65-4740-AFC8-16F5A4692277}"/>
+    <hyperlink ref="C12" r:id="rId62" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A535644C-83A5-4CB0-9829-1AE4B6C2B504}"/>
+    <hyperlink ref="F12" r:id="rId63" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{913F0D72-9F20-4D15-B340-2FD29C293540}"/>
+    <hyperlink ref="B13" r:id="rId64" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{FBF54ADC-A1C6-484F-B1CE-E84D3D12CE07}"/>
+    <hyperlink ref="D13" r:id="rId65" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{EBCBA75B-B2B6-46D1-BCC4-187E6F8FA482}"/>
+    <hyperlink ref="G13" r:id="rId66" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{672F40D7-E05F-452E-A095-3DF7D7820611}"/>
+    <hyperlink ref="E13" r:id="rId67" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{13BB4184-DC18-4BBC-BAA8-3239F6616721}"/>
+    <hyperlink ref="H13" r:id="rId68" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{4EA0DA79-6BAF-49CC-8DCE-6B9B5FCD0BC8}"/>
+    <hyperlink ref="C13" r:id="rId69" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{3BF0366F-8BBC-4F7F-9765-7CA9F1C594B0}"/>
+    <hyperlink ref="F13" r:id="rId70" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{8774BD5F-0DE1-451C-9301-2E3B775F4E8D}"/>
+    <hyperlink ref="B14" r:id="rId71" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{CBE74DF1-1680-46DD-ABDB-247754DF3737}"/>
+    <hyperlink ref="D14" r:id="rId72" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{64E6426F-D4D6-490E-A65B-A0898BCE1BC0}"/>
+    <hyperlink ref="G14" r:id="rId73" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3DCC6CEB-6808-4463-B122-43A7777D5521}"/>
+    <hyperlink ref="E14" r:id="rId74" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{99E89007-0504-4278-A141-B4431A5B700D}"/>
+    <hyperlink ref="H14" r:id="rId75" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{DEBDD966-994E-4773-A45D-02EC25578AAB}"/>
+    <hyperlink ref="C14" r:id="rId76" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{35134365-F806-456C-96EB-A68DA5C1A5C2}"/>
+    <hyperlink ref="F14" r:id="rId77" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{45CF823E-8F4E-4C94-A49D-C29D1560F4AA}"/>
+    <hyperlink ref="B15" r:id="rId78" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{79D5282E-7221-421F-BE1E-FD480BA6BB20}"/>
+    <hyperlink ref="D15" r:id="rId79" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{FFCB8B3B-865A-4780-9B5E-89C395CACC65}"/>
+    <hyperlink ref="G15" r:id="rId80" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{32E870DD-0569-4685-A9DE-0CC61CD0F1D1}"/>
+    <hyperlink ref="E15" r:id="rId81" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{06EDB94B-C1E8-4035-AEF5-EDA8329F815E}"/>
+    <hyperlink ref="H15" r:id="rId82" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{99730D50-CAAA-4855-BE7F-B9A4241F9E56}"/>
+    <hyperlink ref="C15" r:id="rId83" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6C68D715-0E54-40B1-8315-250BBEA9DCE8}"/>
+    <hyperlink ref="F15" r:id="rId84" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E892457F-9BBE-4D46-8F00-6224F881DA65}"/>
+    <hyperlink ref="B16" r:id="rId85" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{0ABFFA40-61BF-48AF-B693-9719E5BB2CED}"/>
+    <hyperlink ref="D16" r:id="rId86" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{C25E1253-0381-49D8-A8FD-E44CCAFA258F}"/>
+    <hyperlink ref="G16" r:id="rId87" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{72D281C8-A48F-4404-B3E3-7914FCC5F761}"/>
+    <hyperlink ref="E16" r:id="rId88" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{C99C42F0-8FDA-4A85-97BB-06A7E33F76C5}"/>
+    <hyperlink ref="H16" r:id="rId89" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{93761553-79E8-484F-866F-D8B1E3FD28A0}"/>
+    <hyperlink ref="C16" r:id="rId90" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6D0ED953-7B0D-4823-8B3D-D1FF50BA7798}"/>
+    <hyperlink ref="F16" r:id="rId91" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{834830F4-7D94-4107-AC9E-546C9FC0D8F4}"/>
+    <hyperlink ref="B17" r:id="rId92" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{FFC47A93-753D-45BD-84A9-2C8E939096CC}"/>
+    <hyperlink ref="D17" r:id="rId93" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{AF0F0963-788E-48F3-A864-05F399832899}"/>
+    <hyperlink ref="G17" r:id="rId94" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{72E3CFFE-E38C-4DD2-B168-F110EDF62D6E}"/>
+    <hyperlink ref="E17" r:id="rId95" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B0B793BC-CC52-49E6-A302-E554AACE338F}"/>
+    <hyperlink ref="H17" r:id="rId96" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{84CFA2E7-097E-4FF6-BC99-FC04B537C996}"/>
+    <hyperlink ref="C17" r:id="rId97" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{1A871C21-A8E2-4EBB-963F-CA348AD9651A}"/>
+    <hyperlink ref="F17" r:id="rId98" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A7B5ECC3-FF32-473E-BD29-9A447ED7CC1D}"/>
+    <hyperlink ref="B18" r:id="rId99" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{8351149E-A13D-417A-9F1E-EF71EEE3CF9D}"/>
+    <hyperlink ref="D18" r:id="rId100" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D56C4A55-52AB-4DA7-A6D1-C5F00DD4C338}"/>
+    <hyperlink ref="G18" r:id="rId101" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{1F116C9C-ECEB-4DC8-B4E0-6EA0B3B42056}"/>
+    <hyperlink ref="E18" r:id="rId102" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E04B4FA5-A2F2-4C64-9EDE-5F5DE9D8E9A6}"/>
+    <hyperlink ref="H18" r:id="rId103" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{71E4EE44-A29F-4526-BA38-4EF53739DD93}"/>
+    <hyperlink ref="C18" r:id="rId104" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{50D394ED-C29A-432C-A933-365144F1C1DD}"/>
+    <hyperlink ref="F18" r:id="rId105" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{BC5B7E0C-A7F6-42F9-8504-D17DB9FFEE05}"/>
+    <hyperlink ref="B19" r:id="rId106" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{798B3080-A508-48AE-8947-A168CE8BF5F7}"/>
+    <hyperlink ref="D19" r:id="rId107" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{66E6880A-CC47-48B1-ADDB-643A6025D5A9}"/>
+    <hyperlink ref="G19" r:id="rId108" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{E3D3CA17-3882-449D-AC0F-ACBE44FB0CD6}"/>
+    <hyperlink ref="E19" r:id="rId109" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{EFA11580-0B85-4714-9384-FDFA75234BA3}"/>
+    <hyperlink ref="H19" r:id="rId110" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{834ECA52-269F-4F0D-A927-285BF359ECC0}"/>
+    <hyperlink ref="C19" r:id="rId111" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{BE317CF9-1E01-4590-BFAB-8F768FE4477A}"/>
+    <hyperlink ref="F19" r:id="rId112" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{164C42ED-384F-4154-8FCF-D6D7BC210AAF}"/>
+    <hyperlink ref="B20" r:id="rId113" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{AB067417-A1E3-4D8D-AFA1-60C1242EC87A}"/>
+    <hyperlink ref="D20" r:id="rId114" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{892BF312-20B0-461C-BB21-2B38FB6601EC}"/>
+    <hyperlink ref="G20" r:id="rId115" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{7069171E-E0A8-42D6-9B18-A96FA9D9670A}"/>
+    <hyperlink ref="E20" r:id="rId116" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{FFEEC264-23C3-479B-836C-6A7816220486}"/>
+    <hyperlink ref="H20" r:id="rId117" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{8DF90A02-4A69-4CB4-B691-62DAEBF30861}"/>
+    <hyperlink ref="C20" r:id="rId118" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{2D9A0811-ECD0-4E83-B084-1ED048494949}"/>
+    <hyperlink ref="F20" r:id="rId119" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{30A5F476-97D8-45CA-93AC-BA3557449927}"/>
+    <hyperlink ref="B21" r:id="rId120" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{62DA024A-85CA-46C9-869E-370FAE8589E5}"/>
+    <hyperlink ref="D21" r:id="rId121" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{EA42C0A6-67E7-4439-BE9E-05F68C36A4FA}"/>
+    <hyperlink ref="G21" r:id="rId122" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{D63DF082-3A10-41FC-B993-EF3EC220C9AB}"/>
+    <hyperlink ref="E21" r:id="rId123" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{3E823444-4C36-4B65-9D15-1268A1FE7ECA}"/>
+    <hyperlink ref="H21" r:id="rId124" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{90328037-E39D-4C38-912C-7DBC6B124B2A}"/>
+    <hyperlink ref="C21" r:id="rId125" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{028309F5-49F5-4FC1-BC95-7F1BE93C0705}"/>
+    <hyperlink ref="F21" r:id="rId126" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E2B5DE71-E3A5-44E6-B360-4286FBD48AE1}"/>
+    <hyperlink ref="B22" r:id="rId127" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{31447D0C-7E99-4C15-8F45-B42CC49F24A4}"/>
+    <hyperlink ref="D22" r:id="rId128" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{B9D7FE24-FBAA-4EB1-9277-1F39AEFA3D8F}"/>
+    <hyperlink ref="G22" r:id="rId129" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{925AEBAD-45BC-4B41-8FC8-97567672446B}"/>
+    <hyperlink ref="E22" r:id="rId130" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{8403DAED-8C63-4AC2-A93D-0685568BAFDF}"/>
+    <hyperlink ref="H22" r:id="rId131" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{FB2B5D59-99CC-4335-9921-DFA15239FD2A}"/>
+    <hyperlink ref="C22" r:id="rId132" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{06CEADBE-F1BC-4C87-A636-B777FCB603B8}"/>
+    <hyperlink ref="F22" r:id="rId133" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C2949024-F0A1-4413-BBEB-B3208DEA7F3F}"/>
+    <hyperlink ref="B23" r:id="rId134" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{067B3D9B-C59E-449C-A13D-FD6561FD25E2}"/>
+    <hyperlink ref="D23" r:id="rId135" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{C6C5DA57-66A4-4A76-BFB8-708F79614290}"/>
+    <hyperlink ref="G23" r:id="rId136" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C4CD30A9-0235-46D2-9B58-91CF14B5399E}"/>
+    <hyperlink ref="E23" r:id="rId137" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F666FC5A-FAF7-4C70-A3F7-6F5B003A0504}"/>
+    <hyperlink ref="H23" r:id="rId138" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{8E2741DA-00B9-42C6-BF7A-CECB5C7A5EA1}"/>
+    <hyperlink ref="C23" r:id="rId139" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{0D997503-988D-4ABD-AB1C-BD103EB89410}"/>
+    <hyperlink ref="F23" r:id="rId140" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{2ACCA93B-4796-47AB-81CB-D2211D51E00E}"/>
+    <hyperlink ref="B24" r:id="rId141" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{6830705C-D441-44A3-86F5-32984F945991}"/>
+    <hyperlink ref="D24" r:id="rId142" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{736592D5-6D1E-408F-B02E-7244D465FD50}"/>
+    <hyperlink ref="G24" r:id="rId143" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{587ACEF7-F5F3-4109-B719-EBB4C4183040}"/>
+    <hyperlink ref="E24" r:id="rId144" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{0AFA3ED1-7292-4F03-996F-6A2A2D3A0953}"/>
+    <hyperlink ref="H24" r:id="rId145" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{C6B1CC50-91FE-481B-9F69-5737077BBA18}"/>
+    <hyperlink ref="C24" r:id="rId146" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6146E52B-A975-495D-B437-788544ED822D}"/>
+    <hyperlink ref="F24" r:id="rId147" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C44E6C0C-1849-48D8-8B81-3196429ABA91}"/>
+    <hyperlink ref="B25" r:id="rId148" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{B43341AF-D98D-40F3-A8CD-5A0F65C07BA4}"/>
+    <hyperlink ref="D25" r:id="rId149" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{7A43F814-4F67-499F-B300-B7019649656E}"/>
+    <hyperlink ref="G25" r:id="rId150" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{28E206CD-E58B-40CF-8BF0-84D3EC8D1B01}"/>
+    <hyperlink ref="E25" r:id="rId151" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D95661B6-48BD-41FC-A1CA-911866114506}"/>
+    <hyperlink ref="H25" r:id="rId152" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{B73535A0-B20E-40D5-A0DC-3D649F279C0E}"/>
+    <hyperlink ref="C25" r:id="rId153" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{2B842A76-1F4A-4BC2-8068-6C73CF537F6D}"/>
+    <hyperlink ref="F25" r:id="rId154" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F73C53F8-0B19-41F9-BE13-0B988EDE38B4}"/>
+    <hyperlink ref="B26" r:id="rId155" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{8C577972-191E-4506-9C4B-728263CF5F3B}"/>
+    <hyperlink ref="D26" r:id="rId156" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{5970EA26-C2A2-4DB6-9A59-528605C672EF}"/>
+    <hyperlink ref="G26" r:id="rId157" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{BC5BA146-1368-42A3-8FB1-C82206325E70}"/>
+    <hyperlink ref="E26" r:id="rId158" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{BDAF99B8-EE08-4A76-8335-CF08C8628DE1}"/>
+    <hyperlink ref="H26" r:id="rId159" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{01616887-05D0-44BA-870D-B1FF7AEFFCE8}"/>
+    <hyperlink ref="C26" r:id="rId160" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C5B7DB27-233C-4F2A-A0F1-5D5C8E4D7006}"/>
+    <hyperlink ref="F26" r:id="rId161" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{28FE0AF6-07C2-4BCF-9C84-4FA3F8947E90}"/>
+    <hyperlink ref="B27" r:id="rId162" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{3F1BFDB0-8FEF-4B03-9B80-BFBBA6DED58A}"/>
+    <hyperlink ref="D27" r:id="rId163" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{88820CF6-3163-490D-8566-3290DF72A3AA}"/>
+    <hyperlink ref="G27" r:id="rId164" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{962F555A-013B-4318-974D-5FC1690AC4CD}"/>
+    <hyperlink ref="E27" r:id="rId165" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{1B012E19-D779-402E-96A5-9B470EC23FA3}"/>
+    <hyperlink ref="H27" r:id="rId166" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{185DC5EB-5D6F-40E5-9597-979F5B23144A}"/>
+    <hyperlink ref="C27" r:id="rId167" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{9EC0D9BE-7428-41E0-B690-F9C98D4C905E}"/>
+    <hyperlink ref="F27" r:id="rId168" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{D924C78A-7EB1-4B73-AD46-9CF3D3D00B10}"/>
+    <hyperlink ref="B2" r:id="rId169" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C3E7CF5B-8526-4329-8920-3C4D26EC31A9}"/>
+    <hyperlink ref="D2" r:id="rId170" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{12BD1984-0B08-4350-8ED9-C83B6B039111}"/>
+    <hyperlink ref="G2" r:id="rId171" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{1B273B89-FFAB-4775-A13C-A2BCC76215A9}"/>
+    <hyperlink ref="E2" r:id="rId172" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A96C42EE-3C33-42BA-A901-F4EF8F429CD7}"/>
+    <hyperlink ref="H2" r:id="rId173" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{34864220-955C-4802-B200-B6D5E3959E41}"/>
+    <hyperlink ref="C2" r:id="rId174" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{7BB6763D-FC38-4CD1-A317-5AFDB91A97CA}"/>
+    <hyperlink ref="F2" r:id="rId175" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{FEF51C2F-6D76-448E-806F-F2878600C9E6}"/>
+    <hyperlink ref="B3" r:id="rId176" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{7D78EEF5-3AA8-4B35-917B-EC14A98B256C}"/>
+    <hyperlink ref="D3" r:id="rId177" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{7FCE6098-B630-4CD9-A80C-DF5B1EB8D4EC}"/>
+    <hyperlink ref="G3" r:id="rId178" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{314923AC-AC7D-42A6-A582-A858BE7A06B0}"/>
+    <hyperlink ref="E3" r:id="rId179" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{7989CAE1-1F3F-41E8-8309-E17CFDC6160B}"/>
+    <hyperlink ref="H3" r:id="rId180" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{0521050B-BD22-42E2-9A80-3B6B44655902}"/>
+    <hyperlink ref="C3" r:id="rId181" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{76EF4C34-D9F9-4CE3-941C-F4703F7E2D2C}"/>
+    <hyperlink ref="F3" r:id="rId182" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{4650FFD7-0961-400E-920D-B72AB6BD4105}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId155"/>
-  <drawing r:id="rId156"/>
+  <pageSetup orientation="portrait" r:id="rId183"/>
+  <drawing r:id="rId184"/>
   <tableParts count="1">
-    <tablePart r:id="rId157"/>
+    <tablePart r:id="rId185"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC3F3FC-17EF-4D6A-9290-8FAFFC789915}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.5546875" customWidth="1"/>
@@ -15454,7 +15767,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -15471,7 +15784,7 @@
     </row>
     <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B2" s="13">
         <v>0</v>
@@ -15489,7 +15802,7 @@
     </row>
     <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B3" s="14">
         <v>0</v>
@@ -15507,7 +15820,7 @@
     </row>
     <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B4" s="14">
         <v>0</v>
@@ -15525,7 +15838,7 @@
     </row>
     <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B5" s="14">
         <v>0</v>
@@ -15543,7 +15856,7 @@
     </row>
     <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B6" s="14">
         <v>5</v>
@@ -15561,7 +15874,7 @@
     </row>
     <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B7" s="14">
         <v>5</v>
@@ -15579,7 +15892,7 @@
     </row>
     <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B8" s="14">
         <v>5</v>
@@ -15597,7 +15910,7 @@
     </row>
     <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B9" s="14">
         <v>6</v>
@@ -15615,7 +15928,7 @@
     </row>
     <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B10" s="14">
         <v>6</v>
@@ -15633,7 +15946,7 @@
     </row>
     <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B11" s="14">
         <v>12</v>
@@ -15650,7 +15963,7 @@
     </row>
     <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B12" s="14">
         <v>22</v>
@@ -15668,7 +15981,7 @@
     </row>
     <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B13" s="14">
         <v>27</v>
@@ -15686,7 +15999,7 @@
     </row>
     <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B14" s="14">
         <v>27</v>
@@ -15704,7 +16017,7 @@
     </row>
     <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B15" s="14">
         <v>44</v>
@@ -15722,7 +16035,7 @@
     </row>
     <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B16" s="14">
         <v>57</v>
@@ -15740,7 +16053,7 @@
     </row>
     <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B17" s="14">
         <v>68</v>
@@ -15758,7 +16071,7 @@
     </row>
     <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B18" s="14">
         <v>80</v>
@@ -15772,6 +16085,24 @@
       <c r="E18" s="14">
         <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
         <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="A19" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" s="14">
+        <v>92</v>
+      </c>
+      <c r="C19" s="14">
+        <v>6</v>
+      </c>
+      <c r="D19" s="14">
+        <v>13</v>
+      </c>
+      <c r="E19" s="14">
+        <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/SDET_SQA_DATA.xlsx
+++ b/data/SDET_SQA_DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WHSU\Desktop\Workspace\CycleView\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00A1364-E8D9-45F6-A83A-3350FC33E41F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B79CA17-A71E-46CA-B55B-949EFCBB968D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{EB11FF79-EF06-B64E-AA6A-0CFF391A8BD1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{EB11FF79-EF06-B64E-AA6A-0CFF391A8BD1}"/>
   </bookViews>
   <sheets>
     <sheet name="TestAutomationProgress" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="104">
   <si>
     <t>TODO (P1)</t>
   </si>
@@ -352,6 +352,9 @@
   <si>
     <t>26W06</t>
   </si>
+  <si>
+    <t>26W07</t>
+  </si>
 </sst>
 </file>
 
@@ -539,10 +542,6 @@
   </cellStyles>
   <dxfs count="36">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -718,6 +717,33 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -792,13 +818,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -823,6 +842,13 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -843,36 +869,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -901,6 +901,9 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1088,9 +1091,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$27</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$28</c:f>
               <c:strCache>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>25W32</c:v>
                 </c:pt>
@@ -1168,16 +1171,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>26W06</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26W07</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$B$2:$B$27</c:f>
+              <c:f>TestAutomationProgress!$B$2:$B$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -1254,6 +1260,9 @@
                   <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="25">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>31</c:v>
                 </c:pt>
               </c:numCache>
@@ -1351,9 +1360,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$27</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$28</c:f>
               <c:strCache>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>25W32</c:v>
                 </c:pt>
@@ -1431,16 +1440,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>26W06</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26W07</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$C$2:$C$27</c:f>
+              <c:f>TestAutomationProgress!$C$2:$C$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1517,6 +1529,9 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="25">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
@@ -1614,9 +1629,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$27</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$28</c:f>
               <c:strCache>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>25W32</c:v>
                 </c:pt>
@@ -1694,16 +1709,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>26W06</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26W07</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$D$2:$D$27</c:f>
+              <c:f>TestAutomationProgress!$D$2:$D$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>115</c:v>
                 </c:pt>
@@ -1780,6 +1798,9 @@
                   <c:v>161</c:v>
                 </c:pt>
                 <c:pt idx="25">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>161</c:v>
                 </c:pt>
               </c:numCache>
@@ -2209,7 +2230,7 @@
                   <c:v>v1.37</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>v1.38</c:v>
+                  <c:v>v1.39</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2269,7 +2290,7 @@
                   <c:v>1350</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>388</c:v>
+                  <c:v>614</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2358,7 +2379,7 @@
                   <c:v>v1.37</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>v1.38</c:v>
+                  <c:v>v1.39</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2515,7 +2536,7 @@
                   <c:v>v1.37</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>v1.38</c:v>
+                  <c:v>v1.39</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2718,7 +2739,7 @@
                   <c:v>v1.37</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>v1.38</c:v>
+                  <c:v>v1.39</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2778,7 +2799,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2867,7 +2888,7 @@
                   <c:v>v1.37</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>v1.38</c:v>
+                  <c:v>v1.39</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3018,7 +3039,7 @@
                   <c:v>v1.37</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>v1.38</c:v>
+                  <c:v>v1.39</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3078,7 +3099,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>494</c:v>
+                  <c:v>196</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3244,7 +3265,7 @@
                   <c:v>v1.37</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>v1.38</c:v>
+                  <c:v>v1.39</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3304,7 +3325,7 @@
                   <c:v>1374</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>882</c:v>
+                  <c:v>814</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3678,9 +3699,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$31</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$32</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -3770,16 +3791,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>26W06</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>26W07</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$B$2:$B$31</c:f>
+              <c:f>'SOVA-TestResult'!$B$2:$B$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>38</c:v>
                 </c:pt>
@@ -3845,6 +3869,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>723</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3938,9 +3965,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$31</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$32</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4030,16 +4057,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>26W06</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>26W07</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$C$2:$C$31</c:f>
+              <c:f>'SOVA-TestResult'!$C$2:$C$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4105,6 +4135,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4141,9 +4174,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$31</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$32</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4233,16 +4266,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>26W06</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>26W07</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$D$2:$D$31</c:f>
+              <c:f>'SOVA-TestResult'!$D$2:$D$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4308,6 +4344,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4344,9 +4383,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$31</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$32</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4436,16 +4475,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>26W06</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>26W07</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$E$2:$E$31</c:f>
+              <c:f>'SOVA-TestResult'!$E$2:$E$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
                 </c:pt>
@@ -4511,6 +4553,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4621,9 +4666,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$31</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$32</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4713,16 +4758,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>26W06</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>26W07</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$F$2:$F$31</c:f>
+              <c:f>'SOVA-TestResult'!$F$2:$F$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>11</c:v>
                 </c:pt>
@@ -4788,6 +4836,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4827,9 +4878,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$31</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$32</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4919,16 +4970,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>26W06</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>26W07</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$G$2:$G$31</c:f>
+              <c:f>'SOVA-TestResult'!$G$2:$G$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4993,7 +5047,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>455</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5035,9 +5092,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$31</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$32</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -5127,16 +5184,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>26W06</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>26W07</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$H$2:$H$31</c:f>
+              <c:f>'SOVA-TestResult'!$H$2:$H$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>54</c:v>
                 </c:pt>
@@ -5201,7 +5261,10 @@
                   <c:v>464</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>639</c:v>
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>753</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5683,25 +5746,25 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>17</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>8</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>7</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5865,10 +5928,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
@@ -6202,10 +6265,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
@@ -6369,7 +6432,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
@@ -6524,25 +6587,25 @@
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>37</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>34</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>17</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="17">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>8</c:v>
                 </c:pt>
-                <c:pt idx="18">
-                  <c:v>4</c:v>
-                </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6708,10 +6771,10 @@
                   <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>7</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7175,10 +7238,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>158</c:v>
+                  <c:v>162</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>22</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -7244,13 +7307,13 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>11</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>6</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7501,10 +7564,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>1</c:v>
@@ -7761,7 +7824,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>1</c:v>
@@ -8024,10 +8087,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="24">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -8158,7 +8221,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -8224,10 +8287,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0</c:v>
@@ -8415,7 +8478,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>120</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>2</c:v>
@@ -8481,10 +8544,10 @@
                   <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>26</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0</c:v>
@@ -8620,7 +8683,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>74</c:v>
+                  <c:v>76</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>3</c:v>
@@ -8825,10 +8888,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>357</c:v>
+                  <c:v>369</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>23</c:v>
@@ -8891,16 +8954,16 @@
                   <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>34</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>27</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11832,13 +11895,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>171448</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>133348</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -11872,15 +11935,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1028700</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:colOff>1057275</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11914,13 +11977,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>69662</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1057275</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>31562</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -12032,8 +12095,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}" name="Table2" displayName="Table2" ref="A1:E27" totalsRowShown="0" headerRowDxfId="35">
-  <autoFilter ref="A1:E27" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}" name="Table2" displayName="Table2" ref="A1:E28" totalsRowShown="0" headerRowDxfId="35">
+  <autoFilter ref="A1:E28" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F25F0D34-0297-4771-8BBB-350BCDD85D46}" name="Week"/>
     <tableColumn id="2" xr3:uid="{39CFCD12-3130-47A8-A140-DBF602F1743D}" name="Done"/>
@@ -12058,7 +12121,7 @@
     <tableColumn id="5" xr3:uid="{DC0F99B4-F7A9-4F8A-BBA0-6D907EC37C98}" name="Failed"/>
     <tableColumn id="6" xr3:uid="{2F758004-8A07-4C9F-A1EF-D5DABF4F31F0}" name="Partially Failed"/>
     <tableColumn id="7" xr3:uid="{DA700F0A-CDCF-4F77-AE73-82D409134037}" name="Untested"/>
-    <tableColumn id="8" xr3:uid="{F186EC08-2AB3-485D-B982-BDBCE5ABE745}" name="Total" dataDxfId="0">
+    <tableColumn id="8" xr3:uid="{F186EC08-2AB3-485D-B982-BDBCE5ABE745}" name="Total" dataDxfId="32">
       <calculatedColumnFormula>SUM(Table1[[#This Row],[Passed]:[Untested]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12067,8 +12130,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}" name="Table3" displayName="Table3" ref="A1:H31" totalsRowShown="0" headerRowDxfId="32">
-  <autoFilter ref="A1:H31" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}" name="Table3" displayName="Table3" ref="A1:H32" totalsRowShown="0" headerRowDxfId="31">
+  <autoFilter ref="A1:H32" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{8103CDF3-74DC-4B31-821D-E20368EA5455}" name="Versions"/>
     <tableColumn id="2" xr3:uid="{6C3B261F-FA51-42D2-821A-F22633569372}" name="Passed"/>
@@ -12077,7 +12140,7 @@
     <tableColumn id="5" xr3:uid="{41B83D2F-6D51-4667-B2B2-F76F6482C1D1}" name="Failed"/>
     <tableColumn id="6" xr3:uid="{26F61733-CA12-4B2B-8922-ABF23FA1A0CF}" name="Partially Failed"/>
     <tableColumn id="7" xr3:uid="{D40FAE8C-0F59-4E72-8577-B404EAC3FBFC}" name="Untested"/>
-    <tableColumn id="8" xr3:uid="{9EDBB1BE-19AD-4F52-9FAF-1ED9F6FC2EBD}" name="Total" dataDxfId="31">
+    <tableColumn id="8" xr3:uid="{9EDBB1BE-19AD-4F52-9FAF-1ED9F6FC2EBD}" name="Total" dataDxfId="30">
       <calculatedColumnFormula>SUM(Table3[[#This Row],[Passed]:[Untested]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12086,17 +12149,17 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{E4AD0B7A-EC5B-4838-AC2B-8475A3B6644B}" name="Table7" displayName="Table7" ref="A1:H21" totalsRowShown="0" headerRowDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{E4AD0B7A-EC5B-4838-AC2B-8475A3B6644B}" name="Table7" displayName="Table7" ref="A1:H21" totalsRowShown="0" headerRowDxfId="29">
   <autoFilter ref="A1:H21" xr:uid="{E4AD0B7A-EC5B-4838-AC2B-8475A3B6644B}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{58F8A895-CEBE-41D2-B7BB-1681C0697C85}" name="Version"/>
-    <tableColumn id="2" xr3:uid="{CE08A48D-2419-484B-993C-54A546869B61}" name="To Do" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{FC519478-6B36-4D96-93F3-3AF4B1D70F3E}" name="In Progress" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{52258D92-71B9-4E63-A3AA-5ABE6B4F3D23}" name="In Review" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{C5EE39F3-E9DF-4F2E-9576-6DDB97E21DB3}" name="In QA" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{CC106112-C63E-4AA5-9AAA-D0A99983E0DD}" name="Internal Test" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{C69EECCF-E5E5-4372-B171-2B35FE10B60D}" name="Done" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{C7A900BC-8967-4049-AE22-7F9EDE21E913}" name="Total" dataDxfId="15" totalsRowDxfId="23">
+    <tableColumn id="2" xr3:uid="{CE08A48D-2419-484B-993C-54A546869B61}" name="To Do" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{FC519478-6B36-4D96-93F3-3AF4B1D70F3E}" name="In Progress" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{52258D92-71B9-4E63-A3AA-5ABE6B4F3D23}" name="In Review" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{C5EE39F3-E9DF-4F2E-9576-6DDB97E21DB3}" name="In QA" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{CC106112-C63E-4AA5-9AAA-D0A99983E0DD}" name="Internal Test" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{C69EECCF-E5E5-4372-B171-2B35FE10B60D}" name="Done" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{C7A900BC-8967-4049-AE22-7F9EDE21E913}" name="Total" dataDxfId="22" totalsRowDxfId="21">
       <calculatedColumnFormula>SUM(Table7[[#This Row],[To Do]:[Done]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12105,18 +12168,18 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}" name="Table5" displayName="Table5" ref="A1:I27" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" headerRowBorderDxfId="11" tableBorderDxfId="12" totalsRowBorderDxfId="10" dataCellStyle="Hyperlink">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}" name="Table5" displayName="Table5" ref="A1:I27" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17" totalsRowBorderDxfId="16" dataCellStyle="Hyperlink">
   <autoFilter ref="A1:I27" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{5BE08AE0-E0B5-4B46-9423-456B88C2D9BC}" name="Sprint" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{030F9647-4FC0-4C7E-9B3A-AB099CC59EBA}" name="To Do (0%)" dataDxfId="8" dataCellStyle="Hyperlink"/>
-    <tableColumn id="3" xr3:uid="{7D2923F3-E2CF-4FD9-A7A5-68C36BB95591}" name="STARTING (10 ~ 40%)" dataDxfId="7" dataCellStyle="Hyperlink"/>
-    <tableColumn id="4" xr3:uid="{48FB5317-7F3B-4F74-B244-5A49C7749EBD}" name="In Progress (50 ~ 70%)" dataDxfId="6" dataCellStyle="Hyperlink"/>
-    <tableColumn id="5" xr3:uid="{86F5CCB5-C4C2-4C36-935A-657F085500B1}" name="IN REVIEW (80%)" dataDxfId="5" dataCellStyle="Hyperlink"/>
-    <tableColumn id="9" xr3:uid="{51D22AE3-424C-4604-9869-D672DED4301F}" name="READY FOR TESTING (90%)" dataDxfId="4" dataCellStyle="Hyperlink"/>
-    <tableColumn id="6" xr3:uid="{33C9BCE6-D9EB-4032-9B0A-DDD9A4051A2D}" name="Done (100%)" dataDxfId="3" dataCellStyle="Hyperlink"/>
-    <tableColumn id="8" xr3:uid="{D624FC89-A88E-45AC-9D22-66D66702B8C5}" name="WON'T DO (100%)" dataDxfId="2" dataCellStyle="Hyperlink"/>
-    <tableColumn id="7" xr3:uid="{EFEEB7EC-E2D1-40EA-B265-A558311E5D30}" name="Total" dataDxfId="1" dataCellStyle="Hyperlink">
+    <tableColumn id="1" xr3:uid="{5BE08AE0-E0B5-4B46-9423-456B88C2D9BC}" name="Sprint" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{030F9647-4FC0-4C7E-9B3A-AB099CC59EBA}" name="To Do (0%)" dataDxfId="6" dataCellStyle="Hyperlink"/>
+    <tableColumn id="3" xr3:uid="{7D2923F3-E2CF-4FD9-A7A5-68C36BB95591}" name="STARTING (10 ~ 40%)" dataDxfId="5" dataCellStyle="Hyperlink"/>
+    <tableColumn id="4" xr3:uid="{48FB5317-7F3B-4F74-B244-5A49C7749EBD}" name="In Progress (50 ~ 70%)" dataDxfId="4" dataCellStyle="Hyperlink"/>
+    <tableColumn id="5" xr3:uid="{86F5CCB5-C4C2-4C36-935A-657F085500B1}" name="IN REVIEW (80%)" dataDxfId="3" dataCellStyle="Hyperlink"/>
+    <tableColumn id="9" xr3:uid="{51D22AE3-424C-4604-9869-D672DED4301F}" name="READY FOR TESTING (90%)" dataDxfId="2" dataCellStyle="Hyperlink"/>
+    <tableColumn id="6" xr3:uid="{33C9BCE6-D9EB-4032-9B0A-DDD9A4051A2D}" name="Done (100%)" dataDxfId="1" dataCellStyle="Hyperlink"/>
+    <tableColumn id="8" xr3:uid="{D624FC89-A88E-45AC-9D22-66D66702B8C5}" name="WON'T DO (100%)" dataDxfId="0" dataCellStyle="Hyperlink"/>
+    <tableColumn id="7" xr3:uid="{EFEEB7EC-E2D1-40EA-B265-A558311E5D30}" name="Total" dataDxfId="14" dataCellStyle="Hyperlink">
       <calculatedColumnFormula>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12125,14 +12188,14 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}" name="Table25" displayName="Table25" ref="A1:E19" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
-  <autoFilter ref="A1:E19" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}" name="Table25" displayName="Table25" ref="A1:E20" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:E20" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7070D9F2-0ED1-4F39-8D72-28B37C8E98F2}" name="Week" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{1173F443-CC27-4C6E-A432-BF66DB2A740E}" name="Done" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{2EE10CB5-1AF1-4B50-9456-B3A666DD5338}" name="In Review/Progress" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{328D0A00-85F0-4BFF-81FE-C023998A3701}" name="TODO (P1)" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{E385808E-1FCD-451C-9807-DAF18A42B704}" name="Total" dataDxfId="16">
+    <tableColumn id="1" xr3:uid="{7070D9F2-0ED1-4F39-8D72-28B37C8E98F2}" name="Week" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{1173F443-CC27-4C6E-A432-BF66DB2A740E}" name="Done" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{2EE10CB5-1AF1-4B50-9456-B3A666DD5338}" name="In Review/Progress" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{328D0A00-85F0-4BFF-81FE-C023998A3701}" name="TODO (P1)" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{E385808E-1FCD-451C-9807-DAF18A42B704}" name="Total" dataDxfId="7">
       <calculatedColumnFormula>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12457,7 +12520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D733A42-966D-5F4E-B061-B304543CE88E}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.77734375" customWidth="1"/>
@@ -12947,6 +13010,24 @@
         <v>161</v>
       </c>
       <c r="E27" s="12">
+        <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28">
+        <v>31</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28">
+        <v>161</v>
+      </c>
+      <c r="E28" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
         <v>195</v>
       </c>
@@ -13431,10 +13512,10 @@
     </row>
     <row r="18" spans="1:8" ht="21.95" customHeight="1">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B18">
-        <v>388</v>
+        <v>614</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -13443,17 +13524,17 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>494</v>
+        <v>196</v>
       </c>
       <c r="H18">
         <f>SUM(Table1[[#This Row],[Passed]:[Untested]])</f>
-        <v>882</v>
+        <v>814</v>
       </c>
     </row>
   </sheetData>
@@ -13468,7 +13549,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA6EDF6-834F-DA49-B3FC-BFE1673433AB}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
@@ -14130,11 +14211,38 @@
         <v>6</v>
       </c>
       <c r="G31">
-        <v>455</v>
+        <v>0</v>
       </c>
       <c r="H31" s="12">
         <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
-        <v>639</v>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="A32" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32">
+        <v>723</v>
+      </c>
+      <c r="C32">
+        <v>12</v>
+      </c>
+      <c r="D32">
+        <v>3</v>
+      </c>
+      <c r="E32">
+        <v>7</v>
+      </c>
+      <c r="F32">
+        <v>8</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32" s="12">
+        <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
+        <v>753</v>
       </c>
     </row>
   </sheetData>
@@ -14191,22 +14299,22 @@
       <c r="A2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2">
         <v>15</v>
       </c>
-      <c r="C2" s="3">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3">
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>61</v>
       </c>
       <c r="H2">
@@ -14218,22 +14326,22 @@
       <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3">
         <v>7</v>
       </c>
-      <c r="C3" s="3">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" s="3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>46</v>
       </c>
       <c r="H3">
@@ -14245,22 +14353,22 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>18</v>
       </c>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
         <v>2</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>43</v>
       </c>
       <c r="H4">
@@ -14272,22 +14380,22 @@
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>17</v>
       </c>
-      <c r="C5" s="3">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="3">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>33</v>
       </c>
       <c r="H5">
@@ -14299,22 +14407,22 @@
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>26</v>
       </c>
-      <c r="C6" s="3">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" s="3">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>25</v>
       </c>
       <c r="H6">
@@ -14326,22 +14434,22 @@
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>14</v>
       </c>
-      <c r="C7" s="3">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3">
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" s="3">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>56</v>
       </c>
       <c r="H7">
@@ -14353,22 +14461,22 @@
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>10</v>
       </c>
-      <c r="C8" s="3">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3">
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
         <v>40</v>
       </c>
       <c r="H8">
@@ -14380,22 +14488,22 @@
       <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>6</v>
       </c>
-      <c r="C9" s="3">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3">
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
         <v>33</v>
       </c>
       <c r="H9">
@@ -14407,22 +14515,22 @@
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10">
         <v>11</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10">
         <v>1</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
         <v>29</v>
       </c>
       <c r="H10">
@@ -14434,22 +14542,22 @@
       <c r="A11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11">
         <v>2</v>
       </c>
-      <c r="C11" s="3">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3">
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" s="3">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3">
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
         <v>1</v>
       </c>
       <c r="H11">
@@ -14461,22 +14569,22 @@
       <c r="A12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12">
         <v>13</v>
       </c>
-      <c r="C12" s="3">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3">
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
         <v>9</v>
       </c>
       <c r="H12">
@@ -14488,22 +14596,22 @@
       <c r="A13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="3">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3">
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" s="3">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3">
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <v>12</v>
       </c>
       <c r="H13">
@@ -14515,22 +14623,22 @@
       <c r="A14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14">
         <v>4</v>
       </c>
-      <c r="C14" s="3">
-        <v>0</v>
-      </c>
-      <c r="D14" s="3">
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
         <v>9</v>
       </c>
       <c r="H14">
@@ -14542,23 +14650,23 @@
       <c r="A15" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="3">
-        <v>17</v>
-      </c>
-      <c r="C15" s="3">
-        <v>0</v>
-      </c>
-      <c r="D15" s="3">
+      <c r="B15">
+        <v>16</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>37</v>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>38</v>
       </c>
       <c r="H15">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
@@ -14569,22 +14677,22 @@
       <c r="A16" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16">
         <v>5</v>
       </c>
-      <c r="C16" s="3">
-        <v>0</v>
-      </c>
-      <c r="D16" s="3">
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16" s="3">
-        <v>0</v>
-      </c>
-      <c r="G16" s="3">
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
         <v>37</v>
       </c>
       <c r="H16">
@@ -14596,23 +14704,23 @@
       <c r="A17" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="3">
-        <v>8</v>
-      </c>
-      <c r="C17" s="3">
+      <c r="B17">
+        <v>7</v>
+      </c>
+      <c r="C17">
         <v>1</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <v>34</v>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>35</v>
       </c>
       <c r="H17">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
@@ -14623,23 +14731,23 @@
       <c r="A18" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="3">
-        <v>7</v>
-      </c>
-      <c r="C18" s="3">
-        <v>0</v>
-      </c>
-      <c r="D18" s="3">
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3">
-        <v>17</v>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>18</v>
       </c>
       <c r="H18">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
@@ -14650,23 +14758,23 @@
       <c r="A19" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19">
         <v>2</v>
       </c>
-      <c r="C19" s="3">
-        <v>2</v>
-      </c>
-      <c r="D19" s="3">
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3">
-        <v>2</v>
-      </c>
-      <c r="G19" s="3">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>10</v>
       </c>
       <c r="H19">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
@@ -14677,54 +14785,54 @@
       <c r="A20" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="3">
-        <v>2</v>
-      </c>
-      <c r="C20" s="3">
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
         <v>1</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>4</v>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>8</v>
       </c>
       <c r="H20">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
         <v>1</v>
-      </c>
-      <c r="C21" s="3">
-        <v>0</v>
-      </c>
-      <c r="D21" s="3">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3">
-        <v>0</v>
       </c>
       <c r="H21">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -14786,7 +14894,7 @@
         <v>100</v>
       </c>
       <c r="B2" s="5">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C2" s="5">
         <v>0</v>
@@ -14798,17 +14906,17 @@
         <v>4</v>
       </c>
       <c r="F2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="5">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H2" s="5">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I2" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>357</v>
+        <v>369</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18" thickBot="1">
@@ -14816,7 +14924,7 @@
         <v>101</v>
       </c>
       <c r="B3" s="5">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C3" s="5">
         <v>0</v>
@@ -14838,7 +14946,7 @@
       </c>
       <c r="I3" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" thickBot="1">
@@ -15449,26 +15557,26 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5">
         <v>1</v>
       </c>
-      <c r="D24" s="5">
-        <v>1</v>
-      </c>
-      <c r="E24" s="5">
-        <v>0</v>
-      </c>
-      <c r="F24" s="5">
-        <v>2</v>
-      </c>
       <c r="G24" s="5">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H24" s="5">
         <v>2</v>
       </c>
       <c r="I24" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="18" thickBot="1">
@@ -15476,29 +15584,29 @@
         <v>92</v>
       </c>
       <c r="B25" s="5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C25" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5">
         <v>1</v>
       </c>
       <c r="E25" s="5">
+        <v>3</v>
+      </c>
+      <c r="F25" s="5">
         <v>1</v>
       </c>
-      <c r="F25" s="5">
-        <v>5</v>
-      </c>
       <c r="G25" s="5">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H25" s="5">
         <v>3</v>
       </c>
       <c r="I25" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="18" thickBot="1">
@@ -15506,7 +15614,7 @@
         <v>98</v>
       </c>
       <c r="B26" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C26" s="5">
         <v>1</v>
@@ -15515,7 +15623,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="5">
         <v>0</v>
@@ -15528,7 +15636,7 @@
       </c>
       <c r="I26" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="18" thickBot="1">
@@ -15536,7 +15644,7 @@
         <v>99</v>
       </c>
       <c r="B27" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C27" s="5">
         <v>0</v>
@@ -15558,194 +15666,194 @@
       </c>
       <c r="I27" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{809911B9-76F9-4F05-BF2D-6BBC76E4F9A4}"/>
-    <hyperlink ref="D4" r:id="rId2" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{6B099EA0-04DA-43D1-8F27-EB9428CB8EF8}"/>
-    <hyperlink ref="G4" r:id="rId3" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{53437BDB-B9CF-4A77-8F51-0EC19C84E287}"/>
-    <hyperlink ref="E4" r:id="rId4" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{4A483F77-3DFE-4943-883F-066FD629EC60}"/>
-    <hyperlink ref="H4" r:id="rId5" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{4432C5CA-1687-45C6-A1FC-ACAE6248977B}"/>
-    <hyperlink ref="C4" r:id="rId6" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{CA463E28-82E9-4EC4-9F5C-36811632F5FB}"/>
-    <hyperlink ref="F4" r:id="rId7" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{8BCCA4C3-1A13-4861-8312-700629419ABB}"/>
-    <hyperlink ref="B5" r:id="rId8" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{43008575-D248-4C37-B84B-B58F31C9E710}"/>
-    <hyperlink ref="D5" r:id="rId9" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{1653F765-3F3B-4B2E-9D36-538466BF23A6}"/>
-    <hyperlink ref="G5" r:id="rId10" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{7070D2B0-7E6D-4074-A27C-E36E1E8AE2A5}"/>
-    <hyperlink ref="E5" r:id="rId11" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A76495A5-96A4-4290-8219-6C5408113A6F}"/>
-    <hyperlink ref="H5" r:id="rId12" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{C97C35D6-A179-4245-AA36-94D184175927}"/>
-    <hyperlink ref="C5" r:id="rId13" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{523C3F12-61CD-463C-A5FF-92656933318E}"/>
-    <hyperlink ref="F5" r:id="rId14" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E5410F34-7F6C-4F8C-B0AD-9230565A782A}"/>
-    <hyperlink ref="B6" r:id="rId15" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{AE9F9892-18D8-4BA4-97EA-2CBE8E8C303E}"/>
-    <hyperlink ref="D6" r:id="rId16" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{CB4D0C42-DB0E-4D72-B16C-151732989921}"/>
-    <hyperlink ref="G6" r:id="rId17" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{67892A8E-723C-4B5E-B1F9-DB1BB20C8917}"/>
-    <hyperlink ref="E6" r:id="rId18" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{336B88ED-F758-4271-8635-3A8D1D1D556A}"/>
-    <hyperlink ref="H6" r:id="rId19" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{2F756263-1270-43F6-950C-92BD3164EBBB}"/>
-    <hyperlink ref="C6" r:id="rId20" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{ACF67BC0-89FE-4D5A-B97B-812F44746C6D}"/>
-    <hyperlink ref="F6" r:id="rId21" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{9F1F05CA-A99B-4163-9466-5FF138BFBF50}"/>
-    <hyperlink ref="B7" r:id="rId22" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{FA4C0BF9-A9A1-4B46-9050-76DD68287419}"/>
-    <hyperlink ref="D7" r:id="rId23" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{22FE5682-848C-4093-AB72-5C6137AD99CE}"/>
-    <hyperlink ref="G7" r:id="rId24" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{DB9974B9-7BAC-40B7-BD0C-B06113AFB915}"/>
-    <hyperlink ref="E7" r:id="rId25" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{72130AC9-2DFB-417B-9555-D30217DEFFED}"/>
-    <hyperlink ref="H7" r:id="rId26" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{F680F49E-77A1-4803-8990-F1267B8509E7}"/>
-    <hyperlink ref="C7" r:id="rId27" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A107A0E4-D25D-4B5C-A287-2BA40D3A6CE1}"/>
-    <hyperlink ref="F7" r:id="rId28" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{71ABECD1-D053-4327-BA34-1AE3EFC5E005}"/>
-    <hyperlink ref="B8" r:id="rId29" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C2A15436-EB0D-41A7-BA99-74AC0265F40C}"/>
-    <hyperlink ref="D8" r:id="rId30" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{BE5C5B59-D82A-44B8-A178-0635264600AC}"/>
-    <hyperlink ref="G8" r:id="rId31" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{8CBB9692-A79C-44A2-A7A8-0FF31F3EE08A}"/>
-    <hyperlink ref="E8" r:id="rId32" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A45B00C8-CA31-4639-A512-D2CB8C9CC5E8}"/>
-    <hyperlink ref="H8" r:id="rId33" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{440016F2-D63E-4478-B81F-448FD1ECB262}"/>
-    <hyperlink ref="C8" r:id="rId34" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{EDE311DC-E60C-483B-BC39-7648489A0E99}"/>
-    <hyperlink ref="F8" r:id="rId35" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{8921717D-4DD0-415F-8786-1A949A18110F}"/>
-    <hyperlink ref="B9" r:id="rId36" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{5FF5D9F2-3D2C-415F-8402-AAD3FF701320}"/>
-    <hyperlink ref="D9" r:id="rId37" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D005BEE4-355C-4621-9CEF-3B254C7E0267}"/>
-    <hyperlink ref="G9" r:id="rId38" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{85757C4C-E150-4401-83A1-A24FA0FBD79B}"/>
-    <hyperlink ref="E9" r:id="rId39" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{78AFBF1B-52DE-4CDC-8CFC-C164967D0753}"/>
-    <hyperlink ref="H9" r:id="rId40" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{DCD465D9-29F4-4B28-BDFC-E5E9884A5FE8}"/>
-    <hyperlink ref="C9" r:id="rId41" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{0CCF4C5A-035E-4648-A9FF-3756DB75E273}"/>
-    <hyperlink ref="F9" r:id="rId42" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C2A2B8CD-FB8E-4535-8062-810B0CF2288A}"/>
-    <hyperlink ref="B10" r:id="rId43" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{CBC4FA39-776C-4DE2-93BB-37E2E644BA0D}"/>
-    <hyperlink ref="D10" r:id="rId44" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{AC65ED6C-148F-4532-A62A-FD801B17E639}"/>
-    <hyperlink ref="G10" r:id="rId45" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{AEB89E02-CD1F-421B-A29E-19CC77E06704}"/>
-    <hyperlink ref="E10" r:id="rId46" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F6B12E1B-1989-4478-9816-516133A06C54}"/>
-    <hyperlink ref="H10" r:id="rId47" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{8D3B67BF-765B-45B9-A673-1E5BA756D87E}"/>
-    <hyperlink ref="C10" r:id="rId48" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{268C54F3-9625-489E-AE1A-FE1C1FB23F04}"/>
-    <hyperlink ref="F10" r:id="rId49" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{BA5625FF-62E4-47D4-BDB9-CA6D7F76F92C}"/>
-    <hyperlink ref="B11" r:id="rId50" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A49E1934-7EFC-455B-A85C-337EC77B1B65}"/>
-    <hyperlink ref="D11" r:id="rId51" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{5C38973C-96E9-408E-B8CD-65DB985B2A99}"/>
-    <hyperlink ref="G11" r:id="rId52" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{BA200205-AA70-480C-AF68-32217E59167A}"/>
-    <hyperlink ref="E11" r:id="rId53" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{C054038C-7AD9-415D-BCC9-5A8C143768BD}"/>
-    <hyperlink ref="H11" r:id="rId54" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E5E35CC8-29BF-474E-9761-62C45C4172A8}"/>
-    <hyperlink ref="C11" r:id="rId55" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{3A5D8691-EA28-4A7D-B37C-0D93C59035D5}"/>
-    <hyperlink ref="F11" r:id="rId56" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{4BFFD283-E2FE-4C13-AD26-2210AA94B599}"/>
-    <hyperlink ref="B12" r:id="rId57" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{F8593ACE-636B-403A-A712-EF8DDC49A22E}"/>
-    <hyperlink ref="D12" r:id="rId58" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D725BBD2-653C-40D9-945F-BE91C8EB9733}"/>
-    <hyperlink ref="G12" r:id="rId59" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F95614A1-E6C4-4633-967B-FE665C115ED5}"/>
-    <hyperlink ref="E12" r:id="rId60" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E9EB2556-D891-4D22-8D3B-99640293CFEA}"/>
-    <hyperlink ref="H12" r:id="rId61" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{C77D8C36-5F65-4740-AFC8-16F5A4692277}"/>
-    <hyperlink ref="C12" r:id="rId62" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A535644C-83A5-4CB0-9829-1AE4B6C2B504}"/>
-    <hyperlink ref="F12" r:id="rId63" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{913F0D72-9F20-4D15-B340-2FD29C293540}"/>
-    <hyperlink ref="B13" r:id="rId64" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{FBF54ADC-A1C6-484F-B1CE-E84D3D12CE07}"/>
-    <hyperlink ref="D13" r:id="rId65" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{EBCBA75B-B2B6-46D1-BCC4-187E6F8FA482}"/>
-    <hyperlink ref="G13" r:id="rId66" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{672F40D7-E05F-452E-A095-3DF7D7820611}"/>
-    <hyperlink ref="E13" r:id="rId67" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{13BB4184-DC18-4BBC-BAA8-3239F6616721}"/>
-    <hyperlink ref="H13" r:id="rId68" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{4EA0DA79-6BAF-49CC-8DCE-6B9B5FCD0BC8}"/>
-    <hyperlink ref="C13" r:id="rId69" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{3BF0366F-8BBC-4F7F-9765-7CA9F1C594B0}"/>
-    <hyperlink ref="F13" r:id="rId70" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{8774BD5F-0DE1-451C-9301-2E3B775F4E8D}"/>
-    <hyperlink ref="B14" r:id="rId71" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{CBE74DF1-1680-46DD-ABDB-247754DF3737}"/>
-    <hyperlink ref="D14" r:id="rId72" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{64E6426F-D4D6-490E-A65B-A0898BCE1BC0}"/>
-    <hyperlink ref="G14" r:id="rId73" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3DCC6CEB-6808-4463-B122-43A7777D5521}"/>
-    <hyperlink ref="E14" r:id="rId74" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{99E89007-0504-4278-A141-B4431A5B700D}"/>
-    <hyperlink ref="H14" r:id="rId75" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{DEBDD966-994E-4773-A45D-02EC25578AAB}"/>
-    <hyperlink ref="C14" r:id="rId76" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{35134365-F806-456C-96EB-A68DA5C1A5C2}"/>
-    <hyperlink ref="F14" r:id="rId77" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{45CF823E-8F4E-4C94-A49D-C29D1560F4AA}"/>
-    <hyperlink ref="B15" r:id="rId78" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{79D5282E-7221-421F-BE1E-FD480BA6BB20}"/>
-    <hyperlink ref="D15" r:id="rId79" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{FFCB8B3B-865A-4780-9B5E-89C395CACC65}"/>
-    <hyperlink ref="G15" r:id="rId80" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{32E870DD-0569-4685-A9DE-0CC61CD0F1D1}"/>
-    <hyperlink ref="E15" r:id="rId81" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{06EDB94B-C1E8-4035-AEF5-EDA8329F815E}"/>
-    <hyperlink ref="H15" r:id="rId82" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{99730D50-CAAA-4855-BE7F-B9A4241F9E56}"/>
-    <hyperlink ref="C15" r:id="rId83" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6C68D715-0E54-40B1-8315-250BBEA9DCE8}"/>
-    <hyperlink ref="F15" r:id="rId84" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E892457F-9BBE-4D46-8F00-6224F881DA65}"/>
-    <hyperlink ref="B16" r:id="rId85" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{0ABFFA40-61BF-48AF-B693-9719E5BB2CED}"/>
-    <hyperlink ref="D16" r:id="rId86" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{C25E1253-0381-49D8-A8FD-E44CCAFA258F}"/>
-    <hyperlink ref="G16" r:id="rId87" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{72D281C8-A48F-4404-B3E3-7914FCC5F761}"/>
-    <hyperlink ref="E16" r:id="rId88" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{C99C42F0-8FDA-4A85-97BB-06A7E33F76C5}"/>
-    <hyperlink ref="H16" r:id="rId89" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{93761553-79E8-484F-866F-D8B1E3FD28A0}"/>
-    <hyperlink ref="C16" r:id="rId90" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6D0ED953-7B0D-4823-8B3D-D1FF50BA7798}"/>
-    <hyperlink ref="F16" r:id="rId91" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{834830F4-7D94-4107-AC9E-546C9FC0D8F4}"/>
-    <hyperlink ref="B17" r:id="rId92" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{FFC47A93-753D-45BD-84A9-2C8E939096CC}"/>
-    <hyperlink ref="D17" r:id="rId93" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{AF0F0963-788E-48F3-A864-05F399832899}"/>
-    <hyperlink ref="G17" r:id="rId94" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{72E3CFFE-E38C-4DD2-B168-F110EDF62D6E}"/>
-    <hyperlink ref="E17" r:id="rId95" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B0B793BC-CC52-49E6-A302-E554AACE338F}"/>
-    <hyperlink ref="H17" r:id="rId96" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{84CFA2E7-097E-4FF6-BC99-FC04B537C996}"/>
-    <hyperlink ref="C17" r:id="rId97" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{1A871C21-A8E2-4EBB-963F-CA348AD9651A}"/>
-    <hyperlink ref="F17" r:id="rId98" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A7B5ECC3-FF32-473E-BD29-9A447ED7CC1D}"/>
-    <hyperlink ref="B18" r:id="rId99" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{8351149E-A13D-417A-9F1E-EF71EEE3CF9D}"/>
-    <hyperlink ref="D18" r:id="rId100" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D56C4A55-52AB-4DA7-A6D1-C5F00DD4C338}"/>
-    <hyperlink ref="G18" r:id="rId101" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{1F116C9C-ECEB-4DC8-B4E0-6EA0B3B42056}"/>
-    <hyperlink ref="E18" r:id="rId102" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E04B4FA5-A2F2-4C64-9EDE-5F5DE9D8E9A6}"/>
-    <hyperlink ref="H18" r:id="rId103" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{71E4EE44-A29F-4526-BA38-4EF53739DD93}"/>
-    <hyperlink ref="C18" r:id="rId104" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{50D394ED-C29A-432C-A933-365144F1C1DD}"/>
-    <hyperlink ref="F18" r:id="rId105" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{BC5B7E0C-A7F6-42F9-8504-D17DB9FFEE05}"/>
-    <hyperlink ref="B19" r:id="rId106" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{798B3080-A508-48AE-8947-A168CE8BF5F7}"/>
-    <hyperlink ref="D19" r:id="rId107" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{66E6880A-CC47-48B1-ADDB-643A6025D5A9}"/>
-    <hyperlink ref="G19" r:id="rId108" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{E3D3CA17-3882-449D-AC0F-ACBE44FB0CD6}"/>
-    <hyperlink ref="E19" r:id="rId109" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{EFA11580-0B85-4714-9384-FDFA75234BA3}"/>
-    <hyperlink ref="H19" r:id="rId110" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{834ECA52-269F-4F0D-A927-285BF359ECC0}"/>
-    <hyperlink ref="C19" r:id="rId111" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{BE317CF9-1E01-4590-BFAB-8F768FE4477A}"/>
-    <hyperlink ref="F19" r:id="rId112" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{164C42ED-384F-4154-8FCF-D6D7BC210AAF}"/>
-    <hyperlink ref="B20" r:id="rId113" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{AB067417-A1E3-4D8D-AFA1-60C1242EC87A}"/>
-    <hyperlink ref="D20" r:id="rId114" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{892BF312-20B0-461C-BB21-2B38FB6601EC}"/>
-    <hyperlink ref="G20" r:id="rId115" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{7069171E-E0A8-42D6-9B18-A96FA9D9670A}"/>
-    <hyperlink ref="E20" r:id="rId116" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{FFEEC264-23C3-479B-836C-6A7816220486}"/>
-    <hyperlink ref="H20" r:id="rId117" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{8DF90A02-4A69-4CB4-B691-62DAEBF30861}"/>
-    <hyperlink ref="C20" r:id="rId118" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{2D9A0811-ECD0-4E83-B084-1ED048494949}"/>
-    <hyperlink ref="F20" r:id="rId119" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{30A5F476-97D8-45CA-93AC-BA3557449927}"/>
-    <hyperlink ref="B21" r:id="rId120" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{62DA024A-85CA-46C9-869E-370FAE8589E5}"/>
-    <hyperlink ref="D21" r:id="rId121" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{EA42C0A6-67E7-4439-BE9E-05F68C36A4FA}"/>
-    <hyperlink ref="G21" r:id="rId122" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{D63DF082-3A10-41FC-B993-EF3EC220C9AB}"/>
-    <hyperlink ref="E21" r:id="rId123" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{3E823444-4C36-4B65-9D15-1268A1FE7ECA}"/>
-    <hyperlink ref="H21" r:id="rId124" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{90328037-E39D-4C38-912C-7DBC6B124B2A}"/>
-    <hyperlink ref="C21" r:id="rId125" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{028309F5-49F5-4FC1-BC95-7F1BE93C0705}"/>
-    <hyperlink ref="F21" r:id="rId126" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E2B5DE71-E3A5-44E6-B360-4286FBD48AE1}"/>
-    <hyperlink ref="B22" r:id="rId127" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{31447D0C-7E99-4C15-8F45-B42CC49F24A4}"/>
-    <hyperlink ref="D22" r:id="rId128" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{B9D7FE24-FBAA-4EB1-9277-1F39AEFA3D8F}"/>
-    <hyperlink ref="G22" r:id="rId129" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{925AEBAD-45BC-4B41-8FC8-97567672446B}"/>
-    <hyperlink ref="E22" r:id="rId130" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{8403DAED-8C63-4AC2-A93D-0685568BAFDF}"/>
-    <hyperlink ref="H22" r:id="rId131" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{FB2B5D59-99CC-4335-9921-DFA15239FD2A}"/>
-    <hyperlink ref="C22" r:id="rId132" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{06CEADBE-F1BC-4C87-A636-B777FCB603B8}"/>
-    <hyperlink ref="F22" r:id="rId133" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C2949024-F0A1-4413-BBEB-B3208DEA7F3F}"/>
-    <hyperlink ref="B23" r:id="rId134" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{067B3D9B-C59E-449C-A13D-FD6561FD25E2}"/>
-    <hyperlink ref="D23" r:id="rId135" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{C6C5DA57-66A4-4A76-BFB8-708F79614290}"/>
-    <hyperlink ref="G23" r:id="rId136" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C4CD30A9-0235-46D2-9B58-91CF14B5399E}"/>
-    <hyperlink ref="E23" r:id="rId137" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F666FC5A-FAF7-4C70-A3F7-6F5B003A0504}"/>
-    <hyperlink ref="H23" r:id="rId138" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{8E2741DA-00B9-42C6-BF7A-CECB5C7A5EA1}"/>
-    <hyperlink ref="C23" r:id="rId139" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{0D997503-988D-4ABD-AB1C-BD103EB89410}"/>
-    <hyperlink ref="F23" r:id="rId140" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{2ACCA93B-4796-47AB-81CB-D2211D51E00E}"/>
-    <hyperlink ref="B24" r:id="rId141" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{6830705C-D441-44A3-86F5-32984F945991}"/>
-    <hyperlink ref="D24" r:id="rId142" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{736592D5-6D1E-408F-B02E-7244D465FD50}"/>
-    <hyperlink ref="G24" r:id="rId143" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{587ACEF7-F5F3-4109-B719-EBB4C4183040}"/>
-    <hyperlink ref="E24" r:id="rId144" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{0AFA3ED1-7292-4F03-996F-6A2A2D3A0953}"/>
-    <hyperlink ref="H24" r:id="rId145" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{C6B1CC50-91FE-481B-9F69-5737077BBA18}"/>
-    <hyperlink ref="C24" r:id="rId146" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6146E52B-A975-495D-B437-788544ED822D}"/>
-    <hyperlink ref="F24" r:id="rId147" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C44E6C0C-1849-48D8-8B81-3196429ABA91}"/>
-    <hyperlink ref="B25" r:id="rId148" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{B43341AF-D98D-40F3-A8CD-5A0F65C07BA4}"/>
-    <hyperlink ref="D25" r:id="rId149" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{7A43F814-4F67-499F-B300-B7019649656E}"/>
-    <hyperlink ref="G25" r:id="rId150" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{28E206CD-E58B-40CF-8BF0-84D3EC8D1B01}"/>
-    <hyperlink ref="E25" r:id="rId151" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D95661B6-48BD-41FC-A1CA-911866114506}"/>
-    <hyperlink ref="H25" r:id="rId152" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{B73535A0-B20E-40D5-A0DC-3D649F279C0E}"/>
-    <hyperlink ref="C25" r:id="rId153" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{2B842A76-1F4A-4BC2-8068-6C73CF537F6D}"/>
-    <hyperlink ref="F25" r:id="rId154" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F73C53F8-0B19-41F9-BE13-0B988EDE38B4}"/>
-    <hyperlink ref="B26" r:id="rId155" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{8C577972-191E-4506-9C4B-728263CF5F3B}"/>
-    <hyperlink ref="D26" r:id="rId156" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{5970EA26-C2A2-4DB6-9A59-528605C672EF}"/>
-    <hyperlink ref="G26" r:id="rId157" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{BC5BA146-1368-42A3-8FB1-C82206325E70}"/>
-    <hyperlink ref="E26" r:id="rId158" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{BDAF99B8-EE08-4A76-8335-CF08C8628DE1}"/>
-    <hyperlink ref="H26" r:id="rId159" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{01616887-05D0-44BA-870D-B1FF7AEFFCE8}"/>
-    <hyperlink ref="C26" r:id="rId160" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C5B7DB27-233C-4F2A-A0F1-5D5C8E4D7006}"/>
-    <hyperlink ref="F26" r:id="rId161" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{28FE0AF6-07C2-4BCF-9C84-4FA3F8947E90}"/>
-    <hyperlink ref="B27" r:id="rId162" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{3F1BFDB0-8FEF-4B03-9B80-BFBBA6DED58A}"/>
-    <hyperlink ref="D27" r:id="rId163" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{88820CF6-3163-490D-8566-3290DF72A3AA}"/>
-    <hyperlink ref="G27" r:id="rId164" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{962F555A-013B-4318-974D-5FC1690AC4CD}"/>
-    <hyperlink ref="E27" r:id="rId165" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{1B012E19-D779-402E-96A5-9B470EC23FA3}"/>
-    <hyperlink ref="H27" r:id="rId166" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{185DC5EB-5D6F-40E5-9597-979F5B23144A}"/>
-    <hyperlink ref="C27" r:id="rId167" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{9EC0D9BE-7428-41E0-B690-F9C98D4C905E}"/>
-    <hyperlink ref="F27" r:id="rId168" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{D924C78A-7EB1-4B73-AD46-9CF3D3D00B10}"/>
-    <hyperlink ref="B2" r:id="rId169" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C3E7CF5B-8526-4329-8920-3C4D26EC31A9}"/>
-    <hyperlink ref="D2" r:id="rId170" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{12BD1984-0B08-4350-8ED9-C83B6B039111}"/>
-    <hyperlink ref="G2" r:id="rId171" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{1B273B89-FFAB-4775-A13C-A2BCC76215A9}"/>
-    <hyperlink ref="E2" r:id="rId172" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A96C42EE-3C33-42BA-A901-F4EF8F429CD7}"/>
-    <hyperlink ref="H2" r:id="rId173" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{34864220-955C-4802-B200-B6D5E3959E41}"/>
-    <hyperlink ref="C2" r:id="rId174" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{7BB6763D-FC38-4CD1-A317-5AFDB91A97CA}"/>
-    <hyperlink ref="F2" r:id="rId175" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{FEF51C2F-6D76-448E-806F-F2878600C9E6}"/>
-    <hyperlink ref="B3" r:id="rId176" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{7D78EEF5-3AA8-4B35-917B-EC14A98B256C}"/>
-    <hyperlink ref="D3" r:id="rId177" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{7FCE6098-B630-4CD9-A80C-DF5B1EB8D4EC}"/>
-    <hyperlink ref="G3" r:id="rId178" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{314923AC-AC7D-42A6-A582-A858BE7A06B0}"/>
-    <hyperlink ref="E3" r:id="rId179" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{7989CAE1-1F3F-41E8-8309-E17CFDC6160B}"/>
-    <hyperlink ref="H3" r:id="rId180" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{0521050B-BD22-42E2-9A80-3B6B44655902}"/>
-    <hyperlink ref="C3" r:id="rId181" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{76EF4C34-D9F9-4CE3-941C-F4703F7E2D2C}"/>
-    <hyperlink ref="F3" r:id="rId182" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{4650FFD7-0961-400E-920D-B72AB6BD4105}"/>
+    <hyperlink ref="B2" r:id="rId1" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{BF8CA9E5-2F44-49C5-9583-F43D0A229C79}"/>
+    <hyperlink ref="D2" r:id="rId2" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{CD39E288-4AFE-44C4-A645-D33F825377F5}"/>
+    <hyperlink ref="G2" r:id="rId3" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{511EF0F3-1565-4207-81DE-83F4167B2D90}"/>
+    <hyperlink ref="E2" r:id="rId4" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{64BEB31F-0420-4096-AFF0-832EE7ACBFC7}"/>
+    <hyperlink ref="H2" r:id="rId5" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{4AB59AD4-9369-480C-A2CA-40A6B02A58A3}"/>
+    <hyperlink ref="C2" r:id="rId6" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{163878DD-34F6-42C3-900C-C506AEC3C870}"/>
+    <hyperlink ref="F2" r:id="rId7" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{8D7893F5-BFFF-468E-A141-D3589461842F}"/>
+    <hyperlink ref="B4" r:id="rId8" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{DCA6508D-6739-4E29-9D57-AFA23C32277E}"/>
+    <hyperlink ref="D4" r:id="rId9" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{5D82EBDE-B1AF-42AB-813F-43F2DD00C5BC}"/>
+    <hyperlink ref="G4" r:id="rId10" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{33E8F0EC-4F01-450E-BAA7-EAB194046D08}"/>
+    <hyperlink ref="E4" r:id="rId11" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{5AEE9758-D700-49E4-9B01-C5551E98CA6A}"/>
+    <hyperlink ref="H4" r:id="rId12" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{0363EEDC-31A2-42E8-84CB-754B34501EC9}"/>
+    <hyperlink ref="C4" r:id="rId13" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{0FA7A97F-A3AD-4A6C-BEFE-146F0F61789F}"/>
+    <hyperlink ref="F4" r:id="rId14" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{0878F59A-0484-4327-AB4E-2B7C5CA629A7}"/>
+    <hyperlink ref="B5" r:id="rId15" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{1C4D5FC9-AE17-4590-9174-EB26D30C7268}"/>
+    <hyperlink ref="D5" r:id="rId16" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D3B78AFF-4A34-4C88-B8F7-58248254A05C}"/>
+    <hyperlink ref="G5" r:id="rId17" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{CDC92034-3199-4A14-A924-6ABB6CF8DDE8}"/>
+    <hyperlink ref="E5" r:id="rId18" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E7AF27F5-E180-4F4E-8FCB-2452492DE5D0}"/>
+    <hyperlink ref="H5" r:id="rId19" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{10F4F01B-0D05-4DC7-B42C-B526B633EA2E}"/>
+    <hyperlink ref="C5" r:id="rId20" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{5CAD8FBC-408B-4D6F-B132-3146E2688EB6}"/>
+    <hyperlink ref="F5" r:id="rId21" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A6CF7003-F1CB-4B62-ACEB-CD28852C04DE}"/>
+    <hyperlink ref="B6" r:id="rId22" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{41A0AC65-F21B-425F-A634-DD90E3DF5C5B}"/>
+    <hyperlink ref="D6" r:id="rId23" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{1927087D-A714-4103-BCB1-B1240256748B}"/>
+    <hyperlink ref="G6" r:id="rId24" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{D70F7F81-375A-46B7-9340-A481AD621D16}"/>
+    <hyperlink ref="E6" r:id="rId25" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E84C155C-6F5F-4586-86FF-91500882041F}"/>
+    <hyperlink ref="H6" r:id="rId26" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{50ED0615-C223-4A2C-8A2C-BAD8A64AE8C6}"/>
+    <hyperlink ref="C6" r:id="rId27" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{483B452B-AC9E-492B-BC87-00D8C10E6BD1}"/>
+    <hyperlink ref="F6" r:id="rId28" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{013302C7-827D-427B-878B-E9E0C45B1741}"/>
+    <hyperlink ref="B7" r:id="rId29" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{CCC11889-F26D-41B0-8F70-777F9D22F32A}"/>
+    <hyperlink ref="D7" r:id="rId30" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{ADD121ED-122B-425E-9716-6A910BD0805A}"/>
+    <hyperlink ref="G7" r:id="rId31" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{D3BBA393-4036-44B9-8F1C-1C2CC6BCFCC2}"/>
+    <hyperlink ref="E7" r:id="rId32" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D5548EB4-B02D-4482-A88D-EFA077DDA8FB}"/>
+    <hyperlink ref="H7" r:id="rId33" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{9CF99D08-FBF6-4517-ACDC-82DEBDBDB5DC}"/>
+    <hyperlink ref="C7" r:id="rId34" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{54905639-2036-48CD-9DA1-AC0E425353DE}"/>
+    <hyperlink ref="F7" r:id="rId35" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{2F4F0C9E-7CB3-45C6-8068-A087534D7C7C}"/>
+    <hyperlink ref="B8" r:id="rId36" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{1C570888-DC70-473A-BA6D-627728948921}"/>
+    <hyperlink ref="D8" r:id="rId37" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{EEF9781C-FB9B-421F-9F78-111857DD24DE}"/>
+    <hyperlink ref="G8" r:id="rId38" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{E1690A74-9C37-4E90-ACE4-8BE7C9EBF7EC}"/>
+    <hyperlink ref="E8" r:id="rId39" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F353AE61-4AD3-46B1-AD67-EE36EBEBF894}"/>
+    <hyperlink ref="H8" r:id="rId40" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{05F921BC-FAC3-4E29-8EEF-A46B42160B5C}"/>
+    <hyperlink ref="C8" r:id="rId41" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{4DE48923-BA03-49B0-9E2B-7AF300930E51}"/>
+    <hyperlink ref="F8" r:id="rId42" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{41CCDFC2-90B2-4C3E-896D-CADB7BFF13D2}"/>
+    <hyperlink ref="B9" r:id="rId43" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{2AA004AA-32A0-4AC2-878A-574A202C52AB}"/>
+    <hyperlink ref="D9" r:id="rId44" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2747391A-0739-466F-85DE-107B233D682F}"/>
+    <hyperlink ref="G9" r:id="rId45" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{335F8DF8-BCDF-461D-A9C3-474248AA98BD}"/>
+    <hyperlink ref="E9" r:id="rId46" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{9D9FBEB0-7377-4CB0-8A43-BBF1F0A45660}"/>
+    <hyperlink ref="H9" r:id="rId47" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{132A046C-6042-4955-98C0-E29ACF60266E}"/>
+    <hyperlink ref="C9" r:id="rId48" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{F87F936A-6148-488B-A91C-10CA53CE0F1B}"/>
+    <hyperlink ref="F9" r:id="rId49" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{387BA32B-432A-49A3-BCAC-BE57C43293CC}"/>
+    <hyperlink ref="B10" r:id="rId50" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{7D8890A4-B206-48D5-B06A-A35AC41899E2}"/>
+    <hyperlink ref="D10" r:id="rId51" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2DECEBB2-3486-4E7D-B15B-C0B1D99B22CD}"/>
+    <hyperlink ref="G10" r:id="rId52" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{942AD767-269A-4DF9-802E-21CA062D3A90}"/>
+    <hyperlink ref="E10" r:id="rId53" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B5834AB4-D5E6-4B15-96E0-7C22DA172898}"/>
+    <hyperlink ref="H10" r:id="rId54" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{C7DD3757-049C-488F-BBB4-CC2C5158EB62}"/>
+    <hyperlink ref="C10" r:id="rId55" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{192D0568-12F8-49D6-ADDE-0CDF96EE068D}"/>
+    <hyperlink ref="F10" r:id="rId56" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{490038C6-81F0-4E6F-82FA-7BEC049DC881}"/>
+    <hyperlink ref="B11" r:id="rId57" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{675020C2-C08B-4982-A660-9A50F8D90B67}"/>
+    <hyperlink ref="D11" r:id="rId58" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{67878041-2290-4A42-96A3-948F277A0925}"/>
+    <hyperlink ref="G11" r:id="rId59" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C9FF9018-2F71-451C-AE25-63B0E3ABE2BF}"/>
+    <hyperlink ref="E11" r:id="rId60" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D653A96C-2EE7-4E83-9EC3-07DCE5DCF5C1}"/>
+    <hyperlink ref="H11" r:id="rId61" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{86B73676-F611-4840-8EC6-ACE1F7A506C0}"/>
+    <hyperlink ref="C11" r:id="rId62" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{3810384C-0078-49B5-ABC7-8F2E2F76090C}"/>
+    <hyperlink ref="F11" r:id="rId63" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{53968197-3A55-42A4-B942-96DB8D8D4B42}"/>
+    <hyperlink ref="B12" r:id="rId64" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A92B67E4-F2C6-4FFC-9870-C08A06C4808A}"/>
+    <hyperlink ref="D12" r:id="rId65" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{4029CD5A-B6A5-4BE0-B1DC-19C61288FEE3}"/>
+    <hyperlink ref="G12" r:id="rId66" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{324378B0-3F46-47A0-B27C-B3137B72415B}"/>
+    <hyperlink ref="E12" r:id="rId67" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D5FDA6B8-1D46-4B01-B4E5-EC39E9035850}"/>
+    <hyperlink ref="H12" r:id="rId68" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{4372200D-F98B-488F-AA84-D8837594290E}"/>
+    <hyperlink ref="C12" r:id="rId69" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{1EBCE976-7D1E-4C84-86B6-6AFEDBFC76DD}"/>
+    <hyperlink ref="F12" r:id="rId70" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{3E7C6BEA-A2D4-415A-88AC-A54AAD0F2BD2}"/>
+    <hyperlink ref="B13" r:id="rId71" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{D9B15A27-6974-4F2C-8572-427955E4773B}"/>
+    <hyperlink ref="D13" r:id="rId72" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{785876D4-D317-476C-A524-5BEE03467976}"/>
+    <hyperlink ref="G13" r:id="rId73" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3602973B-CFCA-4F06-AEE6-6C9CB66B5D41}"/>
+    <hyperlink ref="E13" r:id="rId74" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B353D0B7-F376-4860-886A-BAD7C0AC7DBF}"/>
+    <hyperlink ref="H13" r:id="rId75" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{7A31078F-43FB-4908-9F8E-0E95B463CBC9}"/>
+    <hyperlink ref="C13" r:id="rId76" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{47D7338D-D8A1-489A-B8BB-2E01EAC730C5}"/>
+    <hyperlink ref="F13" r:id="rId77" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A77DD6C4-9C7D-4B27-B980-940906659B64}"/>
+    <hyperlink ref="B14" r:id="rId78" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{25A41323-A06A-49CD-9088-FB939FFF37C7}"/>
+    <hyperlink ref="D14" r:id="rId79" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{92A7FA35-800F-4303-A524-DC4931A5707C}"/>
+    <hyperlink ref="G14" r:id="rId80" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{71B1A2C8-8780-448A-92A7-4A80CF20E1E8}"/>
+    <hyperlink ref="E14" r:id="rId81" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E5ADB792-3242-465C-8D85-7A0591BAAD7B}"/>
+    <hyperlink ref="H14" r:id="rId82" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{A0D970F1-F15E-41E5-8557-179053945D6C}"/>
+    <hyperlink ref="C14" r:id="rId83" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{AFBE1924-9C18-49D0-81D7-C0A91E1F4D3A}"/>
+    <hyperlink ref="F14" r:id="rId84" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{52121796-C8A3-4A3D-ACFF-D950A7775719}"/>
+    <hyperlink ref="B15" r:id="rId85" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{8874C70F-FFDA-406D-85FA-1F39BBA1D859}"/>
+    <hyperlink ref="D15" r:id="rId86" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{AF13EDCD-5C38-4099-81E2-D812237DA7D7}"/>
+    <hyperlink ref="G15" r:id="rId87" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{10CEA241-FE66-4A46-944F-CC83B2040106}"/>
+    <hyperlink ref="E15" r:id="rId88" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{C1871489-0F59-44C8-99E4-E5624A6301F1}"/>
+    <hyperlink ref="H15" r:id="rId89" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{00F88501-E21A-4C6B-BEB3-BD9A9E208C14}"/>
+    <hyperlink ref="C15" r:id="rId90" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{45869C56-B0DC-42D2-965B-6DC4A42C17DE}"/>
+    <hyperlink ref="F15" r:id="rId91" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F52B478C-CB8B-42D7-BD75-F664CFF4CC39}"/>
+    <hyperlink ref="B16" r:id="rId92" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{DA85980A-BD58-44C4-84E6-3B8C58EB8220}"/>
+    <hyperlink ref="D16" r:id="rId93" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{CAF754CD-2398-4DDC-9540-551898340959}"/>
+    <hyperlink ref="G16" r:id="rId94" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{13A36FB3-A31E-4CB5-BC0E-8DA3811A3F25}"/>
+    <hyperlink ref="E16" r:id="rId95" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{8456322F-624D-4DCA-B30E-3391F342BDFA}"/>
+    <hyperlink ref="H16" r:id="rId96" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{07E83961-7899-43C9-9A0E-C07077E3841F}"/>
+    <hyperlink ref="C16" r:id="rId97" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{8B3AF250-90F2-4F89-9D4A-E2908A266FC7}"/>
+    <hyperlink ref="F16" r:id="rId98" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{3288F97A-65EB-4E73-BF3E-5F1B0848661A}"/>
+    <hyperlink ref="B17" r:id="rId99" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{D838ABC2-C56E-4013-9E2D-8B542D31A1E2}"/>
+    <hyperlink ref="D17" r:id="rId100" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{03DBE390-77AC-4FBF-92E5-5F8DCF5FC91E}"/>
+    <hyperlink ref="G17" r:id="rId101" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{1E41047E-561C-4BC0-9633-74181E0DE5CE}"/>
+    <hyperlink ref="E17" r:id="rId102" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{450D8EE6-F7EF-4001-955C-033ACF1B5A07}"/>
+    <hyperlink ref="H17" r:id="rId103" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5AFDAAE9-B537-4E8D-9333-B5DA24533176}"/>
+    <hyperlink ref="C17" r:id="rId104" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{4B789E57-13C9-4141-B49F-769BE170D372}"/>
+    <hyperlink ref="F17" r:id="rId105" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{399ECE78-42DA-4304-BE2B-B560FC73A712}"/>
+    <hyperlink ref="B18" r:id="rId106" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A2ACD8B5-90FD-4AED-9CE3-75BAE12F299D}"/>
+    <hyperlink ref="D18" r:id="rId107" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{647A8500-AA77-4CB4-92F3-FB863127DDA0}"/>
+    <hyperlink ref="G18" r:id="rId108" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{77888FCD-6B2E-44B7-B91A-955247D44A58}"/>
+    <hyperlink ref="E18" r:id="rId109" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{BFCA9D49-2AC9-481D-8CFE-ADDE7748A8C0}"/>
+    <hyperlink ref="H18" r:id="rId110" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{FB647B40-2CDC-4BBA-95B4-AAB9C9E55F99}"/>
+    <hyperlink ref="C18" r:id="rId111" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{919D8C98-8FF9-4003-BF98-AD7997A1228D}"/>
+    <hyperlink ref="F18" r:id="rId112" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{449B6FC6-0658-49B5-A185-A1675AD64AF5}"/>
+    <hyperlink ref="B19" r:id="rId113" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{4C272BB5-6AC5-4FE8-86E5-58EA37D13CCF}"/>
+    <hyperlink ref="D19" r:id="rId114" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{22531DDA-67C2-4765-A819-31C7B67A1DF6}"/>
+    <hyperlink ref="G19" r:id="rId115" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{2497DADD-75D5-42DB-8C72-8CF3CF844851}"/>
+    <hyperlink ref="E19" r:id="rId116" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{5FB9A640-4DFC-4FDD-85DC-09151DB02B4D}"/>
+    <hyperlink ref="H19" r:id="rId117" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{63368EE1-6BEC-4FBF-ADAC-3D326E7CA17E}"/>
+    <hyperlink ref="C19" r:id="rId118" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{47C68A67-D6A8-495A-A548-BF99C850C6FA}"/>
+    <hyperlink ref="F19" r:id="rId119" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{6A216526-E2C6-4869-9FE9-33BC8EF5184B}"/>
+    <hyperlink ref="B20" r:id="rId120" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{92330007-8CAE-4234-BEB0-B9D7AE668D2F}"/>
+    <hyperlink ref="D20" r:id="rId121" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{22F43A73-8E67-4B08-8B08-12D4D6996980}"/>
+    <hyperlink ref="G20" r:id="rId122" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{8B958C38-7577-4676-B8C6-A2625080D51C}"/>
+    <hyperlink ref="E20" r:id="rId123" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{7FA6885E-1FE7-4B70-A250-8208007ADCFB}"/>
+    <hyperlink ref="H20" r:id="rId124" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{38667F45-4794-49AF-B784-0C12F415BB97}"/>
+    <hyperlink ref="C20" r:id="rId125" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{0500A28A-48C0-4540-B0D3-6DACF41DD6DE}"/>
+    <hyperlink ref="F20" r:id="rId126" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{72D89F77-4BE1-426D-8FA1-5C075BEE7A82}"/>
+    <hyperlink ref="B21" r:id="rId127" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{0269B2C6-66C2-4074-875D-2005D866A81D}"/>
+    <hyperlink ref="D21" r:id="rId128" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{EEC11E7A-3EB5-4763-A7AB-44C0EB36EB63}"/>
+    <hyperlink ref="G21" r:id="rId129" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{49CCD3DD-6B84-42FA-BEDC-7460D4C65269}"/>
+    <hyperlink ref="E21" r:id="rId130" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{DE993A93-5F3B-4E4F-9F3D-95F97A000D0A}"/>
+    <hyperlink ref="H21" r:id="rId131" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{675DF57A-EF26-4A4E-86D4-1DCE6D36BAD2}"/>
+    <hyperlink ref="C21" r:id="rId132" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{37A75EE2-50CD-48F0-A387-961F39BCC433}"/>
+    <hyperlink ref="F21" r:id="rId133" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F3A64403-D8CC-4F2A-8523-049C8172DECA}"/>
+    <hyperlink ref="B22" r:id="rId134" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{449F2CBA-8D3C-4109-B3AD-E6149FF12E09}"/>
+    <hyperlink ref="D22" r:id="rId135" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{C653EC58-E1B1-4F3B-85F5-5EE9CFAD1A98}"/>
+    <hyperlink ref="G22" r:id="rId136" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{76CD9903-9A1F-4493-AB25-BA382A5435EA}"/>
+    <hyperlink ref="E22" r:id="rId137" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{0C61C030-9A80-41C8-BD03-CFC9B7CC2C8C}"/>
+    <hyperlink ref="H22" r:id="rId138" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{CE5C244E-9587-4122-A68D-E3BA007220A9}"/>
+    <hyperlink ref="C22" r:id="rId139" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{38910423-F523-4910-B2E5-972694C2F2DE}"/>
+    <hyperlink ref="F22" r:id="rId140" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{44CEA4AB-0D90-402A-860A-F6242462D8B3}"/>
+    <hyperlink ref="B23" r:id="rId141" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{D9E36D0E-12F0-427B-9619-22D5A9E071A2}"/>
+    <hyperlink ref="D23" r:id="rId142" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{3BCF5C34-F4F4-4A5E-9005-FEB824D7DC5D}"/>
+    <hyperlink ref="G23" r:id="rId143" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F1B6C8E3-ED6E-4EA0-BFE2-C5A17E3BEE3A}"/>
+    <hyperlink ref="E23" r:id="rId144" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B486DFF8-8E55-4935-ABB5-A1395E0F0A26}"/>
+    <hyperlink ref="H23" r:id="rId145" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{18578100-7E8C-495E-8E14-401C07B401E4}"/>
+    <hyperlink ref="C23" r:id="rId146" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{FEE12BE8-C3E4-4720-85AE-0E85EC71948D}"/>
+    <hyperlink ref="F23" r:id="rId147" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{B925EDEA-85AD-49A2-8A44-9623F9FA4AEF}"/>
+    <hyperlink ref="B24" r:id="rId148" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{799DA4FD-5509-4CDA-B255-A3054CA6B825}"/>
+    <hyperlink ref="D24" r:id="rId149" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{537AD443-9E12-4DAD-89B6-BCCDCB8B9CD3}"/>
+    <hyperlink ref="G24" r:id="rId150" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{A0A0FC92-9309-42B3-9669-842F0F7B0801}"/>
+    <hyperlink ref="E24" r:id="rId151" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{36E5721F-3591-4B86-9A0D-19945FBE66F3}"/>
+    <hyperlink ref="H24" r:id="rId152" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{31C7F638-061A-479F-BFD2-CD533789494B}"/>
+    <hyperlink ref="C24" r:id="rId153" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{0424C1CC-5AF1-40E4-BA4D-26B515315108}"/>
+    <hyperlink ref="F24" r:id="rId154" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{962432B4-CDA8-488A-AEDE-4FAFEF63D18E}"/>
+    <hyperlink ref="B25" r:id="rId155" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{05D3741C-F215-4356-BD64-129158A3D78A}"/>
+    <hyperlink ref="D25" r:id="rId156" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{C9F7E68D-D895-4A05-B38D-BA06CC79291C}"/>
+    <hyperlink ref="G25" r:id="rId157" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{0FEB5D7A-305C-47F5-A559-FF8F039EB08F}"/>
+    <hyperlink ref="E25" r:id="rId158" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{C3876FAE-A9F6-4ED1-BB95-D7902D3F2DD9}"/>
+    <hyperlink ref="H25" r:id="rId159" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{44C895FA-7F66-4252-8651-46DF026C824B}"/>
+    <hyperlink ref="C25" r:id="rId160" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{2ECB04A3-D900-4727-87E0-D21ECE2FA518}"/>
+    <hyperlink ref="F25" r:id="rId161" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{7D22889B-9F29-4E4A-90D1-D4E4DC28B280}"/>
+    <hyperlink ref="B26" r:id="rId162" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{B694114F-2C7E-46E5-8CD9-D57A4AA6397E}"/>
+    <hyperlink ref="D26" r:id="rId163" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{F3C66B88-FDC7-49B0-8F94-B36460491E4B}"/>
+    <hyperlink ref="G26" r:id="rId164" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{72A297A5-F250-4B2B-A0EB-B232BAE36497}"/>
+    <hyperlink ref="E26" r:id="rId165" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E87E6033-795A-440C-A486-3124B455E7DA}"/>
+    <hyperlink ref="H26" r:id="rId166" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{C688DC34-FE05-40DE-AC1F-A83F8F0AA129}"/>
+    <hyperlink ref="C26" r:id="rId167" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{CE07735F-A421-4F75-804F-E000A46AD850}"/>
+    <hyperlink ref="F26" r:id="rId168" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{090CF1EB-DD13-407B-A285-6CB3A265D350}"/>
+    <hyperlink ref="B27" r:id="rId169" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{324A5E34-4981-47FE-BBEC-1E5C8D03B3DD}"/>
+    <hyperlink ref="D27" r:id="rId170" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{1C55C88F-AE7A-41A0-9539-83DC747C8EBC}"/>
+    <hyperlink ref="G27" r:id="rId171" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F6947834-2771-46B1-8D00-CD01A82ECF68}"/>
+    <hyperlink ref="E27" r:id="rId172" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{9D90988C-F7CA-488A-9BA8-83F12BBA39BA}"/>
+    <hyperlink ref="H27" r:id="rId173" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{7615CC70-7DB9-4F36-A937-ABC79AA278D6}"/>
+    <hyperlink ref="C27" r:id="rId174" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C11492C8-A72D-4649-8832-D77FA35BB1DE}"/>
+    <hyperlink ref="F27" r:id="rId175" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{1D3C3730-1076-44A1-BF8D-D6731EE8B616}"/>
+    <hyperlink ref="B3" r:id="rId176" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{43CA0065-CDF8-4DE1-834B-AB67EFF747AF}"/>
+    <hyperlink ref="D3" r:id="rId177" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{903D6AC1-B35B-4552-8B68-C2B6460A990F}"/>
+    <hyperlink ref="G3" r:id="rId178" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{DE78402D-C3B6-4405-8D3A-30FAA26B26F5}"/>
+    <hyperlink ref="E3" r:id="rId179" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{4231F488-3FDC-4698-A02B-8E9A8AD51487}"/>
+    <hyperlink ref="H3" r:id="rId180" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{D4DB261E-BE13-4220-903B-19CCC0938025}"/>
+    <hyperlink ref="C3" r:id="rId181" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C4E25A95-8FBD-466E-8526-C265BF58C17B}"/>
+    <hyperlink ref="F3" r:id="rId182" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{59913636-87BD-479D-8AC9-D6CC69BD6588}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId183"/>
@@ -15758,7 +15866,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC3F3FC-17EF-4D6A-9290-8FAFFC789915}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.5546875" customWidth="1"/>
@@ -16103,6 +16211,24 @@
       <c r="E19" s="14">
         <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
         <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="14">
+        <v>97</v>
+      </c>
+      <c r="C20" s="14">
+        <v>3</v>
+      </c>
+      <c r="D20" s="14">
+        <v>13</v>
+      </c>
+      <c r="E20" s="14">
+        <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/data/SDET_SQA_DATA.xlsx
+++ b/data/SDET_SQA_DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WHSU\Desktop\Workspace\CycleView\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B79CA17-A71E-46CA-B55B-949EFCBB968D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443002C4-4E3D-47F6-8236-D86F70EE479B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{EB11FF79-EF06-B64E-AA6A-0CFF391A8BD1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB11FF79-EF06-B64E-AA6A-0CFF391A8BD1}"/>
   </bookViews>
   <sheets>
     <sheet name="TestAutomationProgress" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="105">
   <si>
     <t>TODO (P1)</t>
   </si>
@@ -230,9 +230,6 @@
     <t>READY FOR TESTING (90%)</t>
   </si>
   <si>
-    <t>y26w2</t>
-  </si>
-  <si>
     <t>26W01</t>
   </si>
   <si>
@@ -317,12 +314,6 @@
     <t>v1.37</t>
   </si>
   <si>
-    <t>y26w4</t>
-  </si>
-  <si>
-    <t>y26w6</t>
-  </si>
-  <si>
     <t>26W03</t>
   </si>
   <si>
@@ -338,22 +329,34 @@
     <t>v1.39</t>
   </si>
   <si>
-    <t>y26w8</t>
-  </si>
-  <si>
     <t>y26w10</t>
   </si>
   <si>
     <t>None</t>
   </si>
   <si>
-    <t>Candidate</t>
-  </si>
-  <si>
     <t>26W06</t>
   </si>
   <si>
     <t>26W07</t>
+  </si>
+  <si>
+    <t>y26w02</t>
+  </si>
+  <si>
+    <t>y26w04</t>
+  </si>
+  <si>
+    <t>y26w06</t>
+  </si>
+  <si>
+    <t>y26w08</t>
+  </si>
+  <si>
+    <t>26W10</t>
+  </si>
+  <si>
+    <t>26W08</t>
   </si>
 </sst>
 </file>
@@ -542,6 +545,33 @@
   </cellStyles>
   <dxfs count="36">
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -717,33 +747,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1091,9 +1094,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$28</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>25W32</c:v>
                 </c:pt>
@@ -1174,16 +1177,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>26W07</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>26W10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$B$2:$B$28</c:f>
+              <c:f>TestAutomationProgress!$B$2:$B$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -1263,6 +1269,9 @@
                   <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="26">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>31</c:v>
                 </c:pt>
               </c:numCache>
@@ -1360,9 +1369,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$28</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>25W32</c:v>
                 </c:pt>
@@ -1443,16 +1452,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>26W07</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>26W10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$C$2:$C$28</c:f>
+              <c:f>TestAutomationProgress!$C$2:$C$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1532,6 +1544,9 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="26">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
@@ -1629,9 +1644,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$28</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>25W32</c:v>
                 </c:pt>
@@ -1712,16 +1727,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>26W07</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>26W10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$D$2:$D$28</c:f>
+              <c:f>TestAutomationProgress!$D$2:$D$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>115</c:v>
                 </c:pt>
@@ -1801,6 +1819,9 @@
                   <c:v>161</c:v>
                 </c:pt>
                 <c:pt idx="26">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>161</c:v>
                 </c:pt>
               </c:numCache>
@@ -2290,7 +2311,7 @@
                   <c:v>1350</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>614</c:v>
+                  <c:v>860</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2596,7 +2617,7 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2799,7 +2820,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3099,7 +3120,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>196</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3325,7 +3346,7 @@
                   <c:v>1374</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>814</c:v>
+                  <c:v>866</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3699,9 +3720,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$32</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$34</c:f>
               <c:strCache>
-                <c:ptCount val="31"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -3794,16 +3815,22 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>26W07</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>26W08</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>26W10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$B$2:$B$32</c:f>
+              <c:f>'SOVA-TestResult'!$B$2:$B$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>38</c:v>
                 </c:pt>
@@ -3872,6 +3899,12 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>723</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>687</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>218</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3965,9 +3998,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$32</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$34</c:f>
               <c:strCache>
-                <c:ptCount val="31"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4060,16 +4093,22 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>26W07</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>26W08</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>26W10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$C$2:$C$32</c:f>
+              <c:f>'SOVA-TestResult'!$C$2:$C$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4138,6 +4177,12 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4174,9 +4219,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$32</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$34</c:f>
               <c:strCache>
-                <c:ptCount val="31"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4269,16 +4314,22 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>26W07</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>26W08</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>26W10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$D$2:$D$32</c:f>
+              <c:f>'SOVA-TestResult'!$D$2:$D$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4347,6 +4398,12 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4383,9 +4440,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$32</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$34</c:f>
               <c:strCache>
-                <c:ptCount val="31"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4478,16 +4535,22 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>26W07</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>26W08</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>26W10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$E$2:$E$32</c:f>
+              <c:f>'SOVA-TestResult'!$E$2:$E$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
                 </c:pt>
@@ -4556,6 +4619,12 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4666,9 +4735,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$32</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$34</c:f>
               <c:strCache>
-                <c:ptCount val="31"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4761,16 +4830,22 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>26W07</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>26W08</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>26W10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$F$2:$F$32</c:f>
+              <c:f>'SOVA-TestResult'!$F$2:$F$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>11</c:v>
                 </c:pt>
@@ -4839,6 +4914,12 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4878,9 +4959,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$32</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$34</c:f>
               <c:strCache>
-                <c:ptCount val="31"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4973,16 +5054,22 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>26W07</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>26W08</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>26W10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$G$2:$G$32</c:f>
+              <c:f>'SOVA-TestResult'!$G$2:$G$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5050,6 +5137,12 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5092,9 +5185,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$32</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$34</c:f>
               <c:strCache>
-                <c:ptCount val="31"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -5187,16 +5280,22 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>26W07</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>26W08</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>26W10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$H$2:$H$32</c:f>
+              <c:f>'SOVA-TestResult'!$H$2:$H$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>54</c:v>
                 </c:pt>
@@ -5265,6 +5364,12 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>753</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>704</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>218</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5707,64 +5812,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>15</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>26</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>14</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>10</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>11</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5928,7 +6033,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
@@ -6047,13 +6152,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1</c:v>
@@ -6265,13 +6370,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6548,16 +6653,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>61</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>46</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>43</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>33</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>25</c:v>
@@ -6587,10 +6692,10 @@
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>38</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>35</c:v>
@@ -6599,13 +6704,13 @@
                   <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>10</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6717,64 +6822,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>77</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>53</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>63</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>51</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>70</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>50</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>41</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>22</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>13</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>54</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>42</c:v>
                 </c:pt>
-                <c:pt idx="15">
-                  <c:v>43</c:v>
-                </c:pt>
                 <c:pt idx="16">
-                  <c:v>24</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>14</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7147,85 +7252,82 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$27</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$26</c:f>
               <c:strCache>
-                <c:ptCount val="26"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>None</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Candidate</c:v>
+                  <c:v>y25w16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>y25w16</c:v>
+                  <c:v>y25w18</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>y25w18</c:v>
+                  <c:v>y25w20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>y25w20</c:v>
+                  <c:v>y25w22</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>y25w22</c:v>
+                  <c:v>y25w24</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>y25w24</c:v>
+                  <c:v>y25w26</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>y25w26</c:v>
+                  <c:v>y25w28</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>y25w28</c:v>
+                  <c:v>y25w30</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>y25w30</c:v>
+                  <c:v>y25w32</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>y25w32</c:v>
+                  <c:v>y25w34</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>y25w34</c:v>
+                  <c:v>y25w36</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>y25w36</c:v>
+                  <c:v>y25w38</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>y25w38</c:v>
+                  <c:v>y25w40</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>y25w40</c:v>
+                  <c:v>y25w42</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>y25w42</c:v>
+                  <c:v>y25w44</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>y25w44</c:v>
+                  <c:v>y25w46</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>y25w46</c:v>
+                  <c:v>y25w48</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>y25w48</c:v>
+                  <c:v>y25w50</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>y25w50</c:v>
+                  <c:v>y25w52</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>y25w52</c:v>
+                  <c:v>y26w02</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>y26w2</c:v>
+                  <c:v>y26w04</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>y26w4</c:v>
+                  <c:v>y26w06</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>y26w6</c:v>
+                  <c:v>y26w08</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>y26w8</c:v>
-                </c:pt>
-                <c:pt idx="25">
                   <c:v>y26w10</c:v>
                 </c:pt>
               </c:strCache>
@@ -7233,15 +7335,15 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$B$2:$B$27</c:f>
+              <c:f>'SOVA-BugTrend'!$B$2:$B$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>162</c:v>
+                  <c:v>159</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -7259,7 +7361,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>1</c:v>
@@ -7271,13 +7373,13 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0</c:v>
@@ -7289,31 +7391,28 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>7</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>2</c:v>
-                </c:pt>
                 <c:pt idx="23">
-                  <c:v>8</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>5</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7407,85 +7506,82 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$27</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$26</c:f>
               <c:strCache>
-                <c:ptCount val="26"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>None</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Candidate</c:v>
+                  <c:v>y25w16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>y25w16</c:v>
+                  <c:v>y25w18</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>y25w18</c:v>
+                  <c:v>y25w20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>y25w20</c:v>
+                  <c:v>y25w22</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>y25w22</c:v>
+                  <c:v>y25w24</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>y25w24</c:v>
+                  <c:v>y25w26</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>y25w26</c:v>
+                  <c:v>y25w28</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>y25w28</c:v>
+                  <c:v>y25w30</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>y25w30</c:v>
+                  <c:v>y25w32</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>y25w32</c:v>
+                  <c:v>y25w34</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>y25w34</c:v>
+                  <c:v>y25w36</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>y25w36</c:v>
+                  <c:v>y25w38</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>y25w38</c:v>
+                  <c:v>y25w40</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>y25w40</c:v>
+                  <c:v>y25w42</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>y25w42</c:v>
+                  <c:v>y25w44</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>y25w44</c:v>
+                  <c:v>y25w46</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>y25w46</c:v>
+                  <c:v>y25w48</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>y25w48</c:v>
+                  <c:v>y25w50</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>y25w50</c:v>
+                  <c:v>y25w52</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>y25w52</c:v>
+                  <c:v>y26w02</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>y26w2</c:v>
+                  <c:v>y26w04</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>y26w4</c:v>
+                  <c:v>y26w06</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>y26w6</c:v>
+                  <c:v>y26w08</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>y26w8</c:v>
-                </c:pt>
-                <c:pt idx="25">
                   <c:v>y26w10</c:v>
                 </c:pt>
               </c:strCache>
@@ -7493,10 +7589,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$C$2:$C$27</c:f>
+              <c:f>'SOVA-BugTrend'!$C$2:$C$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7571,9 +7667,6 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7667,85 +7760,82 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$27</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$26</c:f>
               <c:strCache>
-                <c:ptCount val="26"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>None</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Candidate</c:v>
+                  <c:v>y25w16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>y25w16</c:v>
+                  <c:v>y25w18</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>y25w18</c:v>
+                  <c:v>y25w20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>y25w20</c:v>
+                  <c:v>y25w22</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>y25w22</c:v>
+                  <c:v>y25w24</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>y25w24</c:v>
+                  <c:v>y25w26</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>y25w26</c:v>
+                  <c:v>y25w28</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>y25w28</c:v>
+                  <c:v>y25w30</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>y25w30</c:v>
+                  <c:v>y25w32</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>y25w32</c:v>
+                  <c:v>y25w34</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>y25w34</c:v>
+                  <c:v>y25w36</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>y25w36</c:v>
+                  <c:v>y25w38</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>y25w38</c:v>
+                  <c:v>y25w40</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>y25w40</c:v>
+                  <c:v>y25w42</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>y25w42</c:v>
+                  <c:v>y25w44</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>y25w44</c:v>
+                  <c:v>y25w46</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>y25w46</c:v>
+                  <c:v>y25w48</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>y25w48</c:v>
+                  <c:v>y25w50</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>y25w50</c:v>
+                  <c:v>y25w52</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>y25w52</c:v>
+                  <c:v>y26w02</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>y26w2</c:v>
+                  <c:v>y26w04</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>y26w4</c:v>
+                  <c:v>y26w06</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>y26w6</c:v>
+                  <c:v>y26w08</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>y26w8</c:v>
-                </c:pt>
-                <c:pt idx="25">
                   <c:v>y26w10</c:v>
                 </c:pt>
               </c:strCache>
@@ -7753,10 +7843,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$D$2:$D$27</c:f>
+              <c:f>'SOVA-BugTrend'!$D$2:$D$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -7827,12 +7917,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -7927,85 +8014,82 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$27</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$26</c:f>
               <c:strCache>
-                <c:ptCount val="26"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>None</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Candidate</c:v>
+                  <c:v>y25w16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>y25w16</c:v>
+                  <c:v>y25w18</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>y25w18</c:v>
+                  <c:v>y25w20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>y25w20</c:v>
+                  <c:v>y25w22</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>y25w22</c:v>
+                  <c:v>y25w24</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>y25w24</c:v>
+                  <c:v>y25w26</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>y25w26</c:v>
+                  <c:v>y25w28</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>y25w28</c:v>
+                  <c:v>y25w30</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>y25w30</c:v>
+                  <c:v>y25w32</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>y25w32</c:v>
+                  <c:v>y25w34</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>y25w34</c:v>
+                  <c:v>y25w36</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>y25w36</c:v>
+                  <c:v>y25w38</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>y25w38</c:v>
+                  <c:v>y25w40</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>y25w40</c:v>
+                  <c:v>y25w42</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>y25w42</c:v>
+                  <c:v>y25w44</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>y25w44</c:v>
+                  <c:v>y25w46</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>y25w46</c:v>
+                  <c:v>y25w48</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>y25w48</c:v>
+                  <c:v>y25w50</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>y25w50</c:v>
+                  <c:v>y25w52</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>y25w52</c:v>
+                  <c:v>y26w02</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>y26w2</c:v>
+                  <c:v>y26w04</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>y26w4</c:v>
+                  <c:v>y26w06</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>y26w6</c:v>
+                  <c:v>y26w08</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>y26w8</c:v>
-                </c:pt>
-                <c:pt idx="25">
                   <c:v>y26w10</c:v>
                 </c:pt>
               </c:strCache>
@@ -8013,10 +8097,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$E$2:$E$27</c:f>
+              <c:f>'SOVA-BugTrend'!$E$2:$E$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
                 </c:pt>
@@ -8084,16 +8168,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8130,85 +8211,82 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$27</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$26</c:f>
               <c:strCache>
-                <c:ptCount val="26"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>None</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Candidate</c:v>
+                  <c:v>y25w16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>y25w16</c:v>
+                  <c:v>y25w18</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>y25w18</c:v>
+                  <c:v>y25w20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>y25w20</c:v>
+                  <c:v>y25w22</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>y25w22</c:v>
+                  <c:v>y25w24</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>y25w24</c:v>
+                  <c:v>y25w26</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>y25w26</c:v>
+                  <c:v>y25w28</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>y25w28</c:v>
+                  <c:v>y25w30</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>y25w30</c:v>
+                  <c:v>y25w32</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>y25w32</c:v>
+                  <c:v>y25w34</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>y25w34</c:v>
+                  <c:v>y25w36</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>y25w36</c:v>
+                  <c:v>y25w38</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>y25w38</c:v>
+                  <c:v>y25w40</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>y25w40</c:v>
+                  <c:v>y25w42</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>y25w42</c:v>
+                  <c:v>y25w44</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>y25w44</c:v>
+                  <c:v>y25w46</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>y25w46</c:v>
+                  <c:v>y25w48</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>y25w48</c:v>
+                  <c:v>y25w50</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>y25w50</c:v>
+                  <c:v>y25w52</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>y25w52</c:v>
+                  <c:v>y26w02</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>y26w2</c:v>
+                  <c:v>y26w04</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>y26w4</c:v>
+                  <c:v>y26w06</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>y26w6</c:v>
+                  <c:v>y26w08</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>y26w8</c:v>
-                </c:pt>
-                <c:pt idx="25">
                   <c:v>y26w10</c:v>
                 </c:pt>
               </c:strCache>
@@ -8216,87 +8294,84 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$F$2:$F$27</c:f>
+              <c:f>'SOVA-BugTrend'!$F$2:$F$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8387,85 +8462,82 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$27</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$26</c:f>
               <c:strCache>
-                <c:ptCount val="26"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>None</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Candidate</c:v>
+                  <c:v>y25w16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>y25w16</c:v>
+                  <c:v>y25w18</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>y25w18</c:v>
+                  <c:v>y25w20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>y25w20</c:v>
+                  <c:v>y25w22</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>y25w22</c:v>
+                  <c:v>y25w24</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>y25w24</c:v>
+                  <c:v>y25w26</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>y25w26</c:v>
+                  <c:v>y25w28</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>y25w28</c:v>
+                  <c:v>y25w30</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>y25w30</c:v>
+                  <c:v>y25w32</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>y25w32</c:v>
+                  <c:v>y25w34</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>y25w34</c:v>
+                  <c:v>y25w36</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>y25w36</c:v>
+                  <c:v>y25w38</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>y25w38</c:v>
+                  <c:v>y25w40</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>y25w40</c:v>
+                  <c:v>y25w42</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>y25w42</c:v>
+                  <c:v>y25w44</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>y25w44</c:v>
+                  <c:v>y25w46</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>y25w46</c:v>
+                  <c:v>y25w48</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>y25w48</c:v>
+                  <c:v>y25w50</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>y25w50</c:v>
+                  <c:v>y25w52</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>y25w52</c:v>
+                  <c:v>y26w02</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>y26w2</c:v>
+                  <c:v>y26w04</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>y26w4</c:v>
+                  <c:v>y26w06</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>y26w6</c:v>
+                  <c:v>y26w08</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>y26w8</c:v>
-                </c:pt>
-                <c:pt idx="25">
                   <c:v>y26w10</c:v>
                 </c:pt>
               </c:strCache>
@@ -8473,87 +8545,84 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$G$2:$G$27</c:f>
+              <c:f>'SOVA-BugTrend'!$G$2:$G$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>125</c:v>
+                  <c:v>133</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>16</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>55</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>35</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>39</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>39</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>29</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>31</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>19</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8592,85 +8661,82 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$27</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$26</c:f>
               <c:strCache>
-                <c:ptCount val="26"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>None</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Candidate</c:v>
+                  <c:v>y25w16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>y25w16</c:v>
+                  <c:v>y25w18</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>y25w18</c:v>
+                  <c:v>y25w20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>y25w20</c:v>
+                  <c:v>y25w22</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>y25w22</c:v>
+                  <c:v>y25w24</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>y25w24</c:v>
+                  <c:v>y25w26</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>y25w26</c:v>
+                  <c:v>y25w28</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>y25w28</c:v>
+                  <c:v>y25w30</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>y25w30</c:v>
+                  <c:v>y25w32</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>y25w32</c:v>
+                  <c:v>y25w34</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>y25w34</c:v>
+                  <c:v>y25w36</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>y25w36</c:v>
+                  <c:v>y25w38</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>y25w38</c:v>
+                  <c:v>y25w40</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>y25w40</c:v>
+                  <c:v>y25w42</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>y25w42</c:v>
+                  <c:v>y25w44</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>y25w44</c:v>
+                  <c:v>y25w46</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>y25w46</c:v>
+                  <c:v>y25w48</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>y25w48</c:v>
+                  <c:v>y25w50</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>y25w50</c:v>
+                  <c:v>y25w52</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>y25w52</c:v>
+                  <c:v>y26w02</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>y26w2</c:v>
+                  <c:v>y26w04</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>y26w4</c:v>
+                  <c:v>y26w06</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>y26w6</c:v>
+                  <c:v>y26w08</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>y26w8</c:v>
-                </c:pt>
-                <c:pt idx="25">
                   <c:v>y26w10</c:v>
                 </c:pt>
               </c:strCache>
@@ -8678,18 +8744,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$H$2:$H$27</c:f>
+              <c:f>'SOVA-BugTrend'!$H$2:$H$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>76</c:v>
+                  <c:v>87</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>2</c:v>
@@ -8698,43 +8764,43 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5</c:v>
-                </c:pt>
                 <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>1</c:v>
@@ -8743,22 +8809,19 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>3</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8797,85 +8860,82 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$27</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$26</c:f>
               <c:strCache>
-                <c:ptCount val="26"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>None</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Candidate</c:v>
+                  <c:v>y25w16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>y25w16</c:v>
+                  <c:v>y25w18</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>y25w18</c:v>
+                  <c:v>y25w20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>y25w20</c:v>
+                  <c:v>y25w22</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>y25w22</c:v>
+                  <c:v>y25w24</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>y25w24</c:v>
+                  <c:v>y25w26</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>y25w26</c:v>
+                  <c:v>y25w28</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>y25w28</c:v>
+                  <c:v>y25w30</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>y25w30</c:v>
+                  <c:v>y25w32</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>y25w32</c:v>
+                  <c:v>y25w34</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>y25w34</c:v>
+                  <c:v>y25w36</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>y25w36</c:v>
+                  <c:v>y25w38</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>y25w38</c:v>
+                  <c:v>y25w40</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>y25w40</c:v>
+                  <c:v>y25w42</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>y25w42</c:v>
+                  <c:v>y25w44</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>y25w44</c:v>
+                  <c:v>y25w46</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>y25w46</c:v>
+                  <c:v>y25w48</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>y25w48</c:v>
+                  <c:v>y25w50</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>y25w50</c:v>
+                  <c:v>y25w52</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>y25w52</c:v>
+                  <c:v>y26w02</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>y26w2</c:v>
+                  <c:v>y26w04</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>y26w4</c:v>
+                  <c:v>y26w06</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>y26w6</c:v>
+                  <c:v>y26w08</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>y26w8</c:v>
-                </c:pt>
-                <c:pt idx="25">
                   <c:v>y26w10</c:v>
                 </c:pt>
               </c:strCache>
@@ -8883,87 +8943,84 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$I$2:$I$27</c:f>
+              <c:f>'SOVA-BugTrend'!$I$2:$I$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>369</c:v>
+                  <c:v>386</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>31</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>23</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>22</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>18</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>59</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>39</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>42</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>53</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>32</c:v>
-                </c:pt>
                 <c:pt idx="13">
-                  <c:v>53</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>25</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>43</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>35</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>29</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>44</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>37</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>36</c:v>
-                </c:pt>
                 <c:pt idx="23">
-                  <c:v>36</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>5</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11895,13 +11952,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>171448</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>133348</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -11977,13 +12034,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>69662</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1057275</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>31562</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -12059,13 +12116,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -12095,8 +12152,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}" name="Table2" displayName="Table2" ref="A1:E28" totalsRowShown="0" headerRowDxfId="35">
-  <autoFilter ref="A1:E28" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}" name="Table2" displayName="Table2" ref="A1:E29" totalsRowShown="0" headerRowDxfId="35">
+  <autoFilter ref="A1:E29" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F25F0D34-0297-4771-8BBB-350BCDD85D46}" name="Week"/>
     <tableColumn id="2" xr3:uid="{39CFCD12-3130-47A8-A140-DBF602F1743D}" name="Done"/>
@@ -12130,8 +12187,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}" name="Table3" displayName="Table3" ref="A1:H32" totalsRowShown="0" headerRowDxfId="31">
-  <autoFilter ref="A1:H32" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}" name="Table3" displayName="Table3" ref="A1:H34" totalsRowShown="0" headerRowDxfId="31">
+  <autoFilter ref="A1:H34" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{8103CDF3-74DC-4B31-821D-E20368EA5455}" name="Versions"/>
     <tableColumn id="2" xr3:uid="{6C3B261F-FA51-42D2-821A-F22633569372}" name="Passed"/>
@@ -12168,18 +12225,18 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}" name="Table5" displayName="Table5" ref="A1:I27" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17" totalsRowBorderDxfId="16" dataCellStyle="Hyperlink">
-  <autoFilter ref="A1:I27" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}" name="Table5" displayName="Table5" ref="A1:I26" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17" totalsRowBorderDxfId="16" dataCellStyle="Hyperlink">
+  <autoFilter ref="A1:I26" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{5BE08AE0-E0B5-4B46-9423-456B88C2D9BC}" name="Sprint" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{030F9647-4FC0-4C7E-9B3A-AB099CC59EBA}" name="To Do (0%)" dataDxfId="6" dataCellStyle="Hyperlink"/>
-    <tableColumn id="3" xr3:uid="{7D2923F3-E2CF-4FD9-A7A5-68C36BB95591}" name="STARTING (10 ~ 40%)" dataDxfId="5" dataCellStyle="Hyperlink"/>
-    <tableColumn id="4" xr3:uid="{48FB5317-7F3B-4F74-B244-5A49C7749EBD}" name="In Progress (50 ~ 70%)" dataDxfId="4" dataCellStyle="Hyperlink"/>
-    <tableColumn id="5" xr3:uid="{86F5CCB5-C4C2-4C36-935A-657F085500B1}" name="IN REVIEW (80%)" dataDxfId="3" dataCellStyle="Hyperlink"/>
-    <tableColumn id="9" xr3:uid="{51D22AE3-424C-4604-9869-D672DED4301F}" name="READY FOR TESTING (90%)" dataDxfId="2" dataCellStyle="Hyperlink"/>
-    <tableColumn id="6" xr3:uid="{33C9BCE6-D9EB-4032-9B0A-DDD9A4051A2D}" name="Done (100%)" dataDxfId="1" dataCellStyle="Hyperlink"/>
-    <tableColumn id="8" xr3:uid="{D624FC89-A88E-45AC-9D22-66D66702B8C5}" name="WON'T DO (100%)" dataDxfId="0" dataCellStyle="Hyperlink"/>
-    <tableColumn id="7" xr3:uid="{EFEEB7EC-E2D1-40EA-B265-A558311E5D30}" name="Total" dataDxfId="14" dataCellStyle="Hyperlink">
+    <tableColumn id="2" xr3:uid="{030F9647-4FC0-4C7E-9B3A-AB099CC59EBA}" name="To Do (0%)" dataDxfId="14" dataCellStyle="Hyperlink"/>
+    <tableColumn id="3" xr3:uid="{7D2923F3-E2CF-4FD9-A7A5-68C36BB95591}" name="STARTING (10 ~ 40%)" dataDxfId="13" dataCellStyle="Hyperlink"/>
+    <tableColumn id="4" xr3:uid="{48FB5317-7F3B-4F74-B244-5A49C7749EBD}" name="In Progress (50 ~ 70%)" dataDxfId="12" dataCellStyle="Hyperlink"/>
+    <tableColumn id="5" xr3:uid="{86F5CCB5-C4C2-4C36-935A-657F085500B1}" name="IN REVIEW (80%)" dataDxfId="11" dataCellStyle="Hyperlink"/>
+    <tableColumn id="9" xr3:uid="{51D22AE3-424C-4604-9869-D672DED4301F}" name="READY FOR TESTING (90%)" dataDxfId="10" dataCellStyle="Hyperlink"/>
+    <tableColumn id="6" xr3:uid="{33C9BCE6-D9EB-4032-9B0A-DDD9A4051A2D}" name="Done (100%)" dataDxfId="9" dataCellStyle="Hyperlink"/>
+    <tableColumn id="8" xr3:uid="{D624FC89-A88E-45AC-9D22-66D66702B8C5}" name="WON'T DO (100%)" dataDxfId="8" dataCellStyle="Hyperlink"/>
+    <tableColumn id="7" xr3:uid="{EFEEB7EC-E2D1-40EA-B265-A558311E5D30}" name="Total" dataDxfId="7" dataCellStyle="Hyperlink">
       <calculatedColumnFormula>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12188,14 +12245,14 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}" name="Table25" displayName="Table25" ref="A1:E20" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="A1:E20" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}" name="Table25" displayName="Table25" ref="A1:E21" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E21" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7070D9F2-0ED1-4F39-8D72-28B37C8E98F2}" name="Week" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{1173F443-CC27-4C6E-A432-BF66DB2A740E}" name="Done" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{2EE10CB5-1AF1-4B50-9456-B3A666DD5338}" name="In Review/Progress" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{328D0A00-85F0-4BFF-81FE-C023998A3701}" name="TODO (P1)" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{E385808E-1FCD-451C-9807-DAF18A42B704}" name="Total" dataDxfId="7">
+    <tableColumn id="1" xr3:uid="{7070D9F2-0ED1-4F39-8D72-28B37C8E98F2}" name="Week" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{1173F443-CC27-4C6E-A432-BF66DB2A740E}" name="Done" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{2EE10CB5-1AF1-4B50-9456-B3A666DD5338}" name="In Review/Progress" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{328D0A00-85F0-4BFF-81FE-C023998A3701}" name="TODO (P1)" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{E385808E-1FCD-451C-9807-DAF18A42B704}" name="Total" dataDxfId="0">
       <calculatedColumnFormula>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12520,7 +12577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D733A42-966D-5F4E-B061-B304543CE88E}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.77734375" customWidth="1"/>
@@ -12548,7 +12605,7 @@
     </row>
     <row r="2" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -12566,7 +12623,7 @@
     </row>
     <row r="3" spans="1:5" ht="21.95" customHeight="1">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -12584,7 +12641,7 @@
     </row>
     <row r="4" spans="1:5" ht="21.95" customHeight="1">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -12602,7 +12659,7 @@
     </row>
     <row r="5" spans="1:5" ht="21.95" customHeight="1">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -12620,7 +12677,7 @@
     </row>
     <row r="6" spans="1:5" ht="21.95" customHeight="1">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B6">
         <v>8</v>
@@ -12638,7 +12695,7 @@
     </row>
     <row r="7" spans="1:5" ht="21.95" customHeight="1">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B7">
         <v>10</v>
@@ -12656,7 +12713,7 @@
     </row>
     <row r="8" spans="1:5" ht="21.95" customHeight="1">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B8">
         <v>12</v>
@@ -12674,7 +12731,7 @@
     </row>
     <row r="9" spans="1:5" ht="21.95" customHeight="1">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B9">
         <v>15</v>
@@ -12692,7 +12749,7 @@
     </row>
     <row r="10" spans="1:5" ht="21.95" customHeight="1">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B10">
         <v>15</v>
@@ -12710,7 +12767,7 @@
     </row>
     <row r="11" spans="1:5" ht="21.95" customHeight="1">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11">
         <v>12</v>
@@ -12728,7 +12785,7 @@
     </row>
     <row r="12" spans="1:5" ht="21.95" customHeight="1">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B12">
         <v>13</v>
@@ -12746,7 +12803,7 @@
     </row>
     <row r="13" spans="1:5" ht="21.95" customHeight="1">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B13">
         <v>15</v>
@@ -12764,7 +12821,7 @@
     </row>
     <row r="14" spans="1:5" ht="21.95" customHeight="1">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B14">
         <v>18</v>
@@ -12782,7 +12839,7 @@
     </row>
     <row r="15" spans="1:5" ht="21.95" customHeight="1">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B15">
         <v>21</v>
@@ -12800,7 +12857,7 @@
     </row>
     <row r="16" spans="1:5" ht="21.95" customHeight="1">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B16">
         <v>22</v>
@@ -12818,7 +12875,7 @@
     </row>
     <row r="17" spans="1:5" ht="21.95" customHeight="1">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B17">
         <v>25</v>
@@ -12836,7 +12893,7 @@
     </row>
     <row r="18" spans="1:5" ht="21.95" customHeight="1">
       <c r="A18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18">
         <v>28</v>
@@ -12854,7 +12911,7 @@
     </row>
     <row r="19" spans="1:5" ht="21.95" customHeight="1">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B19">
         <v>30</v>
@@ -12872,7 +12929,7 @@
     </row>
     <row r="20" spans="1:5" ht="21.95" customHeight="1">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B20">
         <v>32</v>
@@ -12890,7 +12947,7 @@
     </row>
     <row r="21" spans="1:5" ht="21.95" customHeight="1">
       <c r="A21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B21">
         <v>32</v>
@@ -12908,7 +12965,7 @@
     </row>
     <row r="22" spans="1:5" ht="21.95" customHeight="1">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B22">
         <v>32</v>
@@ -12926,7 +12983,7 @@
     </row>
     <row r="23" spans="1:5" ht="21.95" customHeight="1">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B23">
         <v>32</v>
@@ -12944,7 +13001,7 @@
     </row>
     <row r="24" spans="1:5" ht="21.95" customHeight="1">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B24">
         <v>32</v>
@@ -12962,7 +13019,7 @@
     </row>
     <row r="25" spans="1:5" ht="21.95" customHeight="1">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B25">
         <v>32</v>
@@ -12980,7 +13037,7 @@
     </row>
     <row r="26" spans="1:5" ht="21.95" customHeight="1">
       <c r="A26" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B26">
         <v>32</v>
@@ -12998,7 +13055,7 @@
     </row>
     <row r="27" spans="1:5" ht="21.95" customHeight="1">
       <c r="A27" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B27">
         <v>31</v>
@@ -13016,7 +13073,7 @@
     </row>
     <row r="28" spans="1:5" ht="21.95" customHeight="1">
       <c r="A28" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B28">
         <v>31</v>
@@ -13028,6 +13085,24 @@
         <v>161</v>
       </c>
       <c r="E28" s="12">
+        <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A29" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29">
+        <v>31</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+      <c r="D29">
+        <v>161</v>
+      </c>
+      <c r="E29" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
         <v>195</v>
       </c>
@@ -13485,7 +13560,7 @@
     </row>
     <row r="17" spans="1:8" ht="21.95" customHeight="1">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B17">
         <v>1350</v>
@@ -13512,29 +13587,29 @@
     </row>
     <row r="18" spans="1:8" ht="21.95" customHeight="1">
       <c r="A18" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B18">
-        <v>614</v>
+        <v>860</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="H18">
         <f>SUM(Table1[[#This Row],[Passed]:[Untested]])</f>
-        <v>814</v>
+        <v>866</v>
       </c>
     </row>
   </sheetData>
@@ -13549,7 +13624,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA6EDF6-834F-DA49-B3FC-BFE1673433AB}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
@@ -13584,7 +13659,7 @@
     </row>
     <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2">
         <v>38</v>
@@ -13611,12 +13686,12 @@
     </row>
     <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B4">
         <v>43</v>
@@ -13643,12 +13718,12 @@
     </row>
     <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B6">
         <v>58</v>
@@ -13675,12 +13750,12 @@
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B8">
         <v>76</v>
@@ -13707,12 +13782,12 @@
     </row>
     <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B10">
         <v>121</v>
@@ -13739,12 +13814,12 @@
     </row>
     <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B12">
         <v>148</v>
@@ -13771,12 +13846,12 @@
     </row>
     <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B14" s="10">
         <v>148</v>
@@ -13803,13 +13878,13 @@
     </row>
     <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H15" s="12"/>
     </row>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B16">
         <v>231</v>
@@ -13836,13 +13911,13 @@
     </row>
     <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H17" s="12"/>
     </row>
     <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B18">
         <v>249</v>
@@ -13869,7 +13944,7 @@
     </row>
     <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B19">
         <v>155</v>
@@ -13896,7 +13971,7 @@
     </row>
     <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B20">
         <v>225</v>
@@ -13923,7 +13998,7 @@
     </row>
     <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B21">
         <v>281</v>
@@ -13950,7 +14025,7 @@
     </row>
     <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B22">
         <v>291</v>
@@ -13977,7 +14052,7 @@
     </row>
     <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B23">
         <v>267</v>
@@ -14004,7 +14079,7 @@
     </row>
     <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B24">
         <v>343</v>
@@ -14031,7 +14106,7 @@
     </row>
     <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B25">
         <v>351</v>
@@ -14058,7 +14133,7 @@
     </row>
     <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B26">
         <v>142</v>
@@ -14085,7 +14160,7 @@
     </row>
     <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B27">
         <v>442</v>
@@ -14112,7 +14187,7 @@
     </row>
     <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B28">
         <v>518</v>
@@ -14139,7 +14214,7 @@
     </row>
     <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B29">
         <v>636</v>
@@ -14166,7 +14241,7 @@
     </row>
     <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B30">
         <v>436</v>
@@ -14193,7 +14268,7 @@
     </row>
     <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B31">
         <v>171</v>
@@ -14220,7 +14295,7 @@
     </row>
     <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B32">
         <v>723</v>
@@ -14243,6 +14318,60 @@
       <c r="H32" s="12">
         <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
         <v>753</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="A33" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33">
+        <v>687</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>3</v>
+      </c>
+      <c r="F33">
+        <v>12</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33" s="12">
+        <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
+        <v>704</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="A34" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34">
+        <v>218</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34" s="12">
+        <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -14300,13 +14429,13 @@
         <v>19</v>
       </c>
       <c r="B2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -14315,11 +14444,11 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H2">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -14327,7 +14456,7 @@
         <v>20</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -14342,11 +14471,11 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H3">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -14354,13 +14483,13 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -14369,11 +14498,11 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H4">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -14381,7 +14510,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -14396,11 +14525,11 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H5">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -14408,7 +14537,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -14427,7 +14556,7 @@
       </c>
       <c r="H6">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -14435,7 +14564,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -14454,7 +14583,7 @@
       </c>
       <c r="H7">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -14462,7 +14591,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -14481,7 +14610,7 @@
       </c>
       <c r="H8">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -14516,7 +14645,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -14535,7 +14664,7 @@
       </c>
       <c r="H10">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -14543,7 +14672,7 @@
         <v>44</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -14562,7 +14691,7 @@
       </c>
       <c r="H11">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -14570,7 +14699,7 @@
         <v>49</v>
       </c>
       <c r="B12">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -14589,7 +14718,7 @@
       </c>
       <c r="H12">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -14597,7 +14726,7 @@
         <v>50</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -14616,7 +14745,7 @@
       </c>
       <c r="H13">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -14624,7 +14753,7 @@
         <v>53</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -14643,7 +14772,7 @@
       </c>
       <c r="H14">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -14651,7 +14780,7 @@
         <v>54</v>
       </c>
       <c r="B15">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -14666,11 +14795,11 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H15">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -14678,7 +14807,7 @@
         <v>56</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -14693,11 +14822,11 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H16">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -14705,7 +14834,7 @@
         <v>59</v>
       </c>
       <c r="B17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -14724,7 +14853,7 @@
       </c>
       <c r="H17">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -14732,7 +14861,7 @@
         <v>60</v>
       </c>
       <c r="B18">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -14751,42 +14880,42 @@
       </c>
       <c r="H18">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H19">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -14795,7 +14924,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -14810,10 +14939,10 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -14822,17 +14951,17 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H21">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -14847,7 +14976,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7487DEB-55FC-DC4E-A4B1-F7171B8F3237}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.21875" customWidth="1"/>
@@ -14891,10 +15020,10 @@
     </row>
     <row r="2" spans="1:9" ht="18" thickBot="1">
       <c r="A2" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B2" s="5">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C2" s="5">
         <v>0</v>
@@ -14906,25 +15035,25 @@
         <v>4</v>
       </c>
       <c r="F2" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="5">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="H2" s="5">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="I2" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>369</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18" thickBot="1">
       <c r="A3" s="4" t="s">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="B3" s="5">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C3" s="5">
         <v>0</v>
@@ -14939,19 +15068,19 @@
         <v>0</v>
       </c>
       <c r="G3" s="5">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H3" s="5">
         <v>3</v>
       </c>
       <c r="I3" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" thickBot="1">
       <c r="A4" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="5">
         <v>0</v>
@@ -14972,16 +15101,16 @@
         <v>20</v>
       </c>
       <c r="H4" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" thickBot="1">
       <c r="A5" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" s="5">
         <v>0</v>
@@ -14999,19 +15128,19 @@
         <v>0</v>
       </c>
       <c r="G5" s="5">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H5" s="5">
         <v>2</v>
       </c>
       <c r="I5" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="18" thickBot="1">
       <c r="A6" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="5">
         <v>0</v>
@@ -15041,7 +15170,7 @@
     </row>
     <row r="7" spans="1:9" ht="18" thickBot="1">
       <c r="A7" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" s="5">
         <v>0</v>
@@ -15059,19 +15188,19 @@
         <v>0</v>
       </c>
       <c r="G7" s="5">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="H7" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I7" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>18</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="18" thickBot="1">
       <c r="A8" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" s="5">
         <v>0</v>
@@ -15089,22 +15218,22 @@
         <v>0</v>
       </c>
       <c r="G8" s="5">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H8" s="5">
         <v>4</v>
       </c>
       <c r="I8" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>59</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="18" thickBot="1">
       <c r="A9" s="4" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="5">
         <v>0</v>
@@ -15119,19 +15248,19 @@
         <v>0</v>
       </c>
       <c r="G9" s="5">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H9" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I9" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="18" thickBot="1">
       <c r="A10" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="5">
         <v>1</v>
@@ -15152,16 +15281,16 @@
         <v>39</v>
       </c>
       <c r="H10" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I10" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="18" thickBot="1">
       <c r="A11" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="5">
         <v>1</v>
@@ -15179,19 +15308,19 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H11" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I11" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="18" thickBot="1">
       <c r="A12" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="5">
         <v>1</v>
@@ -15209,22 +15338,22 @@
         <v>0</v>
       </c>
       <c r="G12" s="5">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H12" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I12" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18" thickBot="1">
       <c r="A13" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C13" s="5">
         <v>0</v>
@@ -15239,19 +15368,19 @@
         <v>0</v>
       </c>
       <c r="G13" s="5">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H13" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I13" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18" thickBot="1">
       <c r="A14" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" s="5">
         <v>3</v>
@@ -15269,22 +15398,22 @@
         <v>0</v>
       </c>
       <c r="G14" s="5">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="H14" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I14" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>32</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="18" thickBot="1">
       <c r="A15" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" s="5">
         <v>0</v>
@@ -15299,19 +15428,19 @@
         <v>0</v>
       </c>
       <c r="G15" s="5">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H15" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I15" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>53</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="18" thickBot="1">
       <c r="A16" s="4" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B16" s="5">
         <v>0</v>
@@ -15329,19 +15458,19 @@
         <v>0</v>
       </c>
       <c r="G16" s="5">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="H16" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="18" thickBot="1">
       <c r="A17" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B17" s="5">
         <v>0</v>
@@ -15359,19 +15488,19 @@
         <v>0</v>
       </c>
       <c r="G17" s="5">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H17" s="5">
         <v>0</v>
       </c>
       <c r="I17" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="18" thickBot="1">
       <c r="A18" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" s="5">
         <v>0</v>
@@ -15389,22 +15518,22 @@
         <v>0</v>
       </c>
       <c r="G18" s="5">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H18" s="5">
         <v>0</v>
       </c>
       <c r="I18" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="18" thickBot="1">
       <c r="A19" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B19" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C19" s="5">
         <v>0</v>
@@ -15419,19 +15548,19 @@
         <v>0</v>
       </c>
       <c r="G19" s="5">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H19" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="18" thickBot="1">
       <c r="A20" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B20" s="5">
         <v>4</v>
@@ -15449,22 +15578,22 @@
         <v>0</v>
       </c>
       <c r="G20" s="5">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H20" s="5">
         <v>1</v>
       </c>
       <c r="I20" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="18" thickBot="1">
       <c r="A21" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B21" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C21" s="5">
         <v>0</v>
@@ -15479,7 +15608,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="5">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H21" s="5">
         <v>1</v>
@@ -15491,10 +15620,10 @@
     </row>
     <row r="22" spans="1:9" ht="18" thickBot="1">
       <c r="A22" s="4" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="B22" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C22" s="5">
         <v>0</v>
@@ -15512,49 +15641,49 @@
         <v>29</v>
       </c>
       <c r="H22" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="18" thickBot="1">
       <c r="A23" s="4" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="B23" s="5">
+        <v>3</v>
+      </c>
+      <c r="C23" s="5">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5">
+        <v>31</v>
+      </c>
+      <c r="H23" s="5">
         <v>2</v>
-      </c>
-      <c r="C23" s="5">
-        <v>0</v>
-      </c>
-      <c r="D23" s="5">
-        <v>0</v>
-      </c>
-      <c r="E23" s="5">
-        <v>0</v>
-      </c>
-      <c r="F23" s="5">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5">
-        <v>29</v>
-      </c>
-      <c r="H23" s="5">
-        <v>0</v>
       </c>
       <c r="I23" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="18" thickBot="1">
       <c r="A24" s="4" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B24" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C24" s="5">
         <v>0</v>
@@ -15563,58 +15692,58 @@
         <v>0</v>
       </c>
       <c r="E24" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="5">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H24" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I24" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="18" thickBot="1">
       <c r="A25" s="4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B25" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C25" s="5">
         <v>1</v>
       </c>
       <c r="D25" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F25" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="5">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H25" s="5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I25" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="18" thickBot="1">
       <c r="A26" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B26" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C26" s="5">
         <v>1</v>
@@ -15626,247 +15755,210 @@
         <v>1</v>
       </c>
       <c r="F26" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H26" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I26" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="18" thickBot="1">
-      <c r="A27" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B27" s="5">
-        <v>5</v>
-      </c>
-      <c r="C27" s="5">
-        <v>0</v>
-      </c>
-      <c r="D27" s="5">
-        <v>0</v>
-      </c>
-      <c r="E27" s="5">
-        <v>0</v>
-      </c>
-      <c r="F27" s="5">
-        <v>0</v>
-      </c>
-      <c r="G27" s="5">
-        <v>0</v>
-      </c>
-      <c r="H27" s="5">
-        <v>0</v>
-      </c>
-      <c r="I27" s="5">
-        <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{BF8CA9E5-2F44-49C5-9583-F43D0A229C79}"/>
-    <hyperlink ref="D2" r:id="rId2" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{CD39E288-4AFE-44C4-A645-D33F825377F5}"/>
-    <hyperlink ref="G2" r:id="rId3" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{511EF0F3-1565-4207-81DE-83F4167B2D90}"/>
-    <hyperlink ref="E2" r:id="rId4" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{64BEB31F-0420-4096-AFF0-832EE7ACBFC7}"/>
-    <hyperlink ref="H2" r:id="rId5" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{4AB59AD4-9369-480C-A2CA-40A6B02A58A3}"/>
-    <hyperlink ref="C2" r:id="rId6" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{163878DD-34F6-42C3-900C-C506AEC3C870}"/>
-    <hyperlink ref="F2" r:id="rId7" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{8D7893F5-BFFF-468E-A141-D3589461842F}"/>
-    <hyperlink ref="B4" r:id="rId8" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{DCA6508D-6739-4E29-9D57-AFA23C32277E}"/>
-    <hyperlink ref="D4" r:id="rId9" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{5D82EBDE-B1AF-42AB-813F-43F2DD00C5BC}"/>
-    <hyperlink ref="G4" r:id="rId10" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{33E8F0EC-4F01-450E-BAA7-EAB194046D08}"/>
-    <hyperlink ref="E4" r:id="rId11" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{5AEE9758-D700-49E4-9B01-C5551E98CA6A}"/>
-    <hyperlink ref="H4" r:id="rId12" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{0363EEDC-31A2-42E8-84CB-754B34501EC9}"/>
-    <hyperlink ref="C4" r:id="rId13" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{0FA7A97F-A3AD-4A6C-BEFE-146F0F61789F}"/>
-    <hyperlink ref="F4" r:id="rId14" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{0878F59A-0484-4327-AB4E-2B7C5CA629A7}"/>
-    <hyperlink ref="B5" r:id="rId15" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{1C4D5FC9-AE17-4590-9174-EB26D30C7268}"/>
-    <hyperlink ref="D5" r:id="rId16" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D3B78AFF-4A34-4C88-B8F7-58248254A05C}"/>
-    <hyperlink ref="G5" r:id="rId17" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{CDC92034-3199-4A14-A924-6ABB6CF8DDE8}"/>
-    <hyperlink ref="E5" r:id="rId18" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E7AF27F5-E180-4F4E-8FCB-2452492DE5D0}"/>
-    <hyperlink ref="H5" r:id="rId19" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{10F4F01B-0D05-4DC7-B42C-B526B633EA2E}"/>
-    <hyperlink ref="C5" r:id="rId20" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{5CAD8FBC-408B-4D6F-B132-3146E2688EB6}"/>
-    <hyperlink ref="F5" r:id="rId21" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A6CF7003-F1CB-4B62-ACEB-CD28852C04DE}"/>
-    <hyperlink ref="B6" r:id="rId22" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{41A0AC65-F21B-425F-A634-DD90E3DF5C5B}"/>
-    <hyperlink ref="D6" r:id="rId23" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{1927087D-A714-4103-BCB1-B1240256748B}"/>
-    <hyperlink ref="G6" r:id="rId24" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{D70F7F81-375A-46B7-9340-A481AD621D16}"/>
-    <hyperlink ref="E6" r:id="rId25" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E84C155C-6F5F-4586-86FF-91500882041F}"/>
-    <hyperlink ref="H6" r:id="rId26" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{50ED0615-C223-4A2C-8A2C-BAD8A64AE8C6}"/>
-    <hyperlink ref="C6" r:id="rId27" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{483B452B-AC9E-492B-BC87-00D8C10E6BD1}"/>
-    <hyperlink ref="F6" r:id="rId28" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{013302C7-827D-427B-878B-E9E0C45B1741}"/>
-    <hyperlink ref="B7" r:id="rId29" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{CCC11889-F26D-41B0-8F70-777F9D22F32A}"/>
-    <hyperlink ref="D7" r:id="rId30" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{ADD121ED-122B-425E-9716-6A910BD0805A}"/>
-    <hyperlink ref="G7" r:id="rId31" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{D3BBA393-4036-44B9-8F1C-1C2CC6BCFCC2}"/>
-    <hyperlink ref="E7" r:id="rId32" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D5548EB4-B02D-4482-A88D-EFA077DDA8FB}"/>
-    <hyperlink ref="H7" r:id="rId33" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{9CF99D08-FBF6-4517-ACDC-82DEBDBDB5DC}"/>
-    <hyperlink ref="C7" r:id="rId34" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{54905639-2036-48CD-9DA1-AC0E425353DE}"/>
-    <hyperlink ref="F7" r:id="rId35" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{2F4F0C9E-7CB3-45C6-8068-A087534D7C7C}"/>
-    <hyperlink ref="B8" r:id="rId36" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{1C570888-DC70-473A-BA6D-627728948921}"/>
-    <hyperlink ref="D8" r:id="rId37" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{EEF9781C-FB9B-421F-9F78-111857DD24DE}"/>
-    <hyperlink ref="G8" r:id="rId38" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{E1690A74-9C37-4E90-ACE4-8BE7C9EBF7EC}"/>
-    <hyperlink ref="E8" r:id="rId39" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F353AE61-4AD3-46B1-AD67-EE36EBEBF894}"/>
-    <hyperlink ref="H8" r:id="rId40" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{05F921BC-FAC3-4E29-8EEF-A46B42160B5C}"/>
-    <hyperlink ref="C8" r:id="rId41" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{4DE48923-BA03-49B0-9E2B-7AF300930E51}"/>
-    <hyperlink ref="F8" r:id="rId42" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{41CCDFC2-90B2-4C3E-896D-CADB7BFF13D2}"/>
-    <hyperlink ref="B9" r:id="rId43" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{2AA004AA-32A0-4AC2-878A-574A202C52AB}"/>
-    <hyperlink ref="D9" r:id="rId44" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2747391A-0739-466F-85DE-107B233D682F}"/>
-    <hyperlink ref="G9" r:id="rId45" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{335F8DF8-BCDF-461D-A9C3-474248AA98BD}"/>
-    <hyperlink ref="E9" r:id="rId46" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{9D9FBEB0-7377-4CB0-8A43-BBF1F0A45660}"/>
-    <hyperlink ref="H9" r:id="rId47" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{132A046C-6042-4955-98C0-E29ACF60266E}"/>
-    <hyperlink ref="C9" r:id="rId48" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{F87F936A-6148-488B-A91C-10CA53CE0F1B}"/>
-    <hyperlink ref="F9" r:id="rId49" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{387BA32B-432A-49A3-BCAC-BE57C43293CC}"/>
-    <hyperlink ref="B10" r:id="rId50" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{7D8890A4-B206-48D5-B06A-A35AC41899E2}"/>
-    <hyperlink ref="D10" r:id="rId51" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2DECEBB2-3486-4E7D-B15B-C0B1D99B22CD}"/>
-    <hyperlink ref="G10" r:id="rId52" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{942AD767-269A-4DF9-802E-21CA062D3A90}"/>
-    <hyperlink ref="E10" r:id="rId53" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B5834AB4-D5E6-4B15-96E0-7C22DA172898}"/>
-    <hyperlink ref="H10" r:id="rId54" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{C7DD3757-049C-488F-BBB4-CC2C5158EB62}"/>
-    <hyperlink ref="C10" r:id="rId55" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{192D0568-12F8-49D6-ADDE-0CDF96EE068D}"/>
-    <hyperlink ref="F10" r:id="rId56" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{490038C6-81F0-4E6F-82FA-7BEC049DC881}"/>
-    <hyperlink ref="B11" r:id="rId57" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{675020C2-C08B-4982-A660-9A50F8D90B67}"/>
-    <hyperlink ref="D11" r:id="rId58" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{67878041-2290-4A42-96A3-948F277A0925}"/>
-    <hyperlink ref="G11" r:id="rId59" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C9FF9018-2F71-451C-AE25-63B0E3ABE2BF}"/>
-    <hyperlink ref="E11" r:id="rId60" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D653A96C-2EE7-4E83-9EC3-07DCE5DCF5C1}"/>
-    <hyperlink ref="H11" r:id="rId61" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{86B73676-F611-4840-8EC6-ACE1F7A506C0}"/>
-    <hyperlink ref="C11" r:id="rId62" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{3810384C-0078-49B5-ABC7-8F2E2F76090C}"/>
-    <hyperlink ref="F11" r:id="rId63" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{53968197-3A55-42A4-B942-96DB8D8D4B42}"/>
-    <hyperlink ref="B12" r:id="rId64" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A92B67E4-F2C6-4FFC-9870-C08A06C4808A}"/>
-    <hyperlink ref="D12" r:id="rId65" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{4029CD5A-B6A5-4BE0-B1DC-19C61288FEE3}"/>
-    <hyperlink ref="G12" r:id="rId66" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{324378B0-3F46-47A0-B27C-B3137B72415B}"/>
-    <hyperlink ref="E12" r:id="rId67" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D5FDA6B8-1D46-4B01-B4E5-EC39E9035850}"/>
-    <hyperlink ref="H12" r:id="rId68" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{4372200D-F98B-488F-AA84-D8837594290E}"/>
-    <hyperlink ref="C12" r:id="rId69" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{1EBCE976-7D1E-4C84-86B6-6AFEDBFC76DD}"/>
-    <hyperlink ref="F12" r:id="rId70" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{3E7C6BEA-A2D4-415A-88AC-A54AAD0F2BD2}"/>
-    <hyperlink ref="B13" r:id="rId71" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{D9B15A27-6974-4F2C-8572-427955E4773B}"/>
-    <hyperlink ref="D13" r:id="rId72" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{785876D4-D317-476C-A524-5BEE03467976}"/>
-    <hyperlink ref="G13" r:id="rId73" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3602973B-CFCA-4F06-AEE6-6C9CB66B5D41}"/>
-    <hyperlink ref="E13" r:id="rId74" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B353D0B7-F376-4860-886A-BAD7C0AC7DBF}"/>
-    <hyperlink ref="H13" r:id="rId75" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{7A31078F-43FB-4908-9F8E-0E95B463CBC9}"/>
-    <hyperlink ref="C13" r:id="rId76" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{47D7338D-D8A1-489A-B8BB-2E01EAC730C5}"/>
-    <hyperlink ref="F13" r:id="rId77" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A77DD6C4-9C7D-4B27-B980-940906659B64}"/>
-    <hyperlink ref="B14" r:id="rId78" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{25A41323-A06A-49CD-9088-FB939FFF37C7}"/>
-    <hyperlink ref="D14" r:id="rId79" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{92A7FA35-800F-4303-A524-DC4931A5707C}"/>
-    <hyperlink ref="G14" r:id="rId80" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{71B1A2C8-8780-448A-92A7-4A80CF20E1E8}"/>
-    <hyperlink ref="E14" r:id="rId81" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E5ADB792-3242-465C-8D85-7A0591BAAD7B}"/>
-    <hyperlink ref="H14" r:id="rId82" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{A0D970F1-F15E-41E5-8557-179053945D6C}"/>
-    <hyperlink ref="C14" r:id="rId83" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{AFBE1924-9C18-49D0-81D7-C0A91E1F4D3A}"/>
-    <hyperlink ref="F14" r:id="rId84" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{52121796-C8A3-4A3D-ACFF-D950A7775719}"/>
-    <hyperlink ref="B15" r:id="rId85" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{8874C70F-FFDA-406D-85FA-1F39BBA1D859}"/>
-    <hyperlink ref="D15" r:id="rId86" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{AF13EDCD-5C38-4099-81E2-D812237DA7D7}"/>
-    <hyperlink ref="G15" r:id="rId87" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{10CEA241-FE66-4A46-944F-CC83B2040106}"/>
-    <hyperlink ref="E15" r:id="rId88" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{C1871489-0F59-44C8-99E4-E5624A6301F1}"/>
-    <hyperlink ref="H15" r:id="rId89" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{00F88501-E21A-4C6B-BEB3-BD9A9E208C14}"/>
-    <hyperlink ref="C15" r:id="rId90" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{45869C56-B0DC-42D2-965B-6DC4A42C17DE}"/>
-    <hyperlink ref="F15" r:id="rId91" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F52B478C-CB8B-42D7-BD75-F664CFF4CC39}"/>
-    <hyperlink ref="B16" r:id="rId92" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{DA85980A-BD58-44C4-84E6-3B8C58EB8220}"/>
-    <hyperlink ref="D16" r:id="rId93" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{CAF754CD-2398-4DDC-9540-551898340959}"/>
-    <hyperlink ref="G16" r:id="rId94" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{13A36FB3-A31E-4CB5-BC0E-8DA3811A3F25}"/>
-    <hyperlink ref="E16" r:id="rId95" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{8456322F-624D-4DCA-B30E-3391F342BDFA}"/>
-    <hyperlink ref="H16" r:id="rId96" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{07E83961-7899-43C9-9A0E-C07077E3841F}"/>
-    <hyperlink ref="C16" r:id="rId97" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{8B3AF250-90F2-4F89-9D4A-E2908A266FC7}"/>
-    <hyperlink ref="F16" r:id="rId98" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{3288F97A-65EB-4E73-BF3E-5F1B0848661A}"/>
-    <hyperlink ref="B17" r:id="rId99" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{D838ABC2-C56E-4013-9E2D-8B542D31A1E2}"/>
-    <hyperlink ref="D17" r:id="rId100" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{03DBE390-77AC-4FBF-92E5-5F8DCF5FC91E}"/>
-    <hyperlink ref="G17" r:id="rId101" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{1E41047E-561C-4BC0-9633-74181E0DE5CE}"/>
-    <hyperlink ref="E17" r:id="rId102" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{450D8EE6-F7EF-4001-955C-033ACF1B5A07}"/>
-    <hyperlink ref="H17" r:id="rId103" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5AFDAAE9-B537-4E8D-9333-B5DA24533176}"/>
-    <hyperlink ref="C17" r:id="rId104" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{4B789E57-13C9-4141-B49F-769BE170D372}"/>
-    <hyperlink ref="F17" r:id="rId105" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{399ECE78-42DA-4304-BE2B-B560FC73A712}"/>
-    <hyperlink ref="B18" r:id="rId106" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A2ACD8B5-90FD-4AED-9CE3-75BAE12F299D}"/>
-    <hyperlink ref="D18" r:id="rId107" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{647A8500-AA77-4CB4-92F3-FB863127DDA0}"/>
-    <hyperlink ref="G18" r:id="rId108" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{77888FCD-6B2E-44B7-B91A-955247D44A58}"/>
-    <hyperlink ref="E18" r:id="rId109" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{BFCA9D49-2AC9-481D-8CFE-ADDE7748A8C0}"/>
-    <hyperlink ref="H18" r:id="rId110" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{FB647B40-2CDC-4BBA-95B4-AAB9C9E55F99}"/>
-    <hyperlink ref="C18" r:id="rId111" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{919D8C98-8FF9-4003-BF98-AD7997A1228D}"/>
-    <hyperlink ref="F18" r:id="rId112" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{449B6FC6-0658-49B5-A185-A1675AD64AF5}"/>
-    <hyperlink ref="B19" r:id="rId113" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{4C272BB5-6AC5-4FE8-86E5-58EA37D13CCF}"/>
-    <hyperlink ref="D19" r:id="rId114" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{22531DDA-67C2-4765-A819-31C7B67A1DF6}"/>
-    <hyperlink ref="G19" r:id="rId115" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{2497DADD-75D5-42DB-8C72-8CF3CF844851}"/>
-    <hyperlink ref="E19" r:id="rId116" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{5FB9A640-4DFC-4FDD-85DC-09151DB02B4D}"/>
-    <hyperlink ref="H19" r:id="rId117" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{63368EE1-6BEC-4FBF-ADAC-3D326E7CA17E}"/>
-    <hyperlink ref="C19" r:id="rId118" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{47C68A67-D6A8-495A-A548-BF99C850C6FA}"/>
-    <hyperlink ref="F19" r:id="rId119" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{6A216526-E2C6-4869-9FE9-33BC8EF5184B}"/>
-    <hyperlink ref="B20" r:id="rId120" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{92330007-8CAE-4234-BEB0-B9D7AE668D2F}"/>
-    <hyperlink ref="D20" r:id="rId121" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{22F43A73-8E67-4B08-8B08-12D4D6996980}"/>
-    <hyperlink ref="G20" r:id="rId122" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{8B958C38-7577-4676-B8C6-A2625080D51C}"/>
-    <hyperlink ref="E20" r:id="rId123" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{7FA6885E-1FE7-4B70-A250-8208007ADCFB}"/>
-    <hyperlink ref="H20" r:id="rId124" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{38667F45-4794-49AF-B784-0C12F415BB97}"/>
-    <hyperlink ref="C20" r:id="rId125" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{0500A28A-48C0-4540-B0D3-6DACF41DD6DE}"/>
-    <hyperlink ref="F20" r:id="rId126" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{72D89F77-4BE1-426D-8FA1-5C075BEE7A82}"/>
-    <hyperlink ref="B21" r:id="rId127" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{0269B2C6-66C2-4074-875D-2005D866A81D}"/>
-    <hyperlink ref="D21" r:id="rId128" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{EEC11E7A-3EB5-4763-A7AB-44C0EB36EB63}"/>
-    <hyperlink ref="G21" r:id="rId129" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{49CCD3DD-6B84-42FA-BEDC-7460D4C65269}"/>
-    <hyperlink ref="E21" r:id="rId130" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{DE993A93-5F3B-4E4F-9F3D-95F97A000D0A}"/>
-    <hyperlink ref="H21" r:id="rId131" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{675DF57A-EF26-4A4E-86D4-1DCE6D36BAD2}"/>
-    <hyperlink ref="C21" r:id="rId132" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{37A75EE2-50CD-48F0-A387-961F39BCC433}"/>
-    <hyperlink ref="F21" r:id="rId133" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F3A64403-D8CC-4F2A-8523-049C8172DECA}"/>
-    <hyperlink ref="B22" r:id="rId134" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{449F2CBA-8D3C-4109-B3AD-E6149FF12E09}"/>
-    <hyperlink ref="D22" r:id="rId135" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{C653EC58-E1B1-4F3B-85F5-5EE9CFAD1A98}"/>
-    <hyperlink ref="G22" r:id="rId136" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{76CD9903-9A1F-4493-AB25-BA382A5435EA}"/>
-    <hyperlink ref="E22" r:id="rId137" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{0C61C030-9A80-41C8-BD03-CFC9B7CC2C8C}"/>
-    <hyperlink ref="H22" r:id="rId138" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{CE5C244E-9587-4122-A68D-E3BA007220A9}"/>
-    <hyperlink ref="C22" r:id="rId139" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{38910423-F523-4910-B2E5-972694C2F2DE}"/>
-    <hyperlink ref="F22" r:id="rId140" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{44CEA4AB-0D90-402A-860A-F6242462D8B3}"/>
-    <hyperlink ref="B23" r:id="rId141" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{D9E36D0E-12F0-427B-9619-22D5A9E071A2}"/>
-    <hyperlink ref="D23" r:id="rId142" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{3BCF5C34-F4F4-4A5E-9005-FEB824D7DC5D}"/>
-    <hyperlink ref="G23" r:id="rId143" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F1B6C8E3-ED6E-4EA0-BFE2-C5A17E3BEE3A}"/>
-    <hyperlink ref="E23" r:id="rId144" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B486DFF8-8E55-4935-ABB5-A1395E0F0A26}"/>
-    <hyperlink ref="H23" r:id="rId145" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{18578100-7E8C-495E-8E14-401C07B401E4}"/>
-    <hyperlink ref="C23" r:id="rId146" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{FEE12BE8-C3E4-4720-85AE-0E85EC71948D}"/>
-    <hyperlink ref="F23" r:id="rId147" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{B925EDEA-85AD-49A2-8A44-9623F9FA4AEF}"/>
-    <hyperlink ref="B24" r:id="rId148" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{799DA4FD-5509-4CDA-B255-A3054CA6B825}"/>
-    <hyperlink ref="D24" r:id="rId149" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{537AD443-9E12-4DAD-89B6-BCCDCB8B9CD3}"/>
-    <hyperlink ref="G24" r:id="rId150" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{A0A0FC92-9309-42B3-9669-842F0F7B0801}"/>
-    <hyperlink ref="E24" r:id="rId151" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{36E5721F-3591-4B86-9A0D-19945FBE66F3}"/>
-    <hyperlink ref="H24" r:id="rId152" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{31C7F638-061A-479F-BFD2-CD533789494B}"/>
-    <hyperlink ref="C24" r:id="rId153" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{0424C1CC-5AF1-40E4-BA4D-26B515315108}"/>
-    <hyperlink ref="F24" r:id="rId154" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{962432B4-CDA8-488A-AEDE-4FAFEF63D18E}"/>
-    <hyperlink ref="B25" r:id="rId155" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{05D3741C-F215-4356-BD64-129158A3D78A}"/>
-    <hyperlink ref="D25" r:id="rId156" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{C9F7E68D-D895-4A05-B38D-BA06CC79291C}"/>
-    <hyperlink ref="G25" r:id="rId157" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{0FEB5D7A-305C-47F5-A559-FF8F039EB08F}"/>
-    <hyperlink ref="E25" r:id="rId158" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{C3876FAE-A9F6-4ED1-BB95-D7902D3F2DD9}"/>
-    <hyperlink ref="H25" r:id="rId159" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{44C895FA-7F66-4252-8651-46DF026C824B}"/>
-    <hyperlink ref="C25" r:id="rId160" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{2ECB04A3-D900-4727-87E0-D21ECE2FA518}"/>
-    <hyperlink ref="F25" r:id="rId161" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{7D22889B-9F29-4E4A-90D1-D4E4DC28B280}"/>
-    <hyperlink ref="B26" r:id="rId162" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{B694114F-2C7E-46E5-8CD9-D57A4AA6397E}"/>
-    <hyperlink ref="D26" r:id="rId163" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{F3C66B88-FDC7-49B0-8F94-B36460491E4B}"/>
-    <hyperlink ref="G26" r:id="rId164" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{72A297A5-F250-4B2B-A0EB-B232BAE36497}"/>
-    <hyperlink ref="E26" r:id="rId165" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E87E6033-795A-440C-A486-3124B455E7DA}"/>
-    <hyperlink ref="H26" r:id="rId166" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{C688DC34-FE05-40DE-AC1F-A83F8F0AA129}"/>
-    <hyperlink ref="C26" r:id="rId167" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{CE07735F-A421-4F75-804F-E000A46AD850}"/>
-    <hyperlink ref="F26" r:id="rId168" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{090CF1EB-DD13-407B-A285-6CB3A265D350}"/>
-    <hyperlink ref="B27" r:id="rId169" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{324A5E34-4981-47FE-BBEC-1E5C8D03B3DD}"/>
-    <hyperlink ref="D27" r:id="rId170" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{1C55C88F-AE7A-41A0-9539-83DC747C8EBC}"/>
-    <hyperlink ref="G27" r:id="rId171" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F6947834-2771-46B1-8D00-CD01A82ECF68}"/>
-    <hyperlink ref="E27" r:id="rId172" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{9D90988C-F7CA-488A-9BA8-83F12BBA39BA}"/>
-    <hyperlink ref="H27" r:id="rId173" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{7615CC70-7DB9-4F36-A937-ABC79AA278D6}"/>
-    <hyperlink ref="C27" r:id="rId174" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C11492C8-A72D-4649-8832-D77FA35BB1DE}"/>
-    <hyperlink ref="F27" r:id="rId175" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{1D3C3730-1076-44A1-BF8D-D6731EE8B616}"/>
-    <hyperlink ref="B3" r:id="rId176" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{43CA0065-CDF8-4DE1-834B-AB67EFF747AF}"/>
-    <hyperlink ref="D3" r:id="rId177" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{903D6AC1-B35B-4552-8B68-C2B6460A990F}"/>
-    <hyperlink ref="G3" r:id="rId178" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{DE78402D-C3B6-4405-8D3A-30FAA26B26F5}"/>
-    <hyperlink ref="E3" r:id="rId179" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{4231F488-3FDC-4698-A02B-8E9A8AD51487}"/>
-    <hyperlink ref="H3" r:id="rId180" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{D4DB261E-BE13-4220-903B-19CCC0938025}"/>
-    <hyperlink ref="C3" r:id="rId181" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C4E25A95-8FBD-466E-8526-C265BF58C17B}"/>
-    <hyperlink ref="F3" r:id="rId182" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{59913636-87BD-479D-8AC9-D6CC69BD6588}"/>
+    <hyperlink ref="B2" r:id="rId1" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{34711E63-32B5-48FD-8B87-BEB3251F5ECB}"/>
+    <hyperlink ref="D2" r:id="rId2" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{5674E088-BF22-4593-9270-A955F7DBDDD8}"/>
+    <hyperlink ref="G2" r:id="rId3" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{946611E4-F7B6-4C8B-BFBF-C9A3A68DFF5A}"/>
+    <hyperlink ref="E2" r:id="rId4" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{1D63C089-7DE7-4D56-8253-2A85B7E2E854}"/>
+    <hyperlink ref="H2" r:id="rId5" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{0E7325D6-CB9E-4D72-9B94-5429EE488EC3}"/>
+    <hyperlink ref="C2" r:id="rId6" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{8E7C3923-D6A5-45DC-86A3-B70A796E7172}"/>
+    <hyperlink ref="F2" r:id="rId7" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E1D22E9D-62E0-4318-B85E-41B7C5EEBB89}"/>
+    <hyperlink ref="B3" r:id="rId8" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{298EC8DE-589F-4F6D-8374-E7E118C66383}"/>
+    <hyperlink ref="D3" r:id="rId9" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{EF0354A6-72A6-45A7-B9F8-C095AC39946B}"/>
+    <hyperlink ref="G3" r:id="rId10" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{212459D5-B280-45F5-8DAD-E89D3CBF23C9}"/>
+    <hyperlink ref="E3" r:id="rId11" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A10FAEB7-3205-4698-8782-EE8129B37667}"/>
+    <hyperlink ref="H3" r:id="rId12" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{181B9932-AAC4-4563-B268-48C1500B1AF8}"/>
+    <hyperlink ref="C3" r:id="rId13" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6696278C-FD0D-4603-8FEA-DBEE8C87B3B4}"/>
+    <hyperlink ref="F3" r:id="rId14" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{740A6C31-7558-45C9-9DE7-8BC30E3D5F26}"/>
+    <hyperlink ref="B4" r:id="rId15" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{9C03AC9C-16B8-4B8A-9651-90705CB213B4}"/>
+    <hyperlink ref="D4" r:id="rId16" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{6BBDD3AA-BB57-485E-A5FD-2639E2C24A10}"/>
+    <hyperlink ref="G4" r:id="rId17" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{183CF4AA-84FD-4085-9088-676BFDF91E59}"/>
+    <hyperlink ref="E4" r:id="rId18" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{3236CB73-D96E-4774-844A-5927A496D147}"/>
+    <hyperlink ref="H4" r:id="rId19" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{DE797A1D-0843-4525-8117-637B96A06273}"/>
+    <hyperlink ref="C4" r:id="rId20" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{1914DCE3-4AC4-4E0D-850B-E229625C5C2D}"/>
+    <hyperlink ref="F4" r:id="rId21" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A1F186FB-867A-4E97-898C-533544E46C67}"/>
+    <hyperlink ref="B5" r:id="rId22" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{5AECE1B0-9E7D-453B-85D5-7AEC02AE052E}"/>
+    <hyperlink ref="D5" r:id="rId23" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{F866C0B4-C94C-454A-8EAC-04159EED840E}"/>
+    <hyperlink ref="G5" r:id="rId24" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3D8E72F0-DBFB-45C7-BE6F-5AE8BF63EB85}"/>
+    <hyperlink ref="E5" r:id="rId25" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{67BDD5FC-D605-4D13-B5E0-DDB525A50B85}"/>
+    <hyperlink ref="H5" r:id="rId26" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{689B3102-A949-48F8-B962-D1EB8E490A31}"/>
+    <hyperlink ref="C5" r:id="rId27" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{7DB02657-C57E-4DD1-B3FD-899E275FA401}"/>
+    <hyperlink ref="F5" r:id="rId28" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{B5DE74B7-4DCD-46A1-BE7C-BC2AC1D24A43}"/>
+    <hyperlink ref="B6" r:id="rId29" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A06EE209-20C0-43A4-863C-2B0F47EBE350}"/>
+    <hyperlink ref="D6" r:id="rId30" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{346BE594-0974-422D-B03E-72A2932512A0}"/>
+    <hyperlink ref="G6" r:id="rId31" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{7019FB0E-4499-4545-A26C-C626D19E6960}"/>
+    <hyperlink ref="E6" r:id="rId32" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A08EFD40-FE00-471F-9A90-1BA4F3848AF6}"/>
+    <hyperlink ref="H6" r:id="rId33" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{8DF30AF4-FC29-41FA-8DA4-1D5F4FE84D4C}"/>
+    <hyperlink ref="C6" r:id="rId34" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{25DFCB2A-0943-465B-8235-AAADDE1A6669}"/>
+    <hyperlink ref="F6" r:id="rId35" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{9A9866E6-AD9F-4F98-9552-CC66720CFDE8}"/>
+    <hyperlink ref="B7" r:id="rId36" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{6F0972CB-E226-4A6F-83B5-37762AE69CF7}"/>
+    <hyperlink ref="D7" r:id="rId37" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{69B8E6D5-CEB5-4FA7-BA00-5496F14B886F}"/>
+    <hyperlink ref="G7" r:id="rId38" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{874BAEDE-927A-4CA9-9802-C9461EF59317}"/>
+    <hyperlink ref="E7" r:id="rId39" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{C8595C1F-2ADB-4C12-A24E-61A5D9DDF351}"/>
+    <hyperlink ref="H7" r:id="rId40" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{3A607FCB-A3B3-4D06-9113-0A22A06C0B06}"/>
+    <hyperlink ref="C7" r:id="rId41" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{BD3864C1-1EC0-4C52-A267-EC043EBE1076}"/>
+    <hyperlink ref="F7" r:id="rId42" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E6606B96-F372-4853-8917-452561334A7E}"/>
+    <hyperlink ref="B8" r:id="rId43" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{E00C6465-7849-4D4F-B025-D9988DF0B6C7}"/>
+    <hyperlink ref="D8" r:id="rId44" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D753198A-6878-4194-918C-83F3142C0BC4}"/>
+    <hyperlink ref="G8" r:id="rId45" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{91635E97-EFBC-46AA-898D-12D96EF3E9C4}"/>
+    <hyperlink ref="E8" r:id="rId46" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B57207CE-0532-46FE-AFF3-59472BB48E38}"/>
+    <hyperlink ref="H8" r:id="rId47" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{CC9E57EE-D725-4EFA-AD69-131745C57C22}"/>
+    <hyperlink ref="C8" r:id="rId48" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{D4555482-963D-4318-BD61-22868EEC92D5}"/>
+    <hyperlink ref="F8" r:id="rId49" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{BDDC02C8-9F9C-4176-8BC1-421B87555DBC}"/>
+    <hyperlink ref="B9" r:id="rId50" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{B5556016-A043-45E4-BE00-2D1E9BB34F62}"/>
+    <hyperlink ref="D9" r:id="rId51" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{B65D8CFA-196F-479A-B5CF-0255B3A99F74}"/>
+    <hyperlink ref="G9" r:id="rId52" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{97326DE9-214D-4C25-92C1-3EB254CEB50C}"/>
+    <hyperlink ref="E9" r:id="rId53" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A516D73E-0518-425D-9551-A74659057C3F}"/>
+    <hyperlink ref="H9" r:id="rId54" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{51083CC8-8DAF-49B0-B429-0100A57F4FF0}"/>
+    <hyperlink ref="C9" r:id="rId55" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{93435779-D924-4EFB-A63A-F58DDF8F5CFE}"/>
+    <hyperlink ref="F9" r:id="rId56" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{25FC70B2-AC9E-4F52-97AE-777A8284F32D}"/>
+    <hyperlink ref="B10" r:id="rId57" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A34A62D3-D214-40FA-B5D2-026DFE734B32}"/>
+    <hyperlink ref="D10" r:id="rId58" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{B31C976D-4E80-443F-97FE-3C5061D8A319}"/>
+    <hyperlink ref="G10" r:id="rId59" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{7DFDD6E4-A179-4F1E-B661-4E961BCE0BC9}"/>
+    <hyperlink ref="E10" r:id="rId60" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F9DD4FF7-0210-4BB7-A496-64FA7A59BED6}"/>
+    <hyperlink ref="H10" r:id="rId61" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{815BD11A-FCA7-44E6-93C3-86BC524E64C4}"/>
+    <hyperlink ref="C10" r:id="rId62" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{60D496FF-F38F-4EF0-A715-834EC9A9F272}"/>
+    <hyperlink ref="F10" r:id="rId63" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A6DDE5D1-FC3F-400A-A8EA-2B12CC2C4021}"/>
+    <hyperlink ref="B11" r:id="rId64" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{199A8C9C-770B-4208-95A1-D72A67C3318D}"/>
+    <hyperlink ref="D11" r:id="rId65" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2E025D2C-BA76-4192-88DB-31AAD35EF35E}"/>
+    <hyperlink ref="G11" r:id="rId66" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{938608BA-4C20-4023-8DD1-6A443C09039F}"/>
+    <hyperlink ref="E11" r:id="rId67" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A128E572-3614-458E-B8E6-2DB60541092B}"/>
+    <hyperlink ref="H11" r:id="rId68" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{4F43AFA6-C202-4058-AB87-80992762E531}"/>
+    <hyperlink ref="C11" r:id="rId69" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{50DC1068-0618-45EA-B8E3-9DC4BCAE1125}"/>
+    <hyperlink ref="F11" r:id="rId70" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{3F64E4A5-2E50-4F27-99B1-B6AAEC698DAE}"/>
+    <hyperlink ref="B12" r:id="rId71" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{9D35E47D-60D4-44FD-B5A1-27B9D574DB80}"/>
+    <hyperlink ref="D12" r:id="rId72" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2202E8AC-919A-4D43-9C9B-A3AE27D336DB}"/>
+    <hyperlink ref="G12" r:id="rId73" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{E46B5EB1-D9C0-40D6-BE3B-71ACC25A34A5}"/>
+    <hyperlink ref="E12" r:id="rId74" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F5761500-861A-49C4-94FA-4A8B13972158}"/>
+    <hyperlink ref="H12" r:id="rId75" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{6828453F-6DC0-403E-9BDA-AEFBFC7C9DF1}"/>
+    <hyperlink ref="C12" r:id="rId76" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{DFB0592B-C374-4EEC-AC75-F64422D6FC49}"/>
+    <hyperlink ref="F12" r:id="rId77" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{70840C12-8AA1-4F9D-A218-A12C35ABC0D7}"/>
+    <hyperlink ref="B13" r:id="rId78" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{9ED91F79-573B-475E-8917-110837553A80}"/>
+    <hyperlink ref="D13" r:id="rId79" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{73304496-191D-48CC-B514-4172B5501041}"/>
+    <hyperlink ref="G13" r:id="rId80" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{1D79DE91-5AED-4AB1-9C8E-4EB5B035332C}"/>
+    <hyperlink ref="E13" r:id="rId81" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{713AE0CF-967C-4C5F-B83C-E7BFE746E3C1}"/>
+    <hyperlink ref="H13" r:id="rId82" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{403B8CE2-CE2A-41A3-8486-52EB60189D41}"/>
+    <hyperlink ref="C13" r:id="rId83" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{ADC7883D-30BA-47A7-B5B1-A3D535385280}"/>
+    <hyperlink ref="F13" r:id="rId84" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E8F71867-D51A-4E87-A796-42A0F50BA50C}"/>
+    <hyperlink ref="B14" r:id="rId85" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{AE6A39EE-BB08-456B-8885-683CFD8F657E}"/>
+    <hyperlink ref="D14" r:id="rId86" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{6FE8C678-12B3-4F58-9DAC-A0C8D09AB5DB}"/>
+    <hyperlink ref="G14" r:id="rId87" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F79E2A39-DEB6-4A0F-9D7F-9556F29D2DC5}"/>
+    <hyperlink ref="E14" r:id="rId88" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{3B0DE269-B331-4961-A2E5-0B6EB7AC9BFB}"/>
+    <hyperlink ref="H14" r:id="rId89" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{195E7B08-7177-41DB-844C-DBFF92C839CB}"/>
+    <hyperlink ref="C14" r:id="rId90" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{998268BD-9801-4A90-BBB1-509874361D31}"/>
+    <hyperlink ref="F14" r:id="rId91" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{5C78A058-63FC-4F63-9804-694D8F4F2CCB}"/>
+    <hyperlink ref="B15" r:id="rId92" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{FB412802-04D4-443B-AE88-75A5151B8EC6}"/>
+    <hyperlink ref="D15" r:id="rId93" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{DA4B7A3B-C50E-456D-9822-3A6ECF54DFCD}"/>
+    <hyperlink ref="G15" r:id="rId94" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{7FF1A9FD-1AD9-4064-9510-E4734AD64E02}"/>
+    <hyperlink ref="E15" r:id="rId95" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D5CD931C-360B-44F0-BA9C-4FE80C738D57}"/>
+    <hyperlink ref="H15" r:id="rId96" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{0F212D97-7DC6-4E5C-A807-3FA0A6E70322}"/>
+    <hyperlink ref="C15" r:id="rId97" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{8F676768-2EFB-49BC-8E01-27ADA3A491D6}"/>
+    <hyperlink ref="F15" r:id="rId98" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E6B041A7-9A18-4D6C-986F-3B9E0A695E43}"/>
+    <hyperlink ref="B16" r:id="rId99" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{FFF5CD49-0E62-4F84-A2FF-661B874A68F9}"/>
+    <hyperlink ref="D16" r:id="rId100" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{F39A0A11-DBDB-4B6F-A7A3-48EF9BA96CBE}"/>
+    <hyperlink ref="G16" r:id="rId101" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{796D5959-7D06-461C-A72C-56198C3D54DE}"/>
+    <hyperlink ref="E16" r:id="rId102" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{1E834388-067A-4180-B15E-140C218A9ADA}"/>
+    <hyperlink ref="H16" r:id="rId103" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{70D172EB-9750-42E6-9DF8-4D6C68399C31}"/>
+    <hyperlink ref="C16" r:id="rId104" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{DE7DF6C9-B278-455E-B205-054A335514FD}"/>
+    <hyperlink ref="F16" r:id="rId105" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{13EF21C1-BD7E-40AF-AAB6-E5ADB4588238}"/>
+    <hyperlink ref="B17" r:id="rId106" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{3FED6B4C-8EC3-4642-B6E2-CD96CE9E4DCD}"/>
+    <hyperlink ref="D17" r:id="rId107" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{30590572-C973-4C5E-9E59-27D2FF5E326A}"/>
+    <hyperlink ref="G17" r:id="rId108" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{7EA58C71-117A-4453-8FA6-AF23F8D21076}"/>
+    <hyperlink ref="E17" r:id="rId109" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D4C3804E-87BA-437C-B0BA-CAC7DDECBB0F}"/>
+    <hyperlink ref="H17" r:id="rId110" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5C00BBE8-B296-4C40-BD21-33234B738E15}"/>
+    <hyperlink ref="C17" r:id="rId111" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{35534DCC-85EF-46F2-9ACE-FF12B5465F52}"/>
+    <hyperlink ref="F17" r:id="rId112" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{427C7346-8644-4E58-B6B1-51B9C707011C}"/>
+    <hyperlink ref="B18" r:id="rId113" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{E06A75EF-8B5C-4345-9754-FE742F57754D}"/>
+    <hyperlink ref="D18" r:id="rId114" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{25574AAD-FAB4-42F9-AC16-3CD4461261DD}"/>
+    <hyperlink ref="G18" r:id="rId115" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{E1D8BAF3-E148-4FA2-B4D6-7B0512D7501C}"/>
+    <hyperlink ref="E18" r:id="rId116" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{76109AD7-08D0-4CD3-9A8A-5DF6821BE6F0}"/>
+    <hyperlink ref="H18" r:id="rId117" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{ADB7F3D0-4D4D-44BC-AE06-10E02AAE2C39}"/>
+    <hyperlink ref="C18" r:id="rId118" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{354C7527-3F1C-4866-8553-5E751C0C03F4}"/>
+    <hyperlink ref="F18" r:id="rId119" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{AE2A0438-83BE-4C01-911B-01A8605CD1B8}"/>
+    <hyperlink ref="B19" r:id="rId120" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{EA4CD4BC-0FCD-4BEC-87A5-5FDE2C7ADF7A}"/>
+    <hyperlink ref="D19" r:id="rId121" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{BD13236D-C1AC-487A-9857-7E7D985E0BC1}"/>
+    <hyperlink ref="G19" r:id="rId122" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{1CEB5D4A-C23F-4ABA-B9E7-7794C0B2A850}"/>
+    <hyperlink ref="E19" r:id="rId123" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{5EDE8EE5-0466-4619-9723-75F63F401521}"/>
+    <hyperlink ref="H19" r:id="rId124" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{07DBCF5D-015E-46EA-8E86-4CF71174CAE0}"/>
+    <hyperlink ref="C19" r:id="rId125" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{595BA7D6-991E-4E92-AD81-777A3E94066F}"/>
+    <hyperlink ref="F19" r:id="rId126" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{7E58557E-58DC-4A51-BC61-5EB6ABF89445}"/>
+    <hyperlink ref="B20" r:id="rId127" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{E7758CC1-2302-42C0-A59A-82FCC98C4135}"/>
+    <hyperlink ref="D20" r:id="rId128" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{E2D5C100-A2CD-4406-87C5-F73C0D26E9AF}"/>
+    <hyperlink ref="G20" r:id="rId129" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{87724920-F512-4B87-ADF8-5136ADBF9AC2}"/>
+    <hyperlink ref="E20" r:id="rId130" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{85FDDE50-B43E-4D8F-8885-51291FD2161C}"/>
+    <hyperlink ref="H20" r:id="rId131" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{22EFFFF0-F722-4943-A355-5719E8B7EA71}"/>
+    <hyperlink ref="C20" r:id="rId132" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{B8CEDA44-00F1-4712-BC87-7A75F076566D}"/>
+    <hyperlink ref="F20" r:id="rId133" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F2379AE1-8AB0-444A-960A-FE38A60C1AAE}"/>
+    <hyperlink ref="B21" r:id="rId134" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{64A48762-6F4C-4202-825F-5579B90FFCB0}"/>
+    <hyperlink ref="D21" r:id="rId135" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{3B2635F7-EA61-4E3E-8D9C-E9FBA36CFC79}"/>
+    <hyperlink ref="G21" r:id="rId136" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{56BB524B-8F3E-4C9D-981C-F32438E24434}"/>
+    <hyperlink ref="E21" r:id="rId137" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{1F894FCD-A7F8-4469-B8E9-615F22A7D31E}"/>
+    <hyperlink ref="H21" r:id="rId138" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{1D1584F7-6078-4CD9-9F86-7791D3835BF1}"/>
+    <hyperlink ref="C21" r:id="rId139" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{9DFE7914-E974-4747-82BC-FBCC9BD0C4CA}"/>
+    <hyperlink ref="F21" r:id="rId140" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{02DE7248-7DF8-4577-8B9E-A7D6373E0B07}"/>
+    <hyperlink ref="B22" r:id="rId141" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{8A8D667A-F9D6-4A37-998E-975E6D25F77D}"/>
+    <hyperlink ref="D22" r:id="rId142" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2D937BDF-E066-49C2-A0B0-073704665DD3}"/>
+    <hyperlink ref="G22" r:id="rId143" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{827D8597-CBA5-486D-B6E1-5A7A66952C04}"/>
+    <hyperlink ref="E22" r:id="rId144" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{7879F788-3AD6-42C9-889C-E74ED20CA31B}"/>
+    <hyperlink ref="H22" r:id="rId145" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{B79C8A81-57C1-458D-BE53-B4013C47A146}"/>
+    <hyperlink ref="C22" r:id="rId146" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{8A957121-B252-4954-BF66-81CE72E246F0}"/>
+    <hyperlink ref="F22" r:id="rId147" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{58425FE8-279F-48CA-AC8B-D2303DE1D169}"/>
+    <hyperlink ref="B23" r:id="rId148" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{AF811438-4606-412A-874A-33577732A50C}"/>
+    <hyperlink ref="D23" r:id="rId149" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{19416631-1D54-46EB-B1BA-1837234F9118}"/>
+    <hyperlink ref="G23" r:id="rId150" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{514A55A6-FF80-4FE4-85D2-A594187EB644}"/>
+    <hyperlink ref="E23" r:id="rId151" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{0C63EE7E-652C-4376-9267-DF68D2910736}"/>
+    <hyperlink ref="H23" r:id="rId152" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E53EABE4-348F-4FB5-A7BF-B7989447A861}"/>
+    <hyperlink ref="C23" r:id="rId153" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{CAA078DE-41FF-48A8-AA59-EAE4845F675C}"/>
+    <hyperlink ref="F23" r:id="rId154" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{390EF12F-3120-4C7F-BAEC-6C3042E6908B}"/>
+    <hyperlink ref="B24" r:id="rId155" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{D5E804B8-F9E0-43F1-AA2C-B4AF983AB7B8}"/>
+    <hyperlink ref="D24" r:id="rId156" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{DF7C432D-CDE3-481A-9040-D9163C7FDFB3}"/>
+    <hyperlink ref="G24" r:id="rId157" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{48EFB8B6-C61B-4A44-87DE-B9D9610683DE}"/>
+    <hyperlink ref="E24" r:id="rId158" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{021887A6-5E6E-43E8-BABD-ABA89E529EA9}"/>
+    <hyperlink ref="H24" r:id="rId159" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{6E9997D5-B3CC-4878-A029-4209F0E009E7}"/>
+    <hyperlink ref="C24" r:id="rId160" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6C57EC10-FD67-472B-A19C-4DDBDB41516F}"/>
+    <hyperlink ref="F24" r:id="rId161" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{DEEA38A8-FFFE-4FC1-B5B6-401D72C6627F}"/>
+    <hyperlink ref="B25" r:id="rId162" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{D4229FC5-0302-45FF-BF83-221C23A98DBE}"/>
+    <hyperlink ref="D25" r:id="rId163" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{3606DFBA-9F86-4283-83A5-08514FE3D10E}"/>
+    <hyperlink ref="G25" r:id="rId164" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3E6B0CB4-13C2-427C-B956-79F0D6E0222D}"/>
+    <hyperlink ref="E25" r:id="rId165" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D242DDED-3633-4DC6-B8FB-87111D783601}"/>
+    <hyperlink ref="H25" r:id="rId166" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{009D20BC-F4D8-4741-B828-C342D30DBF20}"/>
+    <hyperlink ref="C25" r:id="rId167" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{39159DD6-E0ED-43EA-9926-D694C668CCF8}"/>
+    <hyperlink ref="F25" r:id="rId168" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{D904B1A2-0DFB-4C1A-8B25-B807623148B3}"/>
+    <hyperlink ref="B26" r:id="rId169" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{0AD5C7BF-79E8-4654-BCA5-8CE2ADBC3509}"/>
+    <hyperlink ref="D26" r:id="rId170" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{5CBF48B0-3027-44C1-AD8A-1446D2717275}"/>
+    <hyperlink ref="G26" r:id="rId171" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{7E2B8146-DEC2-4A54-A4E6-B290CBEA301E}"/>
+    <hyperlink ref="E26" r:id="rId172" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{99F40436-34F3-4F03-8198-8C7FB95F7A33}"/>
+    <hyperlink ref="H26" r:id="rId173" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{EE55B56C-DEB2-47B9-8B61-6CD6FDD4265C}"/>
+    <hyperlink ref="C26" r:id="rId174" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{BF18E1E3-E99C-4A32-AD66-218405983DC6}"/>
+    <hyperlink ref="F26" r:id="rId175" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{669BE368-A6CC-4D42-AB08-DA9B51AC0180}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId183"/>
-  <drawing r:id="rId184"/>
+  <pageSetup orientation="portrait" r:id="rId176"/>
+  <drawing r:id="rId177"/>
   <tableParts count="1">
-    <tablePart r:id="rId185"/>
+    <tablePart r:id="rId178"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC3F3FC-17EF-4D6A-9290-8FAFFC789915}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.5546875" customWidth="1"/>
@@ -15892,7 +15984,7 @@
     </row>
     <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B2" s="13">
         <v>0</v>
@@ -15910,7 +16002,7 @@
     </row>
     <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B3" s="14">
         <v>0</v>
@@ -15928,7 +16020,7 @@
     </row>
     <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B4" s="14">
         <v>0</v>
@@ -15946,7 +16038,7 @@
     </row>
     <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B5" s="14">
         <v>0</v>
@@ -15964,7 +16056,7 @@
     </row>
     <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B6" s="14">
         <v>5</v>
@@ -15982,7 +16074,7 @@
     </row>
     <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B7" s="14">
         <v>5</v>
@@ -16000,7 +16092,7 @@
     </row>
     <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" s="14">
         <v>5</v>
@@ -16018,7 +16110,7 @@
     </row>
     <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B9" s="14">
         <v>6</v>
@@ -16036,7 +16128,7 @@
     </row>
     <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B10" s="14">
         <v>6</v>
@@ -16054,7 +16146,7 @@
     </row>
     <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B11" s="14">
         <v>12</v>
@@ -16071,7 +16163,7 @@
     </row>
     <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B12" s="14">
         <v>22</v>
@@ -16089,7 +16181,7 @@
     </row>
     <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B13" s="14">
         <v>27</v>
@@ -16107,7 +16199,7 @@
     </row>
     <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B14" s="14">
         <v>27</v>
@@ -16125,7 +16217,7 @@
     </row>
     <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" s="14">
         <v>44</v>
@@ -16143,7 +16235,7 @@
     </row>
     <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B16" s="14">
         <v>57</v>
@@ -16161,7 +16253,7 @@
     </row>
     <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B17" s="14">
         <v>68</v>
@@ -16179,7 +16271,7 @@
     </row>
     <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B18" s="14">
         <v>80</v>
@@ -16197,7 +16289,7 @@
     </row>
     <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B19" s="14">
         <v>92</v>
@@ -16215,7 +16307,7 @@
     </row>
     <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B20" s="14">
         <v>97</v>
@@ -16227,6 +16319,24 @@
         <v>13</v>
       </c>
       <c r="E20" s="14">
+        <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="14">
+        <v>98</v>
+      </c>
+      <c r="C21" s="14">
+        <v>1</v>
+      </c>
+      <c r="D21" s="14">
+        <v>14</v>
+      </c>
+      <c r="E21" s="14">
         <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
         <v>113</v>
       </c>

--- a/data/SDET_SQA_DATA.xlsx
+++ b/data/SDET_SQA_DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WHSU\Desktop\Workspace\CycleView\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443002C4-4E3D-47F6-8236-D86F70EE479B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DF7603-9865-4C6A-82AB-E701A58DD6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB11FF79-EF06-B64E-AA6A-0CFF391A8BD1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{EB11FF79-EF06-B64E-AA6A-0CFF391A8BD1}"/>
   </bookViews>
   <sheets>
     <sheet name="TestAutomationProgress" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="101">
   <si>
     <t>TODO (P1)</t>
   </si>
@@ -128,9 +128,6 @@
     <t>STARTING (10 ~ 40%)</t>
   </si>
   <si>
-    <t>y25w28</t>
-  </si>
-  <si>
     <t>y25w30</t>
   </si>
   <si>
@@ -150,24 +147,6 @@
   </si>
   <si>
     <t>y25w40</t>
-  </si>
-  <si>
-    <t>y25w16</t>
-  </si>
-  <si>
-    <t>y25w18</t>
-  </si>
-  <si>
-    <t>y25w20</t>
-  </si>
-  <si>
-    <t>y25w22</t>
-  </si>
-  <si>
-    <t>y25w24</t>
-  </si>
-  <si>
-    <t>y25w26</t>
   </si>
   <si>
     <t>In Progress</t>
@@ -332,31 +311,40 @@
     <t>y26w10</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>26W06</t>
   </si>
   <si>
     <t>26W07</t>
   </si>
   <si>
-    <t>y26w02</t>
-  </si>
-  <si>
-    <t>y26w04</t>
-  </si>
-  <si>
-    <t>y26w06</t>
-  </si>
-  <si>
-    <t>y26w08</t>
-  </si>
-  <si>
     <t>26W10</t>
   </si>
   <si>
     <t>26W08</t>
+  </si>
+  <si>
+    <t>v1.40</t>
+  </si>
+  <si>
+    <t>y26w2</t>
+  </si>
+  <si>
+    <t>y26w4</t>
+  </si>
+  <si>
+    <t>y26w6</t>
+  </si>
+  <si>
+    <t>y26w8</t>
+  </si>
+  <si>
+    <t>y26w12</t>
+  </si>
+  <si>
+    <t>Candidate</t>
+  </si>
+  <si>
+    <t>26W11</t>
   </si>
 </sst>
 </file>
@@ -1094,185 +1082,143 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$29</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="28"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>25W32</c:v>
+                  <c:v>25W40</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>25W33</c:v>
+                  <c:v>25W41</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25W34</c:v>
+                  <c:v>25W42</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>25W35</c:v>
+                  <c:v>25W43</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>25W36</c:v>
+                  <c:v>25W44</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>25W37</c:v>
+                  <c:v>25W45</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>25W38</c:v>
+                  <c:v>25W46</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>25W39</c:v>
+                  <c:v>25W47</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>25W40</c:v>
+                  <c:v>25W49</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>25W41</c:v>
+                  <c:v>25W50</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>25W42</c:v>
+                  <c:v>25W51</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>25W43</c:v>
+                  <c:v>25W52</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>25W44</c:v>
+                  <c:v>26W01</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>25W45</c:v>
+                  <c:v>26W02</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>25W46</c:v>
+                  <c:v>26W03</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>25W47</c:v>
+                  <c:v>26W04</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>25W49</c:v>
+                  <c:v>26W05</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>25W50</c:v>
+                  <c:v>26W06</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>25W51</c:v>
+                  <c:v>26W07</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>25W52</c:v>
+                  <c:v>26W10</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>26W01</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>26W02</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>26W03</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>26W04</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>26W05</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26W06</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>26W07</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>26W10</c:v>
+                  <c:v>26W11</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$B$2:$B$29</c:f>
+              <c:f>TestAutomationProgress!$B$2:$B$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>10</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>12</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>15</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>15</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>12</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>13</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>15</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>18</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>21</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>22</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>25</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>28</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>30</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>32</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>32</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>31</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1369,185 +1315,143 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$29</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="28"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>25W32</c:v>
+                  <c:v>25W40</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>25W33</c:v>
+                  <c:v>25W41</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25W34</c:v>
+                  <c:v>25W42</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>25W35</c:v>
+                  <c:v>25W43</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>25W36</c:v>
+                  <c:v>25W44</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>25W37</c:v>
+                  <c:v>25W45</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>25W38</c:v>
+                  <c:v>25W46</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>25W39</c:v>
+                  <c:v>25W47</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>25W40</c:v>
+                  <c:v>25W49</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>25W41</c:v>
+                  <c:v>25W50</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>25W42</c:v>
+                  <c:v>25W51</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>25W43</c:v>
+                  <c:v>25W52</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>25W44</c:v>
+                  <c:v>26W01</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>25W45</c:v>
+                  <c:v>26W02</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>25W46</c:v>
+                  <c:v>26W03</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>25W47</c:v>
+                  <c:v>26W04</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>25W49</c:v>
+                  <c:v>26W05</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>25W50</c:v>
+                  <c:v>26W06</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>25W51</c:v>
+                  <c:v>26W07</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>25W52</c:v>
+                  <c:v>26W10</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>26W01</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>26W02</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>26W03</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>26W04</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>26W05</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26W06</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>26W07</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>26W10</c:v>
+                  <c:v>26W11</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$C$2:$C$29</c:f>
+              <c:f>TestAutomationProgress!$C$2:$C$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="16">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1644,185 +1548,143 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$29</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="28"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>25W32</c:v>
+                  <c:v>25W40</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>25W33</c:v>
+                  <c:v>25W41</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25W34</c:v>
+                  <c:v>25W42</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>25W35</c:v>
+                  <c:v>25W43</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>25W36</c:v>
+                  <c:v>25W44</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>25W37</c:v>
+                  <c:v>25W45</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>25W38</c:v>
+                  <c:v>25W46</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>25W39</c:v>
+                  <c:v>25W47</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>25W40</c:v>
+                  <c:v>25W49</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>25W41</c:v>
+                  <c:v>25W50</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>25W42</c:v>
+                  <c:v>25W51</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>25W43</c:v>
+                  <c:v>25W52</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>25W44</c:v>
+                  <c:v>26W01</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>25W45</c:v>
+                  <c:v>26W02</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>25W46</c:v>
+                  <c:v>26W03</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>25W47</c:v>
+                  <c:v>26W04</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>25W49</c:v>
+                  <c:v>26W05</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>25W50</c:v>
+                  <c:v>26W06</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>25W51</c:v>
+                  <c:v>26W07</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>25W52</c:v>
+                  <c:v>26W10</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>26W01</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>26W02</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>26W03</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>26W04</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>26W05</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26W06</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>26W07</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>26W10</c:v>
+                  <c:v>26W11</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$D$2:$D$29</c:f>
+              <c:f>TestAutomationProgress!$D$2:$D$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>115</c:v>
+                  <c:v>219</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>114</c:v>
+                  <c:v>173</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>109</c:v>
+                  <c:v>172</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>108</c:v>
+                  <c:v>168</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>104</c:v>
+                  <c:v>166</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>228</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>224</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>220</c:v>
+                  <c:v>161</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>219</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>173</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>172</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>168</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>166</c:v>
+                  <c:v>162</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>160</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>160</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>161</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>160</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>160</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>160</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>160</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>162</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>162</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>162</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>162</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>161</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>161</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>161</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>161</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2199,9 +2061,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$18</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$19</c:f>
               <c:strCache>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2252,16 +2114,19 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>v1.39</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>v1.40</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$B$2:$B$18</c:f>
+              <c:f>'Humi-TestResult'!$B$2:$B$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>421</c:v>
                 </c:pt>
@@ -2312,6 +2177,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>860</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>186</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2348,9 +2216,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$18</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$19</c:f>
               <c:strCache>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2401,16 +2269,19 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>v1.39</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>v1.40</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$C$2:$C$18</c:f>
+              <c:f>'Humi-TestResult'!$C$2:$C$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2460,6 +2331,9 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2505,9 +2379,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$18</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$19</c:f>
               <c:strCache>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2558,16 +2432,19 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>v1.39</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>v1.40</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$D$2:$D$18</c:f>
+              <c:f>'Humi-TestResult'!$D$2:$D$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>12</c:v>
                 </c:pt>
@@ -2618,6 +2495,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2708,9 +2588,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$18</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$19</c:f>
               <c:strCache>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2761,16 +2641,19 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>v1.39</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>v1.40</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$E$2:$E$18</c:f>
+              <c:f>'Humi-TestResult'!$E$2:$E$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -2821,6 +2704,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>13</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2857,9 +2743,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$18</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$19</c:f>
               <c:strCache>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2910,16 +2796,19 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>v1.39</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>v1.40</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$F$2:$F$18</c:f>
+              <c:f>'Humi-TestResult'!$F$2:$F$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -2970,6 +2859,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>23</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3008,9 +2900,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$18</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$19</c:f>
               <c:strCache>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -3061,16 +2953,19 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>v1.39</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>v1.40</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$G$2:$G$18</c:f>
+              <c:f>'Humi-TestResult'!$G$2:$G$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3121,6 +3016,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3234,9 +3132,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$18</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$19</c:f>
               <c:strCache>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -3287,16 +3185,19 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>v1.39</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>v1.40</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$H$2:$H$18</c:f>
+              <c:f>'Humi-TestResult'!$H$2:$H$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>442</c:v>
                 </c:pt>
@@ -3347,6 +3248,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>866</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>597</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3720,9 +3624,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$34</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -3821,16 +3725,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>26W10</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>26W11</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$B$2:$B$34</c:f>
+              <c:f>'SOVA-TestResult'!$B$2:$B$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>38</c:v>
                 </c:pt>
@@ -3905,6 +3812,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>218</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>694</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3998,9 +3908,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$34</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4099,16 +4009,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>26W10</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>26W11</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$C$2:$C$34</c:f>
+              <c:f>'SOVA-TestResult'!$C$2:$C$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4182,6 +4095,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4219,9 +4135,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$34</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4320,16 +4236,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>26W10</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>26W11</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$D$2:$D$34</c:f>
+              <c:f>'SOVA-TestResult'!$D$2:$D$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4404,6 +4323,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4440,9 +4362,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$34</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4541,16 +4463,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>26W10</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>26W11</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$E$2:$E$34</c:f>
+              <c:f>'SOVA-TestResult'!$E$2:$E$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
                 </c:pt>
@@ -4624,6 +4549,9 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4735,9 +4663,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$34</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4836,16 +4764,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>26W10</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>26W11</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$F$2:$F$34</c:f>
+              <c:f>'SOVA-TestResult'!$F$2:$F$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>11</c:v>
                 </c:pt>
@@ -4920,6 +4851,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4959,9 +4893,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$34</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -5060,16 +4994,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>26W10</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>26W11</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$G$2:$G$34</c:f>
+              <c:f>'SOVA-TestResult'!$G$2:$G$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5143,6 +5080,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5185,9 +5125,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$34</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -5286,16 +5226,19 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>26W10</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>26W11</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$H$2:$H$34</c:f>
+              <c:f>'SOVA-TestResult'!$H$2:$H$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>54</c:v>
                 </c:pt>
@@ -5370,6 +5313,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>218</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>703</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5739,9 +5685,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$21</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -5801,16 +5747,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>v1.39</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>v1.40</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$B$2:$B$21</c:f>
+              <c:f>'Humi-BugTrend'!$B$2:$B$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>9</c:v>
                 </c:pt>
@@ -5870,6 +5819,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5909,9 +5861,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$21</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -5971,16 +5923,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>v1.39</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>v1.40</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$C$2:$C$21</c:f>
+              <c:f>'Humi-BugTrend'!$C$2:$C$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6040,6 +5995,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6079,9 +6037,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$21</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -6141,16 +6099,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>v1.39</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>v1.40</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$D$2:$D$21</c:f>
+              <c:f>'Humi-BugTrend'!$D$2:$D$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6209,6 +6170,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -6246,9 +6210,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$21</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -6308,16 +6272,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>v1.39</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>v1.40</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$E$2:$E$21</c:f>
+              <c:f>'Humi-BugTrend'!$E$2:$E$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6376,7 +6343,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6413,9 +6383,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$21</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -6475,16 +6445,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>v1.39</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>v1.40</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$F$2:$F$21</c:f>
+              <c:f>'Humi-BugTrend'!$F$2:$F$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6543,6 +6516,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -6580,9 +6556,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$21</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -6642,16 +6618,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>v1.39</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>v1.40</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$G$2:$G$21</c:f>
+              <c:f>'Humi-BugTrend'!$G$2:$G$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>66</c:v>
                 </c:pt>
@@ -6710,7 +6689,10 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6749,9 +6731,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$21</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -6811,16 +6793,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>v1.39</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>v1.40</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$H$2:$H$21</c:f>
+              <c:f>'Humi-BugTrend'!$H$2:$H$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>75</c:v>
                 </c:pt>
@@ -6880,6 +6865,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>27</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7252,167 +7240,131 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$26</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="25"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>None</c:v>
+                  <c:v>Candidate</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>y25w16</c:v>
+                  <c:v>y25w30</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>y25w18</c:v>
+                  <c:v>y25w32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>y25w20</c:v>
+                  <c:v>y25w34</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>y25w22</c:v>
+                  <c:v>y25w36</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>y25w24</c:v>
+                  <c:v>y25w38</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>y25w26</c:v>
+                  <c:v>y25w40</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>y25w28</c:v>
+                  <c:v>y25w42</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>y25w30</c:v>
+                  <c:v>y25w44</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>y25w32</c:v>
+                  <c:v>y25w46</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>y25w34</c:v>
+                  <c:v>y25w48</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>y25w36</c:v>
+                  <c:v>y25w50</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>y25w38</c:v>
+                  <c:v>y25w52</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>y25w40</c:v>
+                  <c:v>y26w2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>y25w42</c:v>
+                  <c:v>y26w4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>y25w44</c:v>
+                  <c:v>y26w6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>y25w46</c:v>
+                  <c:v>y26w8</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>y25w48</c:v>
+                  <c:v>y26w10</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>y25w50</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>y25w52</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>y26w02</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>y26w04</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>y26w06</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>y26w08</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>y26w10</c:v>
+                  <c:v>y26w12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$B$2:$B$26</c:f>
+              <c:f>'SOVA-BugTrend'!$B$2:$B$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>159</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="22">
                   <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7506,93 +7458,75 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$26</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="25"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>None</c:v>
+                  <c:v>Candidate</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>y25w16</c:v>
+                  <c:v>y25w30</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>y25w18</c:v>
+                  <c:v>y25w32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>y25w20</c:v>
+                  <c:v>y25w34</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>y25w22</c:v>
+                  <c:v>y25w36</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>y25w24</c:v>
+                  <c:v>y25w38</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>y25w26</c:v>
+                  <c:v>y25w40</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>y25w28</c:v>
+                  <c:v>y25w42</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>y25w30</c:v>
+                  <c:v>y25w44</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>y25w32</c:v>
+                  <c:v>y25w46</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>y25w34</c:v>
+                  <c:v>y25w48</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>y25w36</c:v>
+                  <c:v>y25w50</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>y25w38</c:v>
+                  <c:v>y25w52</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>y25w40</c:v>
+                  <c:v>y26w2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>y25w42</c:v>
+                  <c:v>y26w4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>y25w44</c:v>
+                  <c:v>y26w6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>y25w46</c:v>
+                  <c:v>y26w8</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>y25w48</c:v>
+                  <c:v>y26w10</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>y25w50</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>y25w52</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>y26w02</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>y26w04</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>y26w06</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>y26w08</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>y26w10</c:v>
+                  <c:v>y26w12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$C$2:$C$26</c:f>
+              <c:f>'SOVA-BugTrend'!$C$2:$C$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7642,31 +7576,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7760,95 +7676,77 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$26</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="25"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>None</c:v>
+                  <c:v>Candidate</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>y25w16</c:v>
+                  <c:v>y25w30</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>y25w18</c:v>
+                  <c:v>y25w32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>y25w20</c:v>
+                  <c:v>y25w34</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>y25w22</c:v>
+                  <c:v>y25w36</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>y25w24</c:v>
+                  <c:v>y25w38</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>y25w26</c:v>
+                  <c:v>y25w40</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>y25w28</c:v>
+                  <c:v>y25w42</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>y25w30</c:v>
+                  <c:v>y25w44</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>y25w32</c:v>
+                  <c:v>y25w46</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>y25w34</c:v>
+                  <c:v>y25w48</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>y25w36</c:v>
+                  <c:v>y25w50</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>y25w38</c:v>
+                  <c:v>y25w52</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>y25w40</c:v>
+                  <c:v>y26w2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>y25w42</c:v>
+                  <c:v>y26w4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>y25w44</c:v>
+                  <c:v>y26w6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>y25w46</c:v>
+                  <c:v>y26w8</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>y25w48</c:v>
+                  <c:v>y26w10</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>y25w50</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>y25w52</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>y26w02</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>y26w04</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>y26w06</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>y26w08</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>y26w10</c:v>
+                  <c:v>y26w12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$D$2:$D$26</c:f>
+              <c:f>'SOVA-BugTrend'!$D$2:$D$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -7902,24 +7800,6 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -8014,95 +7894,77 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$26</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="25"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>None</c:v>
+                  <c:v>Candidate</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>y25w16</c:v>
+                  <c:v>y25w30</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>y25w18</c:v>
+                  <c:v>y25w32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>y25w20</c:v>
+                  <c:v>y25w34</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>y25w22</c:v>
+                  <c:v>y25w36</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>y25w24</c:v>
+                  <c:v>y25w38</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>y25w26</c:v>
+                  <c:v>y25w40</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>y25w28</c:v>
+                  <c:v>y25w42</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>y25w30</c:v>
+                  <c:v>y25w44</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>y25w32</c:v>
+                  <c:v>y25w46</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>y25w34</c:v>
+                  <c:v>y25w48</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>y25w36</c:v>
+                  <c:v>y25w50</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>y25w38</c:v>
+                  <c:v>y25w52</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>y25w40</c:v>
+                  <c:v>y26w2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>y25w42</c:v>
+                  <c:v>y26w4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>y25w44</c:v>
+                  <c:v>y26w6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>y25w46</c:v>
+                  <c:v>y26w8</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>y25w48</c:v>
+                  <c:v>y26w10</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>y25w50</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>y25w52</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>y26w02</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>y26w04</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>y26w06</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>y26w08</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>y26w10</c:v>
+                  <c:v>y26w12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$E$2:$E$26</c:f>
+              <c:f>'SOVA-BugTrend'!$E$2:$E$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -8157,24 +8019,6 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8211,95 +8055,77 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$26</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="25"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>None</c:v>
+                  <c:v>Candidate</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>y25w16</c:v>
+                  <c:v>y25w30</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>y25w18</c:v>
+                  <c:v>y25w32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>y25w20</c:v>
+                  <c:v>y25w34</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>y25w22</c:v>
+                  <c:v>y25w36</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>y25w24</c:v>
+                  <c:v>y25w38</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>y25w26</c:v>
+                  <c:v>y25w40</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>y25w28</c:v>
+                  <c:v>y25w42</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>y25w30</c:v>
+                  <c:v>y25w44</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>y25w32</c:v>
+                  <c:v>y25w46</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>y25w34</c:v>
+                  <c:v>y25w48</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>y25w36</c:v>
+                  <c:v>y25w50</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>y25w38</c:v>
+                  <c:v>y25w52</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>y25w40</c:v>
+                  <c:v>y26w2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>y25w42</c:v>
+                  <c:v>y26w4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>y25w44</c:v>
+                  <c:v>y26w6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>y25w46</c:v>
+                  <c:v>y26w8</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>y25w48</c:v>
+                  <c:v>y26w10</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>y25w50</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>y25w52</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>y26w02</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>y26w04</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>y26w06</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>y26w08</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>y26w10</c:v>
+                  <c:v>y26w12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$F$2:$F$26</c:f>
+              <c:f>'SOVA-BugTrend'!$F$2:$F$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -8350,28 +8176,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8462,167 +8270,131 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$26</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="25"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>None</c:v>
+                  <c:v>Candidate</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>y25w16</c:v>
+                  <c:v>y25w30</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>y25w18</c:v>
+                  <c:v>y25w32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>y25w20</c:v>
+                  <c:v>y25w34</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>y25w22</c:v>
+                  <c:v>y25w36</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>y25w24</c:v>
+                  <c:v>y25w38</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>y25w26</c:v>
+                  <c:v>y25w40</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>y25w28</c:v>
+                  <c:v>y25w42</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>y25w30</c:v>
+                  <c:v>y25w44</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>y25w32</c:v>
+                  <c:v>y25w46</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>y25w34</c:v>
+                  <c:v>y25w48</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>y25w36</c:v>
+                  <c:v>y25w50</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>y25w38</c:v>
+                  <c:v>y25w52</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>y25w40</c:v>
+                  <c:v>y26w2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>y25w42</c:v>
+                  <c:v>y26w4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>y25w44</c:v>
+                  <c:v>y26w6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>y25w46</c:v>
+                  <c:v>y26w8</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>y25w48</c:v>
+                  <c:v>y26w10</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>y25w50</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>y25w52</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>y26w02</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>y26w04</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>y26w06</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>y26w08</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>y26w10</c:v>
+                  <c:v>y26w12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$G$2:$G$26</c:f>
+              <c:f>'SOVA-BugTrend'!$G$2:$G$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>133</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>16</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>55</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>35</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>39</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>39</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>18</c:v>
-                </c:pt>
                 <c:pt idx="11">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>25</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>35</c:v>
-                </c:pt>
                 <c:pt idx="16">
-                  <c:v>29</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>39</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>9</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8661,167 +8433,131 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$26</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="25"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>None</c:v>
+                  <c:v>Candidate</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>y25w16</c:v>
+                  <c:v>y25w30</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>y25w18</c:v>
+                  <c:v>y25w32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>y25w20</c:v>
+                  <c:v>y25w34</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>y25w22</c:v>
+                  <c:v>y25w36</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>y25w24</c:v>
+                  <c:v>y25w38</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>y25w26</c:v>
+                  <c:v>y25w40</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>y25w28</c:v>
+                  <c:v>y25w42</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>y25w30</c:v>
+                  <c:v>y25w44</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>y25w32</c:v>
+                  <c:v>y25w46</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>y25w34</c:v>
+                  <c:v>y25w48</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>y25w36</c:v>
+                  <c:v>y25w50</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>y25w38</c:v>
+                  <c:v>y25w52</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>y25w40</c:v>
+                  <c:v>y26w2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>y25w42</c:v>
+                  <c:v>y26w4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>y25w44</c:v>
+                  <c:v>y26w6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>y25w46</c:v>
+                  <c:v>y26w8</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>y25w48</c:v>
+                  <c:v>y26w10</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>y25w50</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>y25w52</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>y26w02</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>y26w04</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>y26w06</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>y26w08</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>y26w10</c:v>
+                  <c:v>y26w12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$H$2:$H$26</c:f>
+              <c:f>'SOVA-BugTrend'!$H$2:$H$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>87</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>9</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8860,167 +8596,131 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$26</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="25"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>None</c:v>
+                  <c:v>Candidate</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>y25w16</c:v>
+                  <c:v>y25w30</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>y25w18</c:v>
+                  <c:v>y25w32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>y25w20</c:v>
+                  <c:v>y25w34</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>y25w22</c:v>
+                  <c:v>y25w36</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>y25w24</c:v>
+                  <c:v>y25w38</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>y25w26</c:v>
+                  <c:v>y25w40</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>y25w28</c:v>
+                  <c:v>y25w42</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>y25w30</c:v>
+                  <c:v>y25w44</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>y25w32</c:v>
+                  <c:v>y25w46</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>y25w34</c:v>
+                  <c:v>y25w48</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>y25w36</c:v>
+                  <c:v>y25w50</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>y25w38</c:v>
+                  <c:v>y25w52</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>y25w40</c:v>
+                  <c:v>y26w2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>y25w42</c:v>
+                  <c:v>y26w4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>y25w44</c:v>
+                  <c:v>y26w6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>y25w46</c:v>
+                  <c:v>y26w8</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>y25w48</c:v>
+                  <c:v>y26w10</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>y25w50</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>y25w52</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>y26w02</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>y26w04</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>y26w06</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>y26w08</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>y26w10</c:v>
+                  <c:v>y26w12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$I$2:$I$26</c:f>
+              <c:f>'SOVA-BugTrend'!$I$2:$I$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>386</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>23</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>22</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>18</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>18</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>59</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>39</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>42</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>53</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>20</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>32</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>53</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>25</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>43</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>35</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>29</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>44</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>32</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11952,13 +11652,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>171448</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>133348</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -11993,13 +11693,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1057275</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -12034,13 +11734,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>69662</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1057275</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>31562</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -12116,13 +11816,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -12152,8 +11852,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}" name="Table2" displayName="Table2" ref="A1:E29" totalsRowShown="0" headerRowDxfId="35">
-  <autoFilter ref="A1:E29" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}" name="Table2" displayName="Table2" ref="A1:E22" totalsRowShown="0" headerRowDxfId="35">
+  <autoFilter ref="A1:E22" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F25F0D34-0297-4771-8BBB-350BCDD85D46}" name="Week"/>
     <tableColumn id="2" xr3:uid="{39CFCD12-3130-47A8-A140-DBF602F1743D}" name="Done"/>
@@ -12168,8 +11868,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E42B6291-7056-475B-AE1E-CA59C524E5F1}" name="Table1" displayName="Table1" ref="A1:H18" totalsRowShown="0" headerRowDxfId="33">
-  <autoFilter ref="A1:H18" xr:uid="{E42B6291-7056-475B-AE1E-CA59C524E5F1}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E42B6291-7056-475B-AE1E-CA59C524E5F1}" name="Table1" displayName="Table1" ref="A1:H19" totalsRowShown="0" headerRowDxfId="33">
+  <autoFilter ref="A1:H19" xr:uid="{E42B6291-7056-475B-AE1E-CA59C524E5F1}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{9154D4F8-C83D-4DB9-9182-818F32FA7C26}" name="Versions"/>
     <tableColumn id="2" xr3:uid="{1FE19FA2-B8BE-47BC-9953-F802445DE79D}" name="Passed"/>
@@ -12187,8 +11887,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}" name="Table3" displayName="Table3" ref="A1:H34" totalsRowShown="0" headerRowDxfId="31">
-  <autoFilter ref="A1:H34" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}" name="Table3" displayName="Table3" ref="A1:H35" totalsRowShown="0" headerRowDxfId="31">
+  <autoFilter ref="A1:H35" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{8103CDF3-74DC-4B31-821D-E20368EA5455}" name="Versions"/>
     <tableColumn id="2" xr3:uid="{6C3B261F-FA51-42D2-821A-F22633569372}" name="Passed"/>
@@ -12206,8 +11906,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{E4AD0B7A-EC5B-4838-AC2B-8475A3B6644B}" name="Table7" displayName="Table7" ref="A1:H21" totalsRowShown="0" headerRowDxfId="29">
-  <autoFilter ref="A1:H21" xr:uid="{E4AD0B7A-EC5B-4838-AC2B-8475A3B6644B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{E4AD0B7A-EC5B-4838-AC2B-8475A3B6644B}" name="Table7" displayName="Table7" ref="A1:H22" totalsRowShown="0" headerRowDxfId="29">
+  <autoFilter ref="A1:H22" xr:uid="{E4AD0B7A-EC5B-4838-AC2B-8475A3B6644B}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{58F8A895-CEBE-41D2-B7BB-1681C0697C85}" name="Version"/>
     <tableColumn id="2" xr3:uid="{CE08A48D-2419-484B-993C-54A546869B61}" name="To Do" dataDxfId="28"/>
@@ -12225,8 +11925,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}" name="Table5" displayName="Table5" ref="A1:I26" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17" totalsRowBorderDxfId="16" dataCellStyle="Hyperlink">
-  <autoFilter ref="A1:I26" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}" name="Table5" displayName="Table5" ref="A1:I20" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17" totalsRowBorderDxfId="16" dataCellStyle="Hyperlink">
+  <autoFilter ref="A1:I20" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{5BE08AE0-E0B5-4B46-9423-456B88C2D9BC}" name="Sprint" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{030F9647-4FC0-4C7E-9B3A-AB099CC59EBA}" name="To Do (0%)" dataDxfId="14" dataCellStyle="Hyperlink"/>
@@ -12245,8 +11945,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}" name="Table25" displayName="Table25" ref="A1:E21" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A1:E21" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}" name="Table25" displayName="Table25" ref="A1:E22" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E22" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{7070D9F2-0ED1-4F39-8D72-28B37C8E98F2}" name="Week" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{1173F443-CC27-4C6E-A432-BF66DB2A740E}" name="Done" dataDxfId="3"/>
@@ -12577,7 +12277,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D733A42-966D-5F4E-B061-B304543CE88E}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.77734375" customWidth="1"/>
@@ -12588,7 +12288,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -12605,506 +12305,379 @@
     </row>
     <row r="2" spans="1:5" ht="21.95" customHeight="1">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D2">
-        <v>115</v>
+        <v>219</v>
       </c>
       <c r="E2">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>118</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="21.95" customHeight="1">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="E3">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>118</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="21.95" customHeight="1">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>109</v>
-      </c>
-      <c r="E4">
+        <v>172</v>
+      </c>
+      <c r="E4" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>118</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="21.95" customHeight="1">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D5">
-        <v>108</v>
-      </c>
-      <c r="E5">
+        <v>168</v>
+      </c>
+      <c r="E5" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>118</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="21.95" customHeight="1">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>104</v>
-      </c>
-      <c r="E6">
+        <v>166</v>
+      </c>
+      <c r="E6" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>118</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="21.95" customHeight="1">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D7">
-        <v>228</v>
-      </c>
-      <c r="E7">
+        <v>160</v>
+      </c>
+      <c r="E7" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>248</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="21.95" customHeight="1">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="B8">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C8">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8">
-        <v>224</v>
-      </c>
-      <c r="E8">
+        <v>160</v>
+      </c>
+      <c r="E8" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>248</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="21.95" customHeight="1">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="B9">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C9">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D9">
-        <v>220</v>
-      </c>
-      <c r="E9">
+        <v>161</v>
+      </c>
+      <c r="E9" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>248</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="21.95" customHeight="1">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="B10">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C10">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D10">
-        <v>219</v>
-      </c>
-      <c r="E10">
+        <v>160</v>
+      </c>
+      <c r="E10" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>248</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="21.95" customHeight="1">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B11">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C11">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>173</v>
-      </c>
-      <c r="E11">
+        <v>160</v>
+      </c>
+      <c r="E11" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
         <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="21.95" customHeight="1">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B12">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C12">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D12">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E12" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="21.95" customHeight="1">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B13">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C13">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D13">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E13" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="21.95" customHeight="1">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B14">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C14">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D14">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E14" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="21.95" customHeight="1">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C15">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D15">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E15" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="21.95" customHeight="1">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="B16">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C16">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D16">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E16" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="21.95" customHeight="1">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B17">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C17">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E17" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="21.95" customHeight="1">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="B18">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C18">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E18" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="21.95" customHeight="1">
       <c r="A19" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="B19">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D19">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E19" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="21.95" customHeight="1">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="B20">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D20">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E20" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="21.95" customHeight="1">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="B21">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D21">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E21" s="12">
         <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="21.95" customHeight="1">
       <c r="A22" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="B22">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E22" s="12">
-        <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>197</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="21.95" customHeight="1">
-      <c r="A23" t="s">
-        <v>75</v>
-      </c>
-      <c r="B23">
-        <v>32</v>
-      </c>
-      <c r="C23">
-        <v>3</v>
-      </c>
-      <c r="D23">
-        <v>162</v>
-      </c>
-      <c r="E23" s="12">
-        <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>197</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="21.95" customHeight="1">
-      <c r="A24" t="s">
-        <v>90</v>
-      </c>
-      <c r="B24">
-        <v>32</v>
-      </c>
-      <c r="C24">
-        <v>3</v>
-      </c>
-      <c r="D24">
-        <v>162</v>
-      </c>
-      <c r="E24" s="12">
-        <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>197</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="21.95" customHeight="1">
-      <c r="A25" t="s">
-        <v>91</v>
-      </c>
-      <c r="B25">
-        <v>32</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>162</v>
-      </c>
-      <c r="E25" s="12">
-        <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>195</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="21.95" customHeight="1">
-      <c r="A26" t="s">
-        <v>92</v>
-      </c>
-      <c r="B26">
-        <v>32</v>
-      </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26">
-        <v>161</v>
-      </c>
-      <c r="E26" s="12">
-        <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>195</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="21.95" customHeight="1">
-      <c r="A27" t="s">
-        <v>97</v>
-      </c>
-      <c r="B27">
-        <v>31</v>
-      </c>
-      <c r="C27">
-        <v>3</v>
-      </c>
-      <c r="D27">
-        <v>161</v>
-      </c>
-      <c r="E27" s="12">
-        <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>195</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="21.95" customHeight="1">
-      <c r="A28" t="s">
-        <v>98</v>
-      </c>
-      <c r="B28">
-        <v>31</v>
-      </c>
-      <c r="C28">
-        <v>3</v>
-      </c>
-      <c r="D28">
-        <v>161</v>
-      </c>
-      <c r="E28" s="12">
-        <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>195</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="21.95" customHeight="1">
-      <c r="A29" t="s">
-        <v>103</v>
-      </c>
-      <c r="B29">
-        <v>31</v>
-      </c>
-      <c r="C29">
-        <v>3</v>
-      </c>
-      <c r="D29">
-        <v>161</v>
-      </c>
-      <c r="E29" s="12">
-        <f>SUM(Table2[[#This Row],[Done]:[TODO (P1)]])</f>
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -13119,17 +12692,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6429633B-8BD2-084C-8C0F-75969053522F}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" customWidth="1"/>
     <col min="2" max="2" width="11.77734375" customWidth="1"/>
     <col min="3" max="8" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>11</v>
@@ -13344,7 +12917,7 @@
     </row>
     <row r="9" spans="1:8" ht="21.95" customHeight="1">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B9">
         <v>1399</v>
@@ -13371,7 +12944,7 @@
     </row>
     <row r="10" spans="1:8" ht="21.95" customHeight="1">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>1271</v>
@@ -13398,7 +12971,7 @@
     </row>
     <row r="11" spans="1:8" ht="21.95" customHeight="1">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>1333</v>
@@ -13425,7 +12998,7 @@
     </row>
     <row r="12" spans="1:8" ht="21.95" customHeight="1">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B12">
         <v>1475</v>
@@ -13452,7 +13025,7 @@
     </row>
     <row r="13" spans="1:8" ht="21.95" customHeight="1">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B13">
         <v>2031</v>
@@ -13479,7 +13052,7 @@
     </row>
     <row r="14" spans="1:8" ht="21.95" customHeight="1">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B14">
         <v>1755</v>
@@ -13506,7 +13079,7 @@
     </row>
     <row r="15" spans="1:8" ht="21.95" customHeight="1">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B15">
         <v>1892</v>
@@ -13533,7 +13106,7 @@
     </row>
     <row r="16" spans="1:8" ht="21.95" customHeight="1">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B16">
         <v>1642</v>
@@ -13560,7 +13133,7 @@
     </row>
     <row r="17" spans="1:8" ht="21.95" customHeight="1">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B17">
         <v>1350</v>
@@ -13587,7 +13160,7 @@
     </row>
     <row r="18" spans="1:8" ht="21.95" customHeight="1">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B18">
         <v>860</v>
@@ -13610,6 +13183,33 @@
       <c r="H18">
         <f>SUM(Table1[[#This Row],[Passed]:[Untested]])</f>
         <v>866</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="21.95" customHeight="1">
+      <c r="A19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19">
+        <v>186</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>13</v>
+      </c>
+      <c r="F19">
+        <v>23</v>
+      </c>
+      <c r="G19">
+        <v>375</v>
+      </c>
+      <c r="H19">
+        <f>SUM(Table1[[#This Row],[Passed]:[Untested]])</f>
+        <v>597</v>
       </c>
     </row>
   </sheetData>
@@ -13624,7 +13224,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA6EDF6-834F-DA49-B3FC-BFE1673433AB}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
@@ -13633,7 +13233,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>11</v>
@@ -13659,7 +13259,7 @@
     </row>
     <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B2">
         <v>38</v>
@@ -13686,12 +13286,12 @@
     </row>
     <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B4">
         <v>43</v>
@@ -13718,12 +13318,12 @@
     </row>
     <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B6">
         <v>58</v>
@@ -13750,12 +13350,12 @@
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B8">
         <v>76</v>
@@ -13782,12 +13382,12 @@
     </row>
     <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B10">
         <v>121</v>
@@ -13814,12 +13414,12 @@
     </row>
     <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B12">
         <v>148</v>
@@ -13846,12 +13446,12 @@
     </row>
     <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B14" s="10">
         <v>148</v>
@@ -13878,13 +13478,13 @@
     </row>
     <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H15" s="12"/>
     </row>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B16">
         <v>231</v>
@@ -13911,13 +13511,13 @@
     </row>
     <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H17" s="12"/>
     </row>
     <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B18">
         <v>249</v>
@@ -13944,7 +13544,7 @@
     </row>
     <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B19">
         <v>155</v>
@@ -13971,7 +13571,7 @@
     </row>
     <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B20">
         <v>225</v>
@@ -13998,7 +13598,7 @@
     </row>
     <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B21">
         <v>281</v>
@@ -14025,7 +13625,7 @@
     </row>
     <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B22">
         <v>291</v>
@@ -14052,7 +13652,7 @@
     </row>
     <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B23">
         <v>267</v>
@@ -14079,7 +13679,7 @@
     </row>
     <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B24">
         <v>343</v>
@@ -14106,7 +13706,7 @@
     </row>
     <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B25">
         <v>351</v>
@@ -14133,7 +13733,7 @@
     </row>
     <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B26">
         <v>142</v>
@@ -14160,7 +13760,7 @@
     </row>
     <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B27">
         <v>442</v>
@@ -14187,7 +13787,7 @@
     </row>
     <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B28">
         <v>518</v>
@@ -14214,7 +13814,7 @@
     </row>
     <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B29">
         <v>636</v>
@@ -14241,7 +13841,7 @@
     </row>
     <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B30">
         <v>436</v>
@@ -14268,7 +13868,7 @@
     </row>
     <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B31">
         <v>171</v>
@@ -14295,7 +13895,7 @@
     </row>
     <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B32">
         <v>723</v>
@@ -14322,7 +13922,7 @@
     </row>
     <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="B33">
         <v>687</v>
@@ -14349,7 +13949,7 @@
     </row>
     <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="B34">
         <v>218</v>
@@ -14372,6 +13972,33 @@
       <c r="H34" s="12">
         <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
         <v>218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="A35" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B35">
+        <v>694</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>7</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35" s="12">
+        <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
+        <v>703</v>
       </c>
     </row>
   </sheetData>
@@ -14386,7 +14013,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7C79DB4-6EC1-E840-9DE9-46C117A6F960}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
@@ -14406,16 +14033,16 @@
         <v>18</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>1</v>
@@ -14425,7 +14052,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="3" t="s">
+      <c r="A2" t="s">
         <v>19</v>
       </c>
       <c r="B2">
@@ -14452,7 +14079,7 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="3" t="s">
+      <c r="A3" t="s">
         <v>20</v>
       </c>
       <c r="B3">
@@ -14479,7 +14106,7 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="3" t="s">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4">
@@ -14506,7 +14133,7 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="3" t="s">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5">
@@ -14533,7 +14160,7 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="3" t="s">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6">
@@ -14560,7 +14187,7 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="3" t="s">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7">
@@ -14587,7 +14214,7 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="3" t="s">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8">
@@ -14614,7 +14241,7 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="3" t="s">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9">
@@ -14641,7 +14268,7 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="3" t="s">
+      <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10">
@@ -14668,8 +14295,8 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="3" t="s">
-        <v>44</v>
+      <c r="A11" t="s">
+        <v>37</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -14695,8 +14322,8 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="3" t="s">
-        <v>49</v>
+      <c r="A12" t="s">
+        <v>42</v>
       </c>
       <c r="B12">
         <v>12</v>
@@ -14722,8 +14349,8 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="3" t="s">
-        <v>50</v>
+      <c r="A13" t="s">
+        <v>43</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -14749,8 +14376,8 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="3" t="s">
-        <v>53</v>
+      <c r="A14" t="s">
+        <v>46</v>
       </c>
       <c r="B14">
         <v>2</v>
@@ -14776,8 +14403,8 @@
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="3" t="s">
-        <v>54</v>
+      <c r="A15" t="s">
+        <v>47</v>
       </c>
       <c r="B15">
         <v>11</v>
@@ -14803,8 +14430,8 @@
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="3" t="s">
-        <v>56</v>
+      <c r="A16" t="s">
+        <v>49</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -14830,8 +14457,8 @@
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="3" t="s">
-        <v>59</v>
+      <c r="A17" t="s">
+        <v>52</v>
       </c>
       <c r="B17">
         <v>6</v>
@@ -14857,8 +14484,8 @@
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="3" t="s">
-        <v>60</v>
+      <c r="A18" t="s">
+        <v>53</v>
       </c>
       <c r="B18">
         <v>3</v>
@@ -14884,8 +14511,8 @@
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="3" t="s">
-        <v>89</v>
+      <c r="A19" t="s">
+        <v>82</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -14911,8 +14538,8 @@
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="3" t="s">
-        <v>93</v>
+      <c r="A20" t="s">
+        <v>86</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -14938,8 +14565,8 @@
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="3" t="s">
-        <v>94</v>
+      <c r="A21" t="s">
+        <v>87</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -14951,17 +14578,44 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H21">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
         <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22">
+        <v>10</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>7</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>7</v>
+      </c>
+      <c r="H22" s="12">
+        <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -14976,7 +14630,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7487DEB-55FC-DC4E-A4B1-F7171B8F3237}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.21875" customWidth="1"/>
@@ -15000,13 +14654,13 @@
         <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>24</v>
@@ -15020,40 +14674,40 @@
     </row>
     <row r="2" spans="1:9" ht="18" thickBot="1">
       <c r="A2" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B2" s="5">
-        <v>159</v>
+        <v>27</v>
       </c>
       <c r="C2" s="5">
         <v>0</v>
       </c>
       <c r="D2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" s="5">
-        <v>133</v>
+        <v>5</v>
       </c>
       <c r="H2" s="5">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="I2" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>386</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18" thickBot="1">
       <c r="A3" s="4" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="5">
         <v>0</v>
@@ -15068,22 +14722,22 @@
         <v>0</v>
       </c>
       <c r="G3" s="5">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H3" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I3" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>23</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" thickBot="1">
       <c r="A4" s="4" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="5">
         <v>0</v>
@@ -15098,22 +14752,22 @@
         <v>0</v>
       </c>
       <c r="G4" s="5">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H4" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I4" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>22</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" thickBot="1">
       <c r="A5" s="4" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="5">
         <v>0</v>
@@ -15128,22 +14782,22 @@
         <v>0</v>
       </c>
       <c r="G5" s="5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="18" thickBot="1">
       <c r="A6" s="4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B6" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C6" s="5">
         <v>0</v>
@@ -15158,22 +14812,22 @@
         <v>0</v>
       </c>
       <c r="G6" s="5">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H6" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18" thickBot="1">
       <c r="A7" s="4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B7" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C7" s="5">
         <v>0</v>
@@ -15188,19 +14842,19 @@
         <v>0</v>
       </c>
       <c r="G7" s="5">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H7" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="18" thickBot="1">
       <c r="A8" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B8" s="5">
         <v>0</v>
@@ -15218,22 +14872,22 @@
         <v>0</v>
       </c>
       <c r="G8" s="5">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="H8" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I8" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>39</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="18" thickBot="1">
       <c r="A9" s="4" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" s="5">
         <v>0</v>
@@ -15248,22 +14902,22 @@
         <v>0</v>
       </c>
       <c r="G9" s="5">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H9" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="18" thickBot="1">
       <c r="A10" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="5">
         <v>0</v>
@@ -15278,22 +14932,22 @@
         <v>0</v>
       </c>
       <c r="G10" s="5">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H10" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I10" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="18" thickBot="1">
       <c r="A11" s="4" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B11" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" s="5">
         <v>0</v>
@@ -15308,22 +14962,22 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="H11" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I11" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>53</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="18" thickBot="1">
       <c r="A12" s="4" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="B12" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C12" s="5">
         <v>0</v>
@@ -15338,22 +14992,22 @@
         <v>0</v>
       </c>
       <c r="G12" s="5">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="H12" s="5">
         <v>1</v>
       </c>
       <c r="I12" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>20</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18" thickBot="1">
       <c r="A13" s="4" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B13" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" s="5">
         <v>0</v>
@@ -15368,22 +15022,22 @@
         <v>0</v>
       </c>
       <c r="G13" s="5">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H13" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I13" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18" thickBot="1">
       <c r="A14" s="4" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="B14" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C14" s="5">
         <v>0</v>
@@ -15398,22 +15052,22 @@
         <v>0</v>
       </c>
       <c r="G14" s="5">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="H14" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I14" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="18" thickBot="1">
       <c r="A15" s="4" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="B15" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C15" s="5">
         <v>0</v>
@@ -15428,22 +15082,22 @@
         <v>0</v>
       </c>
       <c r="G15" s="5">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H15" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="18" thickBot="1">
       <c r="A16" s="4" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="B16" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C16" s="5">
         <v>0</v>
@@ -15458,22 +15112,22 @@
         <v>0</v>
       </c>
       <c r="G16" s="5">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="H16" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="18" thickBot="1">
       <c r="A17" s="4" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="B17" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C17" s="5">
         <v>0</v>
@@ -15488,25 +15142,25 @@
         <v>0</v>
       </c>
       <c r="G17" s="5">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H17" s="5">
-        <v>0</v>
-      </c>
-      <c r="I17" s="5">
+        <v>5</v>
+      </c>
+      <c r="I17" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="18" thickBot="1">
       <c r="A18" s="4" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="B18" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C18" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="5">
         <v>0</v>
@@ -15518,25 +15172,25 @@
         <v>0</v>
       </c>
       <c r="G18" s="5">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H18" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I18" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="18" thickBot="1">
       <c r="A19" s="4" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="B19" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C19" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5">
         <v>0</v>
@@ -15545,25 +15199,25 @@
         <v>0</v>
       </c>
       <c r="F19" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="5">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="H19" s="5">
-        <v>1</v>
-      </c>
-      <c r="I19" s="5">
+        <v>9</v>
+      </c>
+      <c r="I19" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="18" thickBot="1">
       <c r="A20" s="4" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="B20" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C20" s="5">
         <v>0</v>
@@ -15578,387 +15232,165 @@
         <v>0</v>
       </c>
       <c r="G20" s="5">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H20" s="5">
-        <v>1</v>
-      </c>
-      <c r="I20" s="5">
+        <v>0</v>
+      </c>
+      <c r="I20" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="18" thickBot="1">
-      <c r="A21" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="5">
-        <v>6</v>
-      </c>
-      <c r="C21" s="5">
-        <v>0</v>
-      </c>
-      <c r="D21" s="5">
-        <v>0</v>
-      </c>
-      <c r="E21" s="5">
-        <v>0</v>
-      </c>
-      <c r="F21" s="5">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5">
-        <v>29</v>
-      </c>
-      <c r="H21" s="5">
-        <v>1</v>
-      </c>
-      <c r="I21" s="5">
-        <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="18" thickBot="1">
-      <c r="A22" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B22" s="5">
-        <v>2</v>
-      </c>
-      <c r="C22" s="5">
-        <v>0</v>
-      </c>
-      <c r="D22" s="5">
-        <v>0</v>
-      </c>
-      <c r="E22" s="5">
-        <v>0</v>
-      </c>
-      <c r="F22" s="5">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5">
-        <v>29</v>
-      </c>
-      <c r="H22" s="5">
-        <v>0</v>
-      </c>
-      <c r="I22" s="15">
-        <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="18" thickBot="1">
-      <c r="A23" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B23" s="5">
-        <v>3</v>
-      </c>
-      <c r="C23" s="5">
-        <v>0</v>
-      </c>
-      <c r="D23" s="5">
-        <v>0</v>
-      </c>
-      <c r="E23" s="5">
-        <v>0</v>
-      </c>
-      <c r="F23" s="5">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5">
-        <v>31</v>
-      </c>
-      <c r="H23" s="5">
-        <v>2</v>
-      </c>
-      <c r="I23" s="5">
-        <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="18" thickBot="1">
-      <c r="A24" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="5">
-        <v>7</v>
-      </c>
-      <c r="C24" s="5">
-        <v>0</v>
-      </c>
-      <c r="D24" s="5">
-        <v>0</v>
-      </c>
-      <c r="E24" s="5">
-        <v>1</v>
-      </c>
-      <c r="F24" s="5">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5">
-        <v>24</v>
-      </c>
-      <c r="H24" s="5">
-        <v>5</v>
-      </c>
-      <c r="I24" s="15">
-        <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="18" thickBot="1">
-      <c r="A25" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B25" s="5">
-        <v>6</v>
-      </c>
-      <c r="C25" s="5">
-        <v>1</v>
-      </c>
-      <c r="D25" s="5">
-        <v>0</v>
-      </c>
-      <c r="E25" s="5">
-        <v>0</v>
-      </c>
-      <c r="F25" s="5">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5">
-        <v>11</v>
-      </c>
-      <c r="H25" s="5">
-        <v>8</v>
-      </c>
-      <c r="I25" s="15">
-        <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="18" thickBot="1">
-      <c r="A26" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B26" s="5">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>1</v>
-      </c>
-      <c r="D26" s="5">
-        <v>0</v>
-      </c>
-      <c r="E26" s="5">
-        <v>1</v>
-      </c>
-      <c r="F26" s="5">
-        <v>1</v>
-      </c>
-      <c r="G26" s="5">
         <v>9</v>
-      </c>
-      <c r="H26" s="5">
-        <v>9</v>
-      </c>
-      <c r="I26" s="15">
-        <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>32</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{34711E63-32B5-48FD-8B87-BEB3251F5ECB}"/>
-    <hyperlink ref="D2" r:id="rId2" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{5674E088-BF22-4593-9270-A955F7DBDDD8}"/>
-    <hyperlink ref="G2" r:id="rId3" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{946611E4-F7B6-4C8B-BFBF-C9A3A68DFF5A}"/>
-    <hyperlink ref="E2" r:id="rId4" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{1D63C089-7DE7-4D56-8253-2A85B7E2E854}"/>
-    <hyperlink ref="H2" r:id="rId5" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{0E7325D6-CB9E-4D72-9B94-5429EE488EC3}"/>
-    <hyperlink ref="C2" r:id="rId6" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{8E7C3923-D6A5-45DC-86A3-B70A796E7172}"/>
-    <hyperlink ref="F2" r:id="rId7" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+EMPTY+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E1D22E9D-62E0-4318-B85E-41B7C5EEBB89}"/>
-    <hyperlink ref="B3" r:id="rId8" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{298EC8DE-589F-4F6D-8374-E7E118C66383}"/>
-    <hyperlink ref="D3" r:id="rId9" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{EF0354A6-72A6-45A7-B9F8-C095AC39946B}"/>
-    <hyperlink ref="G3" r:id="rId10" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{212459D5-B280-45F5-8DAD-E89D3CBF23C9}"/>
-    <hyperlink ref="E3" r:id="rId11" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A10FAEB7-3205-4698-8782-EE8129B37667}"/>
-    <hyperlink ref="H3" r:id="rId12" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{181B9932-AAC4-4563-B268-48C1500B1AF8}"/>
-    <hyperlink ref="C3" r:id="rId13" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6696278C-FD0D-4603-8FEA-DBEE8C87B3B4}"/>
-    <hyperlink ref="F3" r:id="rId14" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1463+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{740A6C31-7558-45C9-9DE7-8BC30E3D5F26}"/>
-    <hyperlink ref="B4" r:id="rId15" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{9C03AC9C-16B8-4B8A-9651-90705CB213B4}"/>
-    <hyperlink ref="D4" r:id="rId16" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{6BBDD3AA-BB57-485E-A5FD-2639E2C24A10}"/>
-    <hyperlink ref="G4" r:id="rId17" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{183CF4AA-84FD-4085-9088-676BFDF91E59}"/>
-    <hyperlink ref="E4" r:id="rId18" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{3236CB73-D96E-4774-844A-5927A496D147}"/>
-    <hyperlink ref="H4" r:id="rId19" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{DE797A1D-0843-4525-8117-637B96A06273}"/>
-    <hyperlink ref="C4" r:id="rId20" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{1914DCE3-4AC4-4E0D-850B-E229625C5C2D}"/>
-    <hyperlink ref="F4" r:id="rId21" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1466+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A1F186FB-867A-4E97-898C-533544E46C67}"/>
-    <hyperlink ref="B5" r:id="rId22" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{5AECE1B0-9E7D-453B-85D5-7AEC02AE052E}"/>
-    <hyperlink ref="D5" r:id="rId23" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{F866C0B4-C94C-454A-8EAC-04159EED840E}"/>
-    <hyperlink ref="G5" r:id="rId24" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3D8E72F0-DBFB-45C7-BE6F-5AE8BF63EB85}"/>
-    <hyperlink ref="E5" r:id="rId25" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{67BDD5FC-D605-4D13-B5E0-DDB525A50B85}"/>
-    <hyperlink ref="H5" r:id="rId26" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{689B3102-A949-48F8-B962-D1EB8E490A31}"/>
-    <hyperlink ref="C5" r:id="rId27" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{7DB02657-C57E-4DD1-B3FD-899E275FA401}"/>
-    <hyperlink ref="F5" r:id="rId28" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1496+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{B5DE74B7-4DCD-46A1-BE7C-BC2AC1D24A43}"/>
-    <hyperlink ref="B6" r:id="rId29" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A06EE209-20C0-43A4-863C-2B0F47EBE350}"/>
-    <hyperlink ref="D6" r:id="rId30" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{346BE594-0974-422D-B03E-72A2932512A0}"/>
-    <hyperlink ref="G6" r:id="rId31" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{7019FB0E-4499-4545-A26C-C626D19E6960}"/>
-    <hyperlink ref="E6" r:id="rId32" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A08EFD40-FE00-471F-9A90-1BA4F3848AF6}"/>
-    <hyperlink ref="H6" r:id="rId33" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{8DF30AF4-FC29-41FA-8DA4-1D5F4FE84D4C}"/>
-    <hyperlink ref="C6" r:id="rId34" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{25DFCB2A-0943-465B-8235-AAADDE1A6669}"/>
-    <hyperlink ref="F6" r:id="rId35" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1497+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{9A9866E6-AD9F-4F98-9552-CC66720CFDE8}"/>
-    <hyperlink ref="B7" r:id="rId36" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{6F0972CB-E226-4A6F-83B5-37762AE69CF7}"/>
-    <hyperlink ref="D7" r:id="rId37" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{69B8E6D5-CEB5-4FA7-BA00-5496F14B886F}"/>
-    <hyperlink ref="G7" r:id="rId38" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{874BAEDE-927A-4CA9-9802-C9461EF59317}"/>
-    <hyperlink ref="E7" r:id="rId39" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{C8595C1F-2ADB-4C12-A24E-61A5D9DDF351}"/>
-    <hyperlink ref="H7" r:id="rId40" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{3A607FCB-A3B3-4D06-9113-0A22A06C0B06}"/>
-    <hyperlink ref="C7" r:id="rId41" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{BD3864C1-1EC0-4C52-A267-EC043EBE1076}"/>
-    <hyperlink ref="F7" r:id="rId42" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1498+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E6606B96-F372-4853-8917-452561334A7E}"/>
-    <hyperlink ref="B8" r:id="rId43" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{E00C6465-7849-4D4F-B025-D9988DF0B6C7}"/>
-    <hyperlink ref="D8" r:id="rId44" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D753198A-6878-4194-918C-83F3142C0BC4}"/>
-    <hyperlink ref="G8" r:id="rId45" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{91635E97-EFBC-46AA-898D-12D96EF3E9C4}"/>
-    <hyperlink ref="E8" r:id="rId46" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B57207CE-0532-46FE-AFF3-59472BB48E38}"/>
-    <hyperlink ref="H8" r:id="rId47" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{CC9E57EE-D725-4EFA-AD69-131745C57C22}"/>
-    <hyperlink ref="C8" r:id="rId48" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{D4555482-963D-4318-BD61-22868EEC92D5}"/>
-    <hyperlink ref="F8" r:id="rId49" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+1499+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{BDDC02C8-9F9C-4176-8BC1-421B87555DBC}"/>
-    <hyperlink ref="B9" r:id="rId50" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{B5556016-A043-45E4-BE00-2D1E9BB34F62}"/>
-    <hyperlink ref="D9" r:id="rId51" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{B65D8CFA-196F-479A-B5CF-0255B3A99F74}"/>
-    <hyperlink ref="G9" r:id="rId52" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{97326DE9-214D-4C25-92C1-3EB254CEB50C}"/>
-    <hyperlink ref="E9" r:id="rId53" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A516D73E-0518-425D-9551-A74659057C3F}"/>
-    <hyperlink ref="H9" r:id="rId54" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{51083CC8-8DAF-49B0-B429-0100A57F4FF0}"/>
-    <hyperlink ref="C9" r:id="rId55" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{93435779-D924-4EFB-A63A-F58DDF8F5CFE}"/>
-    <hyperlink ref="F9" r:id="rId56" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{25FC70B2-AC9E-4F52-97AE-777A8284F32D}"/>
-    <hyperlink ref="B10" r:id="rId57" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A34A62D3-D214-40FA-B5D2-026DFE734B32}"/>
-    <hyperlink ref="D10" r:id="rId58" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{B31C976D-4E80-443F-97FE-3C5061D8A319}"/>
-    <hyperlink ref="G10" r:id="rId59" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{7DFDD6E4-A179-4F1E-B661-4E961BCE0BC9}"/>
-    <hyperlink ref="E10" r:id="rId60" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F9DD4FF7-0210-4BB7-A496-64FA7A59BED6}"/>
-    <hyperlink ref="H10" r:id="rId61" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{815BD11A-FCA7-44E6-93C3-86BC524E64C4}"/>
-    <hyperlink ref="C10" r:id="rId62" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{60D496FF-F38F-4EF0-A715-834EC9A9F272}"/>
-    <hyperlink ref="F10" r:id="rId63" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A6DDE5D1-FC3F-400A-A8EA-2B12CC2C4021}"/>
-    <hyperlink ref="B11" r:id="rId64" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{199A8C9C-770B-4208-95A1-D72A67C3318D}"/>
-    <hyperlink ref="D11" r:id="rId65" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2E025D2C-BA76-4192-88DB-31AAD35EF35E}"/>
-    <hyperlink ref="G11" r:id="rId66" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{938608BA-4C20-4023-8DD1-6A443C09039F}"/>
-    <hyperlink ref="E11" r:id="rId67" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A128E572-3614-458E-B8E6-2DB60541092B}"/>
-    <hyperlink ref="H11" r:id="rId68" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{4F43AFA6-C202-4058-AB87-80992762E531}"/>
-    <hyperlink ref="C11" r:id="rId69" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{50DC1068-0618-45EA-B8E3-9DC4BCAE1125}"/>
-    <hyperlink ref="F11" r:id="rId70" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{3F64E4A5-2E50-4F27-99B1-B6AAEC698DAE}"/>
-    <hyperlink ref="B12" r:id="rId71" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{9D35E47D-60D4-44FD-B5A1-27B9D574DB80}"/>
-    <hyperlink ref="D12" r:id="rId72" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2202E8AC-919A-4D43-9C9B-A3AE27D336DB}"/>
-    <hyperlink ref="G12" r:id="rId73" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{E46B5EB1-D9C0-40D6-BE3B-71ACC25A34A5}"/>
-    <hyperlink ref="E12" r:id="rId74" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F5761500-861A-49C4-94FA-4A8B13972158}"/>
-    <hyperlink ref="H12" r:id="rId75" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{6828453F-6DC0-403E-9BDA-AEFBFC7C9DF1}"/>
-    <hyperlink ref="C12" r:id="rId76" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{DFB0592B-C374-4EEC-AC75-F64422D6FC49}"/>
-    <hyperlink ref="F12" r:id="rId77" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{70840C12-8AA1-4F9D-A218-A12C35ABC0D7}"/>
-    <hyperlink ref="B13" r:id="rId78" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{9ED91F79-573B-475E-8917-110837553A80}"/>
-    <hyperlink ref="D13" r:id="rId79" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{73304496-191D-48CC-B514-4172B5501041}"/>
-    <hyperlink ref="G13" r:id="rId80" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{1D79DE91-5AED-4AB1-9C8E-4EB5B035332C}"/>
-    <hyperlink ref="E13" r:id="rId81" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{713AE0CF-967C-4C5F-B83C-E7BFE746E3C1}"/>
-    <hyperlink ref="H13" r:id="rId82" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{403B8CE2-CE2A-41A3-8486-52EB60189D41}"/>
-    <hyperlink ref="C13" r:id="rId83" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{ADC7883D-30BA-47A7-B5B1-A3D535385280}"/>
-    <hyperlink ref="F13" r:id="rId84" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E8F71867-D51A-4E87-A796-42A0F50BA50C}"/>
-    <hyperlink ref="B14" r:id="rId85" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{AE6A39EE-BB08-456B-8885-683CFD8F657E}"/>
-    <hyperlink ref="D14" r:id="rId86" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{6FE8C678-12B3-4F58-9DAC-A0C8D09AB5DB}"/>
-    <hyperlink ref="G14" r:id="rId87" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F79E2A39-DEB6-4A0F-9D7F-9556F29D2DC5}"/>
-    <hyperlink ref="E14" r:id="rId88" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{3B0DE269-B331-4961-A2E5-0B6EB7AC9BFB}"/>
-    <hyperlink ref="H14" r:id="rId89" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{195E7B08-7177-41DB-844C-DBFF92C839CB}"/>
-    <hyperlink ref="C14" r:id="rId90" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{998268BD-9801-4A90-BBB1-509874361D31}"/>
-    <hyperlink ref="F14" r:id="rId91" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{5C78A058-63FC-4F63-9804-694D8F4F2CCB}"/>
-    <hyperlink ref="B15" r:id="rId92" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{FB412802-04D4-443B-AE88-75A5151B8EC6}"/>
-    <hyperlink ref="D15" r:id="rId93" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{DA4B7A3B-C50E-456D-9822-3A6ECF54DFCD}"/>
-    <hyperlink ref="G15" r:id="rId94" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{7FF1A9FD-1AD9-4064-9510-E4734AD64E02}"/>
-    <hyperlink ref="E15" r:id="rId95" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D5CD931C-360B-44F0-BA9C-4FE80C738D57}"/>
-    <hyperlink ref="H15" r:id="rId96" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{0F212D97-7DC6-4E5C-A807-3FA0A6E70322}"/>
-    <hyperlink ref="C15" r:id="rId97" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{8F676768-2EFB-49BC-8E01-27ADA3A491D6}"/>
-    <hyperlink ref="F15" r:id="rId98" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E6B041A7-9A18-4D6C-986F-3B9E0A695E43}"/>
-    <hyperlink ref="B16" r:id="rId99" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{FFF5CD49-0E62-4F84-A2FF-661B874A68F9}"/>
-    <hyperlink ref="D16" r:id="rId100" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{F39A0A11-DBDB-4B6F-A7A3-48EF9BA96CBE}"/>
-    <hyperlink ref="G16" r:id="rId101" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{796D5959-7D06-461C-A72C-56198C3D54DE}"/>
-    <hyperlink ref="E16" r:id="rId102" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{1E834388-067A-4180-B15E-140C218A9ADA}"/>
-    <hyperlink ref="H16" r:id="rId103" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{70D172EB-9750-42E6-9DF8-4D6C68399C31}"/>
-    <hyperlink ref="C16" r:id="rId104" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{DE7DF6C9-B278-455E-B205-054A335514FD}"/>
-    <hyperlink ref="F16" r:id="rId105" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{13EF21C1-BD7E-40AF-AAB6-E5ADB4588238}"/>
-    <hyperlink ref="B17" r:id="rId106" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{3FED6B4C-8EC3-4642-B6E2-CD96CE9E4DCD}"/>
-    <hyperlink ref="D17" r:id="rId107" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{30590572-C973-4C5E-9E59-27D2FF5E326A}"/>
-    <hyperlink ref="G17" r:id="rId108" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{7EA58C71-117A-4453-8FA6-AF23F8D21076}"/>
-    <hyperlink ref="E17" r:id="rId109" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D4C3804E-87BA-437C-B0BA-CAC7DDECBB0F}"/>
-    <hyperlink ref="H17" r:id="rId110" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5C00BBE8-B296-4C40-BD21-33234B738E15}"/>
-    <hyperlink ref="C17" r:id="rId111" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{35534DCC-85EF-46F2-9ACE-FF12B5465F52}"/>
-    <hyperlink ref="F17" r:id="rId112" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{427C7346-8644-4E58-B6B1-51B9C707011C}"/>
-    <hyperlink ref="B18" r:id="rId113" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{E06A75EF-8B5C-4345-9754-FE742F57754D}"/>
-    <hyperlink ref="D18" r:id="rId114" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{25574AAD-FAB4-42F9-AC16-3CD4461261DD}"/>
-    <hyperlink ref="G18" r:id="rId115" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{E1D8BAF3-E148-4FA2-B4D6-7B0512D7501C}"/>
-    <hyperlink ref="E18" r:id="rId116" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{76109AD7-08D0-4CD3-9A8A-5DF6821BE6F0}"/>
-    <hyperlink ref="H18" r:id="rId117" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{ADB7F3D0-4D4D-44BC-AE06-10E02AAE2C39}"/>
-    <hyperlink ref="C18" r:id="rId118" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{354C7527-3F1C-4866-8553-5E751C0C03F4}"/>
-    <hyperlink ref="F18" r:id="rId119" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{AE2A0438-83BE-4C01-911B-01A8605CD1B8}"/>
-    <hyperlink ref="B19" r:id="rId120" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{EA4CD4BC-0FCD-4BEC-87A5-5FDE2C7ADF7A}"/>
-    <hyperlink ref="D19" r:id="rId121" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{BD13236D-C1AC-487A-9857-7E7D985E0BC1}"/>
-    <hyperlink ref="G19" r:id="rId122" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{1CEB5D4A-C23F-4ABA-B9E7-7794C0B2A850}"/>
-    <hyperlink ref="E19" r:id="rId123" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{5EDE8EE5-0466-4619-9723-75F63F401521}"/>
-    <hyperlink ref="H19" r:id="rId124" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{07DBCF5D-015E-46EA-8E86-4CF71174CAE0}"/>
-    <hyperlink ref="C19" r:id="rId125" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{595BA7D6-991E-4E92-AD81-777A3E94066F}"/>
-    <hyperlink ref="F19" r:id="rId126" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{7E58557E-58DC-4A51-BC61-5EB6ABF89445}"/>
-    <hyperlink ref="B20" r:id="rId127" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{E7758CC1-2302-42C0-A59A-82FCC98C4135}"/>
-    <hyperlink ref="D20" r:id="rId128" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{E2D5C100-A2CD-4406-87C5-F73C0D26E9AF}"/>
-    <hyperlink ref="G20" r:id="rId129" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{87724920-F512-4B87-ADF8-5136ADBF9AC2}"/>
-    <hyperlink ref="E20" r:id="rId130" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{85FDDE50-B43E-4D8F-8885-51291FD2161C}"/>
-    <hyperlink ref="H20" r:id="rId131" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{22EFFFF0-F722-4943-A355-5719E8B7EA71}"/>
-    <hyperlink ref="C20" r:id="rId132" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{B8CEDA44-00F1-4712-BC87-7A75F076566D}"/>
-    <hyperlink ref="F20" r:id="rId133" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F2379AE1-8AB0-444A-960A-FE38A60C1AAE}"/>
-    <hyperlink ref="B21" r:id="rId134" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{64A48762-6F4C-4202-825F-5579B90FFCB0}"/>
-    <hyperlink ref="D21" r:id="rId135" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{3B2635F7-EA61-4E3E-8D9C-E9FBA36CFC79}"/>
-    <hyperlink ref="G21" r:id="rId136" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{56BB524B-8F3E-4C9D-981C-F32438E24434}"/>
-    <hyperlink ref="E21" r:id="rId137" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{1F894FCD-A7F8-4469-B8E9-615F22A7D31E}"/>
-    <hyperlink ref="H21" r:id="rId138" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{1D1584F7-6078-4CD9-9F86-7791D3835BF1}"/>
-    <hyperlink ref="C21" r:id="rId139" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{9DFE7914-E974-4747-82BC-FBCC9BD0C4CA}"/>
-    <hyperlink ref="F21" r:id="rId140" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{02DE7248-7DF8-4577-8B9E-A7D6373E0B07}"/>
-    <hyperlink ref="B22" r:id="rId141" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{8A8D667A-F9D6-4A37-998E-975E6D25F77D}"/>
-    <hyperlink ref="D22" r:id="rId142" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2D937BDF-E066-49C2-A0B0-073704665DD3}"/>
-    <hyperlink ref="G22" r:id="rId143" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{827D8597-CBA5-486D-B6E1-5A7A66952C04}"/>
-    <hyperlink ref="E22" r:id="rId144" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{7879F788-3AD6-42C9-889C-E74ED20CA31B}"/>
-    <hyperlink ref="H22" r:id="rId145" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{B79C8A81-57C1-458D-BE53-B4013C47A146}"/>
-    <hyperlink ref="C22" r:id="rId146" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{8A957121-B252-4954-BF66-81CE72E246F0}"/>
-    <hyperlink ref="F22" r:id="rId147" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{58425FE8-279F-48CA-AC8B-D2303DE1D169}"/>
-    <hyperlink ref="B23" r:id="rId148" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{AF811438-4606-412A-874A-33577732A50C}"/>
-    <hyperlink ref="D23" r:id="rId149" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{19416631-1D54-46EB-B1BA-1837234F9118}"/>
-    <hyperlink ref="G23" r:id="rId150" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{514A55A6-FF80-4FE4-85D2-A594187EB644}"/>
-    <hyperlink ref="E23" r:id="rId151" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{0C63EE7E-652C-4376-9267-DF68D2910736}"/>
-    <hyperlink ref="H23" r:id="rId152" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E53EABE4-348F-4FB5-A7BF-B7989447A861}"/>
-    <hyperlink ref="C23" r:id="rId153" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{CAA078DE-41FF-48A8-AA59-EAE4845F675C}"/>
-    <hyperlink ref="F23" r:id="rId154" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{390EF12F-3120-4C7F-BAEC-6C3042E6908B}"/>
-    <hyperlink ref="B24" r:id="rId155" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{D5E804B8-F9E0-43F1-AA2C-B4AF983AB7B8}"/>
-    <hyperlink ref="D24" r:id="rId156" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{DF7C432D-CDE3-481A-9040-D9163C7FDFB3}"/>
-    <hyperlink ref="G24" r:id="rId157" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{48EFB8B6-C61B-4A44-87DE-B9D9610683DE}"/>
-    <hyperlink ref="E24" r:id="rId158" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{021887A6-5E6E-43E8-BABD-ABA89E529EA9}"/>
-    <hyperlink ref="H24" r:id="rId159" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{6E9997D5-B3CC-4878-A029-4209F0E009E7}"/>
-    <hyperlink ref="C24" r:id="rId160" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6C57EC10-FD67-472B-A19C-4DDBDB41516F}"/>
-    <hyperlink ref="F24" r:id="rId161" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{DEEA38A8-FFFE-4FC1-B5B6-401D72C6627F}"/>
-    <hyperlink ref="B25" r:id="rId162" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{D4229FC5-0302-45FF-BF83-221C23A98DBE}"/>
-    <hyperlink ref="D25" r:id="rId163" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{3606DFBA-9F86-4283-83A5-08514FE3D10E}"/>
-    <hyperlink ref="G25" r:id="rId164" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3E6B0CB4-13C2-427C-B956-79F0D6E0222D}"/>
-    <hyperlink ref="E25" r:id="rId165" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D242DDED-3633-4DC6-B8FB-87111D783601}"/>
-    <hyperlink ref="H25" r:id="rId166" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{009D20BC-F4D8-4741-B828-C342D30DBF20}"/>
-    <hyperlink ref="C25" r:id="rId167" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{39159DD6-E0ED-43EA-9926-D694C668CCF8}"/>
-    <hyperlink ref="F25" r:id="rId168" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{D904B1A2-0DFB-4C1A-8B25-B807623148B3}"/>
-    <hyperlink ref="B26" r:id="rId169" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{0AD5C7BF-79E8-4654-BCA5-8CE2ADBC3509}"/>
-    <hyperlink ref="D26" r:id="rId170" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{5CBF48B0-3027-44C1-AD8A-1446D2717275}"/>
-    <hyperlink ref="G26" r:id="rId171" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{7E2B8146-DEC2-4A54-A4E6-B290CBEA301E}"/>
-    <hyperlink ref="E26" r:id="rId172" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{99F40436-34F3-4F03-8198-8C7FB95F7A33}"/>
-    <hyperlink ref="H26" r:id="rId173" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{EE55B56C-DEB2-47B9-8B61-6CD6FDD4265C}"/>
-    <hyperlink ref="C26" r:id="rId174" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{BF18E1E3-E99C-4A32-AD66-218405983DC6}"/>
-    <hyperlink ref="F26" r:id="rId175" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{669BE368-A6CC-4D42-AB08-DA9B51AC0180}"/>
+    <hyperlink ref="B3" r:id="rId1" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{2098A1A6-8889-4C92-A3CB-A2E55B6D3D8E}"/>
+    <hyperlink ref="D3" r:id="rId2" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{9EAA8D1F-7CF7-41EE-88AB-EDBE86EB076D}"/>
+    <hyperlink ref="G3" r:id="rId3" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{DBC6DD3B-9BC7-4C10-88FF-2B5167967149}"/>
+    <hyperlink ref="E3" r:id="rId4" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{FCA2616A-D863-4882-BB15-C4B378E280F5}"/>
+    <hyperlink ref="H3" r:id="rId5" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{CB97AE68-2BAC-451B-BF23-79219E5587D6}"/>
+    <hyperlink ref="C3" r:id="rId6" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{BCEF86E2-ECE2-4E4D-8E7B-AA56CBC06281}"/>
+    <hyperlink ref="F3" r:id="rId7" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E050DEF6-1EC3-40E7-870C-497C15C493B2}"/>
+    <hyperlink ref="B4" r:id="rId8" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A8547C96-C922-4DCC-8B56-1A75D8CDBCFD}"/>
+    <hyperlink ref="D4" r:id="rId9" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{FED3049D-2DB4-4448-903E-999F0CEFF9EE}"/>
+    <hyperlink ref="G4" r:id="rId10" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{AF3FABA1-634F-45B4-8DFC-CDF64921E8AC}"/>
+    <hyperlink ref="E4" r:id="rId11" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D8916A59-BB8F-45DA-BA5B-ED486AF5EE96}"/>
+    <hyperlink ref="H4" r:id="rId12" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{B46C0957-C280-46CF-8828-617816058567}"/>
+    <hyperlink ref="C4" r:id="rId13" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{352DB843-6A08-4252-870F-B50251198DEC}"/>
+    <hyperlink ref="F4" r:id="rId14" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{05A76920-1938-4725-AF2E-8DC460F3316D}"/>
+    <hyperlink ref="B5" r:id="rId15" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{250976D2-6154-4E2A-B642-B72AD64821E8}"/>
+    <hyperlink ref="D5" r:id="rId16" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{38324CE7-95D8-46CE-BC43-70CCC5D8DF2A}"/>
+    <hyperlink ref="G5" r:id="rId17" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{EDFC2F6F-269C-4DF6-A765-5094DA3058B5}"/>
+    <hyperlink ref="E5" r:id="rId18" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{76626B7A-517E-4F0F-B4DC-D1296A83E3F4}"/>
+    <hyperlink ref="H5" r:id="rId19" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{FD7A051E-946E-47BD-9768-79228A37F43C}"/>
+    <hyperlink ref="C5" r:id="rId20" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{E950A481-D16C-4395-AEE5-180C18291C9D}"/>
+    <hyperlink ref="F5" r:id="rId21" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A38F6D4C-C630-4340-A9E7-750B603ADF0B}"/>
+    <hyperlink ref="B6" r:id="rId22" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{FF1DA584-0E12-4B15-A181-CF9F4CBE527E}"/>
+    <hyperlink ref="D6" r:id="rId23" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{C6ED564B-75AA-4ACC-B302-58CFA857765E}"/>
+    <hyperlink ref="G6" r:id="rId24" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3DA03DC2-A0D0-4B06-AA76-6E0B658079ED}"/>
+    <hyperlink ref="E6" r:id="rId25" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{106C37AE-A68E-4F48-A07E-7EAA64E12229}"/>
+    <hyperlink ref="H6" r:id="rId26" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E147D72E-931C-45E9-A252-9B5FF9CF975A}"/>
+    <hyperlink ref="C6" r:id="rId27" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{343CC96C-0DCE-4C22-8B2C-023A73743B9C}"/>
+    <hyperlink ref="F6" r:id="rId28" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{5CEF0F43-E33B-4F38-B207-5DE2909D0E32}"/>
+    <hyperlink ref="B7" r:id="rId29" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{6C3757A0-8C07-4470-8C51-9CE3B6A56ACD}"/>
+    <hyperlink ref="D7" r:id="rId30" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{10092940-59A8-4EF8-9DFC-FFD46CC42D10}"/>
+    <hyperlink ref="G7" r:id="rId31" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{13423C3A-A10F-4205-A0ED-F2765660CB09}"/>
+    <hyperlink ref="E7" r:id="rId32" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{FD30451D-AD7B-43BD-A1E8-DC9026511FB3}"/>
+    <hyperlink ref="H7" r:id="rId33" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{F9C76BBD-A827-41C3-B699-02BFE13CB144}"/>
+    <hyperlink ref="C7" r:id="rId34" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{3D44B294-9CB3-4D8C-94EA-0712F35984D4}"/>
+    <hyperlink ref="F7" r:id="rId35" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{B0E4B923-35A2-4832-BC3E-91AA92600FBD}"/>
+    <hyperlink ref="B8" r:id="rId36" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{01B0FD6F-CC23-4D00-9D9E-76F1E1AEDBD0}"/>
+    <hyperlink ref="D8" r:id="rId37" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{B5F3EE9B-875A-4A65-A261-3B24386685B8}"/>
+    <hyperlink ref="G8" r:id="rId38" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{E8318C55-09B2-493E-974F-1CF36998BA66}"/>
+    <hyperlink ref="E8" r:id="rId39" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A30C6BD3-67C3-4FA7-AFA4-2B517ABD5F04}"/>
+    <hyperlink ref="H8" r:id="rId40" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{FB9D9197-6ED3-4753-B25F-4AC2BBC19043}"/>
+    <hyperlink ref="C8" r:id="rId41" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{3495E31B-F66B-4054-AF05-0BD3FFB7BF9C}"/>
+    <hyperlink ref="F8" r:id="rId42" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{0D7C3972-708B-40CD-B784-03F46CD089BD}"/>
+    <hyperlink ref="B9" r:id="rId43" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{6BC05550-BC9B-4846-8497-41B623C90180}"/>
+    <hyperlink ref="D9" r:id="rId44" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{844EA776-4BB8-4E32-93F8-397C8B5EED8B}"/>
+    <hyperlink ref="G9" r:id="rId45" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{39273C42-E20D-4F46-8ADB-5B533107BD2E}"/>
+    <hyperlink ref="E9" r:id="rId46" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D624BCB2-2F04-41B3-9E4D-5A98C308BA1E}"/>
+    <hyperlink ref="H9" r:id="rId47" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{B6A9F8CD-90ED-44A9-B8C7-CEC09D2BCB38}"/>
+    <hyperlink ref="C9" r:id="rId48" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{D7E5BFA7-2477-4334-83F6-F83C0606EB0D}"/>
+    <hyperlink ref="F9" r:id="rId49" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{701F7D0D-BE65-4455-9589-AAED281D0342}"/>
+    <hyperlink ref="B10" r:id="rId50" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{619373AF-7C61-474D-BD8F-ED9F06BE4505}"/>
+    <hyperlink ref="D10" r:id="rId51" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{CD6EB295-4333-4F74-9619-7B7ABA121619}"/>
+    <hyperlink ref="G10" r:id="rId52" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{5F5E4D8E-9A4D-424C-9A71-E223145814AA}"/>
+    <hyperlink ref="E10" r:id="rId53" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{C2D365FE-0441-4D9B-A7ED-4AAB5FDD3B9E}"/>
+    <hyperlink ref="H10" r:id="rId54" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5613175A-3F78-4156-B335-CE769839F3CF}"/>
+    <hyperlink ref="C10" r:id="rId55" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A326096C-1175-41AD-BCF1-66DC5D1B78FE}"/>
+    <hyperlink ref="F10" r:id="rId56" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C02C81D8-59C5-4CDD-B62C-9AF4F20A8A6C}"/>
+    <hyperlink ref="B11" r:id="rId57" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{3A6DA921-DBCD-4035-9876-3BFC3C1604B6}"/>
+    <hyperlink ref="D11" r:id="rId58" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{94F8DAD5-B42F-40E2-B1D7-D80D84B33543}"/>
+    <hyperlink ref="G11" r:id="rId59" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{77E9140C-0EA5-4A41-9784-8D472DE3C2B1}"/>
+    <hyperlink ref="E11" r:id="rId60" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{4299E878-8E8A-428A-9046-C997F0269E03}"/>
+    <hyperlink ref="H11" r:id="rId61" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{4723CA69-5BF8-4A4B-8267-F3ACFA391F3C}"/>
+    <hyperlink ref="C11" r:id="rId62" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A40A325B-7D4A-4394-9C22-935AA91F4AD7}"/>
+    <hyperlink ref="F11" r:id="rId63" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{9496E075-C7A0-49C6-8EF2-27618CDD47D3}"/>
+    <hyperlink ref="B12" r:id="rId64" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{48ED178E-576D-4FE2-9261-52E00F8095B7}"/>
+    <hyperlink ref="D12" r:id="rId65" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{8D6973E4-22A4-49E7-BF52-BB5A93EFE469}"/>
+    <hyperlink ref="G12" r:id="rId66" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{459AECEF-7BB9-43A4-9907-4B349F578D90}"/>
+    <hyperlink ref="E12" r:id="rId67" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{397F7BE1-3330-4F0F-B7FF-BAA8A473D4D3}"/>
+    <hyperlink ref="H12" r:id="rId68" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{268FDFB4-B5D0-499A-835E-984AC9AF6E93}"/>
+    <hyperlink ref="C12" r:id="rId69" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{5C054285-8A65-44A5-8D9D-36D87E227862}"/>
+    <hyperlink ref="F12" r:id="rId70" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{DD8939FB-5003-4B8A-AB10-4A75C98835A6}"/>
+    <hyperlink ref="B13" r:id="rId71" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{67CD9936-68E3-48D8-82E8-13946174F58F}"/>
+    <hyperlink ref="D13" r:id="rId72" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{A7B80407-4A1F-423C-8D21-86FB57E2574D}"/>
+    <hyperlink ref="G13" r:id="rId73" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C6B54D5D-59AC-4D5E-94C6-D1784C9F9E30}"/>
+    <hyperlink ref="E13" r:id="rId74" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E35AC702-AB7D-43D6-AA9B-D692621C0CA0}"/>
+    <hyperlink ref="H13" r:id="rId75" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5173B969-834B-47DE-A35E-547B7DB21A05}"/>
+    <hyperlink ref="C13" r:id="rId76" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{121BA981-889A-474D-A7CB-6703A006D212}"/>
+    <hyperlink ref="F13" r:id="rId77" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{56C692DD-5B6F-4781-834A-4B060DDA9382}"/>
+    <hyperlink ref="B14" r:id="rId78" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{36C9018F-7B2A-4710-8779-79CFB61BA540}"/>
+    <hyperlink ref="D14" r:id="rId79" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D0CADD27-E665-4D5C-B9FC-6A1F52E74A52}"/>
+    <hyperlink ref="G14" r:id="rId80" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{4D23686B-C993-4BC2-8A4D-25E709D734FE}"/>
+    <hyperlink ref="E14" r:id="rId81" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{C7C090F8-0274-47E7-87BB-458914A781D2}"/>
+    <hyperlink ref="H14" r:id="rId82" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{448CF223-F09F-4B3F-A43C-6D764BBCF623}"/>
+    <hyperlink ref="C14" r:id="rId83" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{34DAFD5D-EC0A-421F-B329-AC164A7172B1}"/>
+    <hyperlink ref="F14" r:id="rId84" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{DFDB4905-7093-4C01-A03D-F02F620303AD}"/>
+    <hyperlink ref="B15" r:id="rId85" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{87E4291E-6331-472E-ADD4-1D6E923A0490}"/>
+    <hyperlink ref="D15" r:id="rId86" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{28DDF373-2708-48F5-B42F-0F7D41CFACA0}"/>
+    <hyperlink ref="G15" r:id="rId87" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{45AF10FD-715F-424E-B4DD-C2C4ECC05DC7}"/>
+    <hyperlink ref="E15" r:id="rId88" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{AFB1243B-0C11-48CC-AD0B-04A64E608D37}"/>
+    <hyperlink ref="H15" r:id="rId89" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E1D0107F-A51D-431D-826A-96EE83F82D10}"/>
+    <hyperlink ref="C15" r:id="rId90" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C794848D-DEF4-4935-94A7-142EF140C27B}"/>
+    <hyperlink ref="F15" r:id="rId91" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{15FF5958-4F08-4CB4-82EF-DA9EFE83B742}"/>
+    <hyperlink ref="B16" r:id="rId92" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{27CAA26C-245C-4133-AA97-B02BAABBEA3C}"/>
+    <hyperlink ref="D16" r:id="rId93" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{54F21B84-6B34-4461-9818-63651934F699}"/>
+    <hyperlink ref="G16" r:id="rId94" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{030DB55D-CCF6-4FC7-AE94-4FE01EB48DB7}"/>
+    <hyperlink ref="E16" r:id="rId95" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{0426DD0E-19E0-4AFD-B584-38D24301B519}"/>
+    <hyperlink ref="H16" r:id="rId96" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{85A59889-912C-4062-9941-5144D4EC8098}"/>
+    <hyperlink ref="C16" r:id="rId97" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{9830EE91-67D8-4628-AC61-3887015B6C83}"/>
+    <hyperlink ref="F16" r:id="rId98" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C2A8D44E-8F43-428F-A19E-24B544363695}"/>
+    <hyperlink ref="B17" r:id="rId99" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{7BA001F9-E81D-4980-923D-DF2519E63CD9}"/>
+    <hyperlink ref="D17" r:id="rId100" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{A03629CE-FD91-49FB-BBC2-72DFCC00098D}"/>
+    <hyperlink ref="G17" r:id="rId101" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{49FAC30B-EB1D-45F1-845D-5F11DFEC9C0E}"/>
+    <hyperlink ref="E17" r:id="rId102" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{188A6A09-9ADF-41AD-BE22-C0F5ED3D5EE3}"/>
+    <hyperlink ref="H17" r:id="rId103" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{1F3B83B5-77AD-4D82-9170-9BF0A5B2B28F}"/>
+    <hyperlink ref="C17" r:id="rId104" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{938BA5CC-C3DB-4E69-AFB7-FDC8EBF1E2E9}"/>
+    <hyperlink ref="F17" r:id="rId105" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F2C514A6-75FE-400A-A5F7-94256B16D11B}"/>
+    <hyperlink ref="B18" r:id="rId106" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{0F07ADFB-21CE-465D-96C3-CE1C00008903}"/>
+    <hyperlink ref="D18" r:id="rId107" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{31F0EF54-D071-40D9-8E58-6FFAF87E78F3}"/>
+    <hyperlink ref="G18" r:id="rId108" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{D0424B80-BAB1-4BAA-B114-C8427E452F4C}"/>
+    <hyperlink ref="E18" r:id="rId109" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{ACA73AE9-0CCF-487D-B7DF-0025FD621B07}"/>
+    <hyperlink ref="H18" r:id="rId110" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{A01F75DE-47BE-4302-99D4-5F42CD9619AF}"/>
+    <hyperlink ref="C18" r:id="rId111" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{BC0D388A-7F38-426B-9DE6-F12EA01BB678}"/>
+    <hyperlink ref="F18" r:id="rId112" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{4AA03DAB-799D-46AE-B13F-1730F652E41B}"/>
+    <hyperlink ref="B19" r:id="rId113" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{30692E3E-53EB-4529-80F6-7ED39BA0B4DC}"/>
+    <hyperlink ref="D19" r:id="rId114" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{0AB3B44E-A51D-4B70-AF79-D7C7AE842490}"/>
+    <hyperlink ref="G19" r:id="rId115" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{86DE956D-8A8C-4F12-96B3-DC4D6DC46406}"/>
+    <hyperlink ref="E19" r:id="rId116" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F03549E5-B834-43DC-B085-88D1D882E4BA}"/>
+    <hyperlink ref="H19" r:id="rId117" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{F6491E77-460C-49FC-BDA9-C53A29FFA9FE}"/>
+    <hyperlink ref="C19" r:id="rId118" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{E7DDC3C1-8756-4E6F-9AFC-36BE1A9607E3}"/>
+    <hyperlink ref="F19" r:id="rId119" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{B70B2D1F-3571-4E92-AB37-84EF75BA8A64}"/>
+    <hyperlink ref="B20" r:id="rId120" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C2DAE2E5-B540-434B-965C-892D1A1AD981}"/>
+    <hyperlink ref="D20" r:id="rId121" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{7B6804BC-1A03-4945-8AA7-7D1CAB3B251E}"/>
+    <hyperlink ref="G20" r:id="rId122" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{5FFB9860-8BDB-40F3-9F6E-DD2A718DFA52}"/>
+    <hyperlink ref="E20" r:id="rId123" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{0D6F8698-56A6-44C3-895D-E1CEF41021E7}"/>
+    <hyperlink ref="H20" r:id="rId124" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E06BC4A8-2BA0-4044-855D-231DC3CBE1BC}"/>
+    <hyperlink ref="C20" r:id="rId125" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{60AABD7A-ACA7-403B-893E-C64E0BEECDCE}"/>
+    <hyperlink ref="F20" r:id="rId126" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{178C74E5-2E9E-44FF-B111-AFFD0A399EFA}"/>
+    <hyperlink ref="B2" r:id="rId127" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{73E79908-50FD-48BA-99A9-7E9401523EA3}"/>
+    <hyperlink ref="D2" r:id="rId128" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{EE7DA335-26CE-49F7-9491-0D7BC15BBBEB}"/>
+    <hyperlink ref="G2" r:id="rId129" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3A869268-FCFD-4361-8026-93A81C74A8BF}"/>
+    <hyperlink ref="E2" r:id="rId130" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{74B92ECE-382C-4533-B495-EE482E18CC44}"/>
+    <hyperlink ref="H2" r:id="rId131" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5A9A6CA3-829B-4476-8709-BBD86CE57582}"/>
+    <hyperlink ref="C2" r:id="rId132" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{E95C3346-5BB9-48BE-B1AD-03416E780588}"/>
+    <hyperlink ref="F2" r:id="rId133" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E7192020-943B-4345-99A3-24CE1248E5DE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId176"/>
-  <drawing r:id="rId177"/>
+  <pageSetup orientation="portrait" r:id="rId134"/>
+  <drawing r:id="rId135"/>
   <tableParts count="1">
-    <tablePart r:id="rId178"/>
+    <tablePart r:id="rId136"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC3F3FC-17EF-4D6A-9290-8FAFFC789915}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.5546875" customWidth="1"/>
@@ -15967,7 +15399,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -15984,7 +15416,7 @@
     </row>
     <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B2" s="13">
         <v>0</v>
@@ -16002,7 +15434,7 @@
     </row>
     <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B3" s="14">
         <v>0</v>
@@ -16020,7 +15452,7 @@
     </row>
     <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B4" s="14">
         <v>0</v>
@@ -16038,7 +15470,7 @@
     </row>
     <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B5" s="14">
         <v>0</v>
@@ -16056,7 +15488,7 @@
     </row>
     <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B6" s="14">
         <v>5</v>
@@ -16074,7 +15506,7 @@
     </row>
     <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B7" s="14">
         <v>5</v>
@@ -16092,7 +15524,7 @@
     </row>
     <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B8" s="14">
         <v>5</v>
@@ -16110,7 +15542,7 @@
     </row>
     <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B9" s="14">
         <v>6</v>
@@ -16128,7 +15560,7 @@
     </row>
     <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B10" s="14">
         <v>6</v>
@@ -16146,7 +15578,7 @@
     </row>
     <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B11" s="14">
         <v>12</v>
@@ -16163,7 +15595,7 @@
     </row>
     <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B12" s="14">
         <v>22</v>
@@ -16181,7 +15613,7 @@
     </row>
     <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B13" s="14">
         <v>27</v>
@@ -16199,7 +15631,7 @@
     </row>
     <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B14" s="14">
         <v>27</v>
@@ -16217,7 +15649,7 @@
     </row>
     <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B15" s="14">
         <v>44</v>
@@ -16235,7 +15667,7 @@
     </row>
     <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B16" s="14">
         <v>57</v>
@@ -16253,7 +15685,7 @@
     </row>
     <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B17" s="14">
         <v>68</v>
@@ -16271,7 +15703,7 @@
     </row>
     <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B18" s="14">
         <v>80</v>
@@ -16289,7 +15721,7 @@
     </row>
     <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B19" s="14">
         <v>92</v>
@@ -16307,7 +15739,7 @@
     </row>
     <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B20" s="14">
         <v>97</v>
@@ -16325,7 +15757,7 @@
     </row>
     <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="B21" s="14">
         <v>98</v>
@@ -16337,6 +15769,24 @@
         <v>14</v>
       </c>
       <c r="E21" s="14">
+        <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B22" s="14">
+        <v>98</v>
+      </c>
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>14</v>
+      </c>
+      <c r="E22" s="14">
         <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
         <v>113</v>
       </c>

--- a/data/SDET_SQA_DATA.xlsx
+++ b/data/SDET_SQA_DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WHSU\Desktop\Workspace\CycleView\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DF7603-9865-4C6A-82AB-E701A58DD6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CE6485-1A6B-4AFA-A372-3854E0B3F401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{EB11FF79-EF06-B64E-AA6A-0CFF391A8BD1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{EB11FF79-EF06-B64E-AA6A-0CFF391A8BD1}"/>
   </bookViews>
   <sheets>
     <sheet name="TestAutomationProgress" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="103">
   <si>
     <t>TODO (P1)</t>
   </si>
@@ -345,6 +345,12 @@
   </si>
   <si>
     <t>26W11</t>
+  </si>
+  <si>
+    <t>y26w14</t>
+  </si>
+  <si>
+    <t>26W12</t>
   </si>
 </sst>
 </file>
@@ -1082,9 +1088,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$22</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>25W40</c:v>
                 </c:pt>
@@ -1147,16 +1153,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>26W11</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>26W12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$B$2:$B$22</c:f>
+              <c:f>TestAutomationProgress!$B$2:$B$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>15</c:v>
                 </c:pt>
@@ -1218,6 +1227,9 @@
                   <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
@@ -1315,9 +1327,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$22</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>25W40</c:v>
                 </c:pt>
@@ -1380,16 +1392,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>26W11</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>26W12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$C$2:$C$22</c:f>
+              <c:f>TestAutomationProgress!$C$2:$C$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>14</c:v>
                 </c:pt>
@@ -1451,6 +1466,9 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1548,9 +1566,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$22</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>25W40</c:v>
                 </c:pt>
@@ -1613,16 +1631,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>26W11</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>26W12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$D$2:$D$22</c:f>
+              <c:f>TestAutomationProgress!$D$2:$D$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>219</c:v>
                 </c:pt>
@@ -1684,6 +1705,9 @@
                   <c:v>161</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>160</c:v>
                 </c:pt>
               </c:numCache>
@@ -2179,7 +2203,7 @@
                   <c:v>860</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>186</c:v>
+                  <c:v>460</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2497,7 +2521,7 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2706,7 +2730,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>13</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2861,7 +2885,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>23</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3018,7 +3042,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>375</c:v>
+                  <c:v>91</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3624,9 +3648,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$35</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$36</c:f>
               <c:strCache>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -3728,16 +3752,19 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>26W11</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>26W12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$B$2:$B$35</c:f>
+              <c:f>'SOVA-TestResult'!$B$2:$B$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>38</c:v>
                 </c:pt>
@@ -3815,6 +3842,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>694</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3908,9 +3938,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$35</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$36</c:f>
               <c:strCache>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4012,16 +4042,19 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>26W11</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>26W12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$C$2:$C$35</c:f>
+              <c:f>'SOVA-TestResult'!$C$2:$C$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4098,6 +4131,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4135,9 +4171,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$35</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$36</c:f>
               <c:strCache>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4239,16 +4275,19 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>26W11</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>26W12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$D$2:$D$35</c:f>
+              <c:f>'SOVA-TestResult'!$D$2:$D$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4326,6 +4365,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4362,9 +4404,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$35</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$36</c:f>
               <c:strCache>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4466,16 +4508,19 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>26W11</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>26W12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$E$2:$E$35</c:f>
+              <c:f>'SOVA-TestResult'!$E$2:$E$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
                 </c:pt>
@@ -4552,6 +4597,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4663,9 +4711,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$35</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$36</c:f>
               <c:strCache>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4767,16 +4815,19 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>26W11</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>26W12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$F$2:$F$35</c:f>
+              <c:f>'SOVA-TestResult'!$F$2:$F$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>11</c:v>
                 </c:pt>
@@ -4854,6 +4905,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4893,9 +4947,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$35</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$36</c:f>
               <c:strCache>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4997,16 +5051,19 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>26W11</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>26W12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$G$2:$G$35</c:f>
+              <c:f>'SOVA-TestResult'!$G$2:$G$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5084,6 +5141,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>485</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5125,9 +5185,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$35</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$36</c:f>
               <c:strCache>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -5229,16 +5289,19 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>26W11</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>26W12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$H$2:$H$35</c:f>
+              <c:f>'SOVA-TestResult'!$H$2:$H$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
                   <c:v>54</c:v>
                 </c:pt>
@@ -5316,6 +5379,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>703</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>485</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5818,10 +5884,10 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>10</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5997,7 +6063,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6346,7 +6412,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>7</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6689,10 +6755,10 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>7</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>7</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6864,10 +6930,10 @@
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>9</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>27</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7240,9 +7306,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$20</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -7299,16 +7365,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>y26w12</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>y26w14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$B$2:$B$20</c:f>
+              <c:f>'SOVA-BugTrend'!$B$2:$B$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>27</c:v>
                 </c:pt>
@@ -7340,31 +7409,34 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="16">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>9</c:v>
-                </c:pt>
                 <c:pt idx="18">
-                  <c:v>7</c:v>
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7458,9 +7530,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$20</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -7517,16 +7589,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>y26w12</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>y26w14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$C$2:$C$20</c:f>
+              <c:f>'SOVA-BugTrend'!$C$2:$C$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7582,6 +7657,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -7676,9 +7754,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$20</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -7735,16 +7813,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>y26w12</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>y26w14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$D$2:$D$20</c:f>
+              <c:f>'SOVA-BugTrend'!$D$2:$D$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7800,6 +7881,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -7894,9 +7978,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$20</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -7953,18 +8037,21 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>y26w12</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>y26w14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$E$2:$E$20</c:f>
+              <c:f>'SOVA-BugTrend'!$E$2:$E$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -8018,6 +8105,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -8055,9 +8145,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$20</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -8114,16 +8204,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>y26w12</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>y26w14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$F$2:$F$20</c:f>
+              <c:f>'SOVA-BugTrend'!$F$2:$F$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8179,6 +8272,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -8270,9 +8366,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$20</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -8329,16 +8425,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>y26w12</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>y26w14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$G$2:$G$20</c:f>
+              <c:f>'SOVA-BugTrend'!$G$2:$G$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>5</c:v>
                 </c:pt>
@@ -8370,31 +8469,34 @@
                   <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>39</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>31</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>29</c:v>
-                </c:pt>
                 <c:pt idx="13">
-                  <c:v>29</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>31</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>25</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>11</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>11</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2</c:v>
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8433,9 +8535,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$20</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -8492,16 +8594,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>y26w12</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>y26w14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$H$2:$H$20</c:f>
+              <c:f>'SOVA-BugTrend'!$H$2:$H$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
@@ -8554,9 +8659,12 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>9</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -8596,9 +8704,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$20</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -8655,18 +8763,21 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>y26w12</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>y26w14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$I$2:$I$20</c:f>
+              <c:f>'SOVA-BugTrend'!$I$2:$I$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>35</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>46</c:v>
@@ -8717,10 +8828,13 @@
                   <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>31</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>9</c:v>
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11652,13 +11766,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>171448</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>133348</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -11734,13 +11848,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>69662</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1057275</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>31562</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -11852,8 +11966,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}" name="Table2" displayName="Table2" ref="A1:E22" totalsRowShown="0" headerRowDxfId="35">
-  <autoFilter ref="A1:E22" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}" name="Table2" displayName="Table2" ref="A1:E23" totalsRowShown="0" headerRowDxfId="35">
+  <autoFilter ref="A1:E23" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F25F0D34-0297-4771-8BBB-350BCDD85D46}" name="Week"/>
     <tableColumn id="2" xr3:uid="{39CFCD12-3130-47A8-A140-DBF602F1743D}" name="Done"/>
@@ -11887,8 +12001,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}" name="Table3" displayName="Table3" ref="A1:H35" totalsRowShown="0" headerRowDxfId="31">
-  <autoFilter ref="A1:H35" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}" name="Table3" displayName="Table3" ref="A1:H36" totalsRowShown="0" headerRowDxfId="31">
+  <autoFilter ref="A1:H36" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{8103CDF3-74DC-4B31-821D-E20368EA5455}" name="Versions"/>
     <tableColumn id="2" xr3:uid="{6C3B261F-FA51-42D2-821A-F22633569372}" name="Passed"/>
@@ -11925,8 +12039,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}" name="Table5" displayName="Table5" ref="A1:I20" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17" totalsRowBorderDxfId="16" dataCellStyle="Hyperlink">
-  <autoFilter ref="A1:I20" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}" name="Table5" displayName="Table5" ref="A1:I21" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17" totalsRowBorderDxfId="16" dataCellStyle="Hyperlink">
+  <autoFilter ref="A1:I21" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{5BE08AE0-E0B5-4B46-9423-456B88C2D9BC}" name="Sprint" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{030F9647-4FC0-4C7E-9B3A-AB099CC59EBA}" name="To Do (0%)" dataDxfId="14" dataCellStyle="Hyperlink"/>
@@ -11945,8 +12059,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}" name="Table25" displayName="Table25" ref="A1:E22" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A1:E22" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}" name="Table25" displayName="Table25" ref="A1:E23" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E23" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{7070D9F2-0ED1-4F39-8D72-28B37C8E98F2}" name="Week" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{1173F443-CC27-4C6E-A432-BF66DB2A740E}" name="Done" dataDxfId="3"/>
@@ -12277,7 +12391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D733A42-966D-5F4E-B061-B304543CE88E}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.77734375" customWidth="1"/>
@@ -12677,6 +12791,23 @@
         <v>160</v>
       </c>
       <c r="E22" s="12">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23">
+        <v>37</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>160</v>
+      </c>
+      <c r="E23" s="12">
         <v>198</v>
       </c>
     </row>
@@ -13190,22 +13321,22 @@
         <v>93</v>
       </c>
       <c r="B19">
-        <v>186</v>
+        <v>460</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F19">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G19">
-        <v>375</v>
+        <v>91</v>
       </c>
       <c r="H19">
         <f>SUM(Table1[[#This Row],[Passed]:[Untested]])</f>
@@ -13224,7 +13355,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA6EDF6-834F-DA49-B3FC-BFE1673433AB}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
@@ -13999,6 +14130,33 @@
       <c r="H35" s="12">
         <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
         <v>703</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="A36" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>485</v>
+      </c>
+      <c r="H36" s="12">
+        <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -14569,7 +14727,7 @@
         <v>87</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -14584,11 +14742,11 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H21">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -14596,26 +14754,26 @@
         <v>93</v>
       </c>
       <c r="B22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H22" s="12">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -14630,7 +14788,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7487DEB-55FC-DC4E-A4B1-F7171B8F3237}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.21875" customWidth="1"/>
@@ -14686,7 +14844,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="5">
         <v>0</v>
@@ -14699,7 +14857,7 @@
       </c>
       <c r="I2" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18" thickBot="1">
@@ -14977,7 +15135,7 @@
         <v>48</v>
       </c>
       <c r="B12" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" s="5">
         <v>0</v>
@@ -14992,7 +15150,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H12" s="5">
         <v>1</v>
@@ -15007,7 +15165,7 @@
         <v>50</v>
       </c>
       <c r="B13" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" s="5">
         <v>0</v>
@@ -15022,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H13" s="5">
         <v>1</v>
@@ -15037,7 +15195,7 @@
         <v>51</v>
       </c>
       <c r="B14" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" s="5">
         <v>0</v>
@@ -15052,7 +15210,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H14" s="5">
         <v>1</v>
@@ -15067,7 +15225,7 @@
         <v>94</v>
       </c>
       <c r="B15" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" s="5">
         <v>0</v>
@@ -15082,7 +15240,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H15" s="5">
         <v>0</v>
@@ -15097,7 +15255,7 @@
         <v>95</v>
       </c>
       <c r="B16" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" s="5">
         <v>0</v>
@@ -15112,7 +15270,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H16" s="5">
         <v>2</v>
@@ -15127,7 +15285,7 @@
         <v>96</v>
       </c>
       <c r="B17" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C17" s="5">
         <v>0</v>
@@ -15142,7 +15300,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="5">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H17" s="5">
         <v>5</v>
@@ -15157,7 +15315,7 @@
         <v>97</v>
       </c>
       <c r="B18" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C18" s="5">
         <v>1</v>
@@ -15172,7 +15330,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="5">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H18" s="5">
         <v>8</v>
@@ -15187,7 +15345,7 @@
         <v>88</v>
       </c>
       <c r="B19" s="5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C19" s="5">
         <v>1</v>
@@ -15202,14 +15360,14 @@
         <v>1</v>
       </c>
       <c r="G19" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H19" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I19" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="18" thickBot="1">
@@ -15217,180 +15375,217 @@
         <v>98</v>
       </c>
       <c r="B20" s="5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D20" s="5">
         <v>0</v>
       </c>
       <c r="E20" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F20" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H20" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>9</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="18" thickBot="1">
+      <c r="A21" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="5">
+        <v>2</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5">
+        <v>0</v>
+      </c>
+      <c r="I21" s="15">
+        <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{2098A1A6-8889-4C92-A3CB-A2E55B6D3D8E}"/>
-    <hyperlink ref="D3" r:id="rId2" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{9EAA8D1F-7CF7-41EE-88AB-EDBE86EB076D}"/>
-    <hyperlink ref="G3" r:id="rId3" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{DBC6DD3B-9BC7-4C10-88FF-2B5167967149}"/>
-    <hyperlink ref="E3" r:id="rId4" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{FCA2616A-D863-4882-BB15-C4B378E280F5}"/>
-    <hyperlink ref="H3" r:id="rId5" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{CB97AE68-2BAC-451B-BF23-79219E5587D6}"/>
-    <hyperlink ref="C3" r:id="rId6" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{BCEF86E2-ECE2-4E4D-8E7B-AA56CBC06281}"/>
-    <hyperlink ref="F3" r:id="rId7" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E050DEF6-1EC3-40E7-870C-497C15C493B2}"/>
-    <hyperlink ref="B4" r:id="rId8" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A8547C96-C922-4DCC-8B56-1A75D8CDBCFD}"/>
-    <hyperlink ref="D4" r:id="rId9" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{FED3049D-2DB4-4448-903E-999F0CEFF9EE}"/>
-    <hyperlink ref="G4" r:id="rId10" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{AF3FABA1-634F-45B4-8DFC-CDF64921E8AC}"/>
-    <hyperlink ref="E4" r:id="rId11" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D8916A59-BB8F-45DA-BA5B-ED486AF5EE96}"/>
-    <hyperlink ref="H4" r:id="rId12" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{B46C0957-C280-46CF-8828-617816058567}"/>
-    <hyperlink ref="C4" r:id="rId13" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{352DB843-6A08-4252-870F-B50251198DEC}"/>
-    <hyperlink ref="F4" r:id="rId14" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{05A76920-1938-4725-AF2E-8DC460F3316D}"/>
-    <hyperlink ref="B5" r:id="rId15" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{250976D2-6154-4E2A-B642-B72AD64821E8}"/>
-    <hyperlink ref="D5" r:id="rId16" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{38324CE7-95D8-46CE-BC43-70CCC5D8DF2A}"/>
-    <hyperlink ref="G5" r:id="rId17" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{EDFC2F6F-269C-4DF6-A765-5094DA3058B5}"/>
-    <hyperlink ref="E5" r:id="rId18" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{76626B7A-517E-4F0F-B4DC-D1296A83E3F4}"/>
-    <hyperlink ref="H5" r:id="rId19" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{FD7A051E-946E-47BD-9768-79228A37F43C}"/>
-    <hyperlink ref="C5" r:id="rId20" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{E950A481-D16C-4395-AEE5-180C18291C9D}"/>
-    <hyperlink ref="F5" r:id="rId21" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A38F6D4C-C630-4340-A9E7-750B603ADF0B}"/>
-    <hyperlink ref="B6" r:id="rId22" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{FF1DA584-0E12-4B15-A181-CF9F4CBE527E}"/>
-    <hyperlink ref="D6" r:id="rId23" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{C6ED564B-75AA-4ACC-B302-58CFA857765E}"/>
-    <hyperlink ref="G6" r:id="rId24" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3DA03DC2-A0D0-4B06-AA76-6E0B658079ED}"/>
-    <hyperlink ref="E6" r:id="rId25" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{106C37AE-A68E-4F48-A07E-7EAA64E12229}"/>
-    <hyperlink ref="H6" r:id="rId26" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E147D72E-931C-45E9-A252-9B5FF9CF975A}"/>
-    <hyperlink ref="C6" r:id="rId27" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{343CC96C-0DCE-4C22-8B2C-023A73743B9C}"/>
-    <hyperlink ref="F6" r:id="rId28" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{5CEF0F43-E33B-4F38-B207-5DE2909D0E32}"/>
-    <hyperlink ref="B7" r:id="rId29" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{6C3757A0-8C07-4470-8C51-9CE3B6A56ACD}"/>
-    <hyperlink ref="D7" r:id="rId30" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{10092940-59A8-4EF8-9DFC-FFD46CC42D10}"/>
-    <hyperlink ref="G7" r:id="rId31" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{13423C3A-A10F-4205-A0ED-F2765660CB09}"/>
-    <hyperlink ref="E7" r:id="rId32" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{FD30451D-AD7B-43BD-A1E8-DC9026511FB3}"/>
-    <hyperlink ref="H7" r:id="rId33" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{F9C76BBD-A827-41C3-B699-02BFE13CB144}"/>
-    <hyperlink ref="C7" r:id="rId34" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{3D44B294-9CB3-4D8C-94EA-0712F35984D4}"/>
-    <hyperlink ref="F7" r:id="rId35" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{B0E4B923-35A2-4832-BC3E-91AA92600FBD}"/>
-    <hyperlink ref="B8" r:id="rId36" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{01B0FD6F-CC23-4D00-9D9E-76F1E1AEDBD0}"/>
-    <hyperlink ref="D8" r:id="rId37" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{B5F3EE9B-875A-4A65-A261-3B24386685B8}"/>
-    <hyperlink ref="G8" r:id="rId38" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{E8318C55-09B2-493E-974F-1CF36998BA66}"/>
-    <hyperlink ref="E8" r:id="rId39" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A30C6BD3-67C3-4FA7-AFA4-2B517ABD5F04}"/>
-    <hyperlink ref="H8" r:id="rId40" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{FB9D9197-6ED3-4753-B25F-4AC2BBC19043}"/>
-    <hyperlink ref="C8" r:id="rId41" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{3495E31B-F66B-4054-AF05-0BD3FFB7BF9C}"/>
-    <hyperlink ref="F8" r:id="rId42" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{0D7C3972-708B-40CD-B784-03F46CD089BD}"/>
-    <hyperlink ref="B9" r:id="rId43" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{6BC05550-BC9B-4846-8497-41B623C90180}"/>
-    <hyperlink ref="D9" r:id="rId44" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{844EA776-4BB8-4E32-93F8-397C8B5EED8B}"/>
-    <hyperlink ref="G9" r:id="rId45" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{39273C42-E20D-4F46-8ADB-5B533107BD2E}"/>
-    <hyperlink ref="E9" r:id="rId46" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D624BCB2-2F04-41B3-9E4D-5A98C308BA1E}"/>
-    <hyperlink ref="H9" r:id="rId47" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{B6A9F8CD-90ED-44A9-B8C7-CEC09D2BCB38}"/>
-    <hyperlink ref="C9" r:id="rId48" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{D7E5BFA7-2477-4334-83F6-F83C0606EB0D}"/>
-    <hyperlink ref="F9" r:id="rId49" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{701F7D0D-BE65-4455-9589-AAED281D0342}"/>
-    <hyperlink ref="B10" r:id="rId50" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{619373AF-7C61-474D-BD8F-ED9F06BE4505}"/>
-    <hyperlink ref="D10" r:id="rId51" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{CD6EB295-4333-4F74-9619-7B7ABA121619}"/>
-    <hyperlink ref="G10" r:id="rId52" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{5F5E4D8E-9A4D-424C-9A71-E223145814AA}"/>
-    <hyperlink ref="E10" r:id="rId53" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{C2D365FE-0441-4D9B-A7ED-4AAB5FDD3B9E}"/>
-    <hyperlink ref="H10" r:id="rId54" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5613175A-3F78-4156-B335-CE769839F3CF}"/>
-    <hyperlink ref="C10" r:id="rId55" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A326096C-1175-41AD-BCF1-66DC5D1B78FE}"/>
-    <hyperlink ref="F10" r:id="rId56" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C02C81D8-59C5-4CDD-B62C-9AF4F20A8A6C}"/>
-    <hyperlink ref="B11" r:id="rId57" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{3A6DA921-DBCD-4035-9876-3BFC3C1604B6}"/>
-    <hyperlink ref="D11" r:id="rId58" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{94F8DAD5-B42F-40E2-B1D7-D80D84B33543}"/>
-    <hyperlink ref="G11" r:id="rId59" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{77E9140C-0EA5-4A41-9784-8D472DE3C2B1}"/>
-    <hyperlink ref="E11" r:id="rId60" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{4299E878-8E8A-428A-9046-C997F0269E03}"/>
-    <hyperlink ref="H11" r:id="rId61" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{4723CA69-5BF8-4A4B-8267-F3ACFA391F3C}"/>
-    <hyperlink ref="C11" r:id="rId62" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A40A325B-7D4A-4394-9C22-935AA91F4AD7}"/>
-    <hyperlink ref="F11" r:id="rId63" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{9496E075-C7A0-49C6-8EF2-27618CDD47D3}"/>
-    <hyperlink ref="B12" r:id="rId64" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{48ED178E-576D-4FE2-9261-52E00F8095B7}"/>
-    <hyperlink ref="D12" r:id="rId65" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{8D6973E4-22A4-49E7-BF52-BB5A93EFE469}"/>
-    <hyperlink ref="G12" r:id="rId66" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{459AECEF-7BB9-43A4-9907-4B349F578D90}"/>
-    <hyperlink ref="E12" r:id="rId67" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{397F7BE1-3330-4F0F-B7FF-BAA8A473D4D3}"/>
-    <hyperlink ref="H12" r:id="rId68" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{268FDFB4-B5D0-499A-835E-984AC9AF6E93}"/>
-    <hyperlink ref="C12" r:id="rId69" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{5C054285-8A65-44A5-8D9D-36D87E227862}"/>
-    <hyperlink ref="F12" r:id="rId70" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{DD8939FB-5003-4B8A-AB10-4A75C98835A6}"/>
-    <hyperlink ref="B13" r:id="rId71" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{67CD9936-68E3-48D8-82E8-13946174F58F}"/>
-    <hyperlink ref="D13" r:id="rId72" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{A7B80407-4A1F-423C-8D21-86FB57E2574D}"/>
-    <hyperlink ref="G13" r:id="rId73" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C6B54D5D-59AC-4D5E-94C6-D1784C9F9E30}"/>
-    <hyperlink ref="E13" r:id="rId74" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E35AC702-AB7D-43D6-AA9B-D692621C0CA0}"/>
-    <hyperlink ref="H13" r:id="rId75" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5173B969-834B-47DE-A35E-547B7DB21A05}"/>
-    <hyperlink ref="C13" r:id="rId76" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{121BA981-889A-474D-A7CB-6703A006D212}"/>
-    <hyperlink ref="F13" r:id="rId77" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{56C692DD-5B6F-4781-834A-4B060DDA9382}"/>
-    <hyperlink ref="B14" r:id="rId78" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{36C9018F-7B2A-4710-8779-79CFB61BA540}"/>
-    <hyperlink ref="D14" r:id="rId79" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D0CADD27-E665-4D5C-B9FC-6A1F52E74A52}"/>
-    <hyperlink ref="G14" r:id="rId80" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{4D23686B-C993-4BC2-8A4D-25E709D734FE}"/>
-    <hyperlink ref="E14" r:id="rId81" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{C7C090F8-0274-47E7-87BB-458914A781D2}"/>
-    <hyperlink ref="H14" r:id="rId82" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{448CF223-F09F-4B3F-A43C-6D764BBCF623}"/>
-    <hyperlink ref="C14" r:id="rId83" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{34DAFD5D-EC0A-421F-B329-AC164A7172B1}"/>
-    <hyperlink ref="F14" r:id="rId84" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{DFDB4905-7093-4C01-A03D-F02F620303AD}"/>
-    <hyperlink ref="B15" r:id="rId85" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{87E4291E-6331-472E-ADD4-1D6E923A0490}"/>
-    <hyperlink ref="D15" r:id="rId86" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{28DDF373-2708-48F5-B42F-0F7D41CFACA0}"/>
-    <hyperlink ref="G15" r:id="rId87" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{45AF10FD-715F-424E-B4DD-C2C4ECC05DC7}"/>
-    <hyperlink ref="E15" r:id="rId88" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{AFB1243B-0C11-48CC-AD0B-04A64E608D37}"/>
-    <hyperlink ref="H15" r:id="rId89" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E1D0107F-A51D-431D-826A-96EE83F82D10}"/>
-    <hyperlink ref="C15" r:id="rId90" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C794848D-DEF4-4935-94A7-142EF140C27B}"/>
-    <hyperlink ref="F15" r:id="rId91" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{15FF5958-4F08-4CB4-82EF-DA9EFE83B742}"/>
-    <hyperlink ref="B16" r:id="rId92" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{27CAA26C-245C-4133-AA97-B02BAABBEA3C}"/>
-    <hyperlink ref="D16" r:id="rId93" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{54F21B84-6B34-4461-9818-63651934F699}"/>
-    <hyperlink ref="G16" r:id="rId94" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{030DB55D-CCF6-4FC7-AE94-4FE01EB48DB7}"/>
-    <hyperlink ref="E16" r:id="rId95" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{0426DD0E-19E0-4AFD-B584-38D24301B519}"/>
-    <hyperlink ref="H16" r:id="rId96" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{85A59889-912C-4062-9941-5144D4EC8098}"/>
-    <hyperlink ref="C16" r:id="rId97" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{9830EE91-67D8-4628-AC61-3887015B6C83}"/>
-    <hyperlink ref="F16" r:id="rId98" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C2A8D44E-8F43-428F-A19E-24B544363695}"/>
-    <hyperlink ref="B17" r:id="rId99" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{7BA001F9-E81D-4980-923D-DF2519E63CD9}"/>
-    <hyperlink ref="D17" r:id="rId100" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{A03629CE-FD91-49FB-BBC2-72DFCC00098D}"/>
-    <hyperlink ref="G17" r:id="rId101" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{49FAC30B-EB1D-45F1-845D-5F11DFEC9C0E}"/>
-    <hyperlink ref="E17" r:id="rId102" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{188A6A09-9ADF-41AD-BE22-C0F5ED3D5EE3}"/>
-    <hyperlink ref="H17" r:id="rId103" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{1F3B83B5-77AD-4D82-9170-9BF0A5B2B28F}"/>
-    <hyperlink ref="C17" r:id="rId104" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{938BA5CC-C3DB-4E69-AFB7-FDC8EBF1E2E9}"/>
-    <hyperlink ref="F17" r:id="rId105" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F2C514A6-75FE-400A-A5F7-94256B16D11B}"/>
-    <hyperlink ref="B18" r:id="rId106" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{0F07ADFB-21CE-465D-96C3-CE1C00008903}"/>
-    <hyperlink ref="D18" r:id="rId107" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{31F0EF54-D071-40D9-8E58-6FFAF87E78F3}"/>
-    <hyperlink ref="G18" r:id="rId108" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{D0424B80-BAB1-4BAA-B114-C8427E452F4C}"/>
-    <hyperlink ref="E18" r:id="rId109" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{ACA73AE9-0CCF-487D-B7DF-0025FD621B07}"/>
-    <hyperlink ref="H18" r:id="rId110" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{A01F75DE-47BE-4302-99D4-5F42CD9619AF}"/>
-    <hyperlink ref="C18" r:id="rId111" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{BC0D388A-7F38-426B-9DE6-F12EA01BB678}"/>
-    <hyperlink ref="F18" r:id="rId112" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{4AA03DAB-799D-46AE-B13F-1730F652E41B}"/>
-    <hyperlink ref="B19" r:id="rId113" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{30692E3E-53EB-4529-80F6-7ED39BA0B4DC}"/>
-    <hyperlink ref="D19" r:id="rId114" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{0AB3B44E-A51D-4B70-AF79-D7C7AE842490}"/>
-    <hyperlink ref="G19" r:id="rId115" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{86DE956D-8A8C-4F12-96B3-DC4D6DC46406}"/>
-    <hyperlink ref="E19" r:id="rId116" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F03549E5-B834-43DC-B085-88D1D882E4BA}"/>
-    <hyperlink ref="H19" r:id="rId117" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{F6491E77-460C-49FC-BDA9-C53A29FFA9FE}"/>
-    <hyperlink ref="C19" r:id="rId118" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{E7DDC3C1-8756-4E6F-9AFC-36BE1A9607E3}"/>
-    <hyperlink ref="F19" r:id="rId119" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{B70B2D1F-3571-4E92-AB37-84EF75BA8A64}"/>
-    <hyperlink ref="B20" r:id="rId120" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C2DAE2E5-B540-434B-965C-892D1A1AD981}"/>
-    <hyperlink ref="D20" r:id="rId121" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{7B6804BC-1A03-4945-8AA7-7D1CAB3B251E}"/>
-    <hyperlink ref="G20" r:id="rId122" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{5FFB9860-8BDB-40F3-9F6E-DD2A718DFA52}"/>
-    <hyperlink ref="E20" r:id="rId123" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{0D6F8698-56A6-44C3-895D-E1CEF41021E7}"/>
-    <hyperlink ref="H20" r:id="rId124" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E06BC4A8-2BA0-4044-855D-231DC3CBE1BC}"/>
-    <hyperlink ref="C20" r:id="rId125" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{60AABD7A-ACA7-403B-893E-C64E0BEECDCE}"/>
-    <hyperlink ref="F20" r:id="rId126" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{178C74E5-2E9E-44FF-B111-AFFD0A399EFA}"/>
-    <hyperlink ref="B2" r:id="rId127" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{73E79908-50FD-48BA-99A9-7E9401523EA3}"/>
-    <hyperlink ref="D2" r:id="rId128" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{EE7DA335-26CE-49F7-9491-0D7BC15BBBEB}"/>
-    <hyperlink ref="G2" r:id="rId129" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3A869268-FCFD-4361-8026-93A81C74A8BF}"/>
-    <hyperlink ref="E2" r:id="rId130" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{74B92ECE-382C-4533-B495-EE482E18CC44}"/>
-    <hyperlink ref="H2" r:id="rId131" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5A9A6CA3-829B-4476-8709-BBD86CE57582}"/>
-    <hyperlink ref="C2" r:id="rId132" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{E95C3346-5BB9-48BE-B1AD-03416E780588}"/>
-    <hyperlink ref="F2" r:id="rId133" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E7192020-943B-4345-99A3-24CE1248E5DE}"/>
+    <hyperlink ref="B3" r:id="rId1" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{50E9E599-5CFD-41ED-A8D8-46BAA4D3EED4}"/>
+    <hyperlink ref="D3" r:id="rId2" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{B85C9760-0D11-4AB9-A49A-614DF0C6073C}"/>
+    <hyperlink ref="G3" r:id="rId3" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{6FEA474A-7B4A-4C76-AD08-43D1060B41E5}"/>
+    <hyperlink ref="E3" r:id="rId4" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{24388256-2CE2-41F4-89B2-EDAC12E6A5B7}"/>
+    <hyperlink ref="H3" r:id="rId5" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{4E124E69-02C5-4ECA-A84C-83D564342A01}"/>
+    <hyperlink ref="C3" r:id="rId6" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{285A6FE9-2F08-4A03-B9B1-70B41F6A395C}"/>
+    <hyperlink ref="F3" r:id="rId7" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C9A5ACB7-3D99-47D3-92FD-A714B5C26045}"/>
+    <hyperlink ref="B4" r:id="rId8" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C5F045C4-E6F9-48B4-BAA6-BAE040424DB9}"/>
+    <hyperlink ref="D4" r:id="rId9" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{6C2EB921-2738-422B-92F3-CF12BBF1F0C3}"/>
+    <hyperlink ref="G4" r:id="rId10" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{E2449A45-7BAD-4D06-9AB2-9055A249B81E}"/>
+    <hyperlink ref="E4" r:id="rId11" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{193FB45E-30D3-4846-AF00-7ED73B5DCC57}"/>
+    <hyperlink ref="H4" r:id="rId12" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{FCBEB0DB-7057-4CE2-8924-F2B730EFC628}"/>
+    <hyperlink ref="C4" r:id="rId13" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{0FD026F5-97BA-45FB-B37A-06EC8AC37D85}"/>
+    <hyperlink ref="F4" r:id="rId14" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F0F2108D-02DD-413E-ACBA-D339BAF7FF84}"/>
+    <hyperlink ref="B5" r:id="rId15" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{BAE147B3-6135-4835-9298-AED303B172E4}"/>
+    <hyperlink ref="D5" r:id="rId16" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{EE7B98F1-C0E3-4264-AC7D-A16A3D8E5F94}"/>
+    <hyperlink ref="G5" r:id="rId17" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{259B2BFC-6F02-46C2-A0CB-7B33AB87C85B}"/>
+    <hyperlink ref="E5" r:id="rId18" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{14A9F5CA-4728-4539-9A46-13F94CD97BC7}"/>
+    <hyperlink ref="H5" r:id="rId19" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{540817AA-E0DE-4BDA-A7C0-27EF137F7909}"/>
+    <hyperlink ref="C5" r:id="rId20" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{9AE2D00F-179D-4717-9C69-DB85BE9D4115}"/>
+    <hyperlink ref="F5" r:id="rId21" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F13274C3-DA0C-4090-85C2-9102BAE4E720}"/>
+    <hyperlink ref="B6" r:id="rId22" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{3BF89A95-47F3-4297-8608-23A45AF8CD66}"/>
+    <hyperlink ref="D6" r:id="rId23" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{6C8DE154-29D5-45CB-9A9F-3D1F9489C57D}"/>
+    <hyperlink ref="G6" r:id="rId24" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{6FC914FE-CC82-4C10-A06B-E1F421C7C3D4}"/>
+    <hyperlink ref="E6" r:id="rId25" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{4AB47F5D-6B13-4A18-AF18-E8848284F481}"/>
+    <hyperlink ref="H6" r:id="rId26" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{0857D33E-F367-42D5-9F4B-6BF43AB3A68A}"/>
+    <hyperlink ref="C6" r:id="rId27" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{7DD744D9-DAE6-48A5-B83D-529C1C75F4C1}"/>
+    <hyperlink ref="F6" r:id="rId28" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{70664B76-5365-44C1-827C-EC11AF155614}"/>
+    <hyperlink ref="B7" r:id="rId29" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{5AC8F9BC-F082-4484-9D6D-782FCE2545E6}"/>
+    <hyperlink ref="D7" r:id="rId30" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2776D09D-0B06-4D38-B8F6-B77270C946F5}"/>
+    <hyperlink ref="G7" r:id="rId31" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{DA7FF8E9-877C-4E73-830D-73673B565842}"/>
+    <hyperlink ref="E7" r:id="rId32" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A69FF9DB-A1AD-4A53-A4F3-4483742FE87E}"/>
+    <hyperlink ref="H7" r:id="rId33" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{67D337DC-8B4E-41A0-97B3-2901CDC61DE4}"/>
+    <hyperlink ref="C7" r:id="rId34" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{61A66B1D-DD4A-4DB1-97B8-E489484A7702}"/>
+    <hyperlink ref="F7" r:id="rId35" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{20AC0E6C-DE89-43F9-95EA-F521180501A9}"/>
+    <hyperlink ref="B8" r:id="rId36" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{0840AA83-8E57-4A4D-B1F0-002D987D9FA7}"/>
+    <hyperlink ref="D8" r:id="rId37" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{0E7FAA92-E325-47E4-906D-9ED8ECF898AB}"/>
+    <hyperlink ref="G8" r:id="rId38" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{312DEF36-A151-4D11-8A05-705B5AED5519}"/>
+    <hyperlink ref="E8" r:id="rId39" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{64F1067D-74DF-46BE-A310-8866B1C9768C}"/>
+    <hyperlink ref="H8" r:id="rId40" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{DEFBFB8B-FDC0-4E81-AA50-73315C288026}"/>
+    <hyperlink ref="C8" r:id="rId41" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{9C4C3E17-5C69-4DBF-9484-A8D64CE2ADCB}"/>
+    <hyperlink ref="F8" r:id="rId42" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{BA77CA9F-4B32-43C6-94F8-D9411E9D7F4D}"/>
+    <hyperlink ref="B9" r:id="rId43" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{5B65AEB4-D6BE-40CA-91F1-CD49DDDDD18F}"/>
+    <hyperlink ref="D9" r:id="rId44" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{90B7FBF8-74E8-424B-AC98-5F883A4D407D}"/>
+    <hyperlink ref="G9" r:id="rId45" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{39348141-46B4-4FC0-85C6-4B117D8D031B}"/>
+    <hyperlink ref="E9" r:id="rId46" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{12D6C63A-617A-406C-AB14-567FD23400A1}"/>
+    <hyperlink ref="H9" r:id="rId47" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{7AEF2B43-9EBE-4071-B54A-E5962991B758}"/>
+    <hyperlink ref="C9" r:id="rId48" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{E0494D17-DC11-4A05-A7BA-7CCAC2CB8A00}"/>
+    <hyperlink ref="F9" r:id="rId49" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{48944CC3-6116-4FFB-8E86-0078E51147A1}"/>
+    <hyperlink ref="B10" r:id="rId50" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{06C3C4A1-9B97-4B72-9816-F483E79F0CB3}"/>
+    <hyperlink ref="D10" r:id="rId51" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{586E5A66-DF99-4CAE-9533-435C08189A2E}"/>
+    <hyperlink ref="G10" r:id="rId52" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{439F45B9-4DDE-4686-8035-EF2E7BD5AE72}"/>
+    <hyperlink ref="E10" r:id="rId53" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{EFB687B8-3182-4384-AFBB-6698E0A7DBE8}"/>
+    <hyperlink ref="H10" r:id="rId54" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{6BED7F43-81E4-4D7F-A0EF-5E1F0654785A}"/>
+    <hyperlink ref="C10" r:id="rId55" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{B87355AB-18E9-4526-839F-2443A9E4F791}"/>
+    <hyperlink ref="F10" r:id="rId56" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{4974306B-1FB2-40A2-B528-E08427347F75}"/>
+    <hyperlink ref="B11" r:id="rId57" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{8B6D3979-3ADB-47A9-AD1C-B7684DEF197B}"/>
+    <hyperlink ref="D11" r:id="rId58" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{C4942774-4AC1-4BC5-B0BD-38FE65AD1002}"/>
+    <hyperlink ref="G11" r:id="rId59" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{D5C6CE63-27AA-4459-92D7-3775CEE155D8}"/>
+    <hyperlink ref="E11" r:id="rId60" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{4F72E7AF-C15C-482B-A87D-D97595B91C08}"/>
+    <hyperlink ref="H11" r:id="rId61" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{D0B8122E-382B-4AA7-8A9D-FEF4F63FBB66}"/>
+    <hyperlink ref="C11" r:id="rId62" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{F7505046-BB14-4F1A-A123-AACCF4617212}"/>
+    <hyperlink ref="F11" r:id="rId63" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{3040BE3B-A157-49B9-8D4C-EB86201C31E3}"/>
+    <hyperlink ref="B12" r:id="rId64" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C8BA4C83-95BA-4559-B932-F5A1056BD98B}"/>
+    <hyperlink ref="D12" r:id="rId65" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{55C40183-53E5-4D85-953F-8B7DD1399FCE}"/>
+    <hyperlink ref="G12" r:id="rId66" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{73F43BB0-87E4-42B4-BA24-7E7BAF28F54F}"/>
+    <hyperlink ref="E12" r:id="rId67" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D8D2B8F9-E738-4017-84CB-6687778196FB}"/>
+    <hyperlink ref="H12" r:id="rId68" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{23BB84CE-DBD1-4A60-B53E-09D40446D792}"/>
+    <hyperlink ref="C12" r:id="rId69" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{CB44B879-42F3-46D0-8BC8-9AD1DF99B5BA}"/>
+    <hyperlink ref="F12" r:id="rId70" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{666B4B5C-0195-4886-9E45-AD2F30A82E22}"/>
+    <hyperlink ref="B13" r:id="rId71" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{B15C9641-34E7-4FEF-80FC-945CB20D306B}"/>
+    <hyperlink ref="D13" r:id="rId72" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{7474072E-B419-414F-B836-EF86FC926568}"/>
+    <hyperlink ref="G13" r:id="rId73" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{CDE67AEC-2EBA-455C-9EE2-1CDBEA32B9E5}"/>
+    <hyperlink ref="E13" r:id="rId74" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{6C5FF922-60C7-421E-81FC-614F9ACB99B4}"/>
+    <hyperlink ref="H13" r:id="rId75" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{57289B00-7025-4349-A08A-1B9747230DB7}"/>
+    <hyperlink ref="C13" r:id="rId76" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{D1457DEF-57B2-4572-9C4E-23D8AD7DC39C}"/>
+    <hyperlink ref="F13" r:id="rId77" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{3B3DA548-22F9-4032-ABA1-15941CD12FEE}"/>
+    <hyperlink ref="B14" r:id="rId78" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{F670E5A0-5FE6-4FEC-906C-3B872544AF26}"/>
+    <hyperlink ref="D14" r:id="rId79" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{BE4AA068-1D4D-492C-98F8-5EA30EE6CAE7}"/>
+    <hyperlink ref="G14" r:id="rId80" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{AAB95841-B793-4805-82B5-FC4380E78149}"/>
+    <hyperlink ref="E14" r:id="rId81" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{3215996B-1CC9-4DCF-83A2-DE991845EACD}"/>
+    <hyperlink ref="H14" r:id="rId82" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{FEE0B498-158F-42B5-9162-413DEB62E762}"/>
+    <hyperlink ref="C14" r:id="rId83" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{B2947B98-5E81-4613-8CCC-78D8E881BC03}"/>
+    <hyperlink ref="F14" r:id="rId84" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{312E5695-1866-4A0B-AE02-5AB02EC42B7F}"/>
+    <hyperlink ref="B15" r:id="rId85" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{CF585A91-1459-4927-9B79-F4D2DCDA21E3}"/>
+    <hyperlink ref="D15" r:id="rId86" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{B90A4A1A-9F6C-4D81-BD30-673F862C14BE}"/>
+    <hyperlink ref="G15" r:id="rId87" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C02DFD04-2908-41AE-92FF-E76C1FF3F094}"/>
+    <hyperlink ref="E15" r:id="rId88" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{38486787-361F-4E5A-AD8B-1AAA716E8ED6}"/>
+    <hyperlink ref="H15" r:id="rId89" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{847F7338-A1F3-4C68-814A-23D71D9A1241}"/>
+    <hyperlink ref="C15" r:id="rId90" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{DFEDB758-7AE3-4D8C-A876-CDD2ECEB38BC}"/>
+    <hyperlink ref="F15" r:id="rId91" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{B0BAFB94-E17A-40A6-AA6B-8F49572CD2EA}"/>
+    <hyperlink ref="B16" r:id="rId92" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{9BACC8D7-43CD-4B68-84FA-0EAC462439F2}"/>
+    <hyperlink ref="D16" r:id="rId93" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D3ED5F46-F1F0-4D25-9D83-397768AE4D18}"/>
+    <hyperlink ref="G16" r:id="rId94" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{6AF37A41-2CBB-4BEB-82AF-F0158246D6BA}"/>
+    <hyperlink ref="E16" r:id="rId95" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E294A650-F17F-4CD0-B1A2-0AB02F758FAB}"/>
+    <hyperlink ref="H16" r:id="rId96" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5F4A56E0-A489-43BC-B918-B229E7A3B683}"/>
+    <hyperlink ref="C16" r:id="rId97" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{FBA5408E-5478-4730-AA35-C7C9B23E8B69}"/>
+    <hyperlink ref="F16" r:id="rId98" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{D2CCCE37-9F9D-44AF-A4F2-B66106301CE6}"/>
+    <hyperlink ref="B17" r:id="rId99" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{3A2F27C0-918C-4377-BCE2-386898C48588}"/>
+    <hyperlink ref="D17" r:id="rId100" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{372EBD09-B259-4D7C-B75E-43F8FE32AC04}"/>
+    <hyperlink ref="G17" r:id="rId101" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{75C45EFD-6D37-47AB-99E2-0ACD483ADC02}"/>
+    <hyperlink ref="E17" r:id="rId102" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{ACB55C8C-9FD1-46AA-8700-035C6E92BD0A}"/>
+    <hyperlink ref="H17" r:id="rId103" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{C9F9453F-6A47-4EF1-B5C4-899B590FFCFF}"/>
+    <hyperlink ref="C17" r:id="rId104" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6C04FC9F-E127-48AB-B8B2-83D4B729D79A}"/>
+    <hyperlink ref="F17" r:id="rId105" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{9EB47DDB-6EFD-47E0-99AF-FDDFA87642C0}"/>
+    <hyperlink ref="B18" r:id="rId106" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{5E191D0F-B37E-49D7-899E-06DC11C8F540}"/>
+    <hyperlink ref="D18" r:id="rId107" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D90F9BB5-0468-4ADD-A7DB-D0F89A958F60}"/>
+    <hyperlink ref="G18" r:id="rId108" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{7602955A-12C9-45CA-ABF3-4106AD778FD2}"/>
+    <hyperlink ref="E18" r:id="rId109" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{36D33C22-46C2-4A9E-9080-DD59506EFEFA}"/>
+    <hyperlink ref="H18" r:id="rId110" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{14F8460F-3B6D-4331-AAA4-A15D30071532}"/>
+    <hyperlink ref="C18" r:id="rId111" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{99E0D922-53B7-4A95-8FF1-7E16C5B0C49F}"/>
+    <hyperlink ref="F18" r:id="rId112" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{17425BFE-FCF5-4253-98EB-A595799BB6A3}"/>
+    <hyperlink ref="B19" r:id="rId113" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{3D33838B-9DA8-4365-B9E5-E0006EA1BAA0}"/>
+    <hyperlink ref="D19" r:id="rId114" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{28301C5C-13B1-4EB8-8C33-975C727C4987}"/>
+    <hyperlink ref="G19" r:id="rId115" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C6FBD222-F519-4FD7-B120-3E2DFE5E735B}"/>
+    <hyperlink ref="E19" r:id="rId116" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{37F655AD-FF9E-4B3C-9D19-A87FCD2F5978}"/>
+    <hyperlink ref="H19" r:id="rId117" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{1970AED8-9FF1-4DB5-B9F2-FB12E6F6B70D}"/>
+    <hyperlink ref="C19" r:id="rId118" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6A276FA8-CA65-4846-BCA0-8D2E0615D8D2}"/>
+    <hyperlink ref="F19" r:id="rId119" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C8DE29AE-5DB1-47BD-8F1A-76A658F995DF}"/>
+    <hyperlink ref="B20" r:id="rId120" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{B55D3ACD-BA84-4A2F-931E-A7BA48A2632A}"/>
+    <hyperlink ref="D20" r:id="rId121" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{74934FEF-5EFB-418D-A97C-E887E11D170F}"/>
+    <hyperlink ref="G20" r:id="rId122" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{2CDD700B-A3EF-440D-9D87-F20229618646}"/>
+    <hyperlink ref="E20" r:id="rId123" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{0F650398-DB50-4489-AE36-703F07C579E8}"/>
+    <hyperlink ref="H20" r:id="rId124" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{C66A7764-EB57-495D-9DDD-4220ADF8DB35}"/>
+    <hyperlink ref="C20" r:id="rId125" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6A2BE896-132A-4F79-AE4D-BDE5C0BB03F3}"/>
+    <hyperlink ref="F20" r:id="rId126" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A2F5A538-3485-406A-8427-4642F73CD9B9}"/>
+    <hyperlink ref="B21" r:id="rId127" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{4E7BF4D0-8875-4D36-9898-C17657226526}"/>
+    <hyperlink ref="D21" r:id="rId128" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{AA9DD13D-FF20-46F5-BD43-67F2FC398A30}"/>
+    <hyperlink ref="G21" r:id="rId129" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{4B4FB0BC-A26A-4D25-8C13-A5B41B22D823}"/>
+    <hyperlink ref="E21" r:id="rId130" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E97A2D9A-0990-4CC8-9E12-B7AFFDF473CA}"/>
+    <hyperlink ref="H21" r:id="rId131" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{13A50D75-9314-4E6C-89F4-4969E75ACA81}"/>
+    <hyperlink ref="C21" r:id="rId132" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{1BBFD2D6-595B-4BD4-807B-904B9AB4DC3D}"/>
+    <hyperlink ref="F21" r:id="rId133" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{DA576953-964D-4757-A144-2D2AB07CDE05}"/>
+    <hyperlink ref="B2" r:id="rId134" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C0A8AA4D-52B7-4A7D-8615-4D55B30EFFFF}"/>
+    <hyperlink ref="D2" r:id="rId135" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{4C0C44D4-CCE0-4217-8F6B-9D30C4606984}"/>
+    <hyperlink ref="G2" r:id="rId136" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{D1678847-FB3D-4552-81DD-8C2981E5CC2A}"/>
+    <hyperlink ref="E2" r:id="rId137" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F8BE245D-EADA-47E2-AC3A-1389F3437174}"/>
+    <hyperlink ref="H2" r:id="rId138" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{8505D4EF-3679-48AB-9FF9-4EFA437C84BA}"/>
+    <hyperlink ref="C2" r:id="rId139" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{EFA63E47-6A81-458C-AA2E-BDF8F26FBD22}"/>
+    <hyperlink ref="F2" r:id="rId140" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{4D4E4EE4-DE43-4F03-8145-0EB95FF79668}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId134"/>
-  <drawing r:id="rId135"/>
+  <pageSetup orientation="portrait" r:id="rId141"/>
+  <drawing r:id="rId142"/>
   <tableParts count="1">
-    <tablePart r:id="rId136"/>
+    <tablePart r:id="rId143"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC3F3FC-17EF-4D6A-9290-8FAFFC789915}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.5546875" customWidth="1"/>
@@ -15787,6 +15982,24 @@
         <v>14</v>
       </c>
       <c r="E22" s="14">
+        <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="A23" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="14">
+        <v>98</v>
+      </c>
+      <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
+        <v>14</v>
+      </c>
+      <c r="E23" s="14">
         <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
         <v>113</v>
       </c>

--- a/data/SDET_SQA_DATA.xlsx
+++ b/data/SDET_SQA_DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WHSU\Desktop\Workspace\CycleView\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CE6485-1A6B-4AFA-A372-3854E0B3F401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCFDB091-DB85-4B41-BE49-DF0CA87066B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{EB11FF79-EF06-B64E-AA6A-0CFF391A8BD1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{EB11FF79-EF06-B64E-AA6A-0CFF391A8BD1}"/>
   </bookViews>
   <sheets>
     <sheet name="TestAutomationProgress" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="105">
   <si>
     <t>TODO (P1)</t>
   </si>
@@ -352,6 +352,12 @@
   <si>
     <t>26W12</t>
   </si>
+  <si>
+    <t>y26w16</t>
+  </si>
+  <si>
+    <t>26W13</t>
+  </si>
 </sst>
 </file>
 
@@ -538,58 +544,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="36">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="medium">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="medium">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -782,6 +736,58 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="medium">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="medium">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1088,9 +1094,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$23</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$24</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>25W40</c:v>
                 </c:pt>
@@ -1156,16 +1162,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>26W12</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>26W13</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$B$2:$B$23</c:f>
+              <c:f>TestAutomationProgress!$B$2:$B$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>15</c:v>
                 </c:pt>
@@ -1230,6 +1239,9 @@
                   <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="21">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
@@ -1327,9 +1339,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$23</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$24</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>25W40</c:v>
                 </c:pt>
@@ -1395,16 +1407,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>26W12</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>26W13</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$C$2:$C$23</c:f>
+              <c:f>TestAutomationProgress!$C$2:$C$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>14</c:v>
                 </c:pt>
@@ -1469,6 +1484,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="21">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1566,9 +1584,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$23</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$24</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>25W40</c:v>
                 </c:pt>
@@ -1634,16 +1652,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>26W12</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>26W13</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$D$2:$D$23</c:f>
+              <c:f>TestAutomationProgress!$D$2:$D$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>219</c:v>
                 </c:pt>
@@ -1708,6 +1729,9 @@
                   <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="21">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>160</c:v>
                 </c:pt>
               </c:numCache>
@@ -2203,7 +2227,7 @@
                   <c:v>860</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>460</c:v>
+                  <c:v>572</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2730,7 +2754,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>19</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2885,7 +2909,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>26</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3042,7 +3066,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>91</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3274,7 +3298,7 @@
                   <c:v>866</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>597</c:v>
+                  <c:v>592</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5887,7 +5911,7 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>8</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6412,7 +6436,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6758,7 +6782,7 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>17</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6933,7 +6957,7 @@
                   <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>30</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7306,9 +7330,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$21</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -7368,18 +7392,21 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>y26w14</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>y26w16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$B$2:$B$21</c:f>
+              <c:f>'SOVA-BugTrend'!$B$2:$B$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>27</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
@@ -7433,10 +7460,13 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>11</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2</c:v>
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7530,9 +7560,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$21</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -7592,16 +7622,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>y26w14</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>y26w16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$C$2:$C$21</c:f>
+              <c:f>'SOVA-BugTrend'!$C$2:$C$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7657,9 +7690,12 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -7754,9 +7790,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$21</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -7816,16 +7852,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>y26w14</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>y26w16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$D$2:$D$21</c:f>
+              <c:f>'SOVA-BugTrend'!$D$2:$D$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7881,9 +7920,12 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -7978,9 +8020,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$21</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -8040,16 +8082,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>y26w14</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>y26w16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$E$2:$E$21</c:f>
+              <c:f>'SOVA-BugTrend'!$E$2:$E$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -8105,9 +8150,12 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -8145,9 +8193,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$21</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -8207,16 +8255,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>y26w14</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>y26w16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$F$2:$F$21</c:f>
+              <c:f>'SOVA-BugTrend'!$F$2:$F$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8269,12 +8320,15 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -8366,9 +8420,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$21</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -8428,16 +8482,19 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>y26w14</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>y26w16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$G$2:$G$21</c:f>
+              <c:f>'SOVA-BugTrend'!$G$2:$G$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>5</c:v>
                 </c:pt>
@@ -8490,12 +8547,15 @@
                   <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>13</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -8535,9 +8595,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$21</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -8597,18 +8657,21 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>y26w14</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>y26w16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$H$2:$H$21</c:f>
+              <c:f>'SOVA-BugTrend'!$H$2:$H$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>6</c:v>
@@ -8665,6 +8728,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -8704,9 +8770,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$21</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -8766,18 +8832,21 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>y26w14</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>y26w16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$I$2:$I$21</c:f>
+              <c:f>'SOVA-BugTrend'!$I$2:$I$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>36</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>46</c:v>
@@ -8831,10 +8900,13 @@
                   <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>24</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2</c:v>
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11766,13 +11838,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>171448</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>55</xdr:row>
       <xdr:rowOff>133348</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -11966,8 +12038,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}" name="Table2" displayName="Table2" ref="A1:E23" totalsRowShown="0" headerRowDxfId="35">
-  <autoFilter ref="A1:E23" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}" name="Table2" displayName="Table2" ref="A1:E24" totalsRowShown="0" headerRowDxfId="35">
+  <autoFilter ref="A1:E24" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F25F0D34-0297-4771-8BBB-350BCDD85D46}" name="Week"/>
     <tableColumn id="2" xr3:uid="{39CFCD12-3130-47A8-A140-DBF602F1743D}" name="Done"/>
@@ -12039,18 +12111,18 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}" name="Table5" displayName="Table5" ref="A1:I21" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17" totalsRowBorderDxfId="16" dataCellStyle="Hyperlink">
-  <autoFilter ref="A1:I21" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}" name="Table5" displayName="Table5" ref="A1:I22" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17" totalsRowBorderDxfId="16" dataCellStyle="Hyperlink">
+  <autoFilter ref="A1:I22" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{5BE08AE0-E0B5-4B46-9423-456B88C2D9BC}" name="Sprint" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{030F9647-4FC0-4C7E-9B3A-AB099CC59EBA}" name="To Do (0%)" dataDxfId="14" dataCellStyle="Hyperlink"/>
-    <tableColumn id="3" xr3:uid="{7D2923F3-E2CF-4FD9-A7A5-68C36BB95591}" name="STARTING (10 ~ 40%)" dataDxfId="13" dataCellStyle="Hyperlink"/>
-    <tableColumn id="4" xr3:uid="{48FB5317-7F3B-4F74-B244-5A49C7749EBD}" name="In Progress (50 ~ 70%)" dataDxfId="12" dataCellStyle="Hyperlink"/>
-    <tableColumn id="5" xr3:uid="{86F5CCB5-C4C2-4C36-935A-657F085500B1}" name="IN REVIEW (80%)" dataDxfId="11" dataCellStyle="Hyperlink"/>
-    <tableColumn id="9" xr3:uid="{51D22AE3-424C-4604-9869-D672DED4301F}" name="READY FOR TESTING (90%)" dataDxfId="10" dataCellStyle="Hyperlink"/>
-    <tableColumn id="6" xr3:uid="{33C9BCE6-D9EB-4032-9B0A-DDD9A4051A2D}" name="Done (100%)" dataDxfId="9" dataCellStyle="Hyperlink"/>
-    <tableColumn id="8" xr3:uid="{D624FC89-A88E-45AC-9D22-66D66702B8C5}" name="WON'T DO (100%)" dataDxfId="8" dataCellStyle="Hyperlink"/>
-    <tableColumn id="7" xr3:uid="{EFEEB7EC-E2D1-40EA-B265-A558311E5D30}" name="Total" dataDxfId="7" dataCellStyle="Hyperlink">
+    <tableColumn id="1" xr3:uid="{5BE08AE0-E0B5-4B46-9423-456B88C2D9BC}" name="Sprint" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{030F9647-4FC0-4C7E-9B3A-AB099CC59EBA}" name="To Do (0%)" dataDxfId="6" dataCellStyle="Hyperlink"/>
+    <tableColumn id="3" xr3:uid="{7D2923F3-E2CF-4FD9-A7A5-68C36BB95591}" name="STARTING (10 ~ 40%)" dataDxfId="5" dataCellStyle="Hyperlink"/>
+    <tableColumn id="4" xr3:uid="{48FB5317-7F3B-4F74-B244-5A49C7749EBD}" name="In Progress (50 ~ 70%)" dataDxfId="4" dataCellStyle="Hyperlink"/>
+    <tableColumn id="5" xr3:uid="{86F5CCB5-C4C2-4C36-935A-657F085500B1}" name="IN REVIEW (80%)" dataDxfId="3" dataCellStyle="Hyperlink"/>
+    <tableColumn id="9" xr3:uid="{51D22AE3-424C-4604-9869-D672DED4301F}" name="READY FOR TESTING (90%)" dataDxfId="2" dataCellStyle="Hyperlink"/>
+    <tableColumn id="6" xr3:uid="{33C9BCE6-D9EB-4032-9B0A-DDD9A4051A2D}" name="Done (100%)" dataDxfId="1" dataCellStyle="Hyperlink"/>
+    <tableColumn id="8" xr3:uid="{D624FC89-A88E-45AC-9D22-66D66702B8C5}" name="WON'T DO (100%)" dataDxfId="0" dataCellStyle="Hyperlink"/>
+    <tableColumn id="7" xr3:uid="{EFEEB7EC-E2D1-40EA-B265-A558311E5D30}" name="Total" dataDxfId="15" dataCellStyle="Hyperlink">
       <calculatedColumnFormula>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12059,14 +12131,14 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}" name="Table25" displayName="Table25" ref="A1:E23" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A1:E23" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}" name="Table25" displayName="Table25" ref="A1:E24" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+  <autoFilter ref="A1:E24" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7070D9F2-0ED1-4F39-8D72-28B37C8E98F2}" name="Week" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{1173F443-CC27-4C6E-A432-BF66DB2A740E}" name="Done" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{2EE10CB5-1AF1-4B50-9456-B3A666DD5338}" name="In Review/Progress" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{328D0A00-85F0-4BFF-81FE-C023998A3701}" name="TODO (P1)" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{E385808E-1FCD-451C-9807-DAF18A42B704}" name="Total" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{7070D9F2-0ED1-4F39-8D72-28B37C8E98F2}" name="Week" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{1173F443-CC27-4C6E-A432-BF66DB2A740E}" name="Done" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{2EE10CB5-1AF1-4B50-9456-B3A666DD5338}" name="In Review/Progress" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{328D0A00-85F0-4BFF-81FE-C023998A3701}" name="TODO (P1)" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{E385808E-1FCD-451C-9807-DAF18A42B704}" name="Total" dataDxfId="8">
       <calculatedColumnFormula>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12391,7 +12463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D733A42-966D-5F4E-B061-B304543CE88E}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.77734375" customWidth="1"/>
@@ -12808,6 +12880,23 @@
         <v>160</v>
       </c>
       <c r="E23" s="12">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A24" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24">
+        <v>37</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>160</v>
+      </c>
+      <c r="E24" s="12">
         <v>198</v>
       </c>
     </row>
@@ -13321,7 +13410,7 @@
         <v>93</v>
       </c>
       <c r="B19">
-        <v>460</v>
+        <v>572</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -13330,17 +13419,17 @@
         <v>1</v>
       </c>
       <c r="E19">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F19">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="G19">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="H19">
         <f>SUM(Table1[[#This Row],[Passed]:[Untested]])</f>
-        <v>597</v>
+        <v>592</v>
       </c>
     </row>
   </sheetData>
@@ -14754,7 +14843,7 @@
         <v>93</v>
       </c>
       <c r="B22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -14763,17 +14852,17 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="H22" s="12">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -14788,7 +14877,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7487DEB-55FC-DC4E-A4B1-F7171B8F3237}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.21875" customWidth="1"/>
@@ -14835,7 +14924,7 @@
         <v>99</v>
       </c>
       <c r="B2" s="5">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C2" s="5">
         <v>0</v>
@@ -14853,11 +14942,11 @@
         <v>5</v>
       </c>
       <c r="H2" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18" thickBot="1">
@@ -15357,10 +15446,10 @@
         <v>0</v>
       </c>
       <c r="F19" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" s="5">
         <v>10</v>
@@ -15375,29 +15464,29 @@
         <v>98</v>
       </c>
       <c r="B20" s="5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C20" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="5">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H20" s="5">
         <v>1</v>
       </c>
       <c r="I20" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="18" thickBot="1">
@@ -15405,10 +15494,10 @@
         <v>101</v>
       </c>
       <c r="B21" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C21" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="5">
         <v>0</v>
@@ -15427,165 +15516,202 @@
       </c>
       <c r="I21" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>2</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="18" thickBot="1">
+      <c r="A22" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="5">
+        <v>5</v>
+      </c>
+      <c r="C22" s="5">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5">
+        <v>0</v>
+      </c>
+      <c r="I22" s="15">
+        <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{50E9E599-5CFD-41ED-A8D8-46BAA4D3EED4}"/>
-    <hyperlink ref="D3" r:id="rId2" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{B85C9760-0D11-4AB9-A49A-614DF0C6073C}"/>
-    <hyperlink ref="G3" r:id="rId3" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{6FEA474A-7B4A-4C76-AD08-43D1060B41E5}"/>
-    <hyperlink ref="E3" r:id="rId4" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{24388256-2CE2-41F4-89B2-EDAC12E6A5B7}"/>
-    <hyperlink ref="H3" r:id="rId5" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{4E124E69-02C5-4ECA-A84C-83D564342A01}"/>
-    <hyperlink ref="C3" r:id="rId6" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{285A6FE9-2F08-4A03-B9B1-70B41F6A395C}"/>
-    <hyperlink ref="F3" r:id="rId7" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C9A5ACB7-3D99-47D3-92FD-A714B5C26045}"/>
-    <hyperlink ref="B4" r:id="rId8" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C5F045C4-E6F9-48B4-BAA6-BAE040424DB9}"/>
-    <hyperlink ref="D4" r:id="rId9" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{6C2EB921-2738-422B-92F3-CF12BBF1F0C3}"/>
-    <hyperlink ref="G4" r:id="rId10" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{E2449A45-7BAD-4D06-9AB2-9055A249B81E}"/>
-    <hyperlink ref="E4" r:id="rId11" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{193FB45E-30D3-4846-AF00-7ED73B5DCC57}"/>
-    <hyperlink ref="H4" r:id="rId12" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{FCBEB0DB-7057-4CE2-8924-F2B730EFC628}"/>
-    <hyperlink ref="C4" r:id="rId13" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{0FD026F5-97BA-45FB-B37A-06EC8AC37D85}"/>
-    <hyperlink ref="F4" r:id="rId14" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F0F2108D-02DD-413E-ACBA-D339BAF7FF84}"/>
-    <hyperlink ref="B5" r:id="rId15" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{BAE147B3-6135-4835-9298-AED303B172E4}"/>
-    <hyperlink ref="D5" r:id="rId16" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{EE7B98F1-C0E3-4264-AC7D-A16A3D8E5F94}"/>
-    <hyperlink ref="G5" r:id="rId17" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{259B2BFC-6F02-46C2-A0CB-7B33AB87C85B}"/>
-    <hyperlink ref="E5" r:id="rId18" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{14A9F5CA-4728-4539-9A46-13F94CD97BC7}"/>
-    <hyperlink ref="H5" r:id="rId19" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{540817AA-E0DE-4BDA-A7C0-27EF137F7909}"/>
-    <hyperlink ref="C5" r:id="rId20" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{9AE2D00F-179D-4717-9C69-DB85BE9D4115}"/>
-    <hyperlink ref="F5" r:id="rId21" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F13274C3-DA0C-4090-85C2-9102BAE4E720}"/>
-    <hyperlink ref="B6" r:id="rId22" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{3BF89A95-47F3-4297-8608-23A45AF8CD66}"/>
-    <hyperlink ref="D6" r:id="rId23" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{6C8DE154-29D5-45CB-9A9F-3D1F9489C57D}"/>
-    <hyperlink ref="G6" r:id="rId24" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{6FC914FE-CC82-4C10-A06B-E1F421C7C3D4}"/>
-    <hyperlink ref="E6" r:id="rId25" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{4AB47F5D-6B13-4A18-AF18-E8848284F481}"/>
-    <hyperlink ref="H6" r:id="rId26" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{0857D33E-F367-42D5-9F4B-6BF43AB3A68A}"/>
-    <hyperlink ref="C6" r:id="rId27" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{7DD744D9-DAE6-48A5-B83D-529C1C75F4C1}"/>
-    <hyperlink ref="F6" r:id="rId28" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{70664B76-5365-44C1-827C-EC11AF155614}"/>
-    <hyperlink ref="B7" r:id="rId29" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{5AC8F9BC-F082-4484-9D6D-782FCE2545E6}"/>
-    <hyperlink ref="D7" r:id="rId30" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2776D09D-0B06-4D38-B8F6-B77270C946F5}"/>
-    <hyperlink ref="G7" r:id="rId31" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{DA7FF8E9-877C-4E73-830D-73673B565842}"/>
-    <hyperlink ref="E7" r:id="rId32" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A69FF9DB-A1AD-4A53-A4F3-4483742FE87E}"/>
-    <hyperlink ref="H7" r:id="rId33" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{67D337DC-8B4E-41A0-97B3-2901CDC61DE4}"/>
-    <hyperlink ref="C7" r:id="rId34" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{61A66B1D-DD4A-4DB1-97B8-E489484A7702}"/>
-    <hyperlink ref="F7" r:id="rId35" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{20AC0E6C-DE89-43F9-95EA-F521180501A9}"/>
-    <hyperlink ref="B8" r:id="rId36" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{0840AA83-8E57-4A4D-B1F0-002D987D9FA7}"/>
-    <hyperlink ref="D8" r:id="rId37" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{0E7FAA92-E325-47E4-906D-9ED8ECF898AB}"/>
-    <hyperlink ref="G8" r:id="rId38" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{312DEF36-A151-4D11-8A05-705B5AED5519}"/>
-    <hyperlink ref="E8" r:id="rId39" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{64F1067D-74DF-46BE-A310-8866B1C9768C}"/>
-    <hyperlink ref="H8" r:id="rId40" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{DEFBFB8B-FDC0-4E81-AA50-73315C288026}"/>
-    <hyperlink ref="C8" r:id="rId41" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{9C4C3E17-5C69-4DBF-9484-A8D64CE2ADCB}"/>
-    <hyperlink ref="F8" r:id="rId42" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{BA77CA9F-4B32-43C6-94F8-D9411E9D7F4D}"/>
-    <hyperlink ref="B9" r:id="rId43" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{5B65AEB4-D6BE-40CA-91F1-CD49DDDDD18F}"/>
-    <hyperlink ref="D9" r:id="rId44" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{90B7FBF8-74E8-424B-AC98-5F883A4D407D}"/>
-    <hyperlink ref="G9" r:id="rId45" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{39348141-46B4-4FC0-85C6-4B117D8D031B}"/>
-    <hyperlink ref="E9" r:id="rId46" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{12D6C63A-617A-406C-AB14-567FD23400A1}"/>
-    <hyperlink ref="H9" r:id="rId47" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{7AEF2B43-9EBE-4071-B54A-E5962991B758}"/>
-    <hyperlink ref="C9" r:id="rId48" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{E0494D17-DC11-4A05-A7BA-7CCAC2CB8A00}"/>
-    <hyperlink ref="F9" r:id="rId49" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{48944CC3-6116-4FFB-8E86-0078E51147A1}"/>
-    <hyperlink ref="B10" r:id="rId50" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{06C3C4A1-9B97-4B72-9816-F483E79F0CB3}"/>
-    <hyperlink ref="D10" r:id="rId51" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{586E5A66-DF99-4CAE-9533-435C08189A2E}"/>
-    <hyperlink ref="G10" r:id="rId52" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{439F45B9-4DDE-4686-8035-EF2E7BD5AE72}"/>
-    <hyperlink ref="E10" r:id="rId53" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{EFB687B8-3182-4384-AFBB-6698E0A7DBE8}"/>
-    <hyperlink ref="H10" r:id="rId54" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{6BED7F43-81E4-4D7F-A0EF-5E1F0654785A}"/>
-    <hyperlink ref="C10" r:id="rId55" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{B87355AB-18E9-4526-839F-2443A9E4F791}"/>
-    <hyperlink ref="F10" r:id="rId56" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{4974306B-1FB2-40A2-B528-E08427347F75}"/>
-    <hyperlink ref="B11" r:id="rId57" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{8B6D3979-3ADB-47A9-AD1C-B7684DEF197B}"/>
-    <hyperlink ref="D11" r:id="rId58" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{C4942774-4AC1-4BC5-B0BD-38FE65AD1002}"/>
-    <hyperlink ref="G11" r:id="rId59" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{D5C6CE63-27AA-4459-92D7-3775CEE155D8}"/>
-    <hyperlink ref="E11" r:id="rId60" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{4F72E7AF-C15C-482B-A87D-D97595B91C08}"/>
-    <hyperlink ref="H11" r:id="rId61" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{D0B8122E-382B-4AA7-8A9D-FEF4F63FBB66}"/>
-    <hyperlink ref="C11" r:id="rId62" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{F7505046-BB14-4F1A-A123-AACCF4617212}"/>
-    <hyperlink ref="F11" r:id="rId63" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{3040BE3B-A157-49B9-8D4C-EB86201C31E3}"/>
-    <hyperlink ref="B12" r:id="rId64" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C8BA4C83-95BA-4559-B932-F5A1056BD98B}"/>
-    <hyperlink ref="D12" r:id="rId65" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{55C40183-53E5-4D85-953F-8B7DD1399FCE}"/>
-    <hyperlink ref="G12" r:id="rId66" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{73F43BB0-87E4-42B4-BA24-7E7BAF28F54F}"/>
-    <hyperlink ref="E12" r:id="rId67" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D8D2B8F9-E738-4017-84CB-6687778196FB}"/>
-    <hyperlink ref="H12" r:id="rId68" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{23BB84CE-DBD1-4A60-B53E-09D40446D792}"/>
-    <hyperlink ref="C12" r:id="rId69" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{CB44B879-42F3-46D0-8BC8-9AD1DF99B5BA}"/>
-    <hyperlink ref="F12" r:id="rId70" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{666B4B5C-0195-4886-9E45-AD2F30A82E22}"/>
-    <hyperlink ref="B13" r:id="rId71" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{B15C9641-34E7-4FEF-80FC-945CB20D306B}"/>
-    <hyperlink ref="D13" r:id="rId72" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{7474072E-B419-414F-B836-EF86FC926568}"/>
-    <hyperlink ref="G13" r:id="rId73" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{CDE67AEC-2EBA-455C-9EE2-1CDBEA32B9E5}"/>
-    <hyperlink ref="E13" r:id="rId74" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{6C5FF922-60C7-421E-81FC-614F9ACB99B4}"/>
-    <hyperlink ref="H13" r:id="rId75" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{57289B00-7025-4349-A08A-1B9747230DB7}"/>
-    <hyperlink ref="C13" r:id="rId76" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{D1457DEF-57B2-4572-9C4E-23D8AD7DC39C}"/>
-    <hyperlink ref="F13" r:id="rId77" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{3B3DA548-22F9-4032-ABA1-15941CD12FEE}"/>
-    <hyperlink ref="B14" r:id="rId78" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{F670E5A0-5FE6-4FEC-906C-3B872544AF26}"/>
-    <hyperlink ref="D14" r:id="rId79" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{BE4AA068-1D4D-492C-98F8-5EA30EE6CAE7}"/>
-    <hyperlink ref="G14" r:id="rId80" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{AAB95841-B793-4805-82B5-FC4380E78149}"/>
-    <hyperlink ref="E14" r:id="rId81" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{3215996B-1CC9-4DCF-83A2-DE991845EACD}"/>
-    <hyperlink ref="H14" r:id="rId82" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{FEE0B498-158F-42B5-9162-413DEB62E762}"/>
-    <hyperlink ref="C14" r:id="rId83" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{B2947B98-5E81-4613-8CCC-78D8E881BC03}"/>
-    <hyperlink ref="F14" r:id="rId84" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{312E5695-1866-4A0B-AE02-5AB02EC42B7F}"/>
-    <hyperlink ref="B15" r:id="rId85" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{CF585A91-1459-4927-9B79-F4D2DCDA21E3}"/>
-    <hyperlink ref="D15" r:id="rId86" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{B90A4A1A-9F6C-4D81-BD30-673F862C14BE}"/>
-    <hyperlink ref="G15" r:id="rId87" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C02DFD04-2908-41AE-92FF-E76C1FF3F094}"/>
-    <hyperlink ref="E15" r:id="rId88" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{38486787-361F-4E5A-AD8B-1AAA716E8ED6}"/>
-    <hyperlink ref="H15" r:id="rId89" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{847F7338-A1F3-4C68-814A-23D71D9A1241}"/>
-    <hyperlink ref="C15" r:id="rId90" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{DFEDB758-7AE3-4D8C-A876-CDD2ECEB38BC}"/>
-    <hyperlink ref="F15" r:id="rId91" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{B0BAFB94-E17A-40A6-AA6B-8F49572CD2EA}"/>
-    <hyperlink ref="B16" r:id="rId92" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{9BACC8D7-43CD-4B68-84FA-0EAC462439F2}"/>
-    <hyperlink ref="D16" r:id="rId93" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D3ED5F46-F1F0-4D25-9D83-397768AE4D18}"/>
-    <hyperlink ref="G16" r:id="rId94" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{6AF37A41-2CBB-4BEB-82AF-F0158246D6BA}"/>
-    <hyperlink ref="E16" r:id="rId95" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E294A650-F17F-4CD0-B1A2-0AB02F758FAB}"/>
-    <hyperlink ref="H16" r:id="rId96" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5F4A56E0-A489-43BC-B918-B229E7A3B683}"/>
-    <hyperlink ref="C16" r:id="rId97" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{FBA5408E-5478-4730-AA35-C7C9B23E8B69}"/>
-    <hyperlink ref="F16" r:id="rId98" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{D2CCCE37-9F9D-44AF-A4F2-B66106301CE6}"/>
-    <hyperlink ref="B17" r:id="rId99" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{3A2F27C0-918C-4377-BCE2-386898C48588}"/>
-    <hyperlink ref="D17" r:id="rId100" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{372EBD09-B259-4D7C-B75E-43F8FE32AC04}"/>
-    <hyperlink ref="G17" r:id="rId101" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{75C45EFD-6D37-47AB-99E2-0ACD483ADC02}"/>
-    <hyperlink ref="E17" r:id="rId102" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{ACB55C8C-9FD1-46AA-8700-035C6E92BD0A}"/>
-    <hyperlink ref="H17" r:id="rId103" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{C9F9453F-6A47-4EF1-B5C4-899B590FFCFF}"/>
-    <hyperlink ref="C17" r:id="rId104" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6C04FC9F-E127-48AB-B8B2-83D4B729D79A}"/>
-    <hyperlink ref="F17" r:id="rId105" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{9EB47DDB-6EFD-47E0-99AF-FDDFA87642C0}"/>
-    <hyperlink ref="B18" r:id="rId106" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{5E191D0F-B37E-49D7-899E-06DC11C8F540}"/>
-    <hyperlink ref="D18" r:id="rId107" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D90F9BB5-0468-4ADD-A7DB-D0F89A958F60}"/>
-    <hyperlink ref="G18" r:id="rId108" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{7602955A-12C9-45CA-ABF3-4106AD778FD2}"/>
-    <hyperlink ref="E18" r:id="rId109" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{36D33C22-46C2-4A9E-9080-DD59506EFEFA}"/>
-    <hyperlink ref="H18" r:id="rId110" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{14F8460F-3B6D-4331-AAA4-A15D30071532}"/>
-    <hyperlink ref="C18" r:id="rId111" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{99E0D922-53B7-4A95-8FF1-7E16C5B0C49F}"/>
-    <hyperlink ref="F18" r:id="rId112" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{17425BFE-FCF5-4253-98EB-A595799BB6A3}"/>
-    <hyperlink ref="B19" r:id="rId113" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{3D33838B-9DA8-4365-B9E5-E0006EA1BAA0}"/>
-    <hyperlink ref="D19" r:id="rId114" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{28301C5C-13B1-4EB8-8C33-975C727C4987}"/>
-    <hyperlink ref="G19" r:id="rId115" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C6FBD222-F519-4FD7-B120-3E2DFE5E735B}"/>
-    <hyperlink ref="E19" r:id="rId116" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{37F655AD-FF9E-4B3C-9D19-A87FCD2F5978}"/>
-    <hyperlink ref="H19" r:id="rId117" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{1970AED8-9FF1-4DB5-B9F2-FB12E6F6B70D}"/>
-    <hyperlink ref="C19" r:id="rId118" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6A276FA8-CA65-4846-BCA0-8D2E0615D8D2}"/>
-    <hyperlink ref="F19" r:id="rId119" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C8DE29AE-5DB1-47BD-8F1A-76A658F995DF}"/>
-    <hyperlink ref="B20" r:id="rId120" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{B55D3ACD-BA84-4A2F-931E-A7BA48A2632A}"/>
-    <hyperlink ref="D20" r:id="rId121" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{74934FEF-5EFB-418D-A97C-E887E11D170F}"/>
-    <hyperlink ref="G20" r:id="rId122" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{2CDD700B-A3EF-440D-9D87-F20229618646}"/>
-    <hyperlink ref="E20" r:id="rId123" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{0F650398-DB50-4489-AE36-703F07C579E8}"/>
-    <hyperlink ref="H20" r:id="rId124" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{C66A7764-EB57-495D-9DDD-4220ADF8DB35}"/>
-    <hyperlink ref="C20" r:id="rId125" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6A2BE896-132A-4F79-AE4D-BDE5C0BB03F3}"/>
-    <hyperlink ref="F20" r:id="rId126" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A2F5A538-3485-406A-8427-4642F73CD9B9}"/>
-    <hyperlink ref="B21" r:id="rId127" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{4E7BF4D0-8875-4D36-9898-C17657226526}"/>
-    <hyperlink ref="D21" r:id="rId128" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{AA9DD13D-FF20-46F5-BD43-67F2FC398A30}"/>
-    <hyperlink ref="G21" r:id="rId129" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{4B4FB0BC-A26A-4D25-8C13-A5B41B22D823}"/>
-    <hyperlink ref="E21" r:id="rId130" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E97A2D9A-0990-4CC8-9E12-B7AFFDF473CA}"/>
-    <hyperlink ref="H21" r:id="rId131" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{13A50D75-9314-4E6C-89F4-4969E75ACA81}"/>
-    <hyperlink ref="C21" r:id="rId132" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{1BBFD2D6-595B-4BD4-807B-904B9AB4DC3D}"/>
-    <hyperlink ref="F21" r:id="rId133" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{DA576953-964D-4757-A144-2D2AB07CDE05}"/>
-    <hyperlink ref="B2" r:id="rId134" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C0A8AA4D-52B7-4A7D-8615-4D55B30EFFFF}"/>
-    <hyperlink ref="D2" r:id="rId135" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{4C0C44D4-CCE0-4217-8F6B-9D30C4606984}"/>
-    <hyperlink ref="G2" r:id="rId136" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{D1678847-FB3D-4552-81DD-8C2981E5CC2A}"/>
-    <hyperlink ref="E2" r:id="rId137" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F8BE245D-EADA-47E2-AC3A-1389F3437174}"/>
-    <hyperlink ref="H2" r:id="rId138" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{8505D4EF-3679-48AB-9FF9-4EFA437C84BA}"/>
-    <hyperlink ref="C2" r:id="rId139" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{EFA63E47-6A81-458C-AA2E-BDF8F26FBD22}"/>
-    <hyperlink ref="F2" r:id="rId140" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{4D4E4EE4-DE43-4F03-8145-0EB95FF79668}"/>
+    <hyperlink ref="B3" r:id="rId1" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{09F7A302-1404-4715-8128-181D35E5D8B9}"/>
+    <hyperlink ref="D3" r:id="rId2" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{76635EFC-D384-419A-A59C-C55EC8240726}"/>
+    <hyperlink ref="G3" r:id="rId3" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{42093993-73C6-4BB9-80D7-36685152171C}"/>
+    <hyperlink ref="E3" r:id="rId4" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{37DC5DA8-1239-4E51-8969-C2BCE4653444}"/>
+    <hyperlink ref="H3" r:id="rId5" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E6FD163E-6C57-4EF3-8B9C-269D8B7B50E2}"/>
+    <hyperlink ref="C3" r:id="rId6" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{D7E85314-DB61-45C5-8060-3EB33C25D3B6}"/>
+    <hyperlink ref="F3" r:id="rId7" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C69F1513-3C37-4AB1-A9B8-3092C1C10148}"/>
+    <hyperlink ref="B4" r:id="rId8" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{76B296F7-BFF3-4A65-9F00-E5C1557AE833}"/>
+    <hyperlink ref="D4" r:id="rId9" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{A19D1D61-53D9-4AB4-BDE3-EBCB3572C0D5}"/>
+    <hyperlink ref="G4" r:id="rId10" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{4AB520F8-F7B0-45A9-9CC3-37170DC9B8DB}"/>
+    <hyperlink ref="E4" r:id="rId11" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B9FCE681-4673-4949-ACB3-8DAE2F7FD250}"/>
+    <hyperlink ref="H4" r:id="rId12" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{027C6980-9510-454F-9FEC-4AF0F8380BAF}"/>
+    <hyperlink ref="C4" r:id="rId13" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{941C500C-86D3-4A7F-92AF-42FEB23C4900}"/>
+    <hyperlink ref="F4" r:id="rId14" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{184E0C28-F946-4D37-9471-166141674777}"/>
+    <hyperlink ref="B5" r:id="rId15" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{CD326838-C12B-451E-B276-AAA4C01E7484}"/>
+    <hyperlink ref="D5" r:id="rId16" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{69ECC71E-7D3B-4FF6-8C8F-20BC6662447E}"/>
+    <hyperlink ref="G5" r:id="rId17" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{143835A4-3D69-4457-A785-FA8353333EFF}"/>
+    <hyperlink ref="E5" r:id="rId18" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{CE5F0CFB-0AC4-4FC9-A917-E619A44BA7F6}"/>
+    <hyperlink ref="H5" r:id="rId19" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{0C7859E8-B6DB-4267-88FC-F2895481CF6E}"/>
+    <hyperlink ref="C5" r:id="rId20" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{96F6155A-1A88-46F7-AF8C-A04AF42C9D84}"/>
+    <hyperlink ref="F5" r:id="rId21" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A52FC7DC-AFE8-4739-822B-48EF80E4F8A9}"/>
+    <hyperlink ref="B6" r:id="rId22" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{36B3D1D5-2F6B-425F-9BF6-C31DF571EC8D}"/>
+    <hyperlink ref="D6" r:id="rId23" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{BB516DE7-BB41-4BFF-8E99-3345517C6192}"/>
+    <hyperlink ref="G6" r:id="rId24" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{B19055D8-3BE4-40F2-BFB8-B1B36097458B}"/>
+    <hyperlink ref="E6" r:id="rId25" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{7FB0FDC2-4FA6-4FFF-A923-E521B206DADA}"/>
+    <hyperlink ref="H6" r:id="rId26" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{40F2FE10-085A-4B9B-B5A3-B3585E2D3D57}"/>
+    <hyperlink ref="C6" r:id="rId27" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{60BE2628-B52A-40B4-90F9-C5EDE979E015}"/>
+    <hyperlink ref="F6" r:id="rId28" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{29580453-F811-482D-B314-07AAFC6CE690}"/>
+    <hyperlink ref="B7" r:id="rId29" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C18D93D7-445A-4642-9072-BE6C545D4EEA}"/>
+    <hyperlink ref="D7" r:id="rId30" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{909A918D-89F9-4228-85A0-85C0F37F66A0}"/>
+    <hyperlink ref="G7" r:id="rId31" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{B41D871E-5260-4559-8823-0484CCDBCE54}"/>
+    <hyperlink ref="E7" r:id="rId32" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{425A623A-4358-45E0-A57F-84C442A0C12A}"/>
+    <hyperlink ref="H7" r:id="rId33" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{3794C7C7-AE24-47F3-8E88-27CE9CDB738E}"/>
+    <hyperlink ref="C7" r:id="rId34" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{4BDCC3AB-46D0-47A5-9C7C-6F427D455C60}"/>
+    <hyperlink ref="F7" r:id="rId35" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{3B6DDE0C-C1AF-4711-9D0C-1A42166E62CD}"/>
+    <hyperlink ref="B8" r:id="rId36" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{F9895A6D-9843-4980-87D5-7F561A25F4EE}"/>
+    <hyperlink ref="D8" r:id="rId37" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{8B6F06C5-816D-4EFE-977E-EEA98DC54177}"/>
+    <hyperlink ref="G8" r:id="rId38" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C1DE1FE9-D2A9-4393-A330-861495F1397B}"/>
+    <hyperlink ref="E8" r:id="rId39" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{323268AD-B222-419C-8EDF-53EB3E3D12B3}"/>
+    <hyperlink ref="H8" r:id="rId40" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{8BAE758B-C416-4110-941E-B57F3FE6989A}"/>
+    <hyperlink ref="C8" r:id="rId41" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{26A588BD-E7C1-4904-9DAC-F4D934653274}"/>
+    <hyperlink ref="F8" r:id="rId42" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{EF34A091-06EE-4C94-AFA1-862768E611EC}"/>
+    <hyperlink ref="B9" r:id="rId43" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{8DD51027-5514-43B2-B003-1FD844525BDB}"/>
+    <hyperlink ref="D9" r:id="rId44" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{06D7DB9E-A731-4275-8B8D-749BB8A8DE36}"/>
+    <hyperlink ref="G9" r:id="rId45" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{A449ED1B-EF40-4E44-97B1-7D5387DF3A1F}"/>
+    <hyperlink ref="E9" r:id="rId46" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D50A010B-57B2-4FD8-8888-6F10E149DCF3}"/>
+    <hyperlink ref="H9" r:id="rId47" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5AD91EDD-33C9-4425-8E88-58FD36E75520}"/>
+    <hyperlink ref="C9" r:id="rId48" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{1A24D3E8-09C0-4222-8C58-51FAFDAA3A47}"/>
+    <hyperlink ref="F9" r:id="rId49" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{10682550-3E0B-4F50-B155-52E1EEDA5CFF}"/>
+    <hyperlink ref="B10" r:id="rId50" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{2A5E2958-4F2E-4E22-A387-18F0C104662C}"/>
+    <hyperlink ref="D10" r:id="rId51" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{6F9749FA-6930-4A72-83C5-706D9B267540}"/>
+    <hyperlink ref="G10" r:id="rId52" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C0E434D6-ADC0-465B-8F29-C07ED74ADF7A}"/>
+    <hyperlink ref="E10" r:id="rId53" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{4385E782-DCE2-46EB-AE44-04C47929936B}"/>
+    <hyperlink ref="H10" r:id="rId54" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{AAD9907A-AA11-458A-8D6D-1F51698549F1}"/>
+    <hyperlink ref="C10" r:id="rId55" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{21DD6728-C112-4AAD-809B-C396CAD352D5}"/>
+    <hyperlink ref="F10" r:id="rId56" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{2A974935-4B2D-4E26-9B92-2BB6A0EE1E64}"/>
+    <hyperlink ref="B11" r:id="rId57" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{E5DB9023-D7A9-4DBE-8B85-13C3C902D0FF}"/>
+    <hyperlink ref="D11" r:id="rId58" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{8437D7FB-2B62-46BD-81A6-DB3237B764CA}"/>
+    <hyperlink ref="G11" r:id="rId59" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{2A2A7F57-1F05-43DB-90E9-FBA7508B9894}"/>
+    <hyperlink ref="E11" r:id="rId60" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{5035A9FE-E981-4CBD-A8F7-1B404DF5EE7D}"/>
+    <hyperlink ref="H11" r:id="rId61" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{9A66F6B8-9650-4765-9711-0B1A92716BE7}"/>
+    <hyperlink ref="C11" r:id="rId62" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A8F626A7-6DB5-4F28-A1B5-E70F5540670B}"/>
+    <hyperlink ref="F11" r:id="rId63" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F99E1958-5A78-4B27-A391-1D79124B8567}"/>
+    <hyperlink ref="B12" r:id="rId64" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{7A1041D0-D797-4FD7-99D9-36E8E76F6A94}"/>
+    <hyperlink ref="D12" r:id="rId65" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{874D845C-6517-4C84-A088-C33F25DAC3A2}"/>
+    <hyperlink ref="G12" r:id="rId66" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{FC49E576-264A-4BE5-B4EB-A57056DABA15}"/>
+    <hyperlink ref="E12" r:id="rId67" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F4C8A260-D999-460D-AF5F-20BBE7309823}"/>
+    <hyperlink ref="H12" r:id="rId68" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{A57B2ABB-BA43-4C18-B9AD-F6F76B7D3ED2}"/>
+    <hyperlink ref="C12" r:id="rId69" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{4D6090D9-597E-4369-A7A4-0B5D779C3251}"/>
+    <hyperlink ref="F12" r:id="rId70" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{07B57694-A7E5-43CE-B09C-B2C3AAA98E0F}"/>
+    <hyperlink ref="B13" r:id="rId71" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{30F6F653-D950-4ABD-A04A-F5ED0D96F7AF}"/>
+    <hyperlink ref="D13" r:id="rId72" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{865D1E36-38C2-4B39-B076-2DE94DF32FF5}"/>
+    <hyperlink ref="G13" r:id="rId73" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3B99E8B8-F142-4A9C-8F7B-31D95C8D63A6}"/>
+    <hyperlink ref="E13" r:id="rId74" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{87DEEA51-0F9E-4338-9435-33EF3FE7EB11}"/>
+    <hyperlink ref="H13" r:id="rId75" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{09A95A1E-BF49-431D-9FEA-6509D2B54683}"/>
+    <hyperlink ref="C13" r:id="rId76" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{E50A17D3-3657-40B8-9025-88FC37F5EC11}"/>
+    <hyperlink ref="F13" r:id="rId77" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{81D88192-7602-48E8-BAB7-FFE6E36CAA20}"/>
+    <hyperlink ref="B14" r:id="rId78" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{99D3CDA9-A807-4A89-BFC4-34060E86EDE9}"/>
+    <hyperlink ref="D14" r:id="rId79" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D2F98FD9-1C26-4639-A342-A42B63A631AF}"/>
+    <hyperlink ref="G14" r:id="rId80" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{823FCF86-5732-427D-84E9-EC3694A1C8AD}"/>
+    <hyperlink ref="E14" r:id="rId81" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{BBD4EE22-A1E6-4B1A-85F3-AAFE447D2B40}"/>
+    <hyperlink ref="H14" r:id="rId82" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{D98E2414-6DFD-4C10-BB08-C1C5891E552F}"/>
+    <hyperlink ref="C14" r:id="rId83" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{2DC6E5F3-6754-4909-9304-919CE75B63F5}"/>
+    <hyperlink ref="F14" r:id="rId84" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{40EBB7EC-56B3-4A69-9BE1-6D6E597DCAD9}"/>
+    <hyperlink ref="B15" r:id="rId85" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{0CA5D80C-7594-4358-B95C-89D992706AE4}"/>
+    <hyperlink ref="D15" r:id="rId86" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{CF62512F-A773-45F8-9F42-882F7CDCE7F0}"/>
+    <hyperlink ref="G15" r:id="rId87" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{CB79D956-B4BA-4729-AA69-7343D8A5C4EF}"/>
+    <hyperlink ref="E15" r:id="rId88" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{89BDD2A7-5A88-44B7-A986-7327D43A5C27}"/>
+    <hyperlink ref="H15" r:id="rId89" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{DDC05ACD-E8D2-4B50-ADBF-0CB90E92EB3A}"/>
+    <hyperlink ref="C15" r:id="rId90" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A8D74216-B6CB-4303-86C7-E1C24E369B2B}"/>
+    <hyperlink ref="F15" r:id="rId91" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{D9253537-EF4A-49FB-87CA-4B8B9476417B}"/>
+    <hyperlink ref="B16" r:id="rId92" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{552AD646-ECD1-47BF-8A8A-EC39ACC335E8}"/>
+    <hyperlink ref="D16" r:id="rId93" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{3270D950-5210-491E-B32D-29BFD0DA003E}"/>
+    <hyperlink ref="G16" r:id="rId94" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{DC960230-5923-4FC1-8A5F-AFA7F804E172}"/>
+    <hyperlink ref="E16" r:id="rId95" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D91E2333-D54E-46ED-B96E-D9C45E14CDBE}"/>
+    <hyperlink ref="H16" r:id="rId96" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5F80B62A-A482-42DF-8B3E-BE9CF3A43039}"/>
+    <hyperlink ref="C16" r:id="rId97" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{EC6F981F-0660-42FB-8882-BC1984DE0824}"/>
+    <hyperlink ref="F16" r:id="rId98" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{491A8D80-D9B2-4D41-BA5C-C2C9438C950C}"/>
+    <hyperlink ref="B17" r:id="rId99" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{32C2C8EC-11DD-4113-A69C-D380AAF3CD71}"/>
+    <hyperlink ref="D17" r:id="rId100" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{745D1048-3102-4A4B-B055-35A5AB4290F3}"/>
+    <hyperlink ref="G17" r:id="rId101" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{7826E88A-A089-4C10-BC8A-0007C1397B23}"/>
+    <hyperlink ref="E17" r:id="rId102" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{84F30163-5D2B-4236-86F3-E27D97D2E032}"/>
+    <hyperlink ref="H17" r:id="rId103" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{DFD30610-B678-4BB1-8DCA-221439D39C3F}"/>
+    <hyperlink ref="C17" r:id="rId104" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{F5145E6A-0A3C-4487-8051-6470D8036E68}"/>
+    <hyperlink ref="F17" r:id="rId105" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{D160F93E-4CAC-44B1-BDFE-856C1013226E}"/>
+    <hyperlink ref="B18" r:id="rId106" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{530B5C57-9592-452D-9A57-F125F6855AD5}"/>
+    <hyperlink ref="D18" r:id="rId107" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D62D69D4-79B3-4E73-8373-D27E83B06E59}"/>
+    <hyperlink ref="G18" r:id="rId108" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{0CEA0B18-B796-4747-AE0D-2F07898CE281}"/>
+    <hyperlink ref="E18" r:id="rId109" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{C8189DF7-38D0-467F-89ED-EED3CE70E433}"/>
+    <hyperlink ref="H18" r:id="rId110" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{F7C097F4-FA89-4BD1-9CA6-ACFD513B9A50}"/>
+    <hyperlink ref="C18" r:id="rId111" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{90F98AE9-A1D8-4064-B2BD-495A6036D85A}"/>
+    <hyperlink ref="F18" r:id="rId112" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{97CCC1AD-4466-4BC7-8545-2D9ADC7E831D}"/>
+    <hyperlink ref="B19" r:id="rId113" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{033D27EE-8C8E-455E-B6E8-46D7CB3D874E}"/>
+    <hyperlink ref="D19" r:id="rId114" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{02F8F30A-EE57-422F-99F3-2EC5CED4EAE4}"/>
+    <hyperlink ref="G19" r:id="rId115" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{012BCE7E-FB10-49D2-BC4E-A0D5BB67C681}"/>
+    <hyperlink ref="E19" r:id="rId116" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{BA2D06C6-C326-4A77-A3D5-6C35ED8CF033}"/>
+    <hyperlink ref="H19" r:id="rId117" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{C177438B-F340-4394-A820-57093B55D0C5}"/>
+    <hyperlink ref="C19" r:id="rId118" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6A174D70-4C79-4250-AF08-FF1AD858F14A}"/>
+    <hyperlink ref="F19" r:id="rId119" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{7CBAAD7D-0353-4A7F-BED6-257956A90360}"/>
+    <hyperlink ref="B20" r:id="rId120" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{5C1B4E50-26BB-489B-895D-43E9C0AE8941}"/>
+    <hyperlink ref="D20" r:id="rId121" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{72EBA505-AF5E-4319-9358-4F1CD247647D}"/>
+    <hyperlink ref="G20" r:id="rId122" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{952BADBD-0308-485D-A9CA-F777645B019D}"/>
+    <hyperlink ref="E20" r:id="rId123" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{EF2C4BC8-3F1E-455D-9B01-65686CDB1D1E}"/>
+    <hyperlink ref="H20" r:id="rId124" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{CD4DB49C-775B-4849-88EC-972C30F5DF56}"/>
+    <hyperlink ref="C20" r:id="rId125" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{81CB0B20-9814-4FA2-AFAB-0D5CF784D221}"/>
+    <hyperlink ref="F20" r:id="rId126" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{01E21626-E228-44BE-A2E6-AC713D413A9D}"/>
+    <hyperlink ref="B21" r:id="rId127" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{6A14D52E-8DB1-4F15-B1E0-B85CDDFA2D12}"/>
+    <hyperlink ref="D21" r:id="rId128" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{CAB7B01F-5BA3-42BE-8401-DE0A4C907FA2}"/>
+    <hyperlink ref="G21" r:id="rId129" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F8AC209C-0DF5-4A65-990D-861AA4C7AABF}"/>
+    <hyperlink ref="E21" r:id="rId130" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A3AF97C9-70E3-40F3-B35A-2FBF23F293DA}"/>
+    <hyperlink ref="H21" r:id="rId131" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{A289880F-3E30-4595-889A-40C963E86411}"/>
+    <hyperlink ref="C21" r:id="rId132" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{4EAFDE29-0925-48F4-9955-8165F66204FE}"/>
+    <hyperlink ref="F21" r:id="rId133" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{6F63993D-4E1F-4C0C-B023-04F171E67936}"/>
+    <hyperlink ref="B22" r:id="rId134" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A22D60C4-B465-4E32-87E8-8A63E6E5D447}"/>
+    <hyperlink ref="D22" r:id="rId135" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D588E6D7-8FA0-4178-BB3F-AE34E3938996}"/>
+    <hyperlink ref="G22" r:id="rId136" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{38C78D12-B6AA-4577-93F7-D798CBD5BC56}"/>
+    <hyperlink ref="E22" r:id="rId137" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{5CE03A88-8E2D-44AE-9C5D-27767C8A02AB}"/>
+    <hyperlink ref="H22" r:id="rId138" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{A356EF5B-9698-438C-A5B5-FD5C94927536}"/>
+    <hyperlink ref="C22" r:id="rId139" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{604F2970-30B6-48BC-8901-B1A120823A55}"/>
+    <hyperlink ref="F22" r:id="rId140" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{CD58D5C7-999B-410E-98EA-AE70B0DBD331}"/>
+    <hyperlink ref="B2" r:id="rId141" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{BCA74B87-10D8-4FAE-8881-4D04E2DA9EE0}"/>
+    <hyperlink ref="D2" r:id="rId142" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{F1D7E55B-7088-4D07-BC77-B2282FFD4739}"/>
+    <hyperlink ref="G2" r:id="rId143" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{35080FDC-BDD2-4A32-8D03-B26F399BAC26}"/>
+    <hyperlink ref="E2" r:id="rId144" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{45352292-330F-4FBB-B864-4DCFC9F28414}"/>
+    <hyperlink ref="H2" r:id="rId145" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{8405DEB6-025E-4BB5-92BD-49CEC4E1D773}"/>
+    <hyperlink ref="C2" r:id="rId146" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{CF3BA994-8600-4BFC-B7F2-8BB39EB49EA2}"/>
+    <hyperlink ref="F2" r:id="rId147" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{624FB2D6-E71A-4FC7-BD2F-5377B68D805B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId141"/>
-  <drawing r:id="rId142"/>
+  <pageSetup orientation="portrait" r:id="rId148"/>
+  <drawing r:id="rId149"/>
   <tableParts count="1">
-    <tablePart r:id="rId143"/>
+    <tablePart r:id="rId150"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC3F3FC-17EF-4D6A-9290-8FAFFC789915}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.5546875" customWidth="1"/>
@@ -16000,6 +16126,24 @@
         <v>14</v>
       </c>
       <c r="E23" s="14">
+        <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="A24" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" s="14">
+        <v>98</v>
+      </c>
+      <c r="C24" s="14">
+        <v>1</v>
+      </c>
+      <c r="D24" s="14">
+        <v>14</v>
+      </c>
+      <c r="E24" s="14">
         <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
         <v>113</v>
       </c>

--- a/data/SDET_SQA_DATA.xlsx
+++ b/data/SDET_SQA_DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WHSU\Desktop\Workspace\CycleView\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCFDB091-DB85-4B41-BE49-DF0CA87066B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3644D7-296B-4D96-9B91-9D196231DB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{EB11FF79-EF06-B64E-AA6A-0CFF391A8BD1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{EB11FF79-EF06-B64E-AA6A-0CFF391A8BD1}"/>
   </bookViews>
   <sheets>
     <sheet name="TestAutomationProgress" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="108">
   <si>
     <t>TODO (P1)</t>
   </si>
@@ -357,6 +357,15 @@
   </si>
   <si>
     <t>26W13</t>
+  </si>
+  <si>
+    <t>v1.41</t>
+  </si>
+  <si>
+    <t>y25w28</t>
+  </si>
+  <si>
+    <t>26W14</t>
   </si>
 </sst>
 </file>
@@ -1094,9 +1103,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$24</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$25</c:f>
               <c:strCache>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>25W40</c:v>
                 </c:pt>
@@ -1165,16 +1174,19 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>26W13</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>26W14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$B$2:$B$24</c:f>
+              <c:f>TestAutomationProgress!$B$2:$B$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>15</c:v>
                 </c:pt>
@@ -1242,6 +1254,9 @@
                   <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="22">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
@@ -1339,9 +1354,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$24</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$25</c:f>
               <c:strCache>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>25W40</c:v>
                 </c:pt>
@@ -1410,16 +1425,19 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>26W13</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>26W14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$C$2:$C$24</c:f>
+              <c:f>TestAutomationProgress!$C$2:$C$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>14</c:v>
                 </c:pt>
@@ -1487,6 +1505,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="22">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1584,9 +1605,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$24</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$25</c:f>
               <c:strCache>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>25W40</c:v>
                 </c:pt>
@@ -1655,16 +1676,19 @@
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>26W13</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>26W14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$D$2:$D$24</c:f>
+              <c:f>TestAutomationProgress!$D$2:$D$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>219</c:v>
                 </c:pt>
@@ -1732,6 +1756,9 @@
                   <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="22">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>160</c:v>
                 </c:pt>
               </c:numCache>
@@ -2109,9 +2136,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$19</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2165,16 +2192,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>v1.40</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>v1.41</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$B$2:$B$19</c:f>
+              <c:f>'Humi-TestResult'!$B$2:$B$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>421</c:v>
                 </c:pt>
@@ -2228,6 +2258,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>572</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2264,9 +2297,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$19</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2320,16 +2353,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>v1.40</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>v1.41</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$C$2:$C$19</c:f>
+              <c:f>'Humi-TestResult'!$C$2:$C$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2382,6 +2418,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2427,9 +2466,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$19</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2483,16 +2522,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>v1.40</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>v1.41</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$D$2:$D$19</c:f>
+              <c:f>'Humi-TestResult'!$D$2:$D$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>12</c:v>
                 </c:pt>
@@ -2546,6 +2588,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2636,9 +2681,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$19</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2692,16 +2737,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>v1.40</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>v1.41</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$E$2:$E$19</c:f>
+              <c:f>'Humi-TestResult'!$E$2:$E$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -2755,6 +2803,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2791,9 +2842,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$19</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2847,16 +2898,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>v1.40</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>v1.41</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$F$2:$F$19</c:f>
+              <c:f>'Humi-TestResult'!$F$2:$F$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -2910,6 +2964,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2948,9 +3005,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$19</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -3004,16 +3061,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>v1.40</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>v1.41</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$G$2:$G$19</c:f>
+              <c:f>'Humi-TestResult'!$G$2:$G$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3067,6 +3127,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3180,9 +3243,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$19</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -3236,16 +3299,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>v1.40</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>v1.41</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$H$2:$H$19</c:f>
+              <c:f>'Humi-TestResult'!$H$2:$H$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>442</c:v>
                 </c:pt>
@@ -3299,6 +3365,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>592</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>281</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3672,9 +3741,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$36</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$38</c:f>
               <c:strCache>
-                <c:ptCount val="35"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -3779,16 +3848,22 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>26W12</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>26W13</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>26W14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$B$2:$B$36</c:f>
+              <c:f>'SOVA-TestResult'!$B$2:$B$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>38</c:v>
                 </c:pt>
@@ -3868,6 +3943,12 @@
                   <c:v>694</c:v>
                 </c:pt>
                 <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>481</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -3962,9 +4043,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$36</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$38</c:f>
               <c:strCache>
-                <c:ptCount val="35"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4069,16 +4150,22 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>26W12</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>26W13</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>26W14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$C$2:$C$36</c:f>
+              <c:f>'SOVA-TestResult'!$C$2:$C$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4158,6 +4245,12 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4195,9 +4288,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$36</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$38</c:f>
               <c:strCache>
-                <c:ptCount val="35"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4302,16 +4395,22 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>26W12</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>26W13</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>26W14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$D$2:$D$36</c:f>
+              <c:f>'SOVA-TestResult'!$D$2:$D$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4391,6 +4490,12 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4428,9 +4533,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$36</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$38</c:f>
               <c:strCache>
-                <c:ptCount val="35"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4535,16 +4640,22 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>26W12</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>26W13</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>26W14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$E$2:$E$36</c:f>
+              <c:f>'SOVA-TestResult'!$E$2:$E$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
                 </c:pt>
@@ -4624,6 +4735,12 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4735,9 +4852,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$36</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$38</c:f>
               <c:strCache>
-                <c:ptCount val="35"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4842,16 +4959,22 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>26W12</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>26W13</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>26W14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$F$2:$F$36</c:f>
+              <c:f>'SOVA-TestResult'!$F$2:$F$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>11</c:v>
                 </c:pt>
@@ -4931,6 +5054,12 @@
                   <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4971,9 +5100,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$36</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$38</c:f>
               <c:strCache>
-                <c:ptCount val="35"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -5078,16 +5207,22 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>26W12</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>26W13</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>26W14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$G$2:$G$36</c:f>
+              <c:f>'SOVA-TestResult'!$G$2:$G$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5167,7 +5302,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>485</c:v>
+                  <c:v>508</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>508</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5209,9 +5350,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$36</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$38</c:f>
               <c:strCache>
-                <c:ptCount val="35"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -5316,16 +5457,22 @@
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>26W12</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>26W13</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>26W14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$H$2:$H$36</c:f>
+              <c:f>'SOVA-TestResult'!$H$2:$H$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>54</c:v>
                 </c:pt>
@@ -5405,7 +5552,13 @@
                   <c:v>703</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>485</c:v>
+                  <c:v>508</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>508</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>508</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5775,9 +5928,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$22</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -5840,16 +5993,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>v1.40</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>v1.41</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$B$2:$B$22</c:f>
+              <c:f>'Humi-BugTrend'!$B$2:$B$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>9</c:v>
                 </c:pt>
@@ -5890,7 +6046,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>11</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0</c:v>
@@ -5908,10 +6064,13 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>9</c:v>
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5951,9 +6110,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$22</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -6016,16 +6175,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>v1.40</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>v1.41</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$C$2:$C$22</c:f>
+              <c:f>'Humi-BugTrend'!$C$2:$C$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6087,6 +6249,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -6127,9 +6292,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$22</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -6192,16 +6357,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>v1.40</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>v1.41</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$D$2:$D$22</c:f>
+              <c:f>'Humi-BugTrend'!$D$2:$D$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6263,6 +6431,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -6300,9 +6471,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$22</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -6365,16 +6536,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>v1.40</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>v1.41</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$E$2:$E$22</c:f>
+              <c:f>'Humi-BugTrend'!$E$2:$E$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6436,6 +6610,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -6473,9 +6650,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$22</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -6538,16 +6715,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>v1.40</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>v1.41</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$F$2:$F$22</c:f>
+              <c:f>'Humi-BugTrend'!$F$2:$F$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6609,6 +6789,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -6646,9 +6829,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$22</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -6711,16 +6894,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>v1.40</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>v1.41</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$G$2:$G$22</c:f>
+              <c:f>'Humi-BugTrend'!$G$2:$G$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>66</c:v>
                 </c:pt>
@@ -6782,7 +6968,10 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>37</c:v>
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6821,9 +7010,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$22</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -6886,16 +7075,19 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>v1.40</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>v1.41</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$H$2:$H$22</c:f>
+              <c:f>'Humi-BugTrend'!$H$2:$H$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>75</c:v>
                 </c:pt>
@@ -6936,7 +7128,7 @@
                   <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>51</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>38</c:v>
@@ -6954,10 +7146,13 @@
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>11</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46</c:v>
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7330,70 +7525,73 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$22</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>y25w28</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>y25w30</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>y25w32</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>y25w34</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>y25w36</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>y25w38</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>y25w40</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>y25w42</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>y25w44</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>y25w46</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>y25w48</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>y25w50</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>y25w52</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>y26w2</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>y26w4</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>y26w6</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>y26w8</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>y26w10</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>y26w12</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>y26w14</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>y26w16</c:v>
                 </c:pt>
               </c:strCache>
@@ -7401,12 +7599,12 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$B$2:$B$22</c:f>
+              <c:f>'SOVA-BugTrend'!$B$2:$B$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>31</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
@@ -7418,13 +7616,13 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -7436,37 +7634,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
                 <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="18">
-                  <c:v>7</c:v>
-                </c:pt>
                 <c:pt idx="19">
-                  <c:v>8</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5</c:v>
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7560,70 +7761,73 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$22</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>y25w28</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>y25w30</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>y25w32</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>y25w34</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>y25w36</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>y25w38</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>y25w40</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>y25w42</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>y25w44</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>y25w46</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>y25w48</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>y25w50</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>y25w52</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>y26w2</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>y26w4</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>y26w6</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>y26w8</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>y26w10</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>y26w12</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>y26w14</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>y26w16</c:v>
                 </c:pt>
               </c:strCache>
@@ -7631,10 +7835,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$C$2:$C$22</c:f>
+              <c:f>'SOVA-BugTrend'!$C$2:$C$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7684,7 +7888,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>1</c:v>
@@ -7697,6 +7901,9 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7790,70 +7997,73 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$22</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>y25w28</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>y25w30</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>y25w32</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>y25w34</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>y25w36</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>y25w38</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>y25w40</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>y25w42</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>y25w44</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>y25w46</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>y25w48</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>y25w50</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>y25w52</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>y26w2</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>y26w4</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>y26w6</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>y26w8</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>y26w10</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>y26w12</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>y26w14</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>y26w16</c:v>
                 </c:pt>
               </c:strCache>
@@ -7861,10 +8071,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$D$2:$D$22</c:f>
+              <c:f>'SOVA-BugTrend'!$D$2:$D$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7920,12 +8130,15 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -8020,70 +8233,73 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$22</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>y25w28</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>y25w30</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>y25w32</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>y25w34</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>y25w36</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>y25w38</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>y25w40</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>y25w42</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>y25w44</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>y25w46</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>y25w48</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>y25w50</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>y25w52</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>y26w2</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>y26w4</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>y26w6</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>y26w8</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>y26w10</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>y26w12</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>y26w14</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>y26w16</c:v>
                 </c:pt>
               </c:strCache>
@@ -8091,71 +8307,74 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$E$2:$E$22</c:f>
+              <c:f>'SOVA-BugTrend'!$E$2:$E$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -8193,70 +8412,73 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$22</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>y25w28</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>y25w30</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>y25w32</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>y25w34</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>y25w36</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>y25w38</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>y25w40</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>y25w42</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>y25w44</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>y25w46</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>y25w48</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>y25w50</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>y25w52</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>y26w2</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>y26w4</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>y26w6</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>y26w8</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>y26w10</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>y26w12</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>y26w14</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>y26w16</c:v>
                 </c:pt>
               </c:strCache>
@@ -8264,10 +8486,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$F$2:$F$22</c:f>
+              <c:f>'SOVA-BugTrend'!$F$2:$F$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8329,6 +8551,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -8420,70 +8645,73 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$22</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>y25w28</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>y25w30</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>y25w32</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>y25w34</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>y25w36</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>y25w38</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>y25w40</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>y25w42</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>y25w44</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>y25w46</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>y25w48</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>y25w50</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>y25w52</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>y26w2</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>y26w4</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>y26w6</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>y26w8</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>y26w10</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>y26w12</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>y26w14</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>y26w16</c:v>
                 </c:pt>
               </c:strCache>
@@ -8491,60 +8719,60 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$G$2:$G$22</c:f>
+              <c:f>'SOVA-BugTrend'!$G$2:$G$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>45</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>18</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>25</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>45</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>24</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>43</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>35</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>29</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>40</c:v>
-                </c:pt>
                 <c:pt idx="11">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>32</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>31</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>33</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>14</c:v>
@@ -8553,10 +8781,13 @@
                   <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8595,70 +8826,73 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$22</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>y25w28</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>y25w30</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>y25w32</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>y25w34</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>y25w36</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>y25w38</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>y25w40</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>y25w42</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>y25w44</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>y25w46</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>y25w48</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>y25w50</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>y25w52</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>y26w2</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>y26w4</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>y26w6</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>y26w8</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>y26w10</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>y26w12</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>y26w14</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>y26w16</c:v>
                 </c:pt>
               </c:strCache>
@@ -8666,72 +8900,75 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$H$2:$H$22</c:f>
+              <c:f>'SOVA-BugTrend'!$H$2:$H$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="17">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8770,70 +9007,73 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$22</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>y25w28</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>y25w30</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>y25w32</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>y25w34</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>y25w36</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>y25w38</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>y25w40</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>y25w42</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>y25w44</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>y25w46</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>y25w48</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>y25w50</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>y25w52</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>y26w2</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>y26w4</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>y26w6</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>y26w8</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>y26w10</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>y26w12</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>y26w14</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>y26w16</c:v>
                 </c:pt>
               </c:strCache>
@@ -8841,72 +9081,75 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$I$2:$I$22</c:f>
+              <c:f>'SOVA-BugTrend'!$I$2:$I$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>39</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>46</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>53</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>32</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>53</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>25</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>43</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>35</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>29</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>44</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>31</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>36</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>37</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>26</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>27</c:v>
                 </c:pt>
-                <c:pt idx="18">
-                  <c:v>25</c:v>
-                </c:pt>
                 <c:pt idx="19">
-                  <c:v>9</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5</c:v>
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11838,13 +12081,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>171448</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>55</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>133348</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -11879,13 +12122,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1057275</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -11919,15 +12162,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>69662</xdr:rowOff>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>41087</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1057275</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>31562</xdr:rowOff>
+      <xdr:colOff>1047750</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>2987</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11961,13 +12204,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>88899</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -12038,8 +12281,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}" name="Table2" displayName="Table2" ref="A1:E24" totalsRowShown="0" headerRowDxfId="35">
-  <autoFilter ref="A1:E24" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}" name="Table2" displayName="Table2" ref="A1:E25" totalsRowShown="0" headerRowDxfId="35">
+  <autoFilter ref="A1:E25" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F25F0D34-0297-4771-8BBB-350BCDD85D46}" name="Week"/>
     <tableColumn id="2" xr3:uid="{39CFCD12-3130-47A8-A140-DBF602F1743D}" name="Done"/>
@@ -12054,8 +12297,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E42B6291-7056-475B-AE1E-CA59C524E5F1}" name="Table1" displayName="Table1" ref="A1:H19" totalsRowShown="0" headerRowDxfId="33">
-  <autoFilter ref="A1:H19" xr:uid="{E42B6291-7056-475B-AE1E-CA59C524E5F1}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E42B6291-7056-475B-AE1E-CA59C524E5F1}" name="Table1" displayName="Table1" ref="A1:H20" totalsRowShown="0" headerRowDxfId="33">
+  <autoFilter ref="A1:H20" xr:uid="{E42B6291-7056-475B-AE1E-CA59C524E5F1}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{9154D4F8-C83D-4DB9-9182-818F32FA7C26}" name="Versions"/>
     <tableColumn id="2" xr3:uid="{1FE19FA2-B8BE-47BC-9953-F802445DE79D}" name="Passed"/>
@@ -12073,8 +12316,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}" name="Table3" displayName="Table3" ref="A1:H36" totalsRowShown="0" headerRowDxfId="31">
-  <autoFilter ref="A1:H36" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}" name="Table3" displayName="Table3" ref="A1:H38" totalsRowShown="0" headerRowDxfId="31">
+  <autoFilter ref="A1:H38" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{8103CDF3-74DC-4B31-821D-E20368EA5455}" name="Versions"/>
     <tableColumn id="2" xr3:uid="{6C3B261F-FA51-42D2-821A-F22633569372}" name="Passed"/>
@@ -12092,8 +12335,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{E4AD0B7A-EC5B-4838-AC2B-8475A3B6644B}" name="Table7" displayName="Table7" ref="A1:H22" totalsRowShown="0" headerRowDxfId="29">
-  <autoFilter ref="A1:H22" xr:uid="{E4AD0B7A-EC5B-4838-AC2B-8475A3B6644B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{E4AD0B7A-EC5B-4838-AC2B-8475A3B6644B}" name="Table7" displayName="Table7" ref="A1:H23" totalsRowShown="0" headerRowDxfId="29">
+  <autoFilter ref="A1:H23" xr:uid="{E4AD0B7A-EC5B-4838-AC2B-8475A3B6644B}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{58F8A895-CEBE-41D2-B7BB-1681C0697C85}" name="Version"/>
     <tableColumn id="2" xr3:uid="{CE08A48D-2419-484B-993C-54A546869B61}" name="To Do" dataDxfId="28"/>
@@ -12111,8 +12354,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}" name="Table5" displayName="Table5" ref="A1:I22" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17" totalsRowBorderDxfId="16" dataCellStyle="Hyperlink">
-  <autoFilter ref="A1:I22" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}" name="Table5" displayName="Table5" ref="A1:I23" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17" totalsRowBorderDxfId="16" dataCellStyle="Hyperlink">
+  <autoFilter ref="A1:I23" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{5BE08AE0-E0B5-4B46-9423-456B88C2D9BC}" name="Sprint" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{030F9647-4FC0-4C7E-9B3A-AB099CC59EBA}" name="To Do (0%)" dataDxfId="6" dataCellStyle="Hyperlink"/>
@@ -12131,8 +12374,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}" name="Table25" displayName="Table25" ref="A1:E24" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
-  <autoFilter ref="A1:E24" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}" name="Table25" displayName="Table25" ref="A1:E25" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+  <autoFilter ref="A1:E25" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{7070D9F2-0ED1-4F39-8D72-28B37C8E98F2}" name="Week" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{1173F443-CC27-4C6E-A432-BF66DB2A740E}" name="Done" dataDxfId="11"/>
@@ -12463,7 +12706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D733A42-966D-5F4E-B061-B304543CE88E}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.77734375" customWidth="1"/>
@@ -12897,6 +13140,23 @@
         <v>160</v>
       </c>
       <c r="E24" s="12">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A25" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25">
+        <v>37</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>160</v>
+      </c>
+      <c r="E25" s="12">
         <v>198</v>
       </c>
     </row>
@@ -12912,7 +13172,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6429633B-8BD2-084C-8C0F-75969053522F}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -13430,6 +13690,33 @@
       <c r="H19">
         <f>SUM(Table1[[#This Row],[Passed]:[Untested]])</f>
         <v>592</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="21.95" customHeight="1">
+      <c r="A20" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20">
+        <v>100</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>181</v>
+      </c>
+      <c r="H20">
+        <f>SUM(Table1[[#This Row],[Passed]:[Untested]])</f>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -13444,7 +13731,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA6EDF6-834F-DA49-B3FC-BFE1673433AB}">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
@@ -14241,11 +14528,65 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>485</v>
+        <v>508</v>
       </c>
       <c r="H36" s="12">
         <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
-        <v>485</v>
+        <v>508</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="A37" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37">
+        <v>481</v>
+      </c>
+      <c r="C37">
+        <v>14</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>4</v>
+      </c>
+      <c r="F37">
+        <v>9</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37" s="12">
+        <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
+        <v>508</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="A38" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>508</v>
+      </c>
+      <c r="H38" s="12">
+        <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
+        <v>508</v>
       </c>
     </row>
   </sheetData>
@@ -14260,7 +14601,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7C79DB4-6EC1-E840-9DE9-46C117A6F960}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
@@ -14654,7 +14995,7 @@
         <v>47</v>
       </c>
       <c r="B15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -14673,7 +15014,7 @@
       </c>
       <c r="H15">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -14816,7 +15157,7 @@
         <v>87</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -14833,9 +15174,9 @@
       <c r="G21">
         <v>8</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="12">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -14843,7 +15184,7 @@
         <v>93</v>
       </c>
       <c r="B22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -14858,11 +15199,38 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>37</v>
-      </c>
-      <c r="H22" s="12">
+        <v>41</v>
+      </c>
+      <c r="H22">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>46</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" s="12">
+        <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -14877,7 +15245,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7487DEB-55FC-DC4E-A4B1-F7171B8F3237}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.21875" customWidth="1"/>
@@ -14924,7 +15292,7 @@
         <v>99</v>
       </c>
       <c r="B2" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="5">
         <v>0</v>
@@ -14933,25 +15301,25 @@
         <v>0</v>
       </c>
       <c r="E2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>0</v>
       </c>
       <c r="G2" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" s="5">
         <v>2</v>
       </c>
       <c r="I2" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18" thickBot="1">
       <c r="A3" s="4" t="s">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="B3" s="5">
         <v>1</v>
@@ -14972,16 +15340,16 @@
         <v>39</v>
       </c>
       <c r="H3" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I3" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" thickBot="1">
       <c r="A4" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" s="5">
         <v>1</v>
@@ -14999,19 +15367,19 @@
         <v>0</v>
       </c>
       <c r="G4" s="5">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H4" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" thickBot="1">
       <c r="A5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" s="5">
         <v>1</v>
@@ -15029,22 +15397,22 @@
         <v>0</v>
       </c>
       <c r="G5" s="5">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>20</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="18" thickBot="1">
       <c r="A6" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6" s="5">
         <v>0</v>
@@ -15059,19 +15427,19 @@
         <v>0</v>
       </c>
       <c r="G6" s="5">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H6" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18" thickBot="1">
       <c r="A7" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B7" s="5">
         <v>3</v>
@@ -15089,22 +15457,22 @@
         <v>0</v>
       </c>
       <c r="G7" s="5">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="H7" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I7" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>53</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="18" thickBot="1">
       <c r="A8" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C8" s="5">
         <v>0</v>
@@ -15119,19 +15487,19 @@
         <v>0</v>
       </c>
       <c r="G8" s="5">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="H8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>25</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="18" thickBot="1">
       <c r="A9" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B9" s="5">
         <v>0</v>
@@ -15149,19 +15517,19 @@
         <v>0</v>
       </c>
       <c r="G9" s="5">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="18" thickBot="1">
       <c r="A10" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B10" s="5">
         <v>0</v>
@@ -15179,19 +15547,19 @@
         <v>0</v>
       </c>
       <c r="G10" s="5">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H10" s="5">
         <v>0</v>
       </c>
       <c r="I10" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="18" thickBot="1">
       <c r="A11" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11" s="5">
         <v>0</v>
@@ -15209,22 +15577,22 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H11" s="5">
         <v>0</v>
       </c>
       <c r="I11" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="18" thickBot="1">
       <c r="A12" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B12" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C12" s="5">
         <v>0</v>
@@ -15239,19 +15607,19 @@
         <v>0</v>
       </c>
       <c r="G12" s="5">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H12" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>44</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18" thickBot="1">
       <c r="A13" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B13" s="5">
         <v>3</v>
@@ -15269,22 +15637,22 @@
         <v>0</v>
       </c>
       <c r="G13" s="5">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H13" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18" thickBot="1">
       <c r="A14" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B14" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" s="5">
         <v>0</v>
@@ -15299,10 +15667,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
@@ -15311,10 +15679,10 @@
     </row>
     <row r="15" spans="1:9" ht="18" thickBot="1">
       <c r="A15" s="4" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="B15" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C15" s="5">
         <v>0</v>
@@ -15329,22 +15697,22 @@
         <v>0</v>
       </c>
       <c r="G15" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H15" s="5">
         <v>0</v>
       </c>
       <c r="I15" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="18" thickBot="1">
       <c r="A16" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B16" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" s="5">
         <v>0</v>
@@ -15359,22 +15727,22 @@
         <v>0</v>
       </c>
       <c r="G16" s="5">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H16" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="18" thickBot="1">
       <c r="A17" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B17" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C17" s="5">
         <v>0</v>
@@ -15389,25 +15757,25 @@
         <v>0</v>
       </c>
       <c r="G17" s="5">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H17" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I17" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="18" thickBot="1">
       <c r="A18" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B18" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="5">
         <v>0</v>
@@ -15419,22 +15787,22 @@
         <v>0</v>
       </c>
       <c r="G18" s="5">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H18" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I18" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="18" thickBot="1">
       <c r="A19" s="4" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B19" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" s="5">
         <v>1</v>
@@ -15452,28 +15820,28 @@
         <v>14</v>
       </c>
       <c r="H19" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I19" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="18" thickBot="1">
       <c r="A20" s="4" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B20" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C20" s="5">
         <v>1</v>
       </c>
       <c r="D20" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="5">
         <v>0</v>
@@ -15482,19 +15850,19 @@
         <v>14</v>
       </c>
       <c r="H20" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I20" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="18" thickBot="1">
       <c r="A21" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B21" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C21" s="5">
         <v>1</v>
@@ -15509,22 +15877,22 @@
         <v>0</v>
       </c>
       <c r="G21" s="5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H21" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I21" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="18" thickBot="1">
       <c r="A22" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B22" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" s="5">
         <v>0</v>
@@ -15533,185 +15901,222 @@
         <v>0</v>
       </c>
       <c r="E22" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" s="5">
         <v>0</v>
       </c>
       <c r="I22" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>5</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="18" thickBot="1">
+      <c r="A23" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" s="5">
+        <v>12</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5">
+        <v>1</v>
+      </c>
+      <c r="H23" s="5">
+        <v>2</v>
+      </c>
+      <c r="I23" s="15">
+        <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{09F7A302-1404-4715-8128-181D35E5D8B9}"/>
-    <hyperlink ref="D3" r:id="rId2" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{76635EFC-D384-419A-A59C-C55EC8240726}"/>
-    <hyperlink ref="G3" r:id="rId3" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{42093993-73C6-4BB9-80D7-36685152171C}"/>
-    <hyperlink ref="E3" r:id="rId4" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{37DC5DA8-1239-4E51-8969-C2BCE4653444}"/>
-    <hyperlink ref="H3" r:id="rId5" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E6FD163E-6C57-4EF3-8B9C-269D8B7B50E2}"/>
-    <hyperlink ref="C3" r:id="rId6" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{D7E85314-DB61-45C5-8060-3EB33C25D3B6}"/>
-    <hyperlink ref="F3" r:id="rId7" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C69F1513-3C37-4AB1-A9B8-3092C1C10148}"/>
-    <hyperlink ref="B4" r:id="rId8" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{76B296F7-BFF3-4A65-9F00-E5C1557AE833}"/>
-    <hyperlink ref="D4" r:id="rId9" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{A19D1D61-53D9-4AB4-BDE3-EBCB3572C0D5}"/>
-    <hyperlink ref="G4" r:id="rId10" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{4AB520F8-F7B0-45A9-9CC3-37170DC9B8DB}"/>
-    <hyperlink ref="E4" r:id="rId11" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B9FCE681-4673-4949-ACB3-8DAE2F7FD250}"/>
-    <hyperlink ref="H4" r:id="rId12" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{027C6980-9510-454F-9FEC-4AF0F8380BAF}"/>
-    <hyperlink ref="C4" r:id="rId13" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{941C500C-86D3-4A7F-92AF-42FEB23C4900}"/>
-    <hyperlink ref="F4" r:id="rId14" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{184E0C28-F946-4D37-9471-166141674777}"/>
-    <hyperlink ref="B5" r:id="rId15" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{CD326838-C12B-451E-B276-AAA4C01E7484}"/>
-    <hyperlink ref="D5" r:id="rId16" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{69ECC71E-7D3B-4FF6-8C8F-20BC6662447E}"/>
-    <hyperlink ref="G5" r:id="rId17" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{143835A4-3D69-4457-A785-FA8353333EFF}"/>
-    <hyperlink ref="E5" r:id="rId18" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{CE5F0CFB-0AC4-4FC9-A917-E619A44BA7F6}"/>
-    <hyperlink ref="H5" r:id="rId19" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{0C7859E8-B6DB-4267-88FC-F2895481CF6E}"/>
-    <hyperlink ref="C5" r:id="rId20" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{96F6155A-1A88-46F7-AF8C-A04AF42C9D84}"/>
-    <hyperlink ref="F5" r:id="rId21" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A52FC7DC-AFE8-4739-822B-48EF80E4F8A9}"/>
-    <hyperlink ref="B6" r:id="rId22" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{36B3D1D5-2F6B-425F-9BF6-C31DF571EC8D}"/>
-    <hyperlink ref="D6" r:id="rId23" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{BB516DE7-BB41-4BFF-8E99-3345517C6192}"/>
-    <hyperlink ref="G6" r:id="rId24" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{B19055D8-3BE4-40F2-BFB8-B1B36097458B}"/>
-    <hyperlink ref="E6" r:id="rId25" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{7FB0FDC2-4FA6-4FFF-A923-E521B206DADA}"/>
-    <hyperlink ref="H6" r:id="rId26" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{40F2FE10-085A-4B9B-B5A3-B3585E2D3D57}"/>
-    <hyperlink ref="C6" r:id="rId27" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{60BE2628-B52A-40B4-90F9-C5EDE979E015}"/>
-    <hyperlink ref="F6" r:id="rId28" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{29580453-F811-482D-B314-07AAFC6CE690}"/>
-    <hyperlink ref="B7" r:id="rId29" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C18D93D7-445A-4642-9072-BE6C545D4EEA}"/>
-    <hyperlink ref="D7" r:id="rId30" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{909A918D-89F9-4228-85A0-85C0F37F66A0}"/>
-    <hyperlink ref="G7" r:id="rId31" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{B41D871E-5260-4559-8823-0484CCDBCE54}"/>
-    <hyperlink ref="E7" r:id="rId32" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{425A623A-4358-45E0-A57F-84C442A0C12A}"/>
-    <hyperlink ref="H7" r:id="rId33" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{3794C7C7-AE24-47F3-8E88-27CE9CDB738E}"/>
-    <hyperlink ref="C7" r:id="rId34" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{4BDCC3AB-46D0-47A5-9C7C-6F427D455C60}"/>
-    <hyperlink ref="F7" r:id="rId35" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{3B6DDE0C-C1AF-4711-9D0C-1A42166E62CD}"/>
-    <hyperlink ref="B8" r:id="rId36" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{F9895A6D-9843-4980-87D5-7F561A25F4EE}"/>
-    <hyperlink ref="D8" r:id="rId37" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{8B6F06C5-816D-4EFE-977E-EEA98DC54177}"/>
-    <hyperlink ref="G8" r:id="rId38" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C1DE1FE9-D2A9-4393-A330-861495F1397B}"/>
-    <hyperlink ref="E8" r:id="rId39" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{323268AD-B222-419C-8EDF-53EB3E3D12B3}"/>
-    <hyperlink ref="H8" r:id="rId40" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{8BAE758B-C416-4110-941E-B57F3FE6989A}"/>
-    <hyperlink ref="C8" r:id="rId41" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{26A588BD-E7C1-4904-9DAC-F4D934653274}"/>
-    <hyperlink ref="F8" r:id="rId42" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{EF34A091-06EE-4C94-AFA1-862768E611EC}"/>
-    <hyperlink ref="B9" r:id="rId43" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{8DD51027-5514-43B2-B003-1FD844525BDB}"/>
-    <hyperlink ref="D9" r:id="rId44" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{06D7DB9E-A731-4275-8B8D-749BB8A8DE36}"/>
-    <hyperlink ref="G9" r:id="rId45" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{A449ED1B-EF40-4E44-97B1-7D5387DF3A1F}"/>
-    <hyperlink ref="E9" r:id="rId46" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D50A010B-57B2-4FD8-8888-6F10E149DCF3}"/>
-    <hyperlink ref="H9" r:id="rId47" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5AD91EDD-33C9-4425-8E88-58FD36E75520}"/>
-    <hyperlink ref="C9" r:id="rId48" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{1A24D3E8-09C0-4222-8C58-51FAFDAA3A47}"/>
-    <hyperlink ref="F9" r:id="rId49" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{10682550-3E0B-4F50-B155-52E1EEDA5CFF}"/>
-    <hyperlink ref="B10" r:id="rId50" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{2A5E2958-4F2E-4E22-A387-18F0C104662C}"/>
-    <hyperlink ref="D10" r:id="rId51" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{6F9749FA-6930-4A72-83C5-706D9B267540}"/>
-    <hyperlink ref="G10" r:id="rId52" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C0E434D6-ADC0-465B-8F29-C07ED74ADF7A}"/>
-    <hyperlink ref="E10" r:id="rId53" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{4385E782-DCE2-46EB-AE44-04C47929936B}"/>
-    <hyperlink ref="H10" r:id="rId54" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{AAD9907A-AA11-458A-8D6D-1F51698549F1}"/>
-    <hyperlink ref="C10" r:id="rId55" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{21DD6728-C112-4AAD-809B-C396CAD352D5}"/>
-    <hyperlink ref="F10" r:id="rId56" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{2A974935-4B2D-4E26-9B92-2BB6A0EE1E64}"/>
-    <hyperlink ref="B11" r:id="rId57" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{E5DB9023-D7A9-4DBE-8B85-13C3C902D0FF}"/>
-    <hyperlink ref="D11" r:id="rId58" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{8437D7FB-2B62-46BD-81A6-DB3237B764CA}"/>
-    <hyperlink ref="G11" r:id="rId59" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{2A2A7F57-1F05-43DB-90E9-FBA7508B9894}"/>
-    <hyperlink ref="E11" r:id="rId60" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{5035A9FE-E981-4CBD-A8F7-1B404DF5EE7D}"/>
-    <hyperlink ref="H11" r:id="rId61" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{9A66F6B8-9650-4765-9711-0B1A92716BE7}"/>
-    <hyperlink ref="C11" r:id="rId62" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A8F626A7-6DB5-4F28-A1B5-E70F5540670B}"/>
-    <hyperlink ref="F11" r:id="rId63" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F99E1958-5A78-4B27-A391-1D79124B8567}"/>
-    <hyperlink ref="B12" r:id="rId64" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{7A1041D0-D797-4FD7-99D9-36E8E76F6A94}"/>
-    <hyperlink ref="D12" r:id="rId65" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{874D845C-6517-4C84-A088-C33F25DAC3A2}"/>
-    <hyperlink ref="G12" r:id="rId66" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{FC49E576-264A-4BE5-B4EB-A57056DABA15}"/>
-    <hyperlink ref="E12" r:id="rId67" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F4C8A260-D999-460D-AF5F-20BBE7309823}"/>
-    <hyperlink ref="H12" r:id="rId68" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{A57B2ABB-BA43-4C18-B9AD-F6F76B7D3ED2}"/>
-    <hyperlink ref="C12" r:id="rId69" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{4D6090D9-597E-4369-A7A4-0B5D779C3251}"/>
-    <hyperlink ref="F12" r:id="rId70" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{07B57694-A7E5-43CE-B09C-B2C3AAA98E0F}"/>
-    <hyperlink ref="B13" r:id="rId71" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{30F6F653-D950-4ABD-A04A-F5ED0D96F7AF}"/>
-    <hyperlink ref="D13" r:id="rId72" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{865D1E36-38C2-4B39-B076-2DE94DF32FF5}"/>
-    <hyperlink ref="G13" r:id="rId73" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3B99E8B8-F142-4A9C-8F7B-31D95C8D63A6}"/>
-    <hyperlink ref="E13" r:id="rId74" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{87DEEA51-0F9E-4338-9435-33EF3FE7EB11}"/>
-    <hyperlink ref="H13" r:id="rId75" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{09A95A1E-BF49-431D-9FEA-6509D2B54683}"/>
-    <hyperlink ref="C13" r:id="rId76" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{E50A17D3-3657-40B8-9025-88FC37F5EC11}"/>
-    <hyperlink ref="F13" r:id="rId77" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{81D88192-7602-48E8-BAB7-FFE6E36CAA20}"/>
-    <hyperlink ref="B14" r:id="rId78" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{99D3CDA9-A807-4A89-BFC4-34060E86EDE9}"/>
-    <hyperlink ref="D14" r:id="rId79" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D2F98FD9-1C26-4639-A342-A42B63A631AF}"/>
-    <hyperlink ref="G14" r:id="rId80" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{823FCF86-5732-427D-84E9-EC3694A1C8AD}"/>
-    <hyperlink ref="E14" r:id="rId81" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{BBD4EE22-A1E6-4B1A-85F3-AAFE447D2B40}"/>
-    <hyperlink ref="H14" r:id="rId82" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{D98E2414-6DFD-4C10-BB08-C1C5891E552F}"/>
-    <hyperlink ref="C14" r:id="rId83" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{2DC6E5F3-6754-4909-9304-919CE75B63F5}"/>
-    <hyperlink ref="F14" r:id="rId84" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{40EBB7EC-56B3-4A69-9BE1-6D6E597DCAD9}"/>
-    <hyperlink ref="B15" r:id="rId85" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{0CA5D80C-7594-4358-B95C-89D992706AE4}"/>
-    <hyperlink ref="D15" r:id="rId86" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{CF62512F-A773-45F8-9F42-882F7CDCE7F0}"/>
-    <hyperlink ref="G15" r:id="rId87" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{CB79D956-B4BA-4729-AA69-7343D8A5C4EF}"/>
-    <hyperlink ref="E15" r:id="rId88" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{89BDD2A7-5A88-44B7-A986-7327D43A5C27}"/>
-    <hyperlink ref="H15" r:id="rId89" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{DDC05ACD-E8D2-4B50-ADBF-0CB90E92EB3A}"/>
-    <hyperlink ref="C15" r:id="rId90" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A8D74216-B6CB-4303-86C7-E1C24E369B2B}"/>
-    <hyperlink ref="F15" r:id="rId91" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{D9253537-EF4A-49FB-87CA-4B8B9476417B}"/>
-    <hyperlink ref="B16" r:id="rId92" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{552AD646-ECD1-47BF-8A8A-EC39ACC335E8}"/>
-    <hyperlink ref="D16" r:id="rId93" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{3270D950-5210-491E-B32D-29BFD0DA003E}"/>
-    <hyperlink ref="G16" r:id="rId94" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{DC960230-5923-4FC1-8A5F-AFA7F804E172}"/>
-    <hyperlink ref="E16" r:id="rId95" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D91E2333-D54E-46ED-B96E-D9C45E14CDBE}"/>
-    <hyperlink ref="H16" r:id="rId96" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5F80B62A-A482-42DF-8B3E-BE9CF3A43039}"/>
-    <hyperlink ref="C16" r:id="rId97" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{EC6F981F-0660-42FB-8882-BC1984DE0824}"/>
-    <hyperlink ref="F16" r:id="rId98" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{491A8D80-D9B2-4D41-BA5C-C2C9438C950C}"/>
-    <hyperlink ref="B17" r:id="rId99" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{32C2C8EC-11DD-4113-A69C-D380AAF3CD71}"/>
-    <hyperlink ref="D17" r:id="rId100" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{745D1048-3102-4A4B-B055-35A5AB4290F3}"/>
-    <hyperlink ref="G17" r:id="rId101" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{7826E88A-A089-4C10-BC8A-0007C1397B23}"/>
-    <hyperlink ref="E17" r:id="rId102" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{84F30163-5D2B-4236-86F3-E27D97D2E032}"/>
-    <hyperlink ref="H17" r:id="rId103" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{DFD30610-B678-4BB1-8DCA-221439D39C3F}"/>
-    <hyperlink ref="C17" r:id="rId104" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{F5145E6A-0A3C-4487-8051-6470D8036E68}"/>
-    <hyperlink ref="F17" r:id="rId105" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{D160F93E-4CAC-44B1-BDFE-856C1013226E}"/>
-    <hyperlink ref="B18" r:id="rId106" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{530B5C57-9592-452D-9A57-F125F6855AD5}"/>
-    <hyperlink ref="D18" r:id="rId107" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D62D69D4-79B3-4E73-8373-D27E83B06E59}"/>
-    <hyperlink ref="G18" r:id="rId108" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{0CEA0B18-B796-4747-AE0D-2F07898CE281}"/>
-    <hyperlink ref="E18" r:id="rId109" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{C8189DF7-38D0-467F-89ED-EED3CE70E433}"/>
-    <hyperlink ref="H18" r:id="rId110" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{F7C097F4-FA89-4BD1-9CA6-ACFD513B9A50}"/>
-    <hyperlink ref="C18" r:id="rId111" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{90F98AE9-A1D8-4064-B2BD-495A6036D85A}"/>
-    <hyperlink ref="F18" r:id="rId112" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{97CCC1AD-4466-4BC7-8545-2D9ADC7E831D}"/>
-    <hyperlink ref="B19" r:id="rId113" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{033D27EE-8C8E-455E-B6E8-46D7CB3D874E}"/>
-    <hyperlink ref="D19" r:id="rId114" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{02F8F30A-EE57-422F-99F3-2EC5CED4EAE4}"/>
-    <hyperlink ref="G19" r:id="rId115" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{012BCE7E-FB10-49D2-BC4E-A0D5BB67C681}"/>
-    <hyperlink ref="E19" r:id="rId116" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{BA2D06C6-C326-4A77-A3D5-6C35ED8CF033}"/>
-    <hyperlink ref="H19" r:id="rId117" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{C177438B-F340-4394-A820-57093B55D0C5}"/>
-    <hyperlink ref="C19" r:id="rId118" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6A174D70-4C79-4250-AF08-FF1AD858F14A}"/>
-    <hyperlink ref="F19" r:id="rId119" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{7CBAAD7D-0353-4A7F-BED6-257956A90360}"/>
-    <hyperlink ref="B20" r:id="rId120" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{5C1B4E50-26BB-489B-895D-43E9C0AE8941}"/>
-    <hyperlink ref="D20" r:id="rId121" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{72EBA505-AF5E-4319-9358-4F1CD247647D}"/>
-    <hyperlink ref="G20" r:id="rId122" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{952BADBD-0308-485D-A9CA-F777645B019D}"/>
-    <hyperlink ref="E20" r:id="rId123" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{EF2C4BC8-3F1E-455D-9B01-65686CDB1D1E}"/>
-    <hyperlink ref="H20" r:id="rId124" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{CD4DB49C-775B-4849-88EC-972C30F5DF56}"/>
-    <hyperlink ref="C20" r:id="rId125" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{81CB0B20-9814-4FA2-AFAB-0D5CF784D221}"/>
-    <hyperlink ref="F20" r:id="rId126" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{01E21626-E228-44BE-A2E6-AC713D413A9D}"/>
-    <hyperlink ref="B21" r:id="rId127" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{6A14D52E-8DB1-4F15-B1E0-B85CDDFA2D12}"/>
-    <hyperlink ref="D21" r:id="rId128" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{CAB7B01F-5BA3-42BE-8401-DE0A4C907FA2}"/>
-    <hyperlink ref="G21" r:id="rId129" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F8AC209C-0DF5-4A65-990D-861AA4C7AABF}"/>
-    <hyperlink ref="E21" r:id="rId130" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A3AF97C9-70E3-40F3-B35A-2FBF23F293DA}"/>
-    <hyperlink ref="H21" r:id="rId131" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{A289880F-3E30-4595-889A-40C963E86411}"/>
-    <hyperlink ref="C21" r:id="rId132" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{4EAFDE29-0925-48F4-9955-8165F66204FE}"/>
-    <hyperlink ref="F21" r:id="rId133" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{6F63993D-4E1F-4C0C-B023-04F171E67936}"/>
-    <hyperlink ref="B22" r:id="rId134" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A22D60C4-B465-4E32-87E8-8A63E6E5D447}"/>
-    <hyperlink ref="D22" r:id="rId135" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D588E6D7-8FA0-4178-BB3F-AE34E3938996}"/>
-    <hyperlink ref="G22" r:id="rId136" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{38C78D12-B6AA-4577-93F7-D798CBD5BC56}"/>
-    <hyperlink ref="E22" r:id="rId137" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{5CE03A88-8E2D-44AE-9C5D-27767C8A02AB}"/>
-    <hyperlink ref="H22" r:id="rId138" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{A356EF5B-9698-438C-A5B5-FD5C94927536}"/>
-    <hyperlink ref="C22" r:id="rId139" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{604F2970-30B6-48BC-8901-B1A120823A55}"/>
-    <hyperlink ref="F22" r:id="rId140" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{CD58D5C7-999B-410E-98EA-AE70B0DBD331}"/>
-    <hyperlink ref="B2" r:id="rId141" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{BCA74B87-10D8-4FAE-8881-4D04E2DA9EE0}"/>
-    <hyperlink ref="D2" r:id="rId142" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{F1D7E55B-7088-4D07-BC77-B2282FFD4739}"/>
-    <hyperlink ref="G2" r:id="rId143" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{35080FDC-BDD2-4A32-8D03-B26F399BAC26}"/>
-    <hyperlink ref="E2" r:id="rId144" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{45352292-330F-4FBB-B864-4DCFC9F28414}"/>
-    <hyperlink ref="H2" r:id="rId145" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{8405DEB6-025E-4BB5-92BD-49CEC4E1D773}"/>
-    <hyperlink ref="C2" r:id="rId146" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{CF3BA994-8600-4BFC-B7F2-8BB39EB49EA2}"/>
-    <hyperlink ref="F2" r:id="rId147" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{624FB2D6-E71A-4FC7-BD2F-5377B68D805B}"/>
+    <hyperlink ref="B3" r:id="rId1" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{2E89BD67-E82F-40C8-BEC1-C75AE1762DD4}"/>
+    <hyperlink ref="D3" r:id="rId2" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{CE68594B-05B5-439D-ABF6-5E224651926C}"/>
+    <hyperlink ref="G3" r:id="rId3" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{16B2C8C9-3A8B-40E7-931D-D65D22AE3CD4}"/>
+    <hyperlink ref="E3" r:id="rId4" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F80B2EE8-6F43-4A21-936D-BB1691FECE3F}"/>
+    <hyperlink ref="H3" r:id="rId5" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{83D942D3-9D1A-4653-A4F7-92653DC57152}"/>
+    <hyperlink ref="C3" r:id="rId6" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6858E24F-A30E-49F6-85D9-8A178C601108}"/>
+    <hyperlink ref="F3" r:id="rId7" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{CB746032-1F1C-4517-B8D9-F83590C5203E}"/>
+    <hyperlink ref="B4" r:id="rId8" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{B2F8D5A2-085E-4DB3-ADDA-31206FAC0F08}"/>
+    <hyperlink ref="D4" r:id="rId9" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{3E78776A-2D07-4253-ABE7-334DDB0FB9E2}"/>
+    <hyperlink ref="G4" r:id="rId10" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C3CC27E3-B01E-406C-A967-DF7DA7607A5D}"/>
+    <hyperlink ref="E4" r:id="rId11" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E6398583-3C00-4F7F-B28D-7FD57C0FD060}"/>
+    <hyperlink ref="H4" r:id="rId12" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{519A46AB-68AE-43A0-872E-326C2091E8AE}"/>
+    <hyperlink ref="C4" r:id="rId13" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{F6EE11D3-A2B5-49A7-B7A9-5F20876A4914}"/>
+    <hyperlink ref="F4" r:id="rId14" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{5F52DAC0-08A3-4BEB-A07D-31EFB54604AD}"/>
+    <hyperlink ref="B5" r:id="rId15" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A646B8B7-0971-4DD1-B26D-A6E8CD087FB1}"/>
+    <hyperlink ref="D5" r:id="rId16" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{923AB338-49D5-459F-98DA-8089E6B15BD6}"/>
+    <hyperlink ref="G5" r:id="rId17" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{B1041FF6-9D3D-4987-B359-861CA80DFB51}"/>
+    <hyperlink ref="E5" r:id="rId18" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{FEB57DC8-3D44-4E96-9EE8-84E2088A9213}"/>
+    <hyperlink ref="H5" r:id="rId19" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{7D698F4D-1721-4621-8E2C-3C4134EAF238}"/>
+    <hyperlink ref="C5" r:id="rId20" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{8EF79D6E-DA29-4D2C-86D6-4C5E5D066483}"/>
+    <hyperlink ref="F5" r:id="rId21" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{8CF44EDF-B169-44D5-A51F-4FAE6424B61F}"/>
+    <hyperlink ref="B6" r:id="rId22" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{911D7FBC-025B-4976-830A-41BCC620D465}"/>
+    <hyperlink ref="D6" r:id="rId23" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{B66C08DD-49B5-4098-917B-C432A2AFA235}"/>
+    <hyperlink ref="G6" r:id="rId24" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{4AAB7F3F-7FA2-4192-9F4C-A5E8B4B34B50}"/>
+    <hyperlink ref="E6" r:id="rId25" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{489B53F6-26B4-4FC6-888E-058A9A604986}"/>
+    <hyperlink ref="H6" r:id="rId26" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{EFBC54BF-F37D-4DBE-8193-022E039E2E4E}"/>
+    <hyperlink ref="C6" r:id="rId27" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{3BCF4CC0-0C8F-47A4-A4B4-77422F935731}"/>
+    <hyperlink ref="F6" r:id="rId28" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{0D5BAF70-4E45-4457-844E-24430A4C04CA}"/>
+    <hyperlink ref="B7" r:id="rId29" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{DAEFF370-805B-4A77-84A2-0B7F8A8FA0DA}"/>
+    <hyperlink ref="D7" r:id="rId30" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{05653456-A1F8-43D9-9C88-FAF05EB698F3}"/>
+    <hyperlink ref="G7" r:id="rId31" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{50D9C598-8DD3-4888-A128-7DEB5883CCA1}"/>
+    <hyperlink ref="E7" r:id="rId32" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{099CB461-FBCD-4E92-A593-A7F207B687D3}"/>
+    <hyperlink ref="H7" r:id="rId33" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{A6601550-6D51-4848-BC23-A14FAB028956}"/>
+    <hyperlink ref="C7" r:id="rId34" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{60BF019F-8A36-4A79-BC18-83519AB51D9C}"/>
+    <hyperlink ref="F7" r:id="rId35" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E84B921C-75F0-490B-BDDB-FF92B34C4FF5}"/>
+    <hyperlink ref="B8" r:id="rId36" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{5E07B0DD-60BA-463D-A4B3-613C5D2455F3}"/>
+    <hyperlink ref="D8" r:id="rId37" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D3B923DA-392F-42A2-8618-BA98D75D1FBD}"/>
+    <hyperlink ref="G8" r:id="rId38" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3C2F2BEF-077E-4998-87D1-DA163ECB865B}"/>
+    <hyperlink ref="E8" r:id="rId39" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{7F0BE0E1-1604-422F-A9D5-20B5B4535F81}"/>
+    <hyperlink ref="H8" r:id="rId40" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{B40CF1D5-8586-4021-908A-FABE941256CB}"/>
+    <hyperlink ref="C8" r:id="rId41" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{19A269D5-AC55-4F5F-9596-7072E9D5109C}"/>
+    <hyperlink ref="F8" r:id="rId42" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{4E62FBB5-69CA-405E-8F8D-5C4F61B49F25}"/>
+    <hyperlink ref="B9" r:id="rId43" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{D54C2677-4CA1-4A92-BDC4-67D05A92F3C0}"/>
+    <hyperlink ref="D9" r:id="rId44" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2FFEC7E5-8BF7-4E69-9C5D-957F20D58D6A}"/>
+    <hyperlink ref="G9" r:id="rId45" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{A6F4D715-A3C5-47F8-A59C-4ECD3E426502}"/>
+    <hyperlink ref="E9" r:id="rId46" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{8935967A-8E75-4D9B-82BC-4AD5B39DDA37}"/>
+    <hyperlink ref="H9" r:id="rId47" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E6BE219D-9527-4CF3-880D-1F56A7A831B7}"/>
+    <hyperlink ref="C9" r:id="rId48" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C3949D62-CB7D-4434-A21A-E4DEC6B0EAFC}"/>
+    <hyperlink ref="F9" r:id="rId49" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{0C30E5AA-F786-4DF6-9C85-F8C6A9F80A41}"/>
+    <hyperlink ref="B10" r:id="rId50" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{43EAC04B-BFEB-441A-9EF8-72579DE6B84D}"/>
+    <hyperlink ref="D10" r:id="rId51" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{806B7B22-6B6C-4660-B79E-C5CDC90D38A7}"/>
+    <hyperlink ref="G10" r:id="rId52" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{602DCC85-DBB0-4ACF-839B-3B92093B2D9E}"/>
+    <hyperlink ref="E10" r:id="rId53" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{3CBEDAC9-4ED9-4904-82E5-C1B7C97D8F84}"/>
+    <hyperlink ref="H10" r:id="rId54" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{D0350FA7-ED6F-4A24-97CF-732FB82FDAF1}"/>
+    <hyperlink ref="C10" r:id="rId55" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{E5419792-E975-4A51-9919-97EC3338E327}"/>
+    <hyperlink ref="F10" r:id="rId56" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{CB65C645-7525-4D05-8C19-0E9E241665E7}"/>
+    <hyperlink ref="B11" r:id="rId57" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{98C023C1-CA96-4DE3-9881-22BE5942C024}"/>
+    <hyperlink ref="D11" r:id="rId58" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{E4B9E15D-623F-4067-AA91-9FBD71257620}"/>
+    <hyperlink ref="G11" r:id="rId59" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{1651BF54-EBC4-4D25-805D-7013CFA7B979}"/>
+    <hyperlink ref="E11" r:id="rId60" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{1D31493D-95B1-43EC-B513-4BE1928C24BC}"/>
+    <hyperlink ref="H11" r:id="rId61" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{FAF2E04C-57F4-48B5-A00F-0CA839212DBB}"/>
+    <hyperlink ref="C11" r:id="rId62" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{D5B6D1DD-7C98-4336-BA2C-7F8C7726903B}"/>
+    <hyperlink ref="F11" r:id="rId63" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{CD4BA075-234D-409A-9674-39E0B6B1F7CA}"/>
+    <hyperlink ref="B12" r:id="rId64" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{29406032-B0F5-48BB-9AEC-1066990CE16E}"/>
+    <hyperlink ref="D12" r:id="rId65" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{E00E0956-DF54-4C37-B6EA-D2397D5BC071}"/>
+    <hyperlink ref="G12" r:id="rId66" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{03654FC0-CBAB-4373-87DC-4C9D6739012A}"/>
+    <hyperlink ref="E12" r:id="rId67" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{87304B2D-730C-4C3C-97B6-3F59F76BA727}"/>
+    <hyperlink ref="H12" r:id="rId68" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{CADA6C1F-37B4-44B0-9315-D33BE03CDE50}"/>
+    <hyperlink ref="C12" r:id="rId69" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{E626E510-0C01-4031-9BBC-0941F5595CE9}"/>
+    <hyperlink ref="F12" r:id="rId70" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{58D199FE-216C-4278-9252-288B59744BFB}"/>
+    <hyperlink ref="B13" r:id="rId71" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{222A7DC7-EB7D-450A-B1AE-D923F7A32A8A}"/>
+    <hyperlink ref="D13" r:id="rId72" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{328268AC-ECED-4914-A5D0-3760E987F72A}"/>
+    <hyperlink ref="G13" r:id="rId73" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{508349F9-BD2F-4BA1-ABD8-6A09096BC099}"/>
+    <hyperlink ref="E13" r:id="rId74" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A16CA7F6-BC81-4FAF-9406-B360BF52AEF9}"/>
+    <hyperlink ref="H13" r:id="rId75" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{8384757C-0F35-4AEB-8947-EEBB77DC6DD4}"/>
+    <hyperlink ref="C13" r:id="rId76" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{409B237A-DBE0-4DCC-873F-357F180266F0}"/>
+    <hyperlink ref="F13" r:id="rId77" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{1ABA134C-F280-4679-9837-FB1B38D5C38D}"/>
+    <hyperlink ref="B14" r:id="rId78" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{76CD4825-7A16-4AFF-BAC8-DEAE642EDFFF}"/>
+    <hyperlink ref="D14" r:id="rId79" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{CCDFDD0B-E2D4-4307-9622-7B69E54B658B}"/>
+    <hyperlink ref="G14" r:id="rId80" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{24A02E7F-E95F-41FC-ABA2-5B08EFE17316}"/>
+    <hyperlink ref="E14" r:id="rId81" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{7660F657-FF1A-4590-940B-D0E40E4E0176}"/>
+    <hyperlink ref="H14" r:id="rId82" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{29879DB2-9140-4D2A-8DDD-756C10B8D867}"/>
+    <hyperlink ref="C14" r:id="rId83" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{E42A6969-0106-45A4-89C7-44DFF5E48382}"/>
+    <hyperlink ref="F14" r:id="rId84" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{36B9BB2A-03B5-45C3-BF7E-9A8A49ADFBA3}"/>
+    <hyperlink ref="B15" r:id="rId85" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{919841E7-1318-4DA4-AE19-8168268A5864}"/>
+    <hyperlink ref="D15" r:id="rId86" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{327A751E-138B-477D-A24E-B4EC7AB2D3D9}"/>
+    <hyperlink ref="G15" r:id="rId87" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{5FDD3638-BF04-419A-A300-25C599BB3BE9}"/>
+    <hyperlink ref="E15" r:id="rId88" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{5294BAF0-0EEF-42FC-B0EE-8951B5670DEA}"/>
+    <hyperlink ref="H15" r:id="rId89" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{BC0B052E-3740-4E56-9BCE-FB27940CFFEE}"/>
+    <hyperlink ref="C15" r:id="rId90" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A04E1637-9AE1-489E-B678-A3FB34C64208}"/>
+    <hyperlink ref="F15" r:id="rId91" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{0B47677D-3A5D-42C4-8EEE-96EA30559B89}"/>
+    <hyperlink ref="B16" r:id="rId92" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{B1C29438-9C55-4920-AB5A-7260D27FDDD2}"/>
+    <hyperlink ref="D16" r:id="rId93" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{A02530ED-49DD-48C2-8C58-45AEE5E11620}"/>
+    <hyperlink ref="G16" r:id="rId94" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{5C382A07-DEF0-4447-9F5D-79E7A252A9EE}"/>
+    <hyperlink ref="E16" r:id="rId95" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{2D1A7E9E-4625-4149-B37E-2D85B5E2AD4A}"/>
+    <hyperlink ref="H16" r:id="rId96" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{38E165F7-B11B-4546-B2B5-F821A9C8AEA1}"/>
+    <hyperlink ref="C16" r:id="rId97" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{AA862749-09D3-4DAA-81B4-A2BA092B94F5}"/>
+    <hyperlink ref="F16" r:id="rId98" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{80B2A072-2B04-4552-9E6A-10DF9506D769}"/>
+    <hyperlink ref="B17" r:id="rId99" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{BE0968BC-81E8-4877-8E0E-0025D8EA28F4}"/>
+    <hyperlink ref="D17" r:id="rId100" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{4E4ECEE9-65B1-4612-9FD7-78531339F2A4}"/>
+    <hyperlink ref="G17" r:id="rId101" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3C435AAC-A60A-43F0-8608-819BD4062BBB}"/>
+    <hyperlink ref="E17" r:id="rId102" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B93C0727-E06B-4D2D-B2E2-8752A5A6ED5E}"/>
+    <hyperlink ref="H17" r:id="rId103" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{827D25AA-976C-4D93-8D75-26220DECCA7E}"/>
+    <hyperlink ref="C17" r:id="rId104" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{09174815-0AFB-4A29-8022-2A342DBE4DBC}"/>
+    <hyperlink ref="F17" r:id="rId105" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{28DA800C-C1EB-4FBB-BE7F-2C4EA6A7722F}"/>
+    <hyperlink ref="B18" r:id="rId106" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{89B24529-3963-4B35-A395-7E5E8067203E}"/>
+    <hyperlink ref="D18" r:id="rId107" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{81721FC9-8730-4ED5-8939-D28602ABB1BA}"/>
+    <hyperlink ref="G18" r:id="rId108" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{D5D1DC77-60BC-4590-BFE3-01408E4B2FA0}"/>
+    <hyperlink ref="E18" r:id="rId109" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A679389C-C112-44A6-BBC8-BD3B7DDD72BC}"/>
+    <hyperlink ref="H18" r:id="rId110" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{DD6F39A5-2CA3-4477-B214-BD054C36527A}"/>
+    <hyperlink ref="C18" r:id="rId111" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{D90D4320-0B3D-4B09-B3A3-8AE51347BD90}"/>
+    <hyperlink ref="F18" r:id="rId112" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C62CFFE7-08AA-4C5A-9C4C-CC562CD9529F}"/>
+    <hyperlink ref="B19" r:id="rId113" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{9D35F396-6128-413B-A309-B0CC2DB78F4A}"/>
+    <hyperlink ref="D19" r:id="rId114" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2BC15D53-C551-49AA-891E-4DBF659FEFF9}"/>
+    <hyperlink ref="G19" r:id="rId115" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{331F9471-CD24-4A79-9F52-5FD5FB79A3E2}"/>
+    <hyperlink ref="E19" r:id="rId116" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F20A672B-8A6C-432E-A93B-EFBBD4C4C65C}"/>
+    <hyperlink ref="H19" r:id="rId117" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5436657F-F0F0-4513-9D6E-C9ED1F63A57D}"/>
+    <hyperlink ref="C19" r:id="rId118" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{EB41AB77-F753-4D55-9FAE-33A2B740C01D}"/>
+    <hyperlink ref="F19" r:id="rId119" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{D3106AF6-986C-441C-AA65-C1A04486187B}"/>
+    <hyperlink ref="B20" r:id="rId120" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{B5659207-37D3-4D71-9D71-79A481F3FCB0}"/>
+    <hyperlink ref="D20" r:id="rId121" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2D9F3458-E389-497E-A1BD-EDE63EF8BD8A}"/>
+    <hyperlink ref="G20" r:id="rId122" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{CCE7959A-0354-4DBE-86D6-C5086D901EA4}"/>
+    <hyperlink ref="E20" r:id="rId123" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{086DEF17-D801-4052-AAED-7707141F691B}"/>
+    <hyperlink ref="H20" r:id="rId124" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{1B905808-104B-4F80-AF93-280BFEA7EDED}"/>
+    <hyperlink ref="C20" r:id="rId125" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{36EF965C-0BDC-4D67-B242-D887C4317F4E}"/>
+    <hyperlink ref="F20" r:id="rId126" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E5E66D5E-149B-46AB-A8DF-EE8D036DFC90}"/>
+    <hyperlink ref="B21" r:id="rId127" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{28EAEFF3-C273-4EAE-86FD-7D48079A2713}"/>
+    <hyperlink ref="D21" r:id="rId128" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{A2ABE71B-702B-4C13-B8EF-463DA9AB8E01}"/>
+    <hyperlink ref="G21" r:id="rId129" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{10EE658C-344B-437A-89A2-A974629451DC}"/>
+    <hyperlink ref="E21" r:id="rId130" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{91924F1B-11FD-427B-AB45-67DE307F21F4}"/>
+    <hyperlink ref="H21" r:id="rId131" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{F8856540-9185-4B43-A737-15E88ECEFFF7}"/>
+    <hyperlink ref="C21" r:id="rId132" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{3998FA45-2BB6-487D-931A-24D16E759733}"/>
+    <hyperlink ref="F21" r:id="rId133" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{7DE3A1F2-A787-4B51-B920-39CCA4456F33}"/>
+    <hyperlink ref="B22" r:id="rId134" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C7D2908A-6D29-4A54-B382-921932825441}"/>
+    <hyperlink ref="D22" r:id="rId135" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{83B2F37F-3C74-46E7-A39F-B7308FC689C5}"/>
+    <hyperlink ref="G22" r:id="rId136" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{B4B15DD8-1BFC-4323-B5AC-FF843480DEF9}"/>
+    <hyperlink ref="E22" r:id="rId137" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{C7C9A7AD-A5BD-4B1B-B208-DDE4B71280B9}"/>
+    <hyperlink ref="H22" r:id="rId138" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{1CA5DDE4-1943-4F9E-915D-93809DCACE23}"/>
+    <hyperlink ref="C22" r:id="rId139" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{7A9A3BD7-1646-4071-A96F-09B25297BD23}"/>
+    <hyperlink ref="F22" r:id="rId140" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F91D0C14-DBE8-412D-B789-B0F4372565F3}"/>
+    <hyperlink ref="B23" r:id="rId141" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{4B774613-D74D-47CE-A41F-29F19C0EB61E}"/>
+    <hyperlink ref="D23" r:id="rId142" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{90496142-F267-486A-84E8-06A240F98E47}"/>
+    <hyperlink ref="G23" r:id="rId143" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{1A15D6C6-12C5-4755-954E-E0727EF8875C}"/>
+    <hyperlink ref="E23" r:id="rId144" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{932AA533-2D83-434C-9DA4-1D0EC8ED5F92}"/>
+    <hyperlink ref="H23" r:id="rId145" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{0D265159-D490-4FDB-B2F2-00CB9B9B2C89}"/>
+    <hyperlink ref="C23" r:id="rId146" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{903BC227-55D0-461C-AB1D-1ADA00D1092C}"/>
+    <hyperlink ref="F23" r:id="rId147" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{AF89C1CE-84BB-41CC-96AA-831E7E420D51}"/>
+    <hyperlink ref="B2" r:id="rId148" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{B0E00C65-D14E-4266-84CD-7B5C276EA22B}"/>
+    <hyperlink ref="D2" r:id="rId149" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{223A17B5-5634-45B9-8DE9-4E7F14C2B3C9}"/>
+    <hyperlink ref="G2" r:id="rId150" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3D555BAF-3C31-4EB0-97E8-B28FFA2CE587}"/>
+    <hyperlink ref="E2" r:id="rId151" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{471F296F-B431-45D5-BAFF-4ECD733C38E0}"/>
+    <hyperlink ref="H2" r:id="rId152" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{4F212458-20BE-49C9-ADB7-8081B6A9C806}"/>
+    <hyperlink ref="C2" r:id="rId153" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{5DF923F4-0829-4A4B-B4CF-5DCA993CBBC6}"/>
+    <hyperlink ref="F2" r:id="rId154" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C11619F5-2377-4F31-8C98-1E3A63269A34}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId148"/>
-  <drawing r:id="rId149"/>
+  <pageSetup orientation="portrait" r:id="rId155"/>
+  <drawing r:id="rId156"/>
   <tableParts count="1">
-    <tablePart r:id="rId150"/>
+    <tablePart r:id="rId157"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC3F3FC-17EF-4D6A-9290-8FAFFC789915}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.5546875" customWidth="1"/>
@@ -16144,6 +16549,24 @@
         <v>14</v>
       </c>
       <c r="E24" s="14">
+        <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="14">
+        <v>98</v>
+      </c>
+      <c r="C25" s="14">
+        <v>1</v>
+      </c>
+      <c r="D25" s="14">
+        <v>14</v>
+      </c>
+      <c r="E25" s="14">
         <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
         <v>113</v>
       </c>

--- a/data/SDET_SQA_DATA.xlsx
+++ b/data/SDET_SQA_DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WHSU\Desktop\Workspace\CycleView\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3644D7-296B-4D96-9B91-9D196231DB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE40250D-F82C-44C8-BD95-9B3E7695F689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{EB11FF79-EF06-B64E-AA6A-0CFF391A8BD1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB11FF79-EF06-B64E-AA6A-0CFF391A8BD1}"/>
   </bookViews>
   <sheets>
     <sheet name="TestAutomationProgress" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="112">
   <si>
     <t>TODO (P1)</t>
   </si>
@@ -367,6 +367,18 @@
   <si>
     <t>26W14</t>
   </si>
+  <si>
+    <t>26W15</t>
+  </si>
+  <si>
+    <t>26W16</t>
+  </si>
+  <si>
+    <t>y26w18</t>
+  </si>
+  <si>
+    <t>v1.42</t>
+  </si>
 </sst>
 </file>
 
@@ -553,6 +565,58 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="36">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="medium">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="medium">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -745,58 +809,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="medium">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="medium">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1103,9 +1115,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$25</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="24"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>25W40</c:v>
                 </c:pt>
@@ -1177,16 +1189,22 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>26W14</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>26W15</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26W16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$B$2:$B$25</c:f>
+              <c:f>TestAutomationProgress!$B$2:$B$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>15</c:v>
                 </c:pt>
@@ -1257,6 +1275,12 @@
                   <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="23">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
@@ -1354,9 +1378,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$25</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="24"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>25W40</c:v>
                 </c:pt>
@@ -1428,16 +1452,22 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>26W14</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>26W15</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26W16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$C$2:$C$25</c:f>
+              <c:f>TestAutomationProgress!$C$2:$C$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>14</c:v>
                 </c:pt>
@@ -1508,6 +1538,12 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="23">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1605,9 +1641,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$25</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$27</c:f>
               <c:strCache>
-                <c:ptCount val="24"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>25W40</c:v>
                 </c:pt>
@@ -1679,16 +1715,22 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>26W14</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>26W15</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26W16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$D$2:$D$25</c:f>
+              <c:f>TestAutomationProgress!$D$2:$D$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>219</c:v>
                 </c:pt>
@@ -1759,6 +1801,12 @@
                   <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="23">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>160</c:v>
                 </c:pt>
               </c:numCache>
@@ -2136,9 +2184,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$20</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2195,16 +2243,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>v1.41</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>v1.42</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$B$2:$B$20</c:f>
+              <c:f>'Humi-TestResult'!$B$2:$B$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>421</c:v>
                 </c:pt>
@@ -2260,7 +2311,10 @@
                   <c:v>572</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>100</c:v>
+                  <c:v>246</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2297,9 +2351,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$20</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2356,16 +2410,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>v1.41</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>v1.42</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$C$2:$C$20</c:f>
+              <c:f>'Humi-TestResult'!$C$2:$C$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2421,6 +2478,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2466,9 +2526,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$20</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2525,16 +2585,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>v1.41</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>v1.42</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$D$2:$D$20</c:f>
+              <c:f>'Humi-TestResult'!$D$2:$D$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>12</c:v>
                 </c:pt>
@@ -2590,6 +2653,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2681,9 +2747,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$20</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2740,16 +2806,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>v1.41</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>v1.42</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$E$2:$E$20</c:f>
+              <c:f>'Humi-TestResult'!$E$2:$E$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -2805,6 +2874,9 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2842,9 +2914,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$20</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -2901,16 +2973,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>v1.41</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>v1.42</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$F$2:$F$20</c:f>
+              <c:f>'Humi-TestResult'!$F$2:$F$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -2966,6 +3041,9 @@
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -3005,9 +3083,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$20</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -3064,16 +3142,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>v1.41</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>v1.42</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$G$2:$G$20</c:f>
+              <c:f>'Humi-TestResult'!$G$2:$G$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3129,7 +3210,10 @@
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>181</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>489</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3243,9 +3327,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-TestResult'!$A$2:$A$20</c:f>
+              <c:f>'Humi-TestResult'!$A$2:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>v1.22</c:v>
                 </c:pt>
@@ -3302,16 +3386,19 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>v1.41</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>v1.42</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-TestResult'!$H$2:$H$20</c:f>
+              <c:f>'Humi-TestResult'!$H$2:$H$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>442</c:v>
                 </c:pt>
@@ -3367,7 +3454,10 @@
                   <c:v>592</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>281</c:v>
+                  <c:v>248</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>489</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3741,9 +3831,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$38</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$39</c:f>
               <c:strCache>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -3854,16 +3944,19 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>26W14</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>26W16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$B$2:$B$38</c:f>
+              <c:f>'SOVA-TestResult'!$B$2:$B$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>38</c:v>
                 </c:pt>
@@ -3949,7 +4042,10 @@
                   <c:v>481</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0</c:v>
+                  <c:v>837</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>957</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4043,9 +4139,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$38</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$39</c:f>
               <c:strCache>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4156,16 +4252,19 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>26W14</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>26W16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$C$2:$C$38</c:f>
+              <c:f>'SOVA-TestResult'!$C$2:$C$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4251,6 +4350,9 @@
                   <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="36">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="37">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4288,9 +4390,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$38</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$39</c:f>
               <c:strCache>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4401,16 +4503,19 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>26W14</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>26W16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$D$2:$D$38</c:f>
+              <c:f>'SOVA-TestResult'!$D$2:$D$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4496,7 +4601,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4533,9 +4641,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$38</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$39</c:f>
               <c:strCache>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4646,16 +4754,19 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>26W14</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>26W16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$E$2:$E$38</c:f>
+              <c:f>'SOVA-TestResult'!$E$2:$E$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
                 </c:pt>
@@ -4741,7 +4852,10 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0</c:v>
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4852,9 +4966,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$38</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$39</c:f>
               <c:strCache>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4965,16 +5079,19 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>26W14</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>26W16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$F$2:$F$38</c:f>
+              <c:f>'SOVA-TestResult'!$F$2:$F$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>11</c:v>
                 </c:pt>
@@ -5060,7 +5177,10 @@
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0</c:v>
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5100,9 +5220,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$38</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$39</c:f>
               <c:strCache>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -5213,16 +5333,19 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>26W14</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>26W16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$G$2:$G$38</c:f>
+              <c:f>'SOVA-TestResult'!$G$2:$G$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5308,7 +5431,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>508</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5350,9 +5476,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$38</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$39</c:f>
               <c:strCache>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -5463,16 +5589,19 @@
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>26W14</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>26W16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$H$2:$H$38</c:f>
+              <c:f>'SOVA-TestResult'!$H$2:$H$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>54</c:v>
                 </c:pt>
@@ -5558,7 +5687,10 @@
                   <c:v>508</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>508</c:v>
+                  <c:v>857</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>967</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6070,7 +6202,7 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6971,7 +7103,7 @@
                   <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7152,7 +7284,7 @@
                   <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7525,9 +7657,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$24</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -7593,16 +7725,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>y26w16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>y26w18</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$B$2:$B$23</c:f>
+              <c:f>'SOVA-BugTrend'!$B$2:$B$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>32</c:v>
                 </c:pt>
@@ -7664,10 +7799,13 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>12</c:v>
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7761,9 +7899,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$24</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -7829,16 +7967,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>y26w16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>y26w18</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$C$2:$C$23</c:f>
+              <c:f>'SOVA-BugTrend'!$C$2:$C$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7903,7 +8044,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7997,9 +8141,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$24</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -8065,16 +8209,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>y26w16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>y26w18</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$D$2:$D$23</c:f>
+              <c:f>'SOVA-BugTrend'!$D$2:$D$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8139,6 +8286,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -8233,9 +8383,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$24</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -8301,16 +8451,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>y26w16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>y26w18</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$E$2:$E$23</c:f>
+              <c:f>'SOVA-BugTrend'!$E$2:$E$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8372,9 +8525,12 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -8412,9 +8568,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$24</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -8480,16 +8636,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>y26w16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>y26w18</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$F$2:$F$23</c:f>
+              <c:f>'SOVA-BugTrend'!$F$2:$F$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8551,9 +8710,12 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -8645,9 +8807,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$24</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -8713,16 +8875,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>y26w16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>y26w18</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$G$2:$G$23</c:f>
+              <c:f>'SOVA-BugTrend'!$G$2:$G$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>6</c:v>
                 </c:pt>
@@ -8781,13 +8946,16 @@
                   <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>17</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8826,9 +8994,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$24</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -8894,16 +9062,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>y26w16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>y26w18</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$H$2:$H$23</c:f>
+              <c:f>'SOVA-BugTrend'!$H$2:$H$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -8962,13 +9133,16 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9007,9 +9181,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'SOVA-BugTrend'!$A$2:$A$24</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>Candidate</c:v>
                 </c:pt>
@@ -9075,16 +9249,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>y26w16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>y26w18</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-BugTrend'!$I$2:$I$23</c:f>
+              <c:f>'SOVA-BugTrend'!$I$2:$I$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>40</c:v>
                 </c:pt>
@@ -9146,10 +9323,13 @@
                   <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12081,13 +12261,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>171448</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>133348</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -12122,14 +12302,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1057275</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12163,13 +12343,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>41087</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1047750</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>2987</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -12245,14 +12425,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12281,8 +12461,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}" name="Table2" displayName="Table2" ref="A1:E25" totalsRowShown="0" headerRowDxfId="35">
-  <autoFilter ref="A1:E25" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}" name="Table2" displayName="Table2" ref="A1:E27" totalsRowShown="0" headerRowDxfId="35">
+  <autoFilter ref="A1:E27" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F25F0D34-0297-4771-8BBB-350BCDD85D46}" name="Week"/>
     <tableColumn id="2" xr3:uid="{39CFCD12-3130-47A8-A140-DBF602F1743D}" name="Done"/>
@@ -12297,8 +12477,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E42B6291-7056-475B-AE1E-CA59C524E5F1}" name="Table1" displayName="Table1" ref="A1:H20" totalsRowShown="0" headerRowDxfId="33">
-  <autoFilter ref="A1:H20" xr:uid="{E42B6291-7056-475B-AE1E-CA59C524E5F1}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E42B6291-7056-475B-AE1E-CA59C524E5F1}" name="Table1" displayName="Table1" ref="A1:H21" totalsRowShown="0" headerRowDxfId="33">
+  <autoFilter ref="A1:H21" xr:uid="{E42B6291-7056-475B-AE1E-CA59C524E5F1}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{9154D4F8-C83D-4DB9-9182-818F32FA7C26}" name="Versions"/>
     <tableColumn id="2" xr3:uid="{1FE19FA2-B8BE-47BC-9953-F802445DE79D}" name="Passed"/>
@@ -12316,8 +12496,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}" name="Table3" displayName="Table3" ref="A1:H38" totalsRowShown="0" headerRowDxfId="31">
-  <autoFilter ref="A1:H38" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}" name="Table3" displayName="Table3" ref="A1:H39" totalsRowShown="0" headerRowDxfId="31">
+  <autoFilter ref="A1:H39" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{8103CDF3-74DC-4B31-821D-E20368EA5455}" name="Versions"/>
     <tableColumn id="2" xr3:uid="{6C3B261F-FA51-42D2-821A-F22633569372}" name="Passed"/>
@@ -12354,18 +12534,18 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}" name="Table5" displayName="Table5" ref="A1:I23" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17" totalsRowBorderDxfId="16" dataCellStyle="Hyperlink">
-  <autoFilter ref="A1:I23" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}" name="Table5" displayName="Table5" ref="A1:I24" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17" totalsRowBorderDxfId="16" dataCellStyle="Hyperlink">
+  <autoFilter ref="A1:I24" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{5BE08AE0-E0B5-4B46-9423-456B88C2D9BC}" name="Sprint" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{030F9647-4FC0-4C7E-9B3A-AB099CC59EBA}" name="To Do (0%)" dataDxfId="6" dataCellStyle="Hyperlink"/>
-    <tableColumn id="3" xr3:uid="{7D2923F3-E2CF-4FD9-A7A5-68C36BB95591}" name="STARTING (10 ~ 40%)" dataDxfId="5" dataCellStyle="Hyperlink"/>
-    <tableColumn id="4" xr3:uid="{48FB5317-7F3B-4F74-B244-5A49C7749EBD}" name="In Progress (50 ~ 70%)" dataDxfId="4" dataCellStyle="Hyperlink"/>
-    <tableColumn id="5" xr3:uid="{86F5CCB5-C4C2-4C36-935A-657F085500B1}" name="IN REVIEW (80%)" dataDxfId="3" dataCellStyle="Hyperlink"/>
-    <tableColumn id="9" xr3:uid="{51D22AE3-424C-4604-9869-D672DED4301F}" name="READY FOR TESTING (90%)" dataDxfId="2" dataCellStyle="Hyperlink"/>
-    <tableColumn id="6" xr3:uid="{33C9BCE6-D9EB-4032-9B0A-DDD9A4051A2D}" name="Done (100%)" dataDxfId="1" dataCellStyle="Hyperlink"/>
-    <tableColumn id="8" xr3:uid="{D624FC89-A88E-45AC-9D22-66D66702B8C5}" name="WON'T DO (100%)" dataDxfId="0" dataCellStyle="Hyperlink"/>
-    <tableColumn id="7" xr3:uid="{EFEEB7EC-E2D1-40EA-B265-A558311E5D30}" name="Total" dataDxfId="15" dataCellStyle="Hyperlink">
+    <tableColumn id="1" xr3:uid="{5BE08AE0-E0B5-4B46-9423-456B88C2D9BC}" name="Sprint" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{030F9647-4FC0-4C7E-9B3A-AB099CC59EBA}" name="To Do (0%)" dataDxfId="14" dataCellStyle="Hyperlink"/>
+    <tableColumn id="3" xr3:uid="{7D2923F3-E2CF-4FD9-A7A5-68C36BB95591}" name="STARTING (10 ~ 40%)" dataDxfId="13" dataCellStyle="Hyperlink"/>
+    <tableColumn id="4" xr3:uid="{48FB5317-7F3B-4F74-B244-5A49C7749EBD}" name="In Progress (50 ~ 70%)" dataDxfId="12" dataCellStyle="Hyperlink"/>
+    <tableColumn id="5" xr3:uid="{86F5CCB5-C4C2-4C36-935A-657F085500B1}" name="IN REVIEW (80%)" dataDxfId="11" dataCellStyle="Hyperlink"/>
+    <tableColumn id="9" xr3:uid="{51D22AE3-424C-4604-9869-D672DED4301F}" name="READY FOR TESTING (90%)" dataDxfId="10" dataCellStyle="Hyperlink"/>
+    <tableColumn id="6" xr3:uid="{33C9BCE6-D9EB-4032-9B0A-DDD9A4051A2D}" name="Done (100%)" dataDxfId="9" dataCellStyle="Hyperlink"/>
+    <tableColumn id="8" xr3:uid="{D624FC89-A88E-45AC-9D22-66D66702B8C5}" name="WON'T DO (100%)" dataDxfId="8" dataCellStyle="Hyperlink"/>
+    <tableColumn id="7" xr3:uid="{EFEEB7EC-E2D1-40EA-B265-A558311E5D30}" name="Total" dataDxfId="7" dataCellStyle="Hyperlink">
       <calculatedColumnFormula>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12374,14 +12554,14 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}" name="Table25" displayName="Table25" ref="A1:E25" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
-  <autoFilter ref="A1:E25" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}" name="Table25" displayName="Table25" ref="A1:E27" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E27" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7070D9F2-0ED1-4F39-8D72-28B37C8E98F2}" name="Week" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{1173F443-CC27-4C6E-A432-BF66DB2A740E}" name="Done" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{2EE10CB5-1AF1-4B50-9456-B3A666DD5338}" name="In Review/Progress" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{328D0A00-85F0-4BFF-81FE-C023998A3701}" name="TODO (P1)" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{E385808E-1FCD-451C-9807-DAF18A42B704}" name="Total" dataDxfId="8">
+    <tableColumn id="1" xr3:uid="{7070D9F2-0ED1-4F39-8D72-28B37C8E98F2}" name="Week" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{1173F443-CC27-4C6E-A432-BF66DB2A740E}" name="Done" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{2EE10CB5-1AF1-4B50-9456-B3A666DD5338}" name="In Review/Progress" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{328D0A00-85F0-4BFF-81FE-C023998A3701}" name="TODO (P1)" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{E385808E-1FCD-451C-9807-DAF18A42B704}" name="Total" dataDxfId="0">
       <calculatedColumnFormula>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12706,7 +12886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D733A42-966D-5F4E-B061-B304543CE88E}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.77734375" customWidth="1"/>
@@ -13157,6 +13337,40 @@
         <v>160</v>
       </c>
       <c r="E25" s="12">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A26" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26">
+        <v>37</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>160</v>
+      </c>
+      <c r="E26" s="12">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27">
+        <v>37</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>160</v>
+      </c>
+      <c r="E27" s="12">
         <v>198</v>
       </c>
     </row>
@@ -13172,7 +13386,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6429633B-8BD2-084C-8C0F-75969053522F}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -13697,13 +13911,14 @@
         <v>105</v>
       </c>
       <c r="B20">
-        <v>100</v>
+        <f>179+67</f>
+        <v>246</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -13712,11 +13927,38 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <f>SUM(Table1[[#This Row],[Passed]:[Untested]])</f>
-        <v>281</v>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="21.95" customHeight="1">
+      <c r="A21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>489</v>
+      </c>
+      <c r="H21">
+        <f>SUM(Table1[[#This Row],[Passed]:[Untested]])</f>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -13731,7 +13973,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA6EDF6-834F-DA49-B3FC-BFE1673433AB}">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
@@ -14567,26 +14809,53 @@
         <v>107</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>837</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G38">
-        <v>508</v>
+        <v>0</v>
       </c>
       <c r="H38" s="12">
         <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
-        <v>508</v>
+        <v>857</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="A39" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B39">
+        <v>957</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+      <c r="E39">
+        <v>5</v>
+      </c>
+      <c r="F39">
+        <v>3</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39" s="12">
+        <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
+        <v>967</v>
       </c>
     </row>
   </sheetData>
@@ -15211,7 +15480,7 @@
         <v>105</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -15226,11 +15495,11 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" s="12">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -15245,7 +15514,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7487DEB-55FC-DC4E-A4B1-F7171B8F3237}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.21875" customWidth="1"/>
@@ -15877,10 +16146,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H21" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I21" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
@@ -15892,7 +16161,7 @@
         <v>101</v>
       </c>
       <c r="B22" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C22" s="5">
         <v>0</v>
@@ -15901,20 +16170,20 @@
         <v>0</v>
       </c>
       <c r="E22" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H22" s="5">
         <v>0</v>
       </c>
       <c r="I22" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="18" thickBot="1">
@@ -15922,201 +16191,238 @@
         <v>103</v>
       </c>
       <c r="B23" s="5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C23" s="5">
+        <v>2</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5">
         <v>1</v>
       </c>
-      <c r="D23" s="5">
-        <v>0</v>
-      </c>
-      <c r="E23" s="5">
-        <v>0</v>
-      </c>
-      <c r="F23" s="5">
-        <v>0</v>
-      </c>
       <c r="G23" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>16</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="18" thickBot="1">
+      <c r="A24" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="5">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5">
+        <v>0</v>
+      </c>
+      <c r="I24" s="15">
+        <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{2E89BD67-E82F-40C8-BEC1-C75AE1762DD4}"/>
-    <hyperlink ref="D3" r:id="rId2" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{CE68594B-05B5-439D-ABF6-5E224651926C}"/>
-    <hyperlink ref="G3" r:id="rId3" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{16B2C8C9-3A8B-40E7-931D-D65D22AE3CD4}"/>
-    <hyperlink ref="E3" r:id="rId4" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F80B2EE8-6F43-4A21-936D-BB1691FECE3F}"/>
-    <hyperlink ref="H3" r:id="rId5" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{83D942D3-9D1A-4653-A4F7-92653DC57152}"/>
-    <hyperlink ref="C3" r:id="rId6" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6858E24F-A30E-49F6-85D9-8A178C601108}"/>
-    <hyperlink ref="F3" r:id="rId7" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{CB746032-1F1C-4517-B8D9-F83590C5203E}"/>
-    <hyperlink ref="B4" r:id="rId8" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{B2F8D5A2-085E-4DB3-ADDA-31206FAC0F08}"/>
-    <hyperlink ref="D4" r:id="rId9" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{3E78776A-2D07-4253-ABE7-334DDB0FB9E2}"/>
-    <hyperlink ref="G4" r:id="rId10" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C3CC27E3-B01E-406C-A967-DF7DA7607A5D}"/>
-    <hyperlink ref="E4" r:id="rId11" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E6398583-3C00-4F7F-B28D-7FD57C0FD060}"/>
-    <hyperlink ref="H4" r:id="rId12" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{519A46AB-68AE-43A0-872E-326C2091E8AE}"/>
-    <hyperlink ref="C4" r:id="rId13" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{F6EE11D3-A2B5-49A7-B7A9-5F20876A4914}"/>
-    <hyperlink ref="F4" r:id="rId14" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{5F52DAC0-08A3-4BEB-A07D-31EFB54604AD}"/>
-    <hyperlink ref="B5" r:id="rId15" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A646B8B7-0971-4DD1-B26D-A6E8CD087FB1}"/>
-    <hyperlink ref="D5" r:id="rId16" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{923AB338-49D5-459F-98DA-8089E6B15BD6}"/>
-    <hyperlink ref="G5" r:id="rId17" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{B1041FF6-9D3D-4987-B359-861CA80DFB51}"/>
-    <hyperlink ref="E5" r:id="rId18" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{FEB57DC8-3D44-4E96-9EE8-84E2088A9213}"/>
-    <hyperlink ref="H5" r:id="rId19" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{7D698F4D-1721-4621-8E2C-3C4134EAF238}"/>
-    <hyperlink ref="C5" r:id="rId20" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{8EF79D6E-DA29-4D2C-86D6-4C5E5D066483}"/>
-    <hyperlink ref="F5" r:id="rId21" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{8CF44EDF-B169-44D5-A51F-4FAE6424B61F}"/>
-    <hyperlink ref="B6" r:id="rId22" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{911D7FBC-025B-4976-830A-41BCC620D465}"/>
-    <hyperlink ref="D6" r:id="rId23" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{B66C08DD-49B5-4098-917B-C432A2AFA235}"/>
-    <hyperlink ref="G6" r:id="rId24" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{4AAB7F3F-7FA2-4192-9F4C-A5E8B4B34B50}"/>
-    <hyperlink ref="E6" r:id="rId25" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{489B53F6-26B4-4FC6-888E-058A9A604986}"/>
-    <hyperlink ref="H6" r:id="rId26" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{EFBC54BF-F37D-4DBE-8193-022E039E2E4E}"/>
-    <hyperlink ref="C6" r:id="rId27" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{3BCF4CC0-0C8F-47A4-A4B4-77422F935731}"/>
-    <hyperlink ref="F6" r:id="rId28" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{0D5BAF70-4E45-4457-844E-24430A4C04CA}"/>
-    <hyperlink ref="B7" r:id="rId29" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{DAEFF370-805B-4A77-84A2-0B7F8A8FA0DA}"/>
-    <hyperlink ref="D7" r:id="rId30" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{05653456-A1F8-43D9-9C88-FAF05EB698F3}"/>
-    <hyperlink ref="G7" r:id="rId31" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{50D9C598-8DD3-4888-A128-7DEB5883CCA1}"/>
-    <hyperlink ref="E7" r:id="rId32" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{099CB461-FBCD-4E92-A593-A7F207B687D3}"/>
-    <hyperlink ref="H7" r:id="rId33" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{A6601550-6D51-4848-BC23-A14FAB028956}"/>
-    <hyperlink ref="C7" r:id="rId34" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{60BF019F-8A36-4A79-BC18-83519AB51D9C}"/>
-    <hyperlink ref="F7" r:id="rId35" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E84B921C-75F0-490B-BDDB-FF92B34C4FF5}"/>
-    <hyperlink ref="B8" r:id="rId36" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{5E07B0DD-60BA-463D-A4B3-613C5D2455F3}"/>
-    <hyperlink ref="D8" r:id="rId37" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D3B923DA-392F-42A2-8618-BA98D75D1FBD}"/>
-    <hyperlink ref="G8" r:id="rId38" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3C2F2BEF-077E-4998-87D1-DA163ECB865B}"/>
-    <hyperlink ref="E8" r:id="rId39" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{7F0BE0E1-1604-422F-A9D5-20B5B4535F81}"/>
-    <hyperlink ref="H8" r:id="rId40" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{B40CF1D5-8586-4021-908A-FABE941256CB}"/>
-    <hyperlink ref="C8" r:id="rId41" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{19A269D5-AC55-4F5F-9596-7072E9D5109C}"/>
-    <hyperlink ref="F8" r:id="rId42" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{4E62FBB5-69CA-405E-8F8D-5C4F61B49F25}"/>
-    <hyperlink ref="B9" r:id="rId43" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{D54C2677-4CA1-4A92-BDC4-67D05A92F3C0}"/>
-    <hyperlink ref="D9" r:id="rId44" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2FFEC7E5-8BF7-4E69-9C5D-957F20D58D6A}"/>
-    <hyperlink ref="G9" r:id="rId45" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{A6F4D715-A3C5-47F8-A59C-4ECD3E426502}"/>
-    <hyperlink ref="E9" r:id="rId46" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{8935967A-8E75-4D9B-82BC-4AD5B39DDA37}"/>
-    <hyperlink ref="H9" r:id="rId47" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E6BE219D-9527-4CF3-880D-1F56A7A831B7}"/>
-    <hyperlink ref="C9" r:id="rId48" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C3949D62-CB7D-4434-A21A-E4DEC6B0EAFC}"/>
-    <hyperlink ref="F9" r:id="rId49" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{0C30E5AA-F786-4DF6-9C85-F8C6A9F80A41}"/>
-    <hyperlink ref="B10" r:id="rId50" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{43EAC04B-BFEB-441A-9EF8-72579DE6B84D}"/>
-    <hyperlink ref="D10" r:id="rId51" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{806B7B22-6B6C-4660-B79E-C5CDC90D38A7}"/>
-    <hyperlink ref="G10" r:id="rId52" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{602DCC85-DBB0-4ACF-839B-3B92093B2D9E}"/>
-    <hyperlink ref="E10" r:id="rId53" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{3CBEDAC9-4ED9-4904-82E5-C1B7C97D8F84}"/>
-    <hyperlink ref="H10" r:id="rId54" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{D0350FA7-ED6F-4A24-97CF-732FB82FDAF1}"/>
-    <hyperlink ref="C10" r:id="rId55" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{E5419792-E975-4A51-9919-97EC3338E327}"/>
-    <hyperlink ref="F10" r:id="rId56" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{CB65C645-7525-4D05-8C19-0E9E241665E7}"/>
-    <hyperlink ref="B11" r:id="rId57" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{98C023C1-CA96-4DE3-9881-22BE5942C024}"/>
-    <hyperlink ref="D11" r:id="rId58" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{E4B9E15D-623F-4067-AA91-9FBD71257620}"/>
-    <hyperlink ref="G11" r:id="rId59" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{1651BF54-EBC4-4D25-805D-7013CFA7B979}"/>
-    <hyperlink ref="E11" r:id="rId60" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{1D31493D-95B1-43EC-B513-4BE1928C24BC}"/>
-    <hyperlink ref="H11" r:id="rId61" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{FAF2E04C-57F4-48B5-A00F-0CA839212DBB}"/>
-    <hyperlink ref="C11" r:id="rId62" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{D5B6D1DD-7C98-4336-BA2C-7F8C7726903B}"/>
-    <hyperlink ref="F11" r:id="rId63" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{CD4BA075-234D-409A-9674-39E0B6B1F7CA}"/>
-    <hyperlink ref="B12" r:id="rId64" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{29406032-B0F5-48BB-9AEC-1066990CE16E}"/>
-    <hyperlink ref="D12" r:id="rId65" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{E00E0956-DF54-4C37-B6EA-D2397D5BC071}"/>
-    <hyperlink ref="G12" r:id="rId66" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{03654FC0-CBAB-4373-87DC-4C9D6739012A}"/>
-    <hyperlink ref="E12" r:id="rId67" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{87304B2D-730C-4C3C-97B6-3F59F76BA727}"/>
-    <hyperlink ref="H12" r:id="rId68" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{CADA6C1F-37B4-44B0-9315-D33BE03CDE50}"/>
-    <hyperlink ref="C12" r:id="rId69" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{E626E510-0C01-4031-9BBC-0941F5595CE9}"/>
-    <hyperlink ref="F12" r:id="rId70" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{58D199FE-216C-4278-9252-288B59744BFB}"/>
-    <hyperlink ref="B13" r:id="rId71" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{222A7DC7-EB7D-450A-B1AE-D923F7A32A8A}"/>
-    <hyperlink ref="D13" r:id="rId72" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{328268AC-ECED-4914-A5D0-3760E987F72A}"/>
-    <hyperlink ref="G13" r:id="rId73" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{508349F9-BD2F-4BA1-ABD8-6A09096BC099}"/>
-    <hyperlink ref="E13" r:id="rId74" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A16CA7F6-BC81-4FAF-9406-B360BF52AEF9}"/>
-    <hyperlink ref="H13" r:id="rId75" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{8384757C-0F35-4AEB-8947-EEBB77DC6DD4}"/>
-    <hyperlink ref="C13" r:id="rId76" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{409B237A-DBE0-4DCC-873F-357F180266F0}"/>
-    <hyperlink ref="F13" r:id="rId77" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{1ABA134C-F280-4679-9837-FB1B38D5C38D}"/>
-    <hyperlink ref="B14" r:id="rId78" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{76CD4825-7A16-4AFF-BAC8-DEAE642EDFFF}"/>
-    <hyperlink ref="D14" r:id="rId79" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{CCDFDD0B-E2D4-4307-9622-7B69E54B658B}"/>
-    <hyperlink ref="G14" r:id="rId80" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{24A02E7F-E95F-41FC-ABA2-5B08EFE17316}"/>
-    <hyperlink ref="E14" r:id="rId81" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{7660F657-FF1A-4590-940B-D0E40E4E0176}"/>
-    <hyperlink ref="H14" r:id="rId82" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{29879DB2-9140-4D2A-8DDD-756C10B8D867}"/>
-    <hyperlink ref="C14" r:id="rId83" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{E42A6969-0106-45A4-89C7-44DFF5E48382}"/>
-    <hyperlink ref="F14" r:id="rId84" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{36B9BB2A-03B5-45C3-BF7E-9A8A49ADFBA3}"/>
-    <hyperlink ref="B15" r:id="rId85" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{919841E7-1318-4DA4-AE19-8168268A5864}"/>
-    <hyperlink ref="D15" r:id="rId86" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{327A751E-138B-477D-A24E-B4EC7AB2D3D9}"/>
-    <hyperlink ref="G15" r:id="rId87" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{5FDD3638-BF04-419A-A300-25C599BB3BE9}"/>
-    <hyperlink ref="E15" r:id="rId88" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{5294BAF0-0EEF-42FC-B0EE-8951B5670DEA}"/>
-    <hyperlink ref="H15" r:id="rId89" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{BC0B052E-3740-4E56-9BCE-FB27940CFFEE}"/>
-    <hyperlink ref="C15" r:id="rId90" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A04E1637-9AE1-489E-B678-A3FB34C64208}"/>
-    <hyperlink ref="F15" r:id="rId91" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{0B47677D-3A5D-42C4-8EEE-96EA30559B89}"/>
-    <hyperlink ref="B16" r:id="rId92" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{B1C29438-9C55-4920-AB5A-7260D27FDDD2}"/>
-    <hyperlink ref="D16" r:id="rId93" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{A02530ED-49DD-48C2-8C58-45AEE5E11620}"/>
-    <hyperlink ref="G16" r:id="rId94" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{5C382A07-DEF0-4447-9F5D-79E7A252A9EE}"/>
-    <hyperlink ref="E16" r:id="rId95" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{2D1A7E9E-4625-4149-B37E-2D85B5E2AD4A}"/>
-    <hyperlink ref="H16" r:id="rId96" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{38E165F7-B11B-4546-B2B5-F821A9C8AEA1}"/>
-    <hyperlink ref="C16" r:id="rId97" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{AA862749-09D3-4DAA-81B4-A2BA092B94F5}"/>
-    <hyperlink ref="F16" r:id="rId98" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{80B2A072-2B04-4552-9E6A-10DF9506D769}"/>
-    <hyperlink ref="B17" r:id="rId99" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{BE0968BC-81E8-4877-8E0E-0025D8EA28F4}"/>
-    <hyperlink ref="D17" r:id="rId100" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{4E4ECEE9-65B1-4612-9FD7-78531339F2A4}"/>
-    <hyperlink ref="G17" r:id="rId101" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3C435AAC-A60A-43F0-8608-819BD4062BBB}"/>
-    <hyperlink ref="E17" r:id="rId102" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B93C0727-E06B-4D2D-B2E2-8752A5A6ED5E}"/>
-    <hyperlink ref="H17" r:id="rId103" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{827D25AA-976C-4D93-8D75-26220DECCA7E}"/>
-    <hyperlink ref="C17" r:id="rId104" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{09174815-0AFB-4A29-8022-2A342DBE4DBC}"/>
-    <hyperlink ref="F17" r:id="rId105" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{28DA800C-C1EB-4FBB-BE7F-2C4EA6A7722F}"/>
-    <hyperlink ref="B18" r:id="rId106" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{89B24529-3963-4B35-A395-7E5E8067203E}"/>
-    <hyperlink ref="D18" r:id="rId107" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{81721FC9-8730-4ED5-8939-D28602ABB1BA}"/>
-    <hyperlink ref="G18" r:id="rId108" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{D5D1DC77-60BC-4590-BFE3-01408E4B2FA0}"/>
-    <hyperlink ref="E18" r:id="rId109" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A679389C-C112-44A6-BBC8-BD3B7DDD72BC}"/>
-    <hyperlink ref="H18" r:id="rId110" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{DD6F39A5-2CA3-4477-B214-BD054C36527A}"/>
-    <hyperlink ref="C18" r:id="rId111" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{D90D4320-0B3D-4B09-B3A3-8AE51347BD90}"/>
-    <hyperlink ref="F18" r:id="rId112" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C62CFFE7-08AA-4C5A-9C4C-CC562CD9529F}"/>
-    <hyperlink ref="B19" r:id="rId113" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{9D35F396-6128-413B-A309-B0CC2DB78F4A}"/>
-    <hyperlink ref="D19" r:id="rId114" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2BC15D53-C551-49AA-891E-4DBF659FEFF9}"/>
-    <hyperlink ref="G19" r:id="rId115" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{331F9471-CD24-4A79-9F52-5FD5FB79A3E2}"/>
-    <hyperlink ref="E19" r:id="rId116" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F20A672B-8A6C-432E-A93B-EFBBD4C4C65C}"/>
-    <hyperlink ref="H19" r:id="rId117" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5436657F-F0F0-4513-9D6E-C9ED1F63A57D}"/>
-    <hyperlink ref="C19" r:id="rId118" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{EB41AB77-F753-4D55-9FAE-33A2B740C01D}"/>
-    <hyperlink ref="F19" r:id="rId119" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{D3106AF6-986C-441C-AA65-C1A04486187B}"/>
-    <hyperlink ref="B20" r:id="rId120" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{B5659207-37D3-4D71-9D71-79A481F3FCB0}"/>
-    <hyperlink ref="D20" r:id="rId121" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2D9F3458-E389-497E-A1BD-EDE63EF8BD8A}"/>
-    <hyperlink ref="G20" r:id="rId122" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{CCE7959A-0354-4DBE-86D6-C5086D901EA4}"/>
-    <hyperlink ref="E20" r:id="rId123" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{086DEF17-D801-4052-AAED-7707141F691B}"/>
-    <hyperlink ref="H20" r:id="rId124" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{1B905808-104B-4F80-AF93-280BFEA7EDED}"/>
-    <hyperlink ref="C20" r:id="rId125" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{36EF965C-0BDC-4D67-B242-D887C4317F4E}"/>
-    <hyperlink ref="F20" r:id="rId126" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E5E66D5E-149B-46AB-A8DF-EE8D036DFC90}"/>
-    <hyperlink ref="B21" r:id="rId127" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{28EAEFF3-C273-4EAE-86FD-7D48079A2713}"/>
-    <hyperlink ref="D21" r:id="rId128" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{A2ABE71B-702B-4C13-B8EF-463DA9AB8E01}"/>
-    <hyperlink ref="G21" r:id="rId129" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{10EE658C-344B-437A-89A2-A974629451DC}"/>
-    <hyperlink ref="E21" r:id="rId130" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{91924F1B-11FD-427B-AB45-67DE307F21F4}"/>
-    <hyperlink ref="H21" r:id="rId131" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{F8856540-9185-4B43-A737-15E88ECEFFF7}"/>
-    <hyperlink ref="C21" r:id="rId132" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{3998FA45-2BB6-487D-931A-24D16E759733}"/>
-    <hyperlink ref="F21" r:id="rId133" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{7DE3A1F2-A787-4B51-B920-39CCA4456F33}"/>
-    <hyperlink ref="B22" r:id="rId134" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C7D2908A-6D29-4A54-B382-921932825441}"/>
-    <hyperlink ref="D22" r:id="rId135" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{83B2F37F-3C74-46E7-A39F-B7308FC689C5}"/>
-    <hyperlink ref="G22" r:id="rId136" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{B4B15DD8-1BFC-4323-B5AC-FF843480DEF9}"/>
-    <hyperlink ref="E22" r:id="rId137" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{C7C9A7AD-A5BD-4B1B-B208-DDE4B71280B9}"/>
-    <hyperlink ref="H22" r:id="rId138" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{1CA5DDE4-1943-4F9E-915D-93809DCACE23}"/>
-    <hyperlink ref="C22" r:id="rId139" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{7A9A3BD7-1646-4071-A96F-09B25297BD23}"/>
-    <hyperlink ref="F22" r:id="rId140" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F91D0C14-DBE8-412D-B789-B0F4372565F3}"/>
-    <hyperlink ref="B23" r:id="rId141" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{4B774613-D74D-47CE-A41F-29F19C0EB61E}"/>
-    <hyperlink ref="D23" r:id="rId142" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{90496142-F267-486A-84E8-06A240F98E47}"/>
-    <hyperlink ref="G23" r:id="rId143" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{1A15D6C6-12C5-4755-954E-E0727EF8875C}"/>
-    <hyperlink ref="E23" r:id="rId144" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{932AA533-2D83-434C-9DA4-1D0EC8ED5F92}"/>
-    <hyperlink ref="H23" r:id="rId145" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{0D265159-D490-4FDB-B2F2-00CB9B9B2C89}"/>
-    <hyperlink ref="C23" r:id="rId146" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{903BC227-55D0-461C-AB1D-1ADA00D1092C}"/>
-    <hyperlink ref="F23" r:id="rId147" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{AF89C1CE-84BB-41CC-96AA-831E7E420D51}"/>
-    <hyperlink ref="B2" r:id="rId148" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{B0E00C65-D14E-4266-84CD-7B5C276EA22B}"/>
-    <hyperlink ref="D2" r:id="rId149" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{223A17B5-5634-45B9-8DE9-4E7F14C2B3C9}"/>
-    <hyperlink ref="G2" r:id="rId150" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3D555BAF-3C31-4EB0-97E8-B28FFA2CE587}"/>
-    <hyperlink ref="E2" r:id="rId151" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{471F296F-B431-45D5-BAFF-4ECD733C38E0}"/>
-    <hyperlink ref="H2" r:id="rId152" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{4F212458-20BE-49C9-ADB7-8081B6A9C806}"/>
-    <hyperlink ref="C2" r:id="rId153" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{5DF923F4-0829-4A4B-B4CF-5DCA993CBBC6}"/>
-    <hyperlink ref="F2" r:id="rId154" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C11619F5-2377-4F31-8C98-1E3A63269A34}"/>
+    <hyperlink ref="B3" r:id="rId1" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{97F6B08B-6331-4B8C-8F45-657EC3D1E8F9}"/>
+    <hyperlink ref="D3" r:id="rId2" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2CE19764-8741-47E6-85F8-7CA5266C34CB}"/>
+    <hyperlink ref="G3" r:id="rId3" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{CF707013-C81F-4A85-AC48-8FCF6228781D}"/>
+    <hyperlink ref="E3" r:id="rId4" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D762CE94-80AB-4734-93A5-3F8508FE931D}"/>
+    <hyperlink ref="H3" r:id="rId5" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{B93EF06E-2C7D-43C1-B359-60CCA19800CB}"/>
+    <hyperlink ref="C3" r:id="rId6" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{753B0838-D5BE-4F91-9081-9E257AE874C3}"/>
+    <hyperlink ref="F3" r:id="rId7" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{AE59092D-3518-45A2-9C3F-02A6A1D47B0A}"/>
+    <hyperlink ref="B4" r:id="rId8" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{73D7B8FF-149D-473C-BDD3-8EEA2EAA0104}"/>
+    <hyperlink ref="D4" r:id="rId9" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{338ADF01-6813-4C9D-B03A-31B18A007CF8}"/>
+    <hyperlink ref="G4" r:id="rId10" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3E1AB134-96A5-4197-903E-EF3A2259BA3D}"/>
+    <hyperlink ref="E4" r:id="rId11" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{85F19B3A-B9D0-47D0-91D4-956E9C8E6AEE}"/>
+    <hyperlink ref="H4" r:id="rId12" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{6857D4D8-6A00-4708-AC64-E948460F069E}"/>
+    <hyperlink ref="C4" r:id="rId13" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{9D260C02-F8A0-4CC6-9CCF-8227DD109586}"/>
+    <hyperlink ref="F4" r:id="rId14" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F391AB16-864C-4532-9AE9-EDAF9BE839A2}"/>
+    <hyperlink ref="B5" r:id="rId15" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{8D9CA4CA-2C99-49B9-8FE4-0AEB844094E2}"/>
+    <hyperlink ref="D5" r:id="rId16" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{9FEB4A96-9FA8-4DC4-BA13-E4DB16C5E09C}"/>
+    <hyperlink ref="G5" r:id="rId17" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C2FCBAEC-77EE-486B-BB2F-E7187364689E}"/>
+    <hyperlink ref="E5" r:id="rId18" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{2472A073-4D5B-43CF-89E8-2A2E2107B462}"/>
+    <hyperlink ref="H5" r:id="rId19" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{1A0C03D5-0020-4246-9C4D-97AE0A5B0F73}"/>
+    <hyperlink ref="C5" r:id="rId20" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A868CD39-A0B9-4D70-88E3-9CD6EF84BF04}"/>
+    <hyperlink ref="F5" r:id="rId21" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{636AF472-7827-4003-A180-F737B814B3FE}"/>
+    <hyperlink ref="B6" r:id="rId22" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{2B251480-09E8-4A43-AD3C-753FDF561FD3}"/>
+    <hyperlink ref="D6" r:id="rId23" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{5BB7BA55-FF8C-4004-A094-422BC877741B}"/>
+    <hyperlink ref="G6" r:id="rId24" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{193FF21A-0ED8-49AB-AF60-21B747D3794B}"/>
+    <hyperlink ref="E6" r:id="rId25" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{713C196C-10CB-43CD-98A5-4427DA027DB1}"/>
+    <hyperlink ref="H6" r:id="rId26" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E476F302-AF43-4566-BB7D-B874C8986983}"/>
+    <hyperlink ref="C6" r:id="rId27" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{07CA0DE7-2310-47D4-BBE4-F6F66BDB5C3E}"/>
+    <hyperlink ref="F6" r:id="rId28" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{AFD24D83-E5B2-452A-95B9-A2822703D296}"/>
+    <hyperlink ref="B7" r:id="rId29" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{DCC996B8-9960-491F-A751-9CDDC79A61EE}"/>
+    <hyperlink ref="D7" r:id="rId30" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{FE7264C0-0F9D-4443-92BB-C40DECE26D7B}"/>
+    <hyperlink ref="G7" r:id="rId31" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{D5115A28-51E3-4F3A-B1B4-7F9A251D1052}"/>
+    <hyperlink ref="E7" r:id="rId32" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B7ABA0A0-9A6D-4E20-BA5B-8997ECDF265D}"/>
+    <hyperlink ref="H7" r:id="rId33" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{7156FC73-161C-408A-9A74-49E0A3B2D6A7}"/>
+    <hyperlink ref="C7" r:id="rId34" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{3FEBD497-4D52-460D-9057-0F6F38CF4F1D}"/>
+    <hyperlink ref="F7" r:id="rId35" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E1955951-9D86-49A1-B7E4-A829A83D9AEA}"/>
+    <hyperlink ref="B8" r:id="rId36" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{21D631C3-CCAF-4571-BEB4-8934C2A0EA14}"/>
+    <hyperlink ref="D8" r:id="rId37" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{74FCAD1E-672D-4858-A527-8016C02B69F2}"/>
+    <hyperlink ref="G8" r:id="rId38" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{2FD5EA99-7F49-4E6F-90CD-D0417CDA9D43}"/>
+    <hyperlink ref="E8" r:id="rId39" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{408419E7-55DB-4A54-B48F-B1A57DCE1E54}"/>
+    <hyperlink ref="H8" r:id="rId40" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{CA56B963-4041-4A2D-A107-EE6A817089F6}"/>
+    <hyperlink ref="C8" r:id="rId41" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C798F4C5-C890-4D2A-91BC-ED3B44418D1D}"/>
+    <hyperlink ref="F8" r:id="rId42" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{70DAA7BF-2490-4212-A726-3DC65D836F6D}"/>
+    <hyperlink ref="B9" r:id="rId43" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{29752EE5-C54C-489D-9FBB-2AF3B7661FE8}"/>
+    <hyperlink ref="D9" r:id="rId44" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{14EDA7AB-AD21-446B-8CDD-B814135C7218}"/>
+    <hyperlink ref="G9" r:id="rId45" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{380DEAE9-0EAC-42B9-A71D-1ED751710F8B}"/>
+    <hyperlink ref="E9" r:id="rId46" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{06EC0BDC-3CFA-44AB-9836-0A1C78B39465}"/>
+    <hyperlink ref="H9" r:id="rId47" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{57B347BC-893B-4BA7-944F-4A19B27AD104}"/>
+    <hyperlink ref="C9" r:id="rId48" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{19A8BDBF-4974-411F-A11B-AF1BC33D4474}"/>
+    <hyperlink ref="F9" r:id="rId49" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C8535763-75D1-4770-BF9F-D1637AC16360}"/>
+    <hyperlink ref="B10" r:id="rId50" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{1FD3BB21-AF4D-4E52-AADE-B519EEA0E6F8}"/>
+    <hyperlink ref="D10" r:id="rId51" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{615399CA-430B-4E09-94AE-342652153380}"/>
+    <hyperlink ref="G10" r:id="rId52" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F575ACC0-675C-4047-9EB9-FD7F3D22277C}"/>
+    <hyperlink ref="E10" r:id="rId53" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A3397DB6-62C6-466B-9472-A430A42CEB6C}"/>
+    <hyperlink ref="H10" r:id="rId54" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{3B3EE6CC-0D3D-415A-80AF-A6C6BE933731}"/>
+    <hyperlink ref="C10" r:id="rId55" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{7C001704-87D3-41D7-AF65-F99635990AFC}"/>
+    <hyperlink ref="F10" r:id="rId56" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{DD5BB0F2-DBF5-44FD-BAC9-CFE228FE7724}"/>
+    <hyperlink ref="B11" r:id="rId57" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{DDDE3DF0-6E6E-46B5-A29C-33D29B33D304}"/>
+    <hyperlink ref="D11" r:id="rId58" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{52A3BC6B-4C12-438B-B198-BE3634D73DCD}"/>
+    <hyperlink ref="G11" r:id="rId59" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3D811382-00B5-43EA-B32D-3278480D9E68}"/>
+    <hyperlink ref="E11" r:id="rId60" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{803C85B2-F2C8-4AC9-85BA-F16C339B96E6}"/>
+    <hyperlink ref="H11" r:id="rId61" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{21E346AE-2AC3-4A55-8717-7C6ABD2CB25C}"/>
+    <hyperlink ref="C11" r:id="rId62" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{CC47B98E-F61B-49C8-B8EF-AFFBAA4E5447}"/>
+    <hyperlink ref="F11" r:id="rId63" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{855D923A-E1A6-41C9-8B06-3776053E30FE}"/>
+    <hyperlink ref="B12" r:id="rId64" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{EEEA534A-3E56-4005-8B3C-889884CBF0D3}"/>
+    <hyperlink ref="D12" r:id="rId65" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{E65D65D7-94A6-4C4A-9792-59817A87728A}"/>
+    <hyperlink ref="G12" r:id="rId66" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{383B18D0-3DEE-4FAB-A3A5-9F92891C889B}"/>
+    <hyperlink ref="E12" r:id="rId67" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{6C05C6E7-2529-4C75-9098-B3C20460C320}"/>
+    <hyperlink ref="H12" r:id="rId68" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{D4FD4B56-5AB4-494E-8724-56BAB26A761B}"/>
+    <hyperlink ref="C12" r:id="rId69" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{800875E2-867C-485D-8C29-3D8B910B70EB}"/>
+    <hyperlink ref="F12" r:id="rId70" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{1B892854-2C9F-4EB7-82DA-88BCD24757CB}"/>
+    <hyperlink ref="B13" r:id="rId71" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{48E94CC3-E6CB-4057-8C7D-EF75D371AC4E}"/>
+    <hyperlink ref="D13" r:id="rId72" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{786A83B5-36C4-4A25-85D9-B5063E225F64}"/>
+    <hyperlink ref="G13" r:id="rId73" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F3B6E45C-D41B-43CE-AE71-3D0FD1C4B5B8}"/>
+    <hyperlink ref="E13" r:id="rId74" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{1B8A11DA-A114-4D3A-BBD7-7A1C44B63CAB}"/>
+    <hyperlink ref="H13" r:id="rId75" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{73A9633C-3DBF-47C8-AB17-2875D8083CD2}"/>
+    <hyperlink ref="C13" r:id="rId76" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{41BE0B95-7F00-41BD-B26E-F61E0D0ECF57}"/>
+    <hyperlink ref="F13" r:id="rId77" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C5303366-F11C-48A2-A19B-37666DB31384}"/>
+    <hyperlink ref="B14" r:id="rId78" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{1F783EF2-0C56-40FB-A7FC-BBDB76FC95A2}"/>
+    <hyperlink ref="D14" r:id="rId79" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{C80B98EC-3369-4CC5-8D4B-4B0CAE809355}"/>
+    <hyperlink ref="G14" r:id="rId80" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{430F09D6-5389-47F0-92F3-6673E410CCF8}"/>
+    <hyperlink ref="E14" r:id="rId81" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B7B40CED-8051-46D8-AC23-AA0B60E07991}"/>
+    <hyperlink ref="H14" r:id="rId82" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{311E5105-9939-4D2B-B29D-90CE009DC12C}"/>
+    <hyperlink ref="C14" r:id="rId83" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{37C5211C-854A-4824-8F7A-0EE2AD92CF8F}"/>
+    <hyperlink ref="F14" r:id="rId84" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{ECE827E7-7014-4EBE-8731-C173A3E16090}"/>
+    <hyperlink ref="B2" r:id="rId85" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{ECC2139E-791E-4770-9749-924C8171413E}"/>
+    <hyperlink ref="D2" r:id="rId86" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{A3490D76-D554-40B0-94C2-6BCE62D65128}"/>
+    <hyperlink ref="G2" r:id="rId87" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{E73331BD-FAD2-46B3-9C4A-B1F1944F18FC}"/>
+    <hyperlink ref="E2" r:id="rId88" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{363312FF-8351-469B-A0E2-96F2CEBC31DF}"/>
+    <hyperlink ref="H2" r:id="rId89" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{33FD27D8-D06C-4600-84C6-9AF958F84B2B}"/>
+    <hyperlink ref="C2" r:id="rId90" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C0932090-8C86-4ADD-B05E-5218E24825BD}"/>
+    <hyperlink ref="F2" r:id="rId91" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A689B4DB-1B76-459A-A757-14C2A4E04261}"/>
+    <hyperlink ref="B15" r:id="rId92" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{CEC46233-AEB1-43F5-BBF4-45B55E1036E7}"/>
+    <hyperlink ref="D15" r:id="rId93" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{E00230F7-006F-4483-8FF9-293DDDC7BCD2}"/>
+    <hyperlink ref="G15" r:id="rId94" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{08C36869-7439-481C-88F2-C2B5F3E85362}"/>
+    <hyperlink ref="E15" r:id="rId95" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A80CFC3A-2BAA-4A2C-943E-E0A50A2D9378}"/>
+    <hyperlink ref="H15" r:id="rId96" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{8B8D1DAF-6253-472F-9A66-933E4916940C}"/>
+    <hyperlink ref="C15" r:id="rId97" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A6CEB30F-B1BB-4EEF-B70E-3EC83B3E3438}"/>
+    <hyperlink ref="F15" r:id="rId98" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{1D76AB3E-7128-401F-BCD5-4869C78E8EAE}"/>
+    <hyperlink ref="B16" r:id="rId99" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{EBE7433A-5296-449E-BBB7-313B398D004B}"/>
+    <hyperlink ref="D16" r:id="rId100" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D874F7C9-B94F-48A0-915C-704EEAAC0A20}"/>
+    <hyperlink ref="E16" r:id="rId101" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{9F1D3361-B1B3-4C77-84C8-3C11CE2DE020}"/>
+    <hyperlink ref="H16" r:id="rId102" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{D7147B34-65EC-45ED-81A5-F54C88208DB7}"/>
+    <hyperlink ref="C16" r:id="rId103" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C4B33AA8-220C-4E12-8F9A-34AF8A2A6704}"/>
+    <hyperlink ref="F16" r:id="rId104" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{FA2A7FCF-6347-4D7A-80C3-6D8350C82DA4}"/>
+    <hyperlink ref="B17" r:id="rId105" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{59CA8689-C1F2-41EE-A465-066C0E0DEFAF}"/>
+    <hyperlink ref="D17" r:id="rId106" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{F50DDE7E-9D60-4E00-9DC2-6D595997FB9C}"/>
+    <hyperlink ref="E17" r:id="rId107" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{0A86B503-ADC0-444D-ABBB-6764D5EEB2B1}"/>
+    <hyperlink ref="H17" r:id="rId108" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E95F6969-5600-4805-A22E-451097FF33C3}"/>
+    <hyperlink ref="C17" r:id="rId109" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{F5CD2F46-915C-47FF-912B-89000081E733}"/>
+    <hyperlink ref="F17" r:id="rId110" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{200E82B0-B654-4A00-8530-FCEB858874D0}"/>
+    <hyperlink ref="B18" r:id="rId111" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{BCDCF649-5CBC-42E4-8620-1C81AF1B23FF}"/>
+    <hyperlink ref="D18" r:id="rId112" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{E54331BB-C33D-4380-B73F-3756F0FC2F14}"/>
+    <hyperlink ref="E18" r:id="rId113" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{2A006D1C-721E-497A-B5CC-85CAEE423836}"/>
+    <hyperlink ref="H18" r:id="rId114" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{57474496-F8C0-4883-9C04-278511F4F901}"/>
+    <hyperlink ref="C18" r:id="rId115" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{4CA530EA-7090-445A-B98D-FACDA3F39B99}"/>
+    <hyperlink ref="F18" r:id="rId116" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{3FB61006-C835-41E0-A898-176B637118A4}"/>
+    <hyperlink ref="B19" r:id="rId117" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{654A79F9-EC00-4B49-BB80-493704BBFB18}"/>
+    <hyperlink ref="D19" r:id="rId118" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{E38AD4A5-6768-4CD8-914B-6C113E6877F5}"/>
+    <hyperlink ref="E19" r:id="rId119" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{945C014B-9E64-40C4-8707-855DE9581DB7}"/>
+    <hyperlink ref="H19" r:id="rId120" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{CD41350E-CC13-46C9-9B58-5FD048617A17}"/>
+    <hyperlink ref="C19" r:id="rId121" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A5900141-601A-4A94-BF84-E34806FCEE5E}"/>
+    <hyperlink ref="F19" r:id="rId122" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{31386E48-3615-49CF-AFA9-BFCFBF36DEC6}"/>
+    <hyperlink ref="B20" r:id="rId123" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C9CA4C4B-AEBC-4EB6-857A-159C4D3A53E8}"/>
+    <hyperlink ref="D20" r:id="rId124" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{9A281456-11AE-473B-8CBA-EFE9C54F7885}"/>
+    <hyperlink ref="E20" r:id="rId125" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{34A1D8C0-20A6-4436-A4B1-C6F90A138397}"/>
+    <hyperlink ref="H20" r:id="rId126" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{6814B0AE-3A96-4530-8883-02C68E3974C5}"/>
+    <hyperlink ref="C20" r:id="rId127" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{7B7C24DA-E67D-488C-90E9-3AEF3BC30D9B}"/>
+    <hyperlink ref="F20" r:id="rId128" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{B5B90D06-A815-4003-8ACA-27DFC2CAE260}"/>
+    <hyperlink ref="B21" r:id="rId129" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C57E3CD6-E2E1-4878-86C0-C8A4F74B6943}"/>
+    <hyperlink ref="D21" r:id="rId130" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{0C6FD858-1ADF-4092-AA2B-9713208568CA}"/>
+    <hyperlink ref="E21" r:id="rId131" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{6CC6B938-791A-41C1-9389-927962895B22}"/>
+    <hyperlink ref="H21" r:id="rId132" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{DE0D1CEA-7FA4-4205-819F-73863F40783F}"/>
+    <hyperlink ref="C21" r:id="rId133" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{4D39EF51-3FDE-4C27-9EF4-5524AC910EEE}"/>
+    <hyperlink ref="F21" r:id="rId134" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{9DFAE6B0-1AEE-448C-BA14-1F313DBE1602}"/>
+    <hyperlink ref="B22" r:id="rId135" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{BE6D6466-4A5A-4AB2-9EFA-2C4D2C1E8AFF}"/>
+    <hyperlink ref="D22" r:id="rId136" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{7470F8A9-8284-4AEA-9FA2-BF9CE7937358}"/>
+    <hyperlink ref="E22" r:id="rId137" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{7956657D-26D3-4605-9E99-33F3A1D6B6EE}"/>
+    <hyperlink ref="H22" r:id="rId138" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{C623CAE8-6648-4155-A74E-0042B043D15D}"/>
+    <hyperlink ref="C22" r:id="rId139" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{14ECCE02-C0D5-48C6-A5C8-CDCDF283EB78}"/>
+    <hyperlink ref="F22" r:id="rId140" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A9DEE48A-109D-4928-A89F-ABCB122792D5}"/>
+    <hyperlink ref="B23" r:id="rId141" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{5A2F68C6-B54C-4C1F-94CC-2735B4FC62AA}"/>
+    <hyperlink ref="D23" r:id="rId142" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{43B2273B-A0AD-40BF-B3CF-58D6ED229970}"/>
+    <hyperlink ref="E23" r:id="rId143" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F142813D-5F7B-4E11-9FCD-070E0AC8ADEB}"/>
+    <hyperlink ref="H23" r:id="rId144" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{07AA1D2D-87B1-4E5F-9019-007777379DA0}"/>
+    <hyperlink ref="C23" r:id="rId145" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{514E936D-004B-4D0F-BFA9-D24E2C16742C}"/>
+    <hyperlink ref="F23" r:id="rId146" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{D2B98F43-625C-4C5F-B4CD-DAA65AAD3C31}"/>
+    <hyperlink ref="B24" r:id="rId147" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{843EBD87-0262-4B26-B795-F87A820AA39F}"/>
+    <hyperlink ref="D24" r:id="rId148" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D90209FA-5A42-4641-8FFF-5327312A652C}"/>
+    <hyperlink ref="E24" r:id="rId149" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{5BEC239B-6589-4860-9853-978B7AF22DF4}"/>
+    <hyperlink ref="H24" r:id="rId150" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{721280F6-C5CE-4331-88CE-6E49D1B5C6A3}"/>
+    <hyperlink ref="C24" r:id="rId151" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{0D134C8E-43C9-4790-9EB4-58547C99D977}"/>
+    <hyperlink ref="F24" r:id="rId152" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C239BF9C-0D18-44ED-B019-C3E5AA99FF46}"/>
+    <hyperlink ref="G16" r:id="rId153" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{A125BFD2-35B7-40C9-B4E3-CABF3B4FB481}"/>
+    <hyperlink ref="G17" r:id="rId154" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F068A1F6-B397-4F92-8579-C9F34E179374}"/>
+    <hyperlink ref="G18" r:id="rId155" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{6FCF7054-5C99-4F04-86EB-D0211B256B99}"/>
+    <hyperlink ref="G19" r:id="rId156" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{6412AB69-01AB-4A0A-AF48-238CB8933AD9}"/>
+    <hyperlink ref="G20" r:id="rId157" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{EF22CFFE-00E3-4A1C-A810-8165B0B35800}"/>
+    <hyperlink ref="G21" r:id="rId158" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{9F3AD8E1-4C46-4BB4-9335-A8617D665C34}"/>
+    <hyperlink ref="G22" r:id="rId159" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{771970A7-7F19-4D05-9B7C-C3CA4FF29043}"/>
+    <hyperlink ref="G23" r:id="rId160" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{710A57A1-3964-4216-9E22-27B2DBD33277}"/>
+    <hyperlink ref="G24" r:id="rId161" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{5B0ED04E-0ED3-48B4-AE9E-2217221918C2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId155"/>
-  <drawing r:id="rId156"/>
+  <pageSetup orientation="portrait" r:id="rId162"/>
+  <drawing r:id="rId163"/>
   <tableParts count="1">
-    <tablePart r:id="rId157"/>
+    <tablePart r:id="rId164"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC3F3FC-17EF-4D6A-9290-8FAFFC789915}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.5546875" customWidth="1"/>
@@ -16567,6 +16873,42 @@
         <v>14</v>
       </c>
       <c r="E25" s="14">
+        <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" s="14">
+        <v>98</v>
+      </c>
+      <c r="C26" s="14">
+        <v>1</v>
+      </c>
+      <c r="D26" s="14">
+        <v>14</v>
+      </c>
+      <c r="E26" s="14">
+        <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="A27" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" s="14">
+        <v>98</v>
+      </c>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>14</v>
+      </c>
+      <c r="E27" s="14">
         <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
         <v>113</v>
       </c>

--- a/data/SDET_SQA_DATA.xlsx
+++ b/data/SDET_SQA_DATA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WHSU\Desktop\Workspace\CycleView\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE40250D-F82C-44C8-BD95-9B3E7695F689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E66F38C-6694-4EB2-BAF4-90083EEB6E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB11FF79-EF06-B64E-AA6A-0CFF391A8BD1}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="113">
   <si>
     <t>TODO (P1)</t>
   </si>
@@ -379,6 +379,9 @@
   <si>
     <t>v1.42</t>
   </si>
+  <si>
+    <t>26W17</t>
+  </si>
 </sst>
 </file>
 
@@ -565,6 +568,9 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="36">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -896,9 +902,6 @@
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1115,9 +1118,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$27</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$28</c:f>
               <c:strCache>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>25W40</c:v>
                 </c:pt>
@@ -1195,16 +1198,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>26W16</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26W17</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$B$2:$B$27</c:f>
+              <c:f>TestAutomationProgress!$B$2:$B$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>15</c:v>
                 </c:pt>
@@ -1281,6 +1287,9 @@
                   <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="25">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
@@ -1378,9 +1387,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$27</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$28</c:f>
               <c:strCache>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>25W40</c:v>
                 </c:pt>
@@ -1458,16 +1467,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>26W16</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26W17</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$C$2:$C$27</c:f>
+              <c:f>TestAutomationProgress!$C$2:$C$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>14</c:v>
                 </c:pt>
@@ -1544,6 +1556,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="25">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1641,9 +1656,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$27</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$28</c:f>
               <c:strCache>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>25W40</c:v>
                 </c:pt>
@@ -1721,16 +1736,19 @@
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>26W16</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26W17</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$D$2:$D$27</c:f>
+              <c:f>TestAutomationProgress!$D$2:$D$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="26"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>219</c:v>
                 </c:pt>
@@ -1807,6 +1825,9 @@
                   <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="25">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>160</c:v>
                 </c:pt>
               </c:numCache>
@@ -2314,7 +2335,7 @@
                   <c:v>246</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3213,7 +3234,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>489</c:v>
+                  <c:v>506</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3457,7 +3478,7 @@
                   <c:v>248</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>489</c:v>
+                  <c:v>527</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3831,9 +3852,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$39</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -3947,16 +3968,19 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>26W16</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>26W17</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$B$2:$B$39</c:f>
+              <c:f>'SOVA-TestResult'!$B$2:$B$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>38</c:v>
                 </c:pt>
@@ -4046,6 +4070,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>957</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1220</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4139,9 +4166,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$39</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4255,16 +4282,19 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>26W16</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>26W17</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$C$2:$C$39</c:f>
+              <c:f>'SOVA-TestResult'!$C$2:$C$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4353,6 +4383,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="37">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4390,9 +4423,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$39</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4506,16 +4539,19 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>26W16</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>26W17</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$D$2:$D$39</c:f>
+              <c:f>'SOVA-TestResult'!$D$2:$D$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4605,6 +4641,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4641,9 +4680,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$39</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4757,16 +4796,19 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>26W16</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>26W17</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$E$2:$E$39</c:f>
+              <c:f>'SOVA-TestResult'!$E$2:$E$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
                 </c:pt>
@@ -4855,6 +4897,9 @@
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="37">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="38">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -4966,9 +5011,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$39</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -5082,16 +5127,19 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>26W16</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>26W17</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$F$2:$F$39</c:f>
+              <c:f>'SOVA-TestResult'!$F$2:$F$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>11</c:v>
                 </c:pt>
@@ -5181,6 +5229,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5220,9 +5271,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$39</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -5336,16 +5387,19 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>26W16</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>26W17</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$G$2:$G$39</c:f>
+              <c:f>'SOVA-TestResult'!$G$2:$G$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5435,6 +5489,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>284</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5476,9 +5533,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$39</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -5592,16 +5649,19 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>26W16</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>26W17</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$H$2:$H$39</c:f>
+              <c:f>'SOVA-TestResult'!$H$2:$H$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="39"/>
                 <c:pt idx="0">
                   <c:v>54</c:v>
                 </c:pt>
@@ -5691,6 +5751,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>967</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1522</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6060,9 +6123,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$24</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -6128,16 +6191,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>v1.41</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>v1.42</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$B$2:$B$23</c:f>
+              <c:f>'Humi-BugTrend'!$B$2:$B$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>9</c:v>
                 </c:pt>
@@ -6199,10 +6265,13 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>8</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6242,9 +6311,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$24</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -6310,16 +6379,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>v1.41</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>v1.42</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$C$2:$C$23</c:f>
+              <c:f>'Humi-BugTrend'!$C$2:$C$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6384,6 +6456,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -6424,9 +6499,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$24</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -6492,16 +6567,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>v1.41</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>v1.42</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$D$2:$D$23</c:f>
+              <c:f>'Humi-BugTrend'!$D$2:$D$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6566,6 +6644,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -6603,9 +6684,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$24</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -6671,16 +6752,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>v1.41</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>v1.42</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$E$2:$E$23</c:f>
+              <c:f>'Humi-BugTrend'!$E$2:$E$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6746,6 +6830,9 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6782,9 +6869,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$24</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -6850,16 +6937,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>v1.41</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>v1.42</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$F$2:$F$23</c:f>
+              <c:f>'Humi-BugTrend'!$F$2:$F$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6924,6 +7014,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -6961,9 +7054,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$24</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -7029,16 +7122,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>v1.41</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>v1.42</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$G$2:$G$23</c:f>
+              <c:f>'Humi-BugTrend'!$G$2:$G$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>66</c:v>
                 </c:pt>
@@ -7103,6 +7199,9 @@
                   <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="21">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
@@ -7142,9 +7241,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Humi-BugTrend'!$A$2:$A$23</c:f>
+              <c:f>'Humi-BugTrend'!$A$2:$A$24</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>v1.20</c:v>
                 </c:pt>
@@ -7210,16 +7309,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>v1.41</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>v1.42</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Humi-BugTrend'!$H$2:$H$23</c:f>
+              <c:f>'Humi-BugTrend'!$H$2:$H$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>75</c:v>
                 </c:pt>
@@ -7281,10 +7383,13 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>49</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7784,10 +7889,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>3</c:v>
@@ -7802,10 +7907,10 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>15</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>8</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8044,7 +8149,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0</c:v>
@@ -8528,7 +8633,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0</c:v>
@@ -8713,7 +8818,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0</c:v>
@@ -8952,7 +9057,7 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0</c:v>
@@ -9076,7 +9181,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="23"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>2</c:v>
@@ -9121,10 +9226,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>8</c:v>
@@ -9139,7 +9244,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0</c:v>
@@ -9263,7 +9368,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="23"/>
                 <c:pt idx="0">
-                  <c:v>40</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>42</c:v>
@@ -9326,10 +9431,10 @@
                   <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>21</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>8</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12261,13 +12366,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>171448</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>133348</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -12343,13 +12448,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>41087</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1047750</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>2987</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -12384,14 +12489,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>88899</xdr:rowOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>184149</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12461,8 +12566,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}" name="Table2" displayName="Table2" ref="A1:E27" totalsRowShown="0" headerRowDxfId="35">
-  <autoFilter ref="A1:E27" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}" name="Table2" displayName="Table2" ref="A1:E28" totalsRowShown="0" headerRowDxfId="35">
+  <autoFilter ref="A1:E28" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F25F0D34-0297-4771-8BBB-350BCDD85D46}" name="Week"/>
     <tableColumn id="2" xr3:uid="{39CFCD12-3130-47A8-A140-DBF602F1743D}" name="Done"/>
@@ -12496,8 +12601,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}" name="Table3" displayName="Table3" ref="A1:H39" totalsRowShown="0" headerRowDxfId="31">
-  <autoFilter ref="A1:H39" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}" name="Table3" displayName="Table3" ref="A1:H40" totalsRowShown="0" headerRowDxfId="31">
+  <autoFilter ref="A1:H40" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{8103CDF3-74DC-4B31-821D-E20368EA5455}" name="Versions"/>
     <tableColumn id="2" xr3:uid="{6C3B261F-FA51-42D2-821A-F22633569372}" name="Passed"/>
@@ -12515,8 +12620,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{E4AD0B7A-EC5B-4838-AC2B-8475A3B6644B}" name="Table7" displayName="Table7" ref="A1:H23" totalsRowShown="0" headerRowDxfId="29">
-  <autoFilter ref="A1:H23" xr:uid="{E4AD0B7A-EC5B-4838-AC2B-8475A3B6644B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{E4AD0B7A-EC5B-4838-AC2B-8475A3B6644B}" name="Table7" displayName="Table7" ref="A1:H24" totalsRowShown="0" headerRowDxfId="29">
+  <autoFilter ref="A1:H24" xr:uid="{E4AD0B7A-EC5B-4838-AC2B-8475A3B6644B}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{58F8A895-CEBE-41D2-B7BB-1681C0697C85}" name="Version"/>
     <tableColumn id="2" xr3:uid="{CE08A48D-2419-484B-993C-54A546869B61}" name="To Do" dataDxfId="28"/>
@@ -12525,7 +12630,7 @@
     <tableColumn id="4" xr3:uid="{C5EE39F3-E9DF-4F2E-9576-6DDB97E21DB3}" name="In QA" dataDxfId="25"/>
     <tableColumn id="6" xr3:uid="{CC106112-C63E-4AA5-9AAA-D0A99983E0DD}" name="Internal Test" dataDxfId="24"/>
     <tableColumn id="7" xr3:uid="{C69EECCF-E5E5-4372-B171-2B35FE10B60D}" name="Done" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{C7A900BC-8967-4049-AE22-7F9EDE21E913}" name="Total" dataDxfId="22" totalsRowDxfId="21">
+    <tableColumn id="8" xr3:uid="{C7A900BC-8967-4049-AE22-7F9EDE21E913}" name="Total" dataDxfId="0" totalsRowDxfId="22">
       <calculatedColumnFormula>SUM(Table7[[#This Row],[To Do]:[Done]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12534,18 +12639,18 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}" name="Table5" displayName="Table5" ref="A1:I24" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17" totalsRowBorderDxfId="16" dataCellStyle="Hyperlink">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}" name="Table5" displayName="Table5" ref="A1:I24" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18" totalsRowBorderDxfId="17" dataCellStyle="Hyperlink">
   <autoFilter ref="A1:I24" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{5BE08AE0-E0B5-4B46-9423-456B88C2D9BC}" name="Sprint" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{030F9647-4FC0-4C7E-9B3A-AB099CC59EBA}" name="To Do (0%)" dataDxfId="14" dataCellStyle="Hyperlink"/>
-    <tableColumn id="3" xr3:uid="{7D2923F3-E2CF-4FD9-A7A5-68C36BB95591}" name="STARTING (10 ~ 40%)" dataDxfId="13" dataCellStyle="Hyperlink"/>
-    <tableColumn id="4" xr3:uid="{48FB5317-7F3B-4F74-B244-5A49C7749EBD}" name="In Progress (50 ~ 70%)" dataDxfId="12" dataCellStyle="Hyperlink"/>
-    <tableColumn id="5" xr3:uid="{86F5CCB5-C4C2-4C36-935A-657F085500B1}" name="IN REVIEW (80%)" dataDxfId="11" dataCellStyle="Hyperlink"/>
-    <tableColumn id="9" xr3:uid="{51D22AE3-424C-4604-9869-D672DED4301F}" name="READY FOR TESTING (90%)" dataDxfId="10" dataCellStyle="Hyperlink"/>
-    <tableColumn id="6" xr3:uid="{33C9BCE6-D9EB-4032-9B0A-DDD9A4051A2D}" name="Done (100%)" dataDxfId="9" dataCellStyle="Hyperlink"/>
-    <tableColumn id="8" xr3:uid="{D624FC89-A88E-45AC-9D22-66D66702B8C5}" name="WON'T DO (100%)" dataDxfId="8" dataCellStyle="Hyperlink"/>
-    <tableColumn id="7" xr3:uid="{EFEEB7EC-E2D1-40EA-B265-A558311E5D30}" name="Total" dataDxfId="7" dataCellStyle="Hyperlink">
+    <tableColumn id="1" xr3:uid="{5BE08AE0-E0B5-4B46-9423-456B88C2D9BC}" name="Sprint" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{030F9647-4FC0-4C7E-9B3A-AB099CC59EBA}" name="To Do (0%)" dataDxfId="15" dataCellStyle="Hyperlink"/>
+    <tableColumn id="3" xr3:uid="{7D2923F3-E2CF-4FD9-A7A5-68C36BB95591}" name="STARTING (10 ~ 40%)" dataDxfId="14" dataCellStyle="Hyperlink"/>
+    <tableColumn id="4" xr3:uid="{48FB5317-7F3B-4F74-B244-5A49C7749EBD}" name="In Progress (50 ~ 70%)" dataDxfId="13" dataCellStyle="Hyperlink"/>
+    <tableColumn id="5" xr3:uid="{86F5CCB5-C4C2-4C36-935A-657F085500B1}" name="IN REVIEW (80%)" dataDxfId="12" dataCellStyle="Hyperlink"/>
+    <tableColumn id="9" xr3:uid="{51D22AE3-424C-4604-9869-D672DED4301F}" name="READY FOR TESTING (90%)" dataDxfId="11" dataCellStyle="Hyperlink"/>
+    <tableColumn id="6" xr3:uid="{33C9BCE6-D9EB-4032-9B0A-DDD9A4051A2D}" name="Done (100%)" dataDxfId="10" dataCellStyle="Hyperlink"/>
+    <tableColumn id="8" xr3:uid="{D624FC89-A88E-45AC-9D22-66D66702B8C5}" name="WON'T DO (100%)" dataDxfId="9" dataCellStyle="Hyperlink"/>
+    <tableColumn id="7" xr3:uid="{EFEEB7EC-E2D1-40EA-B265-A558311E5D30}" name="Total" dataDxfId="8" dataCellStyle="Hyperlink">
       <calculatedColumnFormula>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12554,14 +12659,14 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}" name="Table25" displayName="Table25" ref="A1:E27" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A1:E27" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}" name="Table25" displayName="Table25" ref="A1:E28" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="A1:E28" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7070D9F2-0ED1-4F39-8D72-28B37C8E98F2}" name="Week" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{1173F443-CC27-4C6E-A432-BF66DB2A740E}" name="Done" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{2EE10CB5-1AF1-4B50-9456-B3A666DD5338}" name="In Review/Progress" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{328D0A00-85F0-4BFF-81FE-C023998A3701}" name="TODO (P1)" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{E385808E-1FCD-451C-9807-DAF18A42B704}" name="Total" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{7070D9F2-0ED1-4F39-8D72-28B37C8E98F2}" name="Week" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{1173F443-CC27-4C6E-A432-BF66DB2A740E}" name="Done" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{2EE10CB5-1AF1-4B50-9456-B3A666DD5338}" name="In Review/Progress" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{328D0A00-85F0-4BFF-81FE-C023998A3701}" name="TODO (P1)" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{E385808E-1FCD-451C-9807-DAF18A42B704}" name="Total" dataDxfId="1">
       <calculatedColumnFormula>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12886,7 +12991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D733A42-966D-5F4E-B061-B304543CE88E}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.77734375" customWidth="1"/>
@@ -13357,7 +13462,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" ht="21.95" customHeight="1">
       <c r="A27" t="s">
         <v>109</v>
       </c>
@@ -13371,6 +13476,23 @@
         <v>160</v>
       </c>
       <c r="E27" s="12">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28">
+        <v>37</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>160</v>
+      </c>
+      <c r="E28" s="12">
         <v>198</v>
       </c>
     </row>
@@ -13939,7 +14061,7 @@
         <v>111</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -13954,11 +14076,11 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="H21">
         <f>SUM(Table1[[#This Row],[Passed]:[Untested]])</f>
-        <v>489</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -13973,7 +14095,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA6EDF6-834F-DA49-B3FC-BFE1673433AB}">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
@@ -14856,6 +14978,33 @@
       <c r="H39" s="12">
         <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
         <v>967</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="A40" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B40">
+        <v>1220</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>4</v>
+      </c>
+      <c r="E40">
+        <v>5</v>
+      </c>
+      <c r="F40">
+        <v>9</v>
+      </c>
+      <c r="G40">
+        <v>284</v>
+      </c>
+      <c r="H40" s="12">
+        <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
+        <v>1522</v>
       </c>
     </row>
   </sheetData>
@@ -14870,7 +15019,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7C79DB4-6EC1-E840-9DE9-46C117A6F960}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
@@ -15416,7 +15565,7 @@
       <c r="G20">
         <v>8</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="12">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
         <v>9</v>
       </c>
@@ -15453,7 +15602,7 @@
         <v>93</v>
       </c>
       <c r="B22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -15472,7 +15621,7 @@
       </c>
       <c r="H22">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -15480,7 +15629,7 @@
         <v>105</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -15495,11 +15644,38 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" s="12">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
         <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24" s="12">
+        <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -15579,11 +15755,11 @@
         <v>6</v>
       </c>
       <c r="H2" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18" thickBot="1">
@@ -16011,7 +16187,7 @@
         <v>95</v>
       </c>
       <c r="B17" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" s="5">
         <v>0</v>
@@ -16029,7 +16205,7 @@
         <v>33</v>
       </c>
       <c r="H17" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
@@ -16041,7 +16217,7 @@
         <v>96</v>
       </c>
       <c r="B18" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" s="5">
         <v>0</v>
@@ -16059,7 +16235,7 @@
         <v>28</v>
       </c>
       <c r="H18" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I18" s="5">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
@@ -16191,29 +16367,29 @@
         <v>103</v>
       </c>
       <c r="B23" s="5">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5">
         <v>0</v>
       </c>
       <c r="E23" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F23" s="5">
+        <v>5</v>
+      </c>
+      <c r="G23" s="5">
+        <v>9</v>
+      </c>
+      <c r="H23" s="5">
         <v>1</v>
-      </c>
-      <c r="G23" s="5">
-        <v>3</v>
-      </c>
-      <c r="H23" s="5">
-        <v>0</v>
       </c>
       <c r="I23" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="18" thickBot="1">
@@ -16221,7 +16397,7 @@
         <v>110</v>
       </c>
       <c r="B24" s="5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C24" s="5">
         <v>0</v>
@@ -16243,173 +16419,173 @@
       </c>
       <c r="I24" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{97F6B08B-6331-4B8C-8F45-657EC3D1E8F9}"/>
-    <hyperlink ref="D3" r:id="rId2" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2CE19764-8741-47E6-85F8-7CA5266C34CB}"/>
-    <hyperlink ref="G3" r:id="rId3" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{CF707013-C81F-4A85-AC48-8FCF6228781D}"/>
-    <hyperlink ref="E3" r:id="rId4" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D762CE94-80AB-4734-93A5-3F8508FE931D}"/>
-    <hyperlink ref="H3" r:id="rId5" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{B93EF06E-2C7D-43C1-B359-60CCA19800CB}"/>
-    <hyperlink ref="C3" r:id="rId6" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{753B0838-D5BE-4F91-9081-9E257AE874C3}"/>
-    <hyperlink ref="F3" r:id="rId7" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{AE59092D-3518-45A2-9C3F-02A6A1D47B0A}"/>
-    <hyperlink ref="B4" r:id="rId8" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{73D7B8FF-149D-473C-BDD3-8EEA2EAA0104}"/>
-    <hyperlink ref="D4" r:id="rId9" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{338ADF01-6813-4C9D-B03A-31B18A007CF8}"/>
-    <hyperlink ref="G4" r:id="rId10" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3E1AB134-96A5-4197-903E-EF3A2259BA3D}"/>
-    <hyperlink ref="E4" r:id="rId11" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{85F19B3A-B9D0-47D0-91D4-956E9C8E6AEE}"/>
-    <hyperlink ref="H4" r:id="rId12" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{6857D4D8-6A00-4708-AC64-E948460F069E}"/>
-    <hyperlink ref="C4" r:id="rId13" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{9D260C02-F8A0-4CC6-9CCF-8227DD109586}"/>
-    <hyperlink ref="F4" r:id="rId14" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F391AB16-864C-4532-9AE9-EDAF9BE839A2}"/>
-    <hyperlink ref="B5" r:id="rId15" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{8D9CA4CA-2C99-49B9-8FE4-0AEB844094E2}"/>
-    <hyperlink ref="D5" r:id="rId16" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{9FEB4A96-9FA8-4DC4-BA13-E4DB16C5E09C}"/>
-    <hyperlink ref="G5" r:id="rId17" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C2FCBAEC-77EE-486B-BB2F-E7187364689E}"/>
-    <hyperlink ref="E5" r:id="rId18" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{2472A073-4D5B-43CF-89E8-2A2E2107B462}"/>
-    <hyperlink ref="H5" r:id="rId19" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{1A0C03D5-0020-4246-9C4D-97AE0A5B0F73}"/>
-    <hyperlink ref="C5" r:id="rId20" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A868CD39-A0B9-4D70-88E3-9CD6EF84BF04}"/>
-    <hyperlink ref="F5" r:id="rId21" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{636AF472-7827-4003-A180-F737B814B3FE}"/>
-    <hyperlink ref="B6" r:id="rId22" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{2B251480-09E8-4A43-AD3C-753FDF561FD3}"/>
-    <hyperlink ref="D6" r:id="rId23" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{5BB7BA55-FF8C-4004-A094-422BC877741B}"/>
-    <hyperlink ref="G6" r:id="rId24" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{193FF21A-0ED8-49AB-AF60-21B747D3794B}"/>
-    <hyperlink ref="E6" r:id="rId25" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{713C196C-10CB-43CD-98A5-4427DA027DB1}"/>
-    <hyperlink ref="H6" r:id="rId26" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E476F302-AF43-4566-BB7D-B874C8986983}"/>
-    <hyperlink ref="C6" r:id="rId27" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{07CA0DE7-2310-47D4-BBE4-F6F66BDB5C3E}"/>
-    <hyperlink ref="F6" r:id="rId28" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{AFD24D83-E5B2-452A-95B9-A2822703D296}"/>
-    <hyperlink ref="B7" r:id="rId29" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{DCC996B8-9960-491F-A751-9CDDC79A61EE}"/>
-    <hyperlink ref="D7" r:id="rId30" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{FE7264C0-0F9D-4443-92BB-C40DECE26D7B}"/>
-    <hyperlink ref="G7" r:id="rId31" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{D5115A28-51E3-4F3A-B1B4-7F9A251D1052}"/>
-    <hyperlink ref="E7" r:id="rId32" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B7ABA0A0-9A6D-4E20-BA5B-8997ECDF265D}"/>
-    <hyperlink ref="H7" r:id="rId33" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{7156FC73-161C-408A-9A74-49E0A3B2D6A7}"/>
-    <hyperlink ref="C7" r:id="rId34" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{3FEBD497-4D52-460D-9057-0F6F38CF4F1D}"/>
-    <hyperlink ref="F7" r:id="rId35" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E1955951-9D86-49A1-B7E4-A829A83D9AEA}"/>
-    <hyperlink ref="B8" r:id="rId36" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{21D631C3-CCAF-4571-BEB4-8934C2A0EA14}"/>
-    <hyperlink ref="D8" r:id="rId37" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{74FCAD1E-672D-4858-A527-8016C02B69F2}"/>
-    <hyperlink ref="G8" r:id="rId38" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{2FD5EA99-7F49-4E6F-90CD-D0417CDA9D43}"/>
-    <hyperlink ref="E8" r:id="rId39" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{408419E7-55DB-4A54-B48F-B1A57DCE1E54}"/>
-    <hyperlink ref="H8" r:id="rId40" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{CA56B963-4041-4A2D-A107-EE6A817089F6}"/>
-    <hyperlink ref="C8" r:id="rId41" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C798F4C5-C890-4D2A-91BC-ED3B44418D1D}"/>
-    <hyperlink ref="F8" r:id="rId42" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{70DAA7BF-2490-4212-A726-3DC65D836F6D}"/>
-    <hyperlink ref="B9" r:id="rId43" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{29752EE5-C54C-489D-9FBB-2AF3B7661FE8}"/>
-    <hyperlink ref="D9" r:id="rId44" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{14EDA7AB-AD21-446B-8CDD-B814135C7218}"/>
-    <hyperlink ref="G9" r:id="rId45" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{380DEAE9-0EAC-42B9-A71D-1ED751710F8B}"/>
-    <hyperlink ref="E9" r:id="rId46" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{06EC0BDC-3CFA-44AB-9836-0A1C78B39465}"/>
-    <hyperlink ref="H9" r:id="rId47" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{57B347BC-893B-4BA7-944F-4A19B27AD104}"/>
-    <hyperlink ref="C9" r:id="rId48" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{19A8BDBF-4974-411F-A11B-AF1BC33D4474}"/>
-    <hyperlink ref="F9" r:id="rId49" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C8535763-75D1-4770-BF9F-D1637AC16360}"/>
-    <hyperlink ref="B10" r:id="rId50" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{1FD3BB21-AF4D-4E52-AADE-B519EEA0E6F8}"/>
-    <hyperlink ref="D10" r:id="rId51" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{615399CA-430B-4E09-94AE-342652153380}"/>
-    <hyperlink ref="G10" r:id="rId52" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F575ACC0-675C-4047-9EB9-FD7F3D22277C}"/>
-    <hyperlink ref="E10" r:id="rId53" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A3397DB6-62C6-466B-9472-A430A42CEB6C}"/>
-    <hyperlink ref="H10" r:id="rId54" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{3B3EE6CC-0D3D-415A-80AF-A6C6BE933731}"/>
-    <hyperlink ref="C10" r:id="rId55" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{7C001704-87D3-41D7-AF65-F99635990AFC}"/>
-    <hyperlink ref="F10" r:id="rId56" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{DD5BB0F2-DBF5-44FD-BAC9-CFE228FE7724}"/>
-    <hyperlink ref="B11" r:id="rId57" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{DDDE3DF0-6E6E-46B5-A29C-33D29B33D304}"/>
-    <hyperlink ref="D11" r:id="rId58" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{52A3BC6B-4C12-438B-B198-BE3634D73DCD}"/>
-    <hyperlink ref="G11" r:id="rId59" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3D811382-00B5-43EA-B32D-3278480D9E68}"/>
-    <hyperlink ref="E11" r:id="rId60" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{803C85B2-F2C8-4AC9-85BA-F16C339B96E6}"/>
-    <hyperlink ref="H11" r:id="rId61" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{21E346AE-2AC3-4A55-8717-7C6ABD2CB25C}"/>
-    <hyperlink ref="C11" r:id="rId62" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{CC47B98E-F61B-49C8-B8EF-AFFBAA4E5447}"/>
-    <hyperlink ref="F11" r:id="rId63" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{855D923A-E1A6-41C9-8B06-3776053E30FE}"/>
-    <hyperlink ref="B12" r:id="rId64" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{EEEA534A-3E56-4005-8B3C-889884CBF0D3}"/>
-    <hyperlink ref="D12" r:id="rId65" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{E65D65D7-94A6-4C4A-9792-59817A87728A}"/>
-    <hyperlink ref="G12" r:id="rId66" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{383B18D0-3DEE-4FAB-A3A5-9F92891C889B}"/>
-    <hyperlink ref="E12" r:id="rId67" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{6C05C6E7-2529-4C75-9098-B3C20460C320}"/>
-    <hyperlink ref="H12" r:id="rId68" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{D4FD4B56-5AB4-494E-8724-56BAB26A761B}"/>
-    <hyperlink ref="C12" r:id="rId69" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{800875E2-867C-485D-8C29-3D8B910B70EB}"/>
-    <hyperlink ref="F12" r:id="rId70" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{1B892854-2C9F-4EB7-82DA-88BCD24757CB}"/>
-    <hyperlink ref="B13" r:id="rId71" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{48E94CC3-E6CB-4057-8C7D-EF75D371AC4E}"/>
-    <hyperlink ref="D13" r:id="rId72" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{786A83B5-36C4-4A25-85D9-B5063E225F64}"/>
-    <hyperlink ref="G13" r:id="rId73" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F3B6E45C-D41B-43CE-AE71-3D0FD1C4B5B8}"/>
-    <hyperlink ref="E13" r:id="rId74" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{1B8A11DA-A114-4D3A-BBD7-7A1C44B63CAB}"/>
-    <hyperlink ref="H13" r:id="rId75" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{73A9633C-3DBF-47C8-AB17-2875D8083CD2}"/>
-    <hyperlink ref="C13" r:id="rId76" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{41BE0B95-7F00-41BD-B26E-F61E0D0ECF57}"/>
-    <hyperlink ref="F13" r:id="rId77" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C5303366-F11C-48A2-A19B-37666DB31384}"/>
-    <hyperlink ref="B14" r:id="rId78" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{1F783EF2-0C56-40FB-A7FC-BBDB76FC95A2}"/>
-    <hyperlink ref="D14" r:id="rId79" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{C80B98EC-3369-4CC5-8D4B-4B0CAE809355}"/>
-    <hyperlink ref="G14" r:id="rId80" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{430F09D6-5389-47F0-92F3-6673E410CCF8}"/>
-    <hyperlink ref="E14" r:id="rId81" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B7B40CED-8051-46D8-AC23-AA0B60E07991}"/>
-    <hyperlink ref="H14" r:id="rId82" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{311E5105-9939-4D2B-B29D-90CE009DC12C}"/>
-    <hyperlink ref="C14" r:id="rId83" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{37C5211C-854A-4824-8F7A-0EE2AD92CF8F}"/>
-    <hyperlink ref="F14" r:id="rId84" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{ECE827E7-7014-4EBE-8731-C173A3E16090}"/>
-    <hyperlink ref="B2" r:id="rId85" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{ECC2139E-791E-4770-9749-924C8171413E}"/>
-    <hyperlink ref="D2" r:id="rId86" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{A3490D76-D554-40B0-94C2-6BCE62D65128}"/>
-    <hyperlink ref="G2" r:id="rId87" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{E73331BD-FAD2-46B3-9C4A-B1F1944F18FC}"/>
-    <hyperlink ref="E2" r:id="rId88" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{363312FF-8351-469B-A0E2-96F2CEBC31DF}"/>
-    <hyperlink ref="H2" r:id="rId89" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{33FD27D8-D06C-4600-84C6-9AF958F84B2B}"/>
-    <hyperlink ref="C2" r:id="rId90" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C0932090-8C86-4ADD-B05E-5218E24825BD}"/>
-    <hyperlink ref="F2" r:id="rId91" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A689B4DB-1B76-459A-A757-14C2A4E04261}"/>
-    <hyperlink ref="B15" r:id="rId92" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{CEC46233-AEB1-43F5-BBF4-45B55E1036E7}"/>
-    <hyperlink ref="D15" r:id="rId93" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{E00230F7-006F-4483-8FF9-293DDDC7BCD2}"/>
-    <hyperlink ref="G15" r:id="rId94" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{08C36869-7439-481C-88F2-C2B5F3E85362}"/>
-    <hyperlink ref="E15" r:id="rId95" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A80CFC3A-2BAA-4A2C-943E-E0A50A2D9378}"/>
-    <hyperlink ref="H15" r:id="rId96" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{8B8D1DAF-6253-472F-9A66-933E4916940C}"/>
-    <hyperlink ref="C15" r:id="rId97" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A6CEB30F-B1BB-4EEF-B70E-3EC83B3E3438}"/>
-    <hyperlink ref="F15" r:id="rId98" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{1D76AB3E-7128-401F-BCD5-4869C78E8EAE}"/>
-    <hyperlink ref="B16" r:id="rId99" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{EBE7433A-5296-449E-BBB7-313B398D004B}"/>
-    <hyperlink ref="D16" r:id="rId100" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D874F7C9-B94F-48A0-915C-704EEAAC0A20}"/>
-    <hyperlink ref="E16" r:id="rId101" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{9F1D3361-B1B3-4C77-84C8-3C11CE2DE020}"/>
-    <hyperlink ref="H16" r:id="rId102" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{D7147B34-65EC-45ED-81A5-F54C88208DB7}"/>
-    <hyperlink ref="C16" r:id="rId103" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C4B33AA8-220C-4E12-8F9A-34AF8A2A6704}"/>
-    <hyperlink ref="F16" r:id="rId104" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{FA2A7FCF-6347-4D7A-80C3-6D8350C82DA4}"/>
-    <hyperlink ref="B17" r:id="rId105" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{59CA8689-C1F2-41EE-A465-066C0E0DEFAF}"/>
-    <hyperlink ref="D17" r:id="rId106" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{F50DDE7E-9D60-4E00-9DC2-6D595997FB9C}"/>
-    <hyperlink ref="E17" r:id="rId107" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{0A86B503-ADC0-444D-ABBB-6764D5EEB2B1}"/>
-    <hyperlink ref="H17" r:id="rId108" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E95F6969-5600-4805-A22E-451097FF33C3}"/>
-    <hyperlink ref="C17" r:id="rId109" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{F5CD2F46-915C-47FF-912B-89000081E733}"/>
-    <hyperlink ref="F17" r:id="rId110" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{200E82B0-B654-4A00-8530-FCEB858874D0}"/>
-    <hyperlink ref="B18" r:id="rId111" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{BCDCF649-5CBC-42E4-8620-1C81AF1B23FF}"/>
-    <hyperlink ref="D18" r:id="rId112" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{E54331BB-C33D-4380-B73F-3756F0FC2F14}"/>
-    <hyperlink ref="E18" r:id="rId113" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{2A006D1C-721E-497A-B5CC-85CAEE423836}"/>
-    <hyperlink ref="H18" r:id="rId114" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{57474496-F8C0-4883-9C04-278511F4F901}"/>
-    <hyperlink ref="C18" r:id="rId115" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{4CA530EA-7090-445A-B98D-FACDA3F39B99}"/>
-    <hyperlink ref="F18" r:id="rId116" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{3FB61006-C835-41E0-A898-176B637118A4}"/>
-    <hyperlink ref="B19" r:id="rId117" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{654A79F9-EC00-4B49-BB80-493704BBFB18}"/>
-    <hyperlink ref="D19" r:id="rId118" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{E38AD4A5-6768-4CD8-914B-6C113E6877F5}"/>
-    <hyperlink ref="E19" r:id="rId119" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{945C014B-9E64-40C4-8707-855DE9581DB7}"/>
-    <hyperlink ref="H19" r:id="rId120" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{CD41350E-CC13-46C9-9B58-5FD048617A17}"/>
-    <hyperlink ref="C19" r:id="rId121" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A5900141-601A-4A94-BF84-E34806FCEE5E}"/>
-    <hyperlink ref="F19" r:id="rId122" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{31386E48-3615-49CF-AFA9-BFCFBF36DEC6}"/>
-    <hyperlink ref="B20" r:id="rId123" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C9CA4C4B-AEBC-4EB6-857A-159C4D3A53E8}"/>
-    <hyperlink ref="D20" r:id="rId124" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{9A281456-11AE-473B-8CBA-EFE9C54F7885}"/>
-    <hyperlink ref="E20" r:id="rId125" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{34A1D8C0-20A6-4436-A4B1-C6F90A138397}"/>
-    <hyperlink ref="H20" r:id="rId126" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{6814B0AE-3A96-4530-8883-02C68E3974C5}"/>
-    <hyperlink ref="C20" r:id="rId127" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{7B7C24DA-E67D-488C-90E9-3AEF3BC30D9B}"/>
-    <hyperlink ref="F20" r:id="rId128" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{B5B90D06-A815-4003-8ACA-27DFC2CAE260}"/>
-    <hyperlink ref="B21" r:id="rId129" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C57E3CD6-E2E1-4878-86C0-C8A4F74B6943}"/>
-    <hyperlink ref="D21" r:id="rId130" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{0C6FD858-1ADF-4092-AA2B-9713208568CA}"/>
-    <hyperlink ref="E21" r:id="rId131" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{6CC6B938-791A-41C1-9389-927962895B22}"/>
-    <hyperlink ref="H21" r:id="rId132" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{DE0D1CEA-7FA4-4205-819F-73863F40783F}"/>
-    <hyperlink ref="C21" r:id="rId133" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{4D39EF51-3FDE-4C27-9EF4-5524AC910EEE}"/>
-    <hyperlink ref="F21" r:id="rId134" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{9DFAE6B0-1AEE-448C-BA14-1F313DBE1602}"/>
-    <hyperlink ref="B22" r:id="rId135" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{BE6D6466-4A5A-4AB2-9EFA-2C4D2C1E8AFF}"/>
-    <hyperlink ref="D22" r:id="rId136" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{7470F8A9-8284-4AEA-9FA2-BF9CE7937358}"/>
-    <hyperlink ref="E22" r:id="rId137" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{7956657D-26D3-4605-9E99-33F3A1D6B6EE}"/>
-    <hyperlink ref="H22" r:id="rId138" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{C623CAE8-6648-4155-A74E-0042B043D15D}"/>
-    <hyperlink ref="C22" r:id="rId139" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{14ECCE02-C0D5-48C6-A5C8-CDCDF283EB78}"/>
-    <hyperlink ref="F22" r:id="rId140" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A9DEE48A-109D-4928-A89F-ABCB122792D5}"/>
-    <hyperlink ref="B23" r:id="rId141" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{5A2F68C6-B54C-4C1F-94CC-2735B4FC62AA}"/>
-    <hyperlink ref="D23" r:id="rId142" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{43B2273B-A0AD-40BF-B3CF-58D6ED229970}"/>
-    <hyperlink ref="E23" r:id="rId143" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F142813D-5F7B-4E11-9FCD-070E0AC8ADEB}"/>
-    <hyperlink ref="H23" r:id="rId144" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{07AA1D2D-87B1-4E5F-9019-007777379DA0}"/>
-    <hyperlink ref="C23" r:id="rId145" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{514E936D-004B-4D0F-BFA9-D24E2C16742C}"/>
-    <hyperlink ref="F23" r:id="rId146" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{D2B98F43-625C-4C5F-B4CD-DAA65AAD3C31}"/>
-    <hyperlink ref="B24" r:id="rId147" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{843EBD87-0262-4B26-B795-F87A820AA39F}"/>
-    <hyperlink ref="D24" r:id="rId148" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D90209FA-5A42-4641-8FFF-5327312A652C}"/>
-    <hyperlink ref="E24" r:id="rId149" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{5BEC239B-6589-4860-9853-978B7AF22DF4}"/>
-    <hyperlink ref="H24" r:id="rId150" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{721280F6-C5CE-4331-88CE-6E49D1B5C6A3}"/>
-    <hyperlink ref="C24" r:id="rId151" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{0D134C8E-43C9-4790-9EB4-58547C99D977}"/>
-    <hyperlink ref="F24" r:id="rId152" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C239BF9C-0D18-44ED-B019-C3E5AA99FF46}"/>
-    <hyperlink ref="G16" r:id="rId153" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{A125BFD2-35B7-40C9-B4E3-CABF3B4FB481}"/>
-    <hyperlink ref="G17" r:id="rId154" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F068A1F6-B397-4F92-8579-C9F34E179374}"/>
-    <hyperlink ref="G18" r:id="rId155" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{6FCF7054-5C99-4F04-86EB-D0211B256B99}"/>
-    <hyperlink ref="G19" r:id="rId156" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{6412AB69-01AB-4A0A-AF48-238CB8933AD9}"/>
-    <hyperlink ref="G20" r:id="rId157" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{EF22CFFE-00E3-4A1C-A810-8165B0B35800}"/>
-    <hyperlink ref="G21" r:id="rId158" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{9F3AD8E1-4C46-4BB4-9335-A8617D665C34}"/>
-    <hyperlink ref="G22" r:id="rId159" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{771970A7-7F19-4D05-9B7C-C3CA4FF29043}"/>
-    <hyperlink ref="G23" r:id="rId160" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{710A57A1-3964-4216-9E22-27B2DBD33277}"/>
-    <hyperlink ref="G24" r:id="rId161" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{5B0ED04E-0ED3-48B4-AE9E-2217221918C2}"/>
+    <hyperlink ref="B2" r:id="rId1" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{ECC2139E-791E-4770-9749-924C8171413E}"/>
+    <hyperlink ref="D2" r:id="rId2" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{A3490D76-D554-40B0-94C2-6BCE62D65128}"/>
+    <hyperlink ref="G2" r:id="rId3" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{E73331BD-FAD2-46B3-9C4A-B1F1944F18FC}"/>
+    <hyperlink ref="E2" r:id="rId4" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{363312FF-8351-469B-A0E2-96F2CEBC31DF}"/>
+    <hyperlink ref="H2" r:id="rId5" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{33FD27D8-D06C-4600-84C6-9AF958F84B2B}"/>
+    <hyperlink ref="C2" r:id="rId6" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C0932090-8C86-4ADD-B05E-5218E24825BD}"/>
+    <hyperlink ref="F2" r:id="rId7" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A689B4DB-1B76-459A-A757-14C2A4E04261}"/>
+    <hyperlink ref="B3" r:id="rId8" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A5CAF974-56E2-4541-BBC1-3EB2AFE89540}"/>
+    <hyperlink ref="D3" r:id="rId9" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{0576CFE6-25FE-4850-A50C-D4EF9C5C288D}"/>
+    <hyperlink ref="G3" r:id="rId10" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{6A3726CF-7A79-4DB0-A35D-01076E6C4CD2}"/>
+    <hyperlink ref="E3" r:id="rId11" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{AC29D7F9-DB7F-4161-BB80-C72D1BBBF39E}"/>
+    <hyperlink ref="H3" r:id="rId12" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{357E5794-FD1F-4928-96FA-1C3EF0E080E5}"/>
+    <hyperlink ref="C3" r:id="rId13" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{4B4462C8-BD6A-4208-93D3-C2D52A2AD585}"/>
+    <hyperlink ref="F3" r:id="rId14" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F3F7DF96-A9FE-4C8F-A0BD-D531A4B077EF}"/>
+    <hyperlink ref="B4" r:id="rId15" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{9E37D979-E337-47AE-B23A-654EBEBEA932}"/>
+    <hyperlink ref="D4" r:id="rId16" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{44BCA075-84AC-4361-B3BF-1737A343B8B4}"/>
+    <hyperlink ref="G4" r:id="rId17" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{DECFC323-AB02-4745-94A7-79CCFB384E3B}"/>
+    <hyperlink ref="E4" r:id="rId18" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{2DD9B9B7-89F3-4818-AF5D-51EF03E1B4C1}"/>
+    <hyperlink ref="H4" r:id="rId19" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{02DCE810-6BB2-4C13-A8E6-29CA9044C881}"/>
+    <hyperlink ref="C4" r:id="rId20" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{9FBD8793-FEAC-49B9-9607-CD8F9F45B1CC}"/>
+    <hyperlink ref="F4" r:id="rId21" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{6F3B394A-72FE-4700-8369-240BB81DCE44}"/>
+    <hyperlink ref="B5" r:id="rId22" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{8BAD55EB-90D0-4AD6-9706-A8D208B27D1D}"/>
+    <hyperlink ref="D5" r:id="rId23" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{14E8BFCC-A84B-40B1-A064-54E14EBE8DDF}"/>
+    <hyperlink ref="G5" r:id="rId24" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{629ECA61-F425-4703-9ABA-B8D87E01FF42}"/>
+    <hyperlink ref="E5" r:id="rId25" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{8EAA964E-F294-43D3-B343-B6AFBB6E94D7}"/>
+    <hyperlink ref="H5" r:id="rId26" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{35B1344A-F214-47AD-BEB4-966C5A0AC2FA}"/>
+    <hyperlink ref="C5" r:id="rId27" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{21928EBB-EB7E-44A4-A8A7-B7AE9CE492F9}"/>
+    <hyperlink ref="F5" r:id="rId28" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{B7263387-7038-4B3C-892B-0FB847A3D713}"/>
+    <hyperlink ref="B6" r:id="rId29" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C3D7ED8C-32E2-4503-B61D-29C7E22DB6C9}"/>
+    <hyperlink ref="D6" r:id="rId30" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{DBA75831-6F53-42DF-92CF-675154509594}"/>
+    <hyperlink ref="G6" r:id="rId31" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C8609D1F-0BD6-4A14-838C-C292282EFD8D}"/>
+    <hyperlink ref="E6" r:id="rId32" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B78856CB-F3FD-47E4-8A85-E94C564F647A}"/>
+    <hyperlink ref="H6" r:id="rId33" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{60DE4A6A-8139-42BC-9A99-3C99A581556F}"/>
+    <hyperlink ref="C6" r:id="rId34" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{FD0FEBA6-4AE5-41D3-A749-932E17983459}"/>
+    <hyperlink ref="F6" r:id="rId35" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{37B8A0DB-FB80-4CE4-9AD7-87443FC7F270}"/>
+    <hyperlink ref="B7" r:id="rId36" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{0B301508-AF4F-44F3-AA4A-2C01021AF851}"/>
+    <hyperlink ref="D7" r:id="rId37" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D713B67D-8832-42F6-A9ED-0062F67E9077}"/>
+    <hyperlink ref="G7" r:id="rId38" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{AC1420BA-8514-49F7-B35E-4D1FD28E76D1}"/>
+    <hyperlink ref="E7" r:id="rId39" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{0ADA16B8-F45C-41D4-8C5F-D956C6D16B42}"/>
+    <hyperlink ref="H7" r:id="rId40" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{64CDDCC6-B91C-49FB-92BD-0780B29DF9FF}"/>
+    <hyperlink ref="C7" r:id="rId41" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{5038F61D-21C0-4FAB-B724-2E28D0CE1074}"/>
+    <hyperlink ref="F7" r:id="rId42" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{0BDE8639-3915-4BC0-ADE8-22266356ABD9}"/>
+    <hyperlink ref="B8" r:id="rId43" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{6318D2F1-4656-4527-9498-CF3C903FA0A2}"/>
+    <hyperlink ref="D8" r:id="rId44" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{412376BB-1894-405F-951A-B5CE5755B22C}"/>
+    <hyperlink ref="G8" r:id="rId45" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{0FBB761D-0658-4CC4-95B7-1B7F9B4A0C64}"/>
+    <hyperlink ref="E8" r:id="rId46" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{4446CB20-73A7-4D73-A3E0-563FCC1184C9}"/>
+    <hyperlink ref="H8" r:id="rId47" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{2D64E32A-DC0B-4E97-863B-43D5146B3BD6}"/>
+    <hyperlink ref="C8" r:id="rId48" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{B4D60C72-EA21-428E-B2E9-4180AADD50C3}"/>
+    <hyperlink ref="F8" r:id="rId49" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{26E3D28F-D7A9-4C2F-B1FB-8D73E913221F}"/>
+    <hyperlink ref="B9" r:id="rId50" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{9C47A2E1-A5F6-4323-B7FC-84E0D2A35A41}"/>
+    <hyperlink ref="D9" r:id="rId51" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2BCFBC9B-A377-4D73-842E-8EC90D3E593E}"/>
+    <hyperlink ref="G9" r:id="rId52" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{51EA0688-1928-4D73-95DF-ACCE217B6EDD}"/>
+    <hyperlink ref="E9" r:id="rId53" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{844BEA60-E68A-4B97-B8AC-74903536E25D}"/>
+    <hyperlink ref="H9" r:id="rId54" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E9793F71-80CD-4A7B-8B18-A825D505BCD2}"/>
+    <hyperlink ref="C9" r:id="rId55" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A8FA0ED8-8CC4-4D9A-B09B-0AA50AF6815A}"/>
+    <hyperlink ref="F9" r:id="rId56" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C5918F7E-E6CF-4041-8AC0-EB9EF66D9236}"/>
+    <hyperlink ref="B10" r:id="rId57" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{350E84CE-F968-4EB3-9710-57F61789AC27}"/>
+    <hyperlink ref="D10" r:id="rId58" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{1CF911AA-89D0-457A-B577-9FBFEC516C58}"/>
+    <hyperlink ref="G10" r:id="rId59" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{5FA3C6C1-A5F6-407A-BFFD-15F2269A2767}"/>
+    <hyperlink ref="E10" r:id="rId60" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D0839BC4-6FC7-4D80-9EB1-A4BE87BE07E1}"/>
+    <hyperlink ref="H10" r:id="rId61" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{61AB3BFA-DFA6-47A6-AC33-D4BE683F81BE}"/>
+    <hyperlink ref="C10" r:id="rId62" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{4077FB81-25D0-47DC-9EFF-EE4AE7C94109}"/>
+    <hyperlink ref="F10" r:id="rId63" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{9CE66375-097B-4A05-B4F2-3B5E95A42BF4}"/>
+    <hyperlink ref="B11" r:id="rId64" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C6E5B636-78F3-4EAF-93B6-65D8DC58F867}"/>
+    <hyperlink ref="D11" r:id="rId65" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{6F198A67-34D3-4656-8825-C850D704E10C}"/>
+    <hyperlink ref="G11" r:id="rId66" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{CE537456-33D0-45E5-982A-F19FF8052478}"/>
+    <hyperlink ref="E11" r:id="rId67" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{5DCCA5EE-A804-44F7-B390-55CE72C84A19}"/>
+    <hyperlink ref="H11" r:id="rId68" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{0AFD189A-A6BF-4EC4-9BD7-28278FC81648}"/>
+    <hyperlink ref="C11" r:id="rId69" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{4EF649A5-D5CB-4DDA-8DAD-E6AD55AFE0B3}"/>
+    <hyperlink ref="F11" r:id="rId70" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{7B4F5059-EDBA-4F62-AF4B-9C4E679550E3}"/>
+    <hyperlink ref="B12" r:id="rId71" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{D372CCC4-0FDD-4D65-B392-8A64C0FE94ED}"/>
+    <hyperlink ref="D12" r:id="rId72" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{9B129C26-45AE-4101-B15F-225ED8002AB0}"/>
+    <hyperlink ref="G12" r:id="rId73" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{706C9157-13C6-427C-89F1-C38DDFC588FD}"/>
+    <hyperlink ref="E12" r:id="rId74" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{17F4C908-6E94-4071-9F12-70297BBBB65E}"/>
+    <hyperlink ref="H12" r:id="rId75" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{3B91C677-9CFD-4B28-A4BC-D4D07CBCB5D0}"/>
+    <hyperlink ref="C12" r:id="rId76" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{74199A6E-B75A-4DAB-B2EA-903A765995AD}"/>
+    <hyperlink ref="F12" r:id="rId77" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{B53CB8B2-9B74-40F7-A907-50D93B32D91B}"/>
+    <hyperlink ref="B13" r:id="rId78" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{2534FD19-020A-4EE1-BE0D-A1D732E046AF}"/>
+    <hyperlink ref="D13" r:id="rId79" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{52FFD7AC-8DAB-4AFE-A94D-9F74875E26B0}"/>
+    <hyperlink ref="G13" r:id="rId80" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{0B71C7B9-CAB9-4513-AEE8-7D902192BB55}"/>
+    <hyperlink ref="E13" r:id="rId81" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{110844CE-359B-4176-832B-AE95F97404F2}"/>
+    <hyperlink ref="H13" r:id="rId82" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{B7FD7691-0569-4FF8-82AC-8300790776CF}"/>
+    <hyperlink ref="C13" r:id="rId83" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{420EA762-9A72-4CA1-846F-EA18FA882FA3}"/>
+    <hyperlink ref="F13" r:id="rId84" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{4EC3DB9C-0F83-4CBC-AC64-AA51A16EE2BB}"/>
+    <hyperlink ref="B14" r:id="rId85" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{0CDC764F-B5AD-4394-B6E4-2B5EB7EAFCC0}"/>
+    <hyperlink ref="D14" r:id="rId86" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{478728AB-BB5A-4678-AFC4-00EBFA8A430A}"/>
+    <hyperlink ref="G14" r:id="rId87" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3A3DE6BA-B502-404A-8CDF-9333661678E6}"/>
+    <hyperlink ref="E14" r:id="rId88" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{9104CEF4-3097-4856-9561-410C4AB4D716}"/>
+    <hyperlink ref="H14" r:id="rId89" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{7AB4578D-9F87-435C-A939-505BDCC02890}"/>
+    <hyperlink ref="C14" r:id="rId90" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{E9224761-6EF7-4233-B031-0B36CF5192D1}"/>
+    <hyperlink ref="F14" r:id="rId91" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{9D093A32-31F4-4BF4-9966-A447932ECD08}"/>
+    <hyperlink ref="B15" r:id="rId92" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{D31B34B6-63A3-45EF-83C9-FCEB40B92C85}"/>
+    <hyperlink ref="D15" r:id="rId93" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{B26BC3A8-0C21-4490-A74A-68DCFB866457}"/>
+    <hyperlink ref="G15" r:id="rId94" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{4FA13B3B-33E2-4F5E-9AAF-0871331575F8}"/>
+    <hyperlink ref="E15" r:id="rId95" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{AD096D74-46D8-4676-A682-119050F75BC5}"/>
+    <hyperlink ref="H15" r:id="rId96" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{76646DD6-ACBA-449B-95AC-850112A3D7DB}"/>
+    <hyperlink ref="C15" r:id="rId97" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{F1EE5D73-6C06-4070-8908-F0A80AB102CB}"/>
+    <hyperlink ref="F15" r:id="rId98" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{6480DEDC-15DA-4230-8F95-DA170BB79EB4}"/>
+    <hyperlink ref="B16" r:id="rId99" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{1FC9F597-7790-4126-A581-1FB24BA9C08B}"/>
+    <hyperlink ref="D16" r:id="rId100" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{702F4E9D-1699-4299-8DF0-3A8D2B5D7123}"/>
+    <hyperlink ref="G16" r:id="rId101" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{35FCE29A-50A4-44FF-9066-48973F4C91B5}"/>
+    <hyperlink ref="E16" r:id="rId102" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{EFAC0BA2-EE20-4299-A873-D414D98F3217}"/>
+    <hyperlink ref="H16" r:id="rId103" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{DECCDEBB-C83B-4E52-98FC-66A9AAEDA79C}"/>
+    <hyperlink ref="C16" r:id="rId104" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{661E1012-FF91-46F9-946A-8B2F1D050030}"/>
+    <hyperlink ref="F16" r:id="rId105" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{7661A61B-87E2-4BD7-AE6F-A6287FA1F4D3}"/>
+    <hyperlink ref="B17" r:id="rId106" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{9B0AD501-C8F0-41DC-9869-CE4A1EDD25B5}"/>
+    <hyperlink ref="D17" r:id="rId107" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{EA3316F1-C551-4840-AEC1-7F4874B16A7A}"/>
+    <hyperlink ref="G17" r:id="rId108" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{A3E76B20-F711-4CDE-B4E2-76803F667939}"/>
+    <hyperlink ref="E17" r:id="rId109" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{6C3961B8-9F78-40EA-BF12-7F09FAA1E55B}"/>
+    <hyperlink ref="H17" r:id="rId110" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{86054EAC-1C0C-459A-B57F-F5446B017C22}"/>
+    <hyperlink ref="C17" r:id="rId111" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{5DC6A7FD-A242-4043-B99B-4F3F4203E10A}"/>
+    <hyperlink ref="F17" r:id="rId112" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{D0A44714-F360-4084-94EE-D2157E2363BE}"/>
+    <hyperlink ref="B18" r:id="rId113" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{FE9D2D7A-48F3-4206-93AF-30FD12A71A4C}"/>
+    <hyperlink ref="D18" r:id="rId114" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{1F39E3ED-8ACA-46C7-873C-04804D51577F}"/>
+    <hyperlink ref="G18" r:id="rId115" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{FF8F86C9-65C0-4794-B4EB-90A483C89A38}"/>
+    <hyperlink ref="E18" r:id="rId116" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{BDB89618-4537-4CAE-AA20-02BB5874E4DE}"/>
+    <hyperlink ref="H18" r:id="rId117" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{79A2314C-A68F-4957-ACE8-755C0C8EE532}"/>
+    <hyperlink ref="C18" r:id="rId118" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C5A3931A-E9D1-442E-AE38-D4E487D0BF61}"/>
+    <hyperlink ref="F18" r:id="rId119" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{FA8C926F-E6F4-4CBE-A45B-B4C8234A7B36}"/>
+    <hyperlink ref="B19" r:id="rId120" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{D40B7D60-4193-46E8-A046-E3F187FCF3C1}"/>
+    <hyperlink ref="D19" r:id="rId121" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{F26D450E-8BBE-4DD8-B705-B678629D2075}"/>
+    <hyperlink ref="G19" r:id="rId122" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{2FA36934-1427-4B38-A559-804FBF47BC65}"/>
+    <hyperlink ref="E19" r:id="rId123" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{4EC41D2E-F872-4288-AEA1-7B9BE9A84BDE}"/>
+    <hyperlink ref="H19" r:id="rId124" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{9E0DE62B-9AF0-40CC-A06E-264A0BBDCABF}"/>
+    <hyperlink ref="C19" r:id="rId125" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{9861109D-6D43-4810-8808-D2A4BFA709A6}"/>
+    <hyperlink ref="F19" r:id="rId126" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F198D3B0-9FD2-44DD-8BB2-38BB5D18B86D}"/>
+    <hyperlink ref="B20" r:id="rId127" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{19050AA6-6287-43E6-9837-A06778D6504B}"/>
+    <hyperlink ref="D20" r:id="rId128" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{7B2B845D-8534-4871-9A80-705FCE99D199}"/>
+    <hyperlink ref="G20" r:id="rId129" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F328DCF1-9F7A-4220-A4E3-CE4F8DBBF6BA}"/>
+    <hyperlink ref="E20" r:id="rId130" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{35A5631F-26B3-4615-8DC7-73EC110A996F}"/>
+    <hyperlink ref="H20" r:id="rId131" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{0123B725-D70C-4A7B-BD81-06240CE14B95}"/>
+    <hyperlink ref="C20" r:id="rId132" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{997F3E00-A938-403A-82C9-DD52813F5B7C}"/>
+    <hyperlink ref="F20" r:id="rId133" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{10876BD8-1357-4FFF-B5CC-9DC33F9C9CF1}"/>
+    <hyperlink ref="B21" r:id="rId134" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{F987F7E0-8334-4C2D-A578-0FDCCB79306F}"/>
+    <hyperlink ref="D21" r:id="rId135" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{E38CB781-3F8D-4757-A96B-FCE3E0FF93C3}"/>
+    <hyperlink ref="G21" r:id="rId136" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{A2630D13-42EA-40D2-BD99-3C6FC7620097}"/>
+    <hyperlink ref="E21" r:id="rId137" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{6F5AEA4B-1F75-42EA-BBC7-FEFC959C659E}"/>
+    <hyperlink ref="H21" r:id="rId138" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{76A89D28-754E-4178-BE1A-EC2C5C3F33ED}"/>
+    <hyperlink ref="C21" r:id="rId139" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{3CEFB97D-7DE4-4803-99AB-90BE85E69A24}"/>
+    <hyperlink ref="F21" r:id="rId140" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{9889BF83-5F02-4D07-B306-D514BD47B9A3}"/>
+    <hyperlink ref="B22" r:id="rId141" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{3C3BBB93-25B6-44A2-9380-CDAD3001162E}"/>
+    <hyperlink ref="D22" r:id="rId142" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{CAE91713-6732-4DC6-BE52-C6EADAE61F50}"/>
+    <hyperlink ref="G22" r:id="rId143" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{6F810329-F5FC-4D08-94BB-AB072658E239}"/>
+    <hyperlink ref="E22" r:id="rId144" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A76838FA-4BBE-4266-9F5D-62AD42C54C40}"/>
+    <hyperlink ref="H22" r:id="rId145" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{FD956301-1543-4223-B682-629D588D073B}"/>
+    <hyperlink ref="C22" r:id="rId146" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{B9F1EB2D-850A-4124-A594-3922A221477B}"/>
+    <hyperlink ref="F22" r:id="rId147" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{35A4E045-4E1E-42B9-B31B-70205F5002D1}"/>
+    <hyperlink ref="B23" r:id="rId148" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{E6C121AE-CA2D-4A02-B242-37D4B17855BF}"/>
+    <hyperlink ref="D23" r:id="rId149" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{1779EAFC-449E-4713-B38C-666945A2996D}"/>
+    <hyperlink ref="G23" r:id="rId150" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{91C1871B-60B7-4122-AE5C-55D3F373E9D5}"/>
+    <hyperlink ref="E23" r:id="rId151" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B31D41C1-E956-454E-8FE6-2D7C76A5A74D}"/>
+    <hyperlink ref="H23" r:id="rId152" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{B81792B0-2634-41CE-B033-69A945428905}"/>
+    <hyperlink ref="C23" r:id="rId153" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{35EA7A80-DA90-4F1B-A029-732D90495731}"/>
+    <hyperlink ref="F23" r:id="rId154" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{6B06A689-72B1-481B-90B4-3C95B96F24FE}"/>
+    <hyperlink ref="B24" r:id="rId155" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C710A40F-9091-4FCD-9984-DFAF1FD08674}"/>
+    <hyperlink ref="D24" r:id="rId156" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{83C91B1E-6C35-4889-8199-4771DEEB4600}"/>
+    <hyperlink ref="G24" r:id="rId157" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C12E69D0-4E8C-4D1C-B9FD-8A096523051F}"/>
+    <hyperlink ref="E24" r:id="rId158" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{86F7C565-8216-4660-856F-42C029107EA7}"/>
+    <hyperlink ref="H24" r:id="rId159" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{A17AD685-FA11-4DD1-905C-9CDE825491E3}"/>
+    <hyperlink ref="C24" r:id="rId160" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{BFF1C317-D150-46DB-AC2E-718F4AB38E1F}"/>
+    <hyperlink ref="F24" r:id="rId161" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E11A8AA3-0447-4986-8F69-9BF566CF1CAF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId162"/>
@@ -16422,7 +16598,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC3F3FC-17EF-4D6A-9290-8FAFFC789915}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.5546875" customWidth="1"/>
@@ -16911,6 +17087,24 @@
       <c r="E27" s="14">
         <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
         <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="A28" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" s="14">
+        <v>100</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
+        <v>98</v>
+      </c>
+      <c r="E28" s="14">
+        <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/data/SDET_SQA_DATA.xlsx
+++ b/data/SDET_SQA_DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WHSU\Desktop\Workspace\CycleView\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E66F38C-6694-4EB2-BAF4-90083EEB6E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62BCBE06-7961-4647-896D-3C1120A653C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB11FF79-EF06-B64E-AA6A-0CFF391A8BD1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{EB11FF79-EF06-B64E-AA6A-0CFF391A8BD1}"/>
   </bookViews>
   <sheets>
     <sheet name="TestAutomationProgress" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="115">
   <si>
     <t>TODO (P1)</t>
   </si>
@@ -382,6 +382,12 @@
   <si>
     <t>26W17</t>
   </si>
+  <si>
+    <t>26W18</t>
+  </si>
+  <si>
+    <t>26W19</t>
+  </si>
 </sst>
 </file>
 
@@ -569,36 +575,6 @@
   </cellStyles>
   <dxfs count="36">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -774,6 +750,33 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -900,6 +903,9 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1118,9 +1124,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$28</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>25W40</c:v>
                 </c:pt>
@@ -1201,16 +1207,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>26W17</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>26W18</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$B$2:$B$28</c:f>
+              <c:f>TestAutomationProgress!$B$2:$B$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>15</c:v>
                 </c:pt>
@@ -1290,6 +1299,9 @@
                   <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="26">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
@@ -1387,9 +1399,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$28</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>25W40</c:v>
                 </c:pt>
@@ -1470,16 +1482,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>26W17</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>26W18</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$C$2:$C$28</c:f>
+              <c:f>TestAutomationProgress!$C$2:$C$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>14</c:v>
                 </c:pt>
@@ -1559,6 +1574,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="26">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1656,9 +1674,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestAutomationProgress!$A$2:$A$28</c:f>
+              <c:f>TestAutomationProgress!$A$2:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>25W40</c:v>
                 </c:pt>
@@ -1739,16 +1757,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>26W17</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>26W18</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestAutomationProgress!$D$2:$D$28</c:f>
+              <c:f>TestAutomationProgress!$D$2:$D$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>219</c:v>
                 </c:pt>
@@ -1828,6 +1849,9 @@
                   <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="26">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>160</c:v>
                 </c:pt>
               </c:numCache>
@@ -3852,9 +3876,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$40</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$42</c:f>
               <c:strCache>
-                <c:ptCount val="39"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -3971,16 +3995,22 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>26W17</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>26W18</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>26W19</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$B$2:$B$40</c:f>
+              <c:f>'SOVA-TestResult'!$B$2:$B$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>38</c:v>
                 </c:pt>
@@ -4073,6 +4103,12 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>1220</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>491</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>231</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4166,9 +4202,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$40</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$42</c:f>
               <c:strCache>
-                <c:ptCount val="39"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4285,16 +4321,22 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>26W17</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>26W18</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>26W19</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$C$2:$C$40</c:f>
+              <c:f>'SOVA-TestResult'!$C$2:$C$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4386,6 +4428,12 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="38">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4423,9 +4471,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$40</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$42</c:f>
               <c:strCache>
-                <c:ptCount val="39"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4542,16 +4590,22 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>26W17</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>26W18</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>26W19</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$D$2:$D$40</c:f>
+              <c:f>'SOVA-TestResult'!$D$2:$D$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4644,6 +4698,12 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4680,9 +4740,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$40</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$42</c:f>
               <c:strCache>
-                <c:ptCount val="39"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -4799,16 +4859,22 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>26W17</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>26W18</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>26W19</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$E$2:$E$40</c:f>
+              <c:f>'SOVA-TestResult'!$E$2:$E$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
                 </c:pt>
@@ -4901,6 +4967,12 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5011,9 +5083,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$40</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$42</c:f>
               <c:strCache>
-                <c:ptCount val="39"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -5130,16 +5202,22 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>26W17</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>26W18</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>26W19</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$F$2:$F$40</c:f>
+              <c:f>'SOVA-TestResult'!$F$2:$F$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>11</c:v>
                 </c:pt>
@@ -5232,6 +5310,12 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5271,9 +5355,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$40</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$42</c:f>
               <c:strCache>
-                <c:ptCount val="39"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -5390,16 +5474,22 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>26W17</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>26W18</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>26W19</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$G$2:$G$40</c:f>
+              <c:f>'SOVA-TestResult'!$G$2:$G$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5492,6 +5582,12 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>284</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>605</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5533,9 +5629,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'SOVA-TestResult'!$A$2:$A$40</c:f>
+              <c:f>'SOVA-TestResult'!$A$2:$A$42</c:f>
               <c:strCache>
-                <c:ptCount val="39"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>25W28</c:v>
                 </c:pt>
@@ -5652,16 +5748,22 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>26W17</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>26W18</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>26W19</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'SOVA-TestResult'!$H$2:$H$40</c:f>
+              <c:f>'SOVA-TestResult'!$H$2:$H$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="39"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
                   <c:v>54</c:v>
                 </c:pt>
@@ -5754,6 +5856,12 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>1522</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>541</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>839</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6271,7 +6379,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7389,7 +7497,7 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>3</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7844,7 +7952,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="23"/>
                 <c:pt idx="0">
-                  <c:v>32</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
@@ -7907,10 +8015,10 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>11</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>12</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8633,7 +8741,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0</c:v>
@@ -8818,7 +8926,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0</c:v>
@@ -9057,7 +9165,7 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0</c:v>
@@ -9368,7 +9476,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="23"/>
                 <c:pt idx="0">
-                  <c:v>41</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>42</c:v>
@@ -9431,10 +9539,10 @@
                   <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>30</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>12</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12448,13 +12556,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>41087</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1047750</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>2987</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -12566,8 +12674,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}" name="Table2" displayName="Table2" ref="A1:E28" totalsRowShown="0" headerRowDxfId="35">
-  <autoFilter ref="A1:E28" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}" name="Table2" displayName="Table2" ref="A1:E29" totalsRowShown="0" headerRowDxfId="35">
+  <autoFilter ref="A1:E29" xr:uid="{423949CE-F107-4F66-9A7B-4594AB1D83D9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F25F0D34-0297-4771-8BBB-350BCDD85D46}" name="Week"/>
     <tableColumn id="2" xr3:uid="{39CFCD12-3130-47A8-A140-DBF602F1743D}" name="Done"/>
@@ -12601,8 +12709,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}" name="Table3" displayName="Table3" ref="A1:H40" totalsRowShown="0" headerRowDxfId="31">
-  <autoFilter ref="A1:H40" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}" name="Table3" displayName="Table3" ref="A1:H42" totalsRowShown="0" headerRowDxfId="31">
+  <autoFilter ref="A1:H42" xr:uid="{E31F3BE9-C534-4A83-AA30-CE297DF28DB5}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{8103CDF3-74DC-4B31-821D-E20368EA5455}" name="Versions"/>
     <tableColumn id="2" xr3:uid="{6C3B261F-FA51-42D2-821A-F22633569372}" name="Passed"/>
@@ -12630,7 +12738,7 @@
     <tableColumn id="4" xr3:uid="{C5EE39F3-E9DF-4F2E-9576-6DDB97E21DB3}" name="In QA" dataDxfId="25"/>
     <tableColumn id="6" xr3:uid="{CC106112-C63E-4AA5-9AAA-D0A99983E0DD}" name="Internal Test" dataDxfId="24"/>
     <tableColumn id="7" xr3:uid="{C69EECCF-E5E5-4372-B171-2B35FE10B60D}" name="Done" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{C7A900BC-8967-4049-AE22-7F9EDE21E913}" name="Total" dataDxfId="0" totalsRowDxfId="22">
+    <tableColumn id="8" xr3:uid="{C7A900BC-8967-4049-AE22-7F9EDE21E913}" name="Total" dataDxfId="22" totalsRowDxfId="21">
       <calculatedColumnFormula>SUM(Table7[[#This Row],[To Do]:[Done]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12639,18 +12747,18 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}" name="Table5" displayName="Table5" ref="A1:I24" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18" totalsRowBorderDxfId="17" dataCellStyle="Hyperlink">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}" name="Table5" displayName="Table5" ref="A1:I24" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17" totalsRowBorderDxfId="16" dataCellStyle="Hyperlink">
   <autoFilter ref="A1:I24" xr:uid="{108F5145-A108-41DB-B2C3-516BE7C86923}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{5BE08AE0-E0B5-4B46-9423-456B88C2D9BC}" name="Sprint" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{030F9647-4FC0-4C7E-9B3A-AB099CC59EBA}" name="To Do (0%)" dataDxfId="15" dataCellStyle="Hyperlink"/>
-    <tableColumn id="3" xr3:uid="{7D2923F3-E2CF-4FD9-A7A5-68C36BB95591}" name="STARTING (10 ~ 40%)" dataDxfId="14" dataCellStyle="Hyperlink"/>
-    <tableColumn id="4" xr3:uid="{48FB5317-7F3B-4F74-B244-5A49C7749EBD}" name="In Progress (50 ~ 70%)" dataDxfId="13" dataCellStyle="Hyperlink"/>
-    <tableColumn id="5" xr3:uid="{86F5CCB5-C4C2-4C36-935A-657F085500B1}" name="IN REVIEW (80%)" dataDxfId="12" dataCellStyle="Hyperlink"/>
-    <tableColumn id="9" xr3:uid="{51D22AE3-424C-4604-9869-D672DED4301F}" name="READY FOR TESTING (90%)" dataDxfId="11" dataCellStyle="Hyperlink"/>
-    <tableColumn id="6" xr3:uid="{33C9BCE6-D9EB-4032-9B0A-DDD9A4051A2D}" name="Done (100%)" dataDxfId="10" dataCellStyle="Hyperlink"/>
-    <tableColumn id="8" xr3:uid="{D624FC89-A88E-45AC-9D22-66D66702B8C5}" name="WON'T DO (100%)" dataDxfId="9" dataCellStyle="Hyperlink"/>
-    <tableColumn id="7" xr3:uid="{EFEEB7EC-E2D1-40EA-B265-A558311E5D30}" name="Total" dataDxfId="8" dataCellStyle="Hyperlink">
+    <tableColumn id="1" xr3:uid="{5BE08AE0-E0B5-4B46-9423-456B88C2D9BC}" name="Sprint" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{030F9647-4FC0-4C7E-9B3A-AB099CC59EBA}" name="To Do (0%)" dataDxfId="6" dataCellStyle="Hyperlink"/>
+    <tableColumn id="3" xr3:uid="{7D2923F3-E2CF-4FD9-A7A5-68C36BB95591}" name="STARTING (10 ~ 40%)" dataDxfId="5" dataCellStyle="Hyperlink"/>
+    <tableColumn id="4" xr3:uid="{48FB5317-7F3B-4F74-B244-5A49C7749EBD}" name="In Progress (50 ~ 70%)" dataDxfId="4" dataCellStyle="Hyperlink"/>
+    <tableColumn id="5" xr3:uid="{86F5CCB5-C4C2-4C36-935A-657F085500B1}" name="IN REVIEW (80%)" dataDxfId="3" dataCellStyle="Hyperlink"/>
+    <tableColumn id="9" xr3:uid="{51D22AE3-424C-4604-9869-D672DED4301F}" name="READY FOR TESTING (90%)" dataDxfId="2" dataCellStyle="Hyperlink"/>
+    <tableColumn id="6" xr3:uid="{33C9BCE6-D9EB-4032-9B0A-DDD9A4051A2D}" name="Done (100%)" dataDxfId="1" dataCellStyle="Hyperlink"/>
+    <tableColumn id="8" xr3:uid="{D624FC89-A88E-45AC-9D22-66D66702B8C5}" name="WON'T DO (100%)" dataDxfId="0" dataCellStyle="Hyperlink"/>
+    <tableColumn id="7" xr3:uid="{EFEEB7EC-E2D1-40EA-B265-A558311E5D30}" name="Total" dataDxfId="14" dataCellStyle="Hyperlink">
       <calculatedColumnFormula>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12659,14 +12767,14 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}" name="Table25" displayName="Table25" ref="A1:E28" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
-  <autoFilter ref="A1:E28" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}" name="Table25" displayName="Table25" ref="A1:E30" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:E30" xr:uid="{2C55E946-0086-4A42-AEAE-DA5ED4E8BB10}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7070D9F2-0ED1-4F39-8D72-28B37C8E98F2}" name="Week" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{1173F443-CC27-4C6E-A432-BF66DB2A740E}" name="Done" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{2EE10CB5-1AF1-4B50-9456-B3A666DD5338}" name="In Review/Progress" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{328D0A00-85F0-4BFF-81FE-C023998A3701}" name="TODO (P1)" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{E385808E-1FCD-451C-9807-DAF18A42B704}" name="Total" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{7070D9F2-0ED1-4F39-8D72-28B37C8E98F2}" name="Week" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{1173F443-CC27-4C6E-A432-BF66DB2A740E}" name="Done" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{2EE10CB5-1AF1-4B50-9456-B3A666DD5338}" name="In Review/Progress" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{328D0A00-85F0-4BFF-81FE-C023998A3701}" name="TODO (P1)" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{E385808E-1FCD-451C-9807-DAF18A42B704}" name="Total" dataDxfId="7">
       <calculatedColumnFormula>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12991,7 +13099,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D733A42-966D-5F4E-B061-B304543CE88E}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.77734375" customWidth="1"/>
@@ -13493,6 +13601,23 @@
         <v>160</v>
       </c>
       <c r="E28" s="12">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29">
+        <v>37</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>160</v>
+      </c>
+      <c r="E29" s="12">
         <v>198</v>
       </c>
     </row>
@@ -14095,7 +14220,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA6EDF6-834F-DA49-B3FC-BFE1673433AB}">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
@@ -15005,6 +15130,60 @@
       <c r="H40" s="12">
         <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
         <v>1522</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="A41" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B41">
+        <v>491</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>6</v>
+      </c>
+      <c r="G41">
+        <v>40</v>
+      </c>
+      <c r="H41" s="12">
+        <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
+        <v>541</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="A42" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B42">
+        <v>231</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>3</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>605</v>
+      </c>
+      <c r="H42" s="12">
+        <f>SUM(Table3[[#This Row],[Passed]:[Untested]])</f>
+        <v>839</v>
       </c>
     </row>
   </sheetData>
@@ -15656,7 +15835,7 @@
         <v>111</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -15675,7 +15854,7 @@
       </c>
       <c r="H24" s="12">
         <f>SUM(Table7[[#This Row],[To Do]:[Done]])</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -15737,7 +15916,7 @@
         <v>99</v>
       </c>
       <c r="B2" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="5">
         <v>0</v>
@@ -15759,7 +15938,7 @@
       </c>
       <c r="I2" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18" thickBot="1">
@@ -16367,7 +16546,7 @@
         <v>103</v>
       </c>
       <c r="B23" s="5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C23" s="5">
         <v>1</v>
@@ -16376,20 +16555,20 @@
         <v>0</v>
       </c>
       <c r="E23" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G23" s="5">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H23" s="5">
         <v>1</v>
       </c>
       <c r="I23" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="18" thickBot="1">
@@ -16397,7 +16576,7 @@
         <v>110</v>
       </c>
       <c r="B24" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C24" s="5">
         <v>0</v>
@@ -16419,173 +16598,173 @@
       </c>
       <c r="I24" s="15">
         <f>SUM(Table5[[#This Row],[To Do (0%)]:[WON''T DO (100%)]])</f>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{ECC2139E-791E-4770-9749-924C8171413E}"/>
-    <hyperlink ref="D2" r:id="rId2" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{A3490D76-D554-40B0-94C2-6BCE62D65128}"/>
-    <hyperlink ref="G2" r:id="rId3" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{E73331BD-FAD2-46B3-9C4A-B1F1944F18FC}"/>
-    <hyperlink ref="E2" r:id="rId4" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{363312FF-8351-469B-A0E2-96F2CEBC31DF}"/>
-    <hyperlink ref="H2" r:id="rId5" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{33FD27D8-D06C-4600-84C6-9AF958F84B2B}"/>
-    <hyperlink ref="C2" r:id="rId6" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C0932090-8C86-4ADD-B05E-5218E24825BD}"/>
-    <hyperlink ref="F2" r:id="rId7" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A689B4DB-1B76-459A-A757-14C2A4E04261}"/>
-    <hyperlink ref="B3" r:id="rId8" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A5CAF974-56E2-4541-BBC1-3EB2AFE89540}"/>
-    <hyperlink ref="D3" r:id="rId9" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{0576CFE6-25FE-4850-A50C-D4EF9C5C288D}"/>
-    <hyperlink ref="G3" r:id="rId10" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{6A3726CF-7A79-4DB0-A35D-01076E6C4CD2}"/>
-    <hyperlink ref="E3" r:id="rId11" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{AC29D7F9-DB7F-4161-BB80-C72D1BBBF39E}"/>
-    <hyperlink ref="H3" r:id="rId12" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{357E5794-FD1F-4928-96FA-1C3EF0E080E5}"/>
-    <hyperlink ref="C3" r:id="rId13" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{4B4462C8-BD6A-4208-93D3-C2D52A2AD585}"/>
-    <hyperlink ref="F3" r:id="rId14" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F3F7DF96-A9FE-4C8F-A0BD-D531A4B077EF}"/>
-    <hyperlink ref="B4" r:id="rId15" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{9E37D979-E337-47AE-B23A-654EBEBEA932}"/>
-    <hyperlink ref="D4" r:id="rId16" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{44BCA075-84AC-4361-B3BF-1737A343B8B4}"/>
-    <hyperlink ref="G4" r:id="rId17" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{DECFC323-AB02-4745-94A7-79CCFB384E3B}"/>
-    <hyperlink ref="E4" r:id="rId18" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{2DD9B9B7-89F3-4818-AF5D-51EF03E1B4C1}"/>
-    <hyperlink ref="H4" r:id="rId19" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{02DCE810-6BB2-4C13-A8E6-29CA9044C881}"/>
-    <hyperlink ref="C4" r:id="rId20" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{9FBD8793-FEAC-49B9-9607-CD8F9F45B1CC}"/>
-    <hyperlink ref="F4" r:id="rId21" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{6F3B394A-72FE-4700-8369-240BB81DCE44}"/>
-    <hyperlink ref="B5" r:id="rId22" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{8BAD55EB-90D0-4AD6-9706-A8D208B27D1D}"/>
-    <hyperlink ref="D5" r:id="rId23" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{14E8BFCC-A84B-40B1-A064-54E14EBE8DDF}"/>
-    <hyperlink ref="G5" r:id="rId24" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{629ECA61-F425-4703-9ABA-B8D87E01FF42}"/>
-    <hyperlink ref="E5" r:id="rId25" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{8EAA964E-F294-43D3-B343-B6AFBB6E94D7}"/>
-    <hyperlink ref="H5" r:id="rId26" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{35B1344A-F214-47AD-BEB4-966C5A0AC2FA}"/>
-    <hyperlink ref="C5" r:id="rId27" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{21928EBB-EB7E-44A4-A8A7-B7AE9CE492F9}"/>
-    <hyperlink ref="F5" r:id="rId28" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{B7263387-7038-4B3C-892B-0FB847A3D713}"/>
-    <hyperlink ref="B6" r:id="rId29" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C3D7ED8C-32E2-4503-B61D-29C7E22DB6C9}"/>
-    <hyperlink ref="D6" r:id="rId30" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{DBA75831-6F53-42DF-92CF-675154509594}"/>
-    <hyperlink ref="G6" r:id="rId31" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C8609D1F-0BD6-4A14-838C-C292282EFD8D}"/>
-    <hyperlink ref="E6" r:id="rId32" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B78856CB-F3FD-47E4-8A85-E94C564F647A}"/>
-    <hyperlink ref="H6" r:id="rId33" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{60DE4A6A-8139-42BC-9A99-3C99A581556F}"/>
-    <hyperlink ref="C6" r:id="rId34" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{FD0FEBA6-4AE5-41D3-A749-932E17983459}"/>
-    <hyperlink ref="F6" r:id="rId35" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{37B8A0DB-FB80-4CE4-9AD7-87443FC7F270}"/>
-    <hyperlink ref="B7" r:id="rId36" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{0B301508-AF4F-44F3-AA4A-2C01021AF851}"/>
-    <hyperlink ref="D7" r:id="rId37" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{D713B67D-8832-42F6-A9ED-0062F67E9077}"/>
-    <hyperlink ref="G7" r:id="rId38" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{AC1420BA-8514-49F7-B35E-4D1FD28E76D1}"/>
-    <hyperlink ref="E7" r:id="rId39" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{0ADA16B8-F45C-41D4-8C5F-D956C6D16B42}"/>
-    <hyperlink ref="H7" r:id="rId40" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{64CDDCC6-B91C-49FB-92BD-0780B29DF9FF}"/>
-    <hyperlink ref="C7" r:id="rId41" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{5038F61D-21C0-4FAB-B724-2E28D0CE1074}"/>
-    <hyperlink ref="F7" r:id="rId42" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{0BDE8639-3915-4BC0-ADE8-22266356ABD9}"/>
-    <hyperlink ref="B8" r:id="rId43" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{6318D2F1-4656-4527-9498-CF3C903FA0A2}"/>
-    <hyperlink ref="D8" r:id="rId44" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{412376BB-1894-405F-951A-B5CE5755B22C}"/>
-    <hyperlink ref="G8" r:id="rId45" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{0FBB761D-0658-4CC4-95B7-1B7F9B4A0C64}"/>
-    <hyperlink ref="E8" r:id="rId46" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{4446CB20-73A7-4D73-A3E0-563FCC1184C9}"/>
-    <hyperlink ref="H8" r:id="rId47" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{2D64E32A-DC0B-4E97-863B-43D5146B3BD6}"/>
-    <hyperlink ref="C8" r:id="rId48" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{B4D60C72-EA21-428E-B2E9-4180AADD50C3}"/>
-    <hyperlink ref="F8" r:id="rId49" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{26E3D28F-D7A9-4C2F-B1FB-8D73E913221F}"/>
-    <hyperlink ref="B9" r:id="rId50" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{9C47A2E1-A5F6-4323-B7FC-84E0D2A35A41}"/>
-    <hyperlink ref="D9" r:id="rId51" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{2BCFBC9B-A377-4D73-842E-8EC90D3E593E}"/>
-    <hyperlink ref="G9" r:id="rId52" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{51EA0688-1928-4D73-95DF-ACCE217B6EDD}"/>
-    <hyperlink ref="E9" r:id="rId53" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{844BEA60-E68A-4B97-B8AC-74903536E25D}"/>
-    <hyperlink ref="H9" r:id="rId54" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E9793F71-80CD-4A7B-8B18-A825D505BCD2}"/>
-    <hyperlink ref="C9" r:id="rId55" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A8FA0ED8-8CC4-4D9A-B09B-0AA50AF6815A}"/>
-    <hyperlink ref="F9" r:id="rId56" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{C5918F7E-E6CF-4041-8AC0-EB9EF66D9236}"/>
-    <hyperlink ref="B10" r:id="rId57" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{350E84CE-F968-4EB3-9710-57F61789AC27}"/>
-    <hyperlink ref="D10" r:id="rId58" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{1CF911AA-89D0-457A-B577-9FBFEC516C58}"/>
-    <hyperlink ref="G10" r:id="rId59" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{5FA3C6C1-A5F6-407A-BFFD-15F2269A2767}"/>
-    <hyperlink ref="E10" r:id="rId60" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D0839BC4-6FC7-4D80-9EB1-A4BE87BE07E1}"/>
-    <hyperlink ref="H10" r:id="rId61" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{61AB3BFA-DFA6-47A6-AC33-D4BE683F81BE}"/>
-    <hyperlink ref="C10" r:id="rId62" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{4077FB81-25D0-47DC-9EFF-EE4AE7C94109}"/>
-    <hyperlink ref="F10" r:id="rId63" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{9CE66375-097B-4A05-B4F2-3B5E95A42BF4}"/>
-    <hyperlink ref="B11" r:id="rId64" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C6E5B636-78F3-4EAF-93B6-65D8DC58F867}"/>
-    <hyperlink ref="D11" r:id="rId65" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{6F198A67-34D3-4656-8825-C850D704E10C}"/>
-    <hyperlink ref="G11" r:id="rId66" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{CE537456-33D0-45E5-982A-F19FF8052478}"/>
-    <hyperlink ref="E11" r:id="rId67" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{5DCCA5EE-A804-44F7-B390-55CE72C84A19}"/>
-    <hyperlink ref="H11" r:id="rId68" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{0AFD189A-A6BF-4EC4-9BD7-28278FC81648}"/>
-    <hyperlink ref="C11" r:id="rId69" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{4EF649A5-D5CB-4DDA-8DAD-E6AD55AFE0B3}"/>
-    <hyperlink ref="F11" r:id="rId70" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{7B4F5059-EDBA-4F62-AF4B-9C4E679550E3}"/>
-    <hyperlink ref="B12" r:id="rId71" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{D372CCC4-0FDD-4D65-B392-8A64C0FE94ED}"/>
-    <hyperlink ref="D12" r:id="rId72" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{9B129C26-45AE-4101-B15F-225ED8002AB0}"/>
-    <hyperlink ref="G12" r:id="rId73" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{706C9157-13C6-427C-89F1-C38DDFC588FD}"/>
-    <hyperlink ref="E12" r:id="rId74" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{17F4C908-6E94-4071-9F12-70297BBBB65E}"/>
-    <hyperlink ref="H12" r:id="rId75" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{3B91C677-9CFD-4B28-A4BC-D4D07CBCB5D0}"/>
-    <hyperlink ref="C12" r:id="rId76" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{74199A6E-B75A-4DAB-B2EA-903A765995AD}"/>
-    <hyperlink ref="F12" r:id="rId77" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{B53CB8B2-9B74-40F7-A907-50D93B32D91B}"/>
-    <hyperlink ref="B13" r:id="rId78" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{2534FD19-020A-4EE1-BE0D-A1D732E046AF}"/>
-    <hyperlink ref="D13" r:id="rId79" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{52FFD7AC-8DAB-4AFE-A94D-9F74875E26B0}"/>
-    <hyperlink ref="G13" r:id="rId80" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{0B71C7B9-CAB9-4513-AEE8-7D902192BB55}"/>
-    <hyperlink ref="E13" r:id="rId81" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{110844CE-359B-4176-832B-AE95F97404F2}"/>
-    <hyperlink ref="H13" r:id="rId82" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{B7FD7691-0569-4FF8-82AC-8300790776CF}"/>
-    <hyperlink ref="C13" r:id="rId83" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{420EA762-9A72-4CA1-846F-EA18FA882FA3}"/>
-    <hyperlink ref="F13" r:id="rId84" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{4EC3DB9C-0F83-4CBC-AC64-AA51A16EE2BB}"/>
-    <hyperlink ref="B14" r:id="rId85" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{0CDC764F-B5AD-4394-B6E4-2B5EB7EAFCC0}"/>
-    <hyperlink ref="D14" r:id="rId86" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{478728AB-BB5A-4678-AFC4-00EBFA8A430A}"/>
-    <hyperlink ref="G14" r:id="rId87" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3A3DE6BA-B502-404A-8CDF-9333661678E6}"/>
-    <hyperlink ref="E14" r:id="rId88" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{9104CEF4-3097-4856-9561-410C4AB4D716}"/>
-    <hyperlink ref="H14" r:id="rId89" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{7AB4578D-9F87-435C-A939-505BDCC02890}"/>
-    <hyperlink ref="C14" r:id="rId90" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{E9224761-6EF7-4233-B031-0B36CF5192D1}"/>
-    <hyperlink ref="F14" r:id="rId91" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{9D093A32-31F4-4BF4-9966-A447932ECD08}"/>
-    <hyperlink ref="B15" r:id="rId92" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{D31B34B6-63A3-45EF-83C9-FCEB40B92C85}"/>
-    <hyperlink ref="D15" r:id="rId93" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{B26BC3A8-0C21-4490-A74A-68DCFB866457}"/>
-    <hyperlink ref="G15" r:id="rId94" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{4FA13B3B-33E2-4F5E-9AAF-0871331575F8}"/>
-    <hyperlink ref="E15" r:id="rId95" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{AD096D74-46D8-4676-A682-119050F75BC5}"/>
-    <hyperlink ref="H15" r:id="rId96" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{76646DD6-ACBA-449B-95AC-850112A3D7DB}"/>
-    <hyperlink ref="C15" r:id="rId97" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{F1EE5D73-6C06-4070-8908-F0A80AB102CB}"/>
-    <hyperlink ref="F15" r:id="rId98" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{6480DEDC-15DA-4230-8F95-DA170BB79EB4}"/>
-    <hyperlink ref="B16" r:id="rId99" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{1FC9F597-7790-4126-A581-1FB24BA9C08B}"/>
-    <hyperlink ref="D16" r:id="rId100" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{702F4E9D-1699-4299-8DF0-3A8D2B5D7123}"/>
-    <hyperlink ref="G16" r:id="rId101" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{35FCE29A-50A4-44FF-9066-48973F4C91B5}"/>
-    <hyperlink ref="E16" r:id="rId102" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{EFAC0BA2-EE20-4299-A873-D414D98F3217}"/>
-    <hyperlink ref="H16" r:id="rId103" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{DECCDEBB-C83B-4E52-98FC-66A9AAEDA79C}"/>
-    <hyperlink ref="C16" r:id="rId104" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{661E1012-FF91-46F9-946A-8B2F1D050030}"/>
-    <hyperlink ref="F16" r:id="rId105" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{7661A61B-87E2-4BD7-AE6F-A6287FA1F4D3}"/>
-    <hyperlink ref="B17" r:id="rId106" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{9B0AD501-C8F0-41DC-9869-CE4A1EDD25B5}"/>
-    <hyperlink ref="D17" r:id="rId107" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{EA3316F1-C551-4840-AEC1-7F4874B16A7A}"/>
-    <hyperlink ref="G17" r:id="rId108" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{A3E76B20-F711-4CDE-B4E2-76803F667939}"/>
-    <hyperlink ref="E17" r:id="rId109" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{6C3961B8-9F78-40EA-BF12-7F09FAA1E55B}"/>
-    <hyperlink ref="H17" r:id="rId110" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{86054EAC-1C0C-459A-B57F-F5446B017C22}"/>
-    <hyperlink ref="C17" r:id="rId111" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{5DC6A7FD-A242-4043-B99B-4F3F4203E10A}"/>
-    <hyperlink ref="F17" r:id="rId112" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{D0A44714-F360-4084-94EE-D2157E2363BE}"/>
-    <hyperlink ref="B18" r:id="rId113" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{FE9D2D7A-48F3-4206-93AF-30FD12A71A4C}"/>
-    <hyperlink ref="D18" r:id="rId114" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{1F39E3ED-8ACA-46C7-873C-04804D51577F}"/>
-    <hyperlink ref="G18" r:id="rId115" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{FF8F86C9-65C0-4794-B4EB-90A483C89A38}"/>
-    <hyperlink ref="E18" r:id="rId116" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{BDB89618-4537-4CAE-AA20-02BB5874E4DE}"/>
-    <hyperlink ref="H18" r:id="rId117" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{79A2314C-A68F-4957-ACE8-755C0C8EE532}"/>
-    <hyperlink ref="C18" r:id="rId118" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C5A3931A-E9D1-442E-AE38-D4E487D0BF61}"/>
-    <hyperlink ref="F18" r:id="rId119" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{FA8C926F-E6F4-4CBE-A45B-B4C8234A7B36}"/>
-    <hyperlink ref="B19" r:id="rId120" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{D40B7D60-4193-46E8-A046-E3F187FCF3C1}"/>
-    <hyperlink ref="D19" r:id="rId121" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{F26D450E-8BBE-4DD8-B705-B678629D2075}"/>
-    <hyperlink ref="G19" r:id="rId122" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{2FA36934-1427-4B38-A559-804FBF47BC65}"/>
-    <hyperlink ref="E19" r:id="rId123" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{4EC41D2E-F872-4288-AEA1-7B9BE9A84BDE}"/>
-    <hyperlink ref="H19" r:id="rId124" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{9E0DE62B-9AF0-40CC-A06E-264A0BBDCABF}"/>
-    <hyperlink ref="C19" r:id="rId125" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{9861109D-6D43-4810-8808-D2A4BFA709A6}"/>
-    <hyperlink ref="F19" r:id="rId126" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{F198D3B0-9FD2-44DD-8BB2-38BB5D18B86D}"/>
-    <hyperlink ref="B20" r:id="rId127" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{19050AA6-6287-43E6-9837-A06778D6504B}"/>
-    <hyperlink ref="D20" r:id="rId128" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{7B2B845D-8534-4871-9A80-705FCE99D199}"/>
-    <hyperlink ref="G20" r:id="rId129" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F328DCF1-9F7A-4220-A4E3-CE4F8DBBF6BA}"/>
-    <hyperlink ref="E20" r:id="rId130" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{35A5631F-26B3-4615-8DC7-73EC110A996F}"/>
-    <hyperlink ref="H20" r:id="rId131" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{0123B725-D70C-4A7B-BD81-06240CE14B95}"/>
-    <hyperlink ref="C20" r:id="rId132" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{997F3E00-A938-403A-82C9-DD52813F5B7C}"/>
-    <hyperlink ref="F20" r:id="rId133" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{10876BD8-1357-4FFF-B5CC-9DC33F9C9CF1}"/>
-    <hyperlink ref="B21" r:id="rId134" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{F987F7E0-8334-4C2D-A578-0FDCCB79306F}"/>
-    <hyperlink ref="D21" r:id="rId135" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{E38CB781-3F8D-4757-A96B-FCE3E0FF93C3}"/>
-    <hyperlink ref="G21" r:id="rId136" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{A2630D13-42EA-40D2-BD99-3C6FC7620097}"/>
-    <hyperlink ref="E21" r:id="rId137" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{6F5AEA4B-1F75-42EA-BBC7-FEFC959C659E}"/>
-    <hyperlink ref="H21" r:id="rId138" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{76A89D28-754E-4178-BE1A-EC2C5C3F33ED}"/>
-    <hyperlink ref="C21" r:id="rId139" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{3CEFB97D-7DE4-4803-99AB-90BE85E69A24}"/>
-    <hyperlink ref="F21" r:id="rId140" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{9889BF83-5F02-4D07-B306-D514BD47B9A3}"/>
-    <hyperlink ref="B22" r:id="rId141" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{3C3BBB93-25B6-44A2-9380-CDAD3001162E}"/>
-    <hyperlink ref="D22" r:id="rId142" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{CAE91713-6732-4DC6-BE52-C6EADAE61F50}"/>
-    <hyperlink ref="G22" r:id="rId143" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{6F810329-F5FC-4D08-94BB-AB072658E239}"/>
-    <hyperlink ref="E22" r:id="rId144" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{A76838FA-4BBE-4266-9F5D-62AD42C54C40}"/>
-    <hyperlink ref="H22" r:id="rId145" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{FD956301-1543-4223-B682-629D588D073B}"/>
-    <hyperlink ref="C22" r:id="rId146" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{B9F1EB2D-850A-4124-A594-3922A221477B}"/>
-    <hyperlink ref="F22" r:id="rId147" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{35A4E045-4E1E-42B9-B31B-70205F5002D1}"/>
-    <hyperlink ref="B23" r:id="rId148" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{E6C121AE-CA2D-4A02-B242-37D4B17855BF}"/>
-    <hyperlink ref="D23" r:id="rId149" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{1779EAFC-449E-4713-B38C-666945A2996D}"/>
-    <hyperlink ref="G23" r:id="rId150" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{91C1871B-60B7-4122-AE5C-55D3F373E9D5}"/>
-    <hyperlink ref="E23" r:id="rId151" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B31D41C1-E956-454E-8FE6-2D7C76A5A74D}"/>
-    <hyperlink ref="H23" r:id="rId152" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{B81792B0-2634-41CE-B033-69A945428905}"/>
-    <hyperlink ref="C23" r:id="rId153" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{35EA7A80-DA90-4F1B-A029-732D90495731}"/>
-    <hyperlink ref="F23" r:id="rId154" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{6B06A689-72B1-481B-90B4-3C95B96F24FE}"/>
-    <hyperlink ref="B24" r:id="rId155" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C710A40F-9091-4FCD-9984-DFAF1FD08674}"/>
-    <hyperlink ref="D24" r:id="rId156" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{83C91B1E-6C35-4889-8199-4771DEEB4600}"/>
-    <hyperlink ref="G24" r:id="rId157" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{C12E69D0-4E8C-4D1C-B9FD-8A096523051F}"/>
-    <hyperlink ref="E24" r:id="rId158" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{86F7C565-8216-4660-856F-42C029107EA7}"/>
-    <hyperlink ref="H24" r:id="rId159" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{A17AD685-FA11-4DD1-905C-9CDE825491E3}"/>
-    <hyperlink ref="C24" r:id="rId160" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{BFF1C317-D150-46DB-AC2E-718F4AB38E1F}"/>
-    <hyperlink ref="F24" r:id="rId161" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E11A8AA3-0447-4986-8F69-9BF566CF1CAF}"/>
+    <hyperlink ref="B3" r:id="rId1" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{168B460B-1189-4B6A-97DB-DFBD044CA357}"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{87979AC8-3C67-46C9-B2D1-2B575FF6372B}"/>
+    <hyperlink ref="E3" r:id="rId3" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{89F58227-6D2E-4D86-A608-DE4634DBA055}"/>
+    <hyperlink ref="H3" r:id="rId4" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{244ADAA9-1F67-4365-84D6-B5D924DCC903}"/>
+    <hyperlink ref="C3" r:id="rId5" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{DEFF685A-AC1F-4E25-819E-E2B2C2815987}"/>
+    <hyperlink ref="F3" r:id="rId6" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{D0B44DAF-A30D-44A2-A03A-6D11BB8BC383}"/>
+    <hyperlink ref="B4" r:id="rId7" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{759A9C60-3D06-450D-A0F4-C51FAADF51F3}"/>
+    <hyperlink ref="G4" r:id="rId8" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{BAFC0AE3-DF26-4D94-91A0-E05FF057E230}"/>
+    <hyperlink ref="E4" r:id="rId9" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{4223D41C-85A7-4C23-BBC3-1E7E22554665}"/>
+    <hyperlink ref="H4" r:id="rId10" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{99853853-96F1-46B3-926E-ADCECC115511}"/>
+    <hyperlink ref="C4" r:id="rId11" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{9D8CE963-3348-4088-9D88-BD0D6265190F}"/>
+    <hyperlink ref="F4" r:id="rId12" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{DB25C9E8-2B5E-4DB3-A1CE-068EEC5ABA0A}"/>
+    <hyperlink ref="B5" r:id="rId13" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{DE18B3A2-4CC8-4443-9C4A-CA983AA1B62C}"/>
+    <hyperlink ref="G5" r:id="rId14" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{518B769E-CF07-4768-82A7-A3FC07682DB3}"/>
+    <hyperlink ref="E5" r:id="rId15" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{3DB7637A-4067-4F72-BDAF-6CE2E1D35CC8}"/>
+    <hyperlink ref="H5" r:id="rId16" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{27209BF5-6609-4B21-96A1-AC7799F986E6}"/>
+    <hyperlink ref="C5" r:id="rId17" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{A91323D5-C60E-4A24-9D57-C720C55B84AE}"/>
+    <hyperlink ref="F5" r:id="rId18" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{3CA28400-B522-4FF0-A280-50402F5A9DF8}"/>
+    <hyperlink ref="B6" r:id="rId19" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{77A34E92-C574-4FC5-A25F-76DB4A802DF8}"/>
+    <hyperlink ref="G6" r:id="rId20" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{26E04DFE-8A29-4E2E-A7DE-1F48521A590E}"/>
+    <hyperlink ref="E6" r:id="rId21" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{486E9DB5-857E-467B-9DE1-6A3DA68B5748}"/>
+    <hyperlink ref="H6" r:id="rId22" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{0EDA66B6-D808-4109-B949-EEBBFBBDA1A3}"/>
+    <hyperlink ref="C6" r:id="rId23" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{3D0A4890-E40B-49DC-AF1F-9F7672240BF6}"/>
+    <hyperlink ref="F6" r:id="rId24" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{0F2684F9-6F6F-4976-9F57-57182982C229}"/>
+    <hyperlink ref="B7" r:id="rId25" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A23E0971-A178-4138-AD78-B5C60C5EF678}"/>
+    <hyperlink ref="G7" r:id="rId26" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{2D8E025E-0CF7-4FFF-BDE7-8BC4DBBD4E8F}"/>
+    <hyperlink ref="E7" r:id="rId27" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{04C1985D-97FC-448E-90F8-C89ACD0F10F0}"/>
+    <hyperlink ref="H7" r:id="rId28" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{1D72EC45-8168-45EC-8920-1F7D0D4CFC32}"/>
+    <hyperlink ref="C7" r:id="rId29" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{C1B88871-31DC-4143-B899-38EAD57F0B84}"/>
+    <hyperlink ref="F7" r:id="rId30" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{38B5808F-A8D7-408B-8219-B82AA7DF4FEA}"/>
+    <hyperlink ref="B8" r:id="rId31" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{F871CCDE-478F-47F6-AF9B-3EE980D951B0}"/>
+    <hyperlink ref="G8" r:id="rId32" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{1554D763-8E4A-42B5-93AA-11FBF6A8F929}"/>
+    <hyperlink ref="E8" r:id="rId33" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{F537DB23-619A-42F5-9CC3-60C37A126D08}"/>
+    <hyperlink ref="H8" r:id="rId34" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{7D03DC53-15D2-42B8-91D9-446DFDBEADA1}"/>
+    <hyperlink ref="C8" r:id="rId35" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{F31E7EAB-23B6-4C8D-9AA3-843AEC7A468F}"/>
+    <hyperlink ref="F8" r:id="rId36" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{26EC3AE7-C787-4732-B232-8649103892BE}"/>
+    <hyperlink ref="B9" r:id="rId37" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{8C04BB5D-E046-42DC-AC38-816D6DDFA130}"/>
+    <hyperlink ref="G9" r:id="rId38" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{FD4327BA-F4BB-4E3E-98A2-E83781E941D1}"/>
+    <hyperlink ref="E9" r:id="rId39" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{431B8313-89F9-444B-A052-728FFA326EC9}"/>
+    <hyperlink ref="H9" r:id="rId40" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{C67B9B32-E3EF-4969-9F8F-6286BE171F57}"/>
+    <hyperlink ref="C9" r:id="rId41" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{8FA328E3-D562-49D1-AE74-C9B94DC74EAE}"/>
+    <hyperlink ref="F9" r:id="rId42" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{B388939D-4A1A-4AAA-A836-A9E431347DCE}"/>
+    <hyperlink ref="B10" r:id="rId43" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{4F2B3DD7-61E2-4E9D-B2FD-8C1A653EA9F6}"/>
+    <hyperlink ref="G10" r:id="rId44" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{6DD3C200-38F1-4657-A606-E01F89C8806C}"/>
+    <hyperlink ref="E10" r:id="rId45" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{9790CA92-1278-4191-8ECB-2181ACCAC20F}"/>
+    <hyperlink ref="H10" r:id="rId46" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{6D163243-5CDE-4493-A67F-099AA1E4DEC1}"/>
+    <hyperlink ref="C10" r:id="rId47" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{B241E75F-A566-4245-88D9-F4D20B15F60A}"/>
+    <hyperlink ref="F10" r:id="rId48" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{27ABC12C-D569-48B1-B37B-1955BD2982E6}"/>
+    <hyperlink ref="B11" r:id="rId49" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{8CFB8A04-574C-4EFF-A2CC-B4FB087EE4BE}"/>
+    <hyperlink ref="G11" r:id="rId50" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{D44046E7-23AB-4667-B9D3-B3C11278DD03}"/>
+    <hyperlink ref="E11" r:id="rId51" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E9F8C5A9-EEB5-4980-812C-3F1297EE062D}"/>
+    <hyperlink ref="H11" r:id="rId52" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{4E656E3B-2F9E-4E48-BF52-CD0BABB88444}"/>
+    <hyperlink ref="C11" r:id="rId53" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{02797E23-F39B-4952-9C54-0490D22A0DAB}"/>
+    <hyperlink ref="F11" r:id="rId54" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{9CFCAF37-E4AE-4D09-A0E2-49F41DF8E16D}"/>
+    <hyperlink ref="B12" r:id="rId55" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{FFF4B21A-F3E7-4D08-9230-FCD9F12B9019}"/>
+    <hyperlink ref="G12" r:id="rId56" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{9116818B-9C2F-4058-8D68-5F0A2F46B21E}"/>
+    <hyperlink ref="E12" r:id="rId57" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{97A75E00-0288-4E98-887E-38E6E662E7C0}"/>
+    <hyperlink ref="H12" r:id="rId58" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{FB2FF7DF-81C6-4ED1-8A4A-B556A4B5386D}"/>
+    <hyperlink ref="C12" r:id="rId59" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{8C0E6436-9E3A-45A3-B138-DB17E194DFA4}"/>
+    <hyperlink ref="F12" r:id="rId60" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E49AEBD4-901F-4EA5-BDE5-30AD5F4DC64A}"/>
+    <hyperlink ref="B13" r:id="rId61" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{B3386E2C-D426-44A5-9736-96472F79D6DD}"/>
+    <hyperlink ref="G13" r:id="rId62" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{4E75CD1A-658A-4AA5-8EAE-9BEDAE289B42}"/>
+    <hyperlink ref="E13" r:id="rId63" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{448998DA-C990-4D1A-B35E-2EC6FDAE055E}"/>
+    <hyperlink ref="H13" r:id="rId64" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{95515463-68AB-460F-BC48-144A72140F56}"/>
+    <hyperlink ref="C13" r:id="rId65" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{F81DF56D-8109-4C77-A2A9-0F866B175789}"/>
+    <hyperlink ref="F13" r:id="rId66" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{B59C2387-1E3A-4DD9-B80F-857D76CD4069}"/>
+    <hyperlink ref="B14" r:id="rId67" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{BBA06BC1-68B1-4762-B09C-88251F7894B9}"/>
+    <hyperlink ref="G14" r:id="rId68" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{A26EF1FD-EFFB-478A-91F6-A436722A8F45}"/>
+    <hyperlink ref="E14" r:id="rId69" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{FEDFCD86-0FF9-41BE-8EB5-B3C219D97A1A}"/>
+    <hyperlink ref="H14" r:id="rId70" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{E9B72255-D284-48C1-84D3-34153AD1884F}"/>
+    <hyperlink ref="C14" r:id="rId71" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{25384728-7347-4BD0-AF9D-FC86C9BA11AC}"/>
+    <hyperlink ref="F14" r:id="rId72" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{25CA80AB-0646-4716-BBE0-3140422C639B}"/>
+    <hyperlink ref="B15" r:id="rId73" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{3C067748-E140-499A-9A4D-A40B42B14CF0}"/>
+    <hyperlink ref="G15" r:id="rId74" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{D1437BD9-E808-4BB2-AA84-B327DFD92562}"/>
+    <hyperlink ref="E15" r:id="rId75" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{005888B3-5954-4EED-9F70-2F2DFB22B37C}"/>
+    <hyperlink ref="H15" r:id="rId76" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{AB890CDE-EE37-4E46-8DD9-1D22E6070482}"/>
+    <hyperlink ref="C15" r:id="rId77" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{DB617914-41A5-46A8-A06F-A6D7FC6930C6}"/>
+    <hyperlink ref="F15" r:id="rId78" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{E004E874-DDEE-4540-A1A1-D85330DC1775}"/>
+    <hyperlink ref="B16" r:id="rId79" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C796410A-37DB-46C2-8336-98D0A4E208CD}"/>
+    <hyperlink ref="G16" r:id="rId80" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{0385B754-C904-4066-90D1-CDA3610B0FCC}"/>
+    <hyperlink ref="E16" r:id="rId81" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{DD380D5A-9244-4CAA-AC41-91EE8CCC4BFB}"/>
+    <hyperlink ref="H16" r:id="rId82" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{FCF6AFF2-0A35-4459-9FE5-8D79D87D7C1A}"/>
+    <hyperlink ref="C16" r:id="rId83" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{7D7741C1-3749-4169-A110-09886260F289}"/>
+    <hyperlink ref="F16" r:id="rId84" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{A82CB7FC-C03D-4735-B51D-F3F04548706C}"/>
+    <hyperlink ref="B17" r:id="rId85" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{4A18921A-F198-402E-8C33-5CF63EF60D54}"/>
+    <hyperlink ref="G17" r:id="rId86" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{992D3201-BF3E-4AD7-B779-5F3F701BA8D3}"/>
+    <hyperlink ref="E17" r:id="rId87" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{4F058FD9-7055-4107-A45B-3CF7E3F15993}"/>
+    <hyperlink ref="H17" r:id="rId88" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{549CE1C6-B399-4B50-A9A0-F1421ECF6802}"/>
+    <hyperlink ref="C17" r:id="rId89" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{54F0EC91-5951-4EB8-955D-75C84B285DF8}"/>
+    <hyperlink ref="F17" r:id="rId90" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{B40FF948-6255-4E82-9742-BAD97E50DB9E}"/>
+    <hyperlink ref="B18" r:id="rId91" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{9922AFE8-69DC-4145-852C-BD93B2D7E526}"/>
+    <hyperlink ref="G18" r:id="rId92" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{99C4406E-37EE-4F8B-A8D5-ACADF9A9DC35}"/>
+    <hyperlink ref="E18" r:id="rId93" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{EB9C5B8B-0F9E-43A4-9E28-D66A870BC8AF}"/>
+    <hyperlink ref="H18" r:id="rId94" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{5D68AA7A-0024-4146-BC34-9B466B7EF347}"/>
+    <hyperlink ref="C18" r:id="rId95" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{748309FD-1722-45AD-A789-157689BEF3B9}"/>
+    <hyperlink ref="F18" r:id="rId96" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{6A1ED350-7205-45C1-97CB-97ED176CBAE7}"/>
+    <hyperlink ref="B19" r:id="rId97" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{6945AE6E-9A75-4B85-9F9A-FC28FA784626}"/>
+    <hyperlink ref="G19" r:id="rId98" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{0D665AAF-DD3E-49BE-BFED-8DAF4AAA133C}"/>
+    <hyperlink ref="E19" r:id="rId99" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{B3CF768B-1BC9-4506-85AF-C617D038A256}"/>
+    <hyperlink ref="H19" r:id="rId100" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{EE7FB426-1B11-4D5A-B4B3-57DDB6DC2379}"/>
+    <hyperlink ref="C19" r:id="rId101" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{1EC4E391-8C8D-468B-BFD5-7A414107517F}"/>
+    <hyperlink ref="F19" r:id="rId102" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{B6C31BD6-DB48-4FE5-AC73-77763CFA6E93}"/>
+    <hyperlink ref="B20" r:id="rId103" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{EE505F2B-B6D3-4C87-9CE6-9D7A08F24E76}"/>
+    <hyperlink ref="G20" r:id="rId104" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{3C53E458-EE5A-4E22-A081-89C60DBA23A0}"/>
+    <hyperlink ref="E20" r:id="rId105" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{57844307-D143-4889-BA0C-0BA59BB7C80B}"/>
+    <hyperlink ref="H20" r:id="rId106" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{127124ED-EB0A-4767-819E-77C1941D0E46}"/>
+    <hyperlink ref="C20" r:id="rId107" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{14A9FD7A-5669-4B03-9430-B38E3F204B20}"/>
+    <hyperlink ref="F20" r:id="rId108" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{36E9B5F7-21FF-4EF8-824C-BB9FC2BA931F}"/>
+    <hyperlink ref="B21" r:id="rId109" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{C6692008-8459-4507-B989-978F29706866}"/>
+    <hyperlink ref="G21" r:id="rId110" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{8EDE051D-A351-4165-A0CD-B1543D19848B}"/>
+    <hyperlink ref="E21" r:id="rId111" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{0B776CE4-8447-4626-BD61-88BA2998F9BC}"/>
+    <hyperlink ref="H21" r:id="rId112" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{BDC98CE2-B4C1-4506-A0C3-F820FAA7E464}"/>
+    <hyperlink ref="C21" r:id="rId113" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{B0793806-1E96-4FBF-823B-FE80992F606D}"/>
+    <hyperlink ref="F21" r:id="rId114" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{5EBC087B-818E-494C-BFEC-5D98E8ABAAD7}"/>
+    <hyperlink ref="B22" r:id="rId115" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{6DC1947A-C48A-4F46-BE5C-40326A37F48E}"/>
+    <hyperlink ref="G22" r:id="rId116" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{A204848A-6664-48BB-BEC1-6436BA873A39}"/>
+    <hyperlink ref="E22" r:id="rId117" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{E19A8FFA-FED7-4384-AC41-E6E5616C6493}"/>
+    <hyperlink ref="H22" r:id="rId118" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{BB96A111-87E9-4C1A-90DF-70DFAEA051A6}"/>
+    <hyperlink ref="C22" r:id="rId119" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{EFF9EE7D-0635-427C-AB30-F90D1712504B}"/>
+    <hyperlink ref="F22" r:id="rId120" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{3693FE38-7EB3-4E32-B38D-F4DA4358ACBA}"/>
+    <hyperlink ref="B23" r:id="rId121" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{A9272D5C-502E-4DD1-88E2-9F0893233653}"/>
+    <hyperlink ref="G23" r:id="rId122" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{F2F2A1F4-0F49-4C65-B8E5-F979D18AD534}"/>
+    <hyperlink ref="E23" r:id="rId123" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{3BFA2DD2-7BDB-429F-B335-35DC868C2612}"/>
+    <hyperlink ref="H23" r:id="rId124" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{800F4798-1877-4786-BC14-AB21184DD3D9}"/>
+    <hyperlink ref="C23" r:id="rId125" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{E596EA66-70F6-40C6-BBE2-C1F26269AFAE}"/>
+    <hyperlink ref="F23" r:id="rId126" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{79F2716F-A3B9-4582-B46E-7CFE863EFBAB}"/>
+    <hyperlink ref="B24" r:id="rId127" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{AC9B0794-25D6-40DA-8BF7-203E7ECC8A7F}"/>
+    <hyperlink ref="G24" r:id="rId128" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{75FC175F-8D6F-4E26-8D7D-8D3EA9E309CF}"/>
+    <hyperlink ref="E24" r:id="rId129" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{D3451EB4-9CEF-4137-81E1-3A7C2FE2CE4E}"/>
+    <hyperlink ref="H24" r:id="rId130" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{776D6DAB-315D-4F7C-A255-E7F319102FD1}"/>
+    <hyperlink ref="C24" r:id="rId131" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{6504F9F0-6FF0-4A4F-8FC4-47C1305237F3}"/>
+    <hyperlink ref="F24" r:id="rId132" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{EB498C27-DD0C-4866-AAD4-89CBF389934E}"/>
+    <hyperlink ref="B2" r:id="rId133" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22To+Do+%280%25%29%22" xr:uid="{6F2897C4-D591-4461-84E6-39BC75932C04}"/>
+    <hyperlink ref="G2" r:id="rId134" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22Done+%28100%25%29%22" xr:uid="{98323EB9-3E4B-4BBC-AD21-C0EBE71AC16B}"/>
+    <hyperlink ref="E2" r:id="rId135" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22IN+REVIEW+%2880%25%29%22" xr:uid="{585F74A4-A7E9-4499-9D04-032A1CA14B10}"/>
+    <hyperlink ref="H2" r:id="rId136" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22WON%27T+DO+%28100%25%29%22" xr:uid="{49DCEDA9-4570-41E9-98B9-44F7A88526E3}"/>
+    <hyperlink ref="C2" r:id="rId137" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22STARTING+%2810+%7E+40%25%29%22" xr:uid="{18B789C6-2E3D-4FFE-8471-E49419EA2AB4}"/>
+    <hyperlink ref="F2" r:id="rId138" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22READY+FOR+TESTING+%2890%25%29%22" xr:uid="{BC3EC03D-1D60-443F-AF41-99880BAD004B}"/>
+    <hyperlink ref="D2" r:id="rId139" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2915+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{9E2BAB85-23A5-4294-99A4-E7D6411DFAF6}"/>
+    <hyperlink ref="D24" r:id="rId140" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5078+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{EB686661-DA27-47FF-8A46-D76BAC87539C}"/>
+    <hyperlink ref="D23" r:id="rId141" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5045+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{23B650E0-C52D-43CC-9D37-672ECCC703CA}"/>
+    <hyperlink ref="D22" r:id="rId142" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+5044+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{B0F550F8-06C6-458F-81BE-199FF300AB63}"/>
+    <hyperlink ref="D21" r:id="rId143" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4910+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{4E82F980-9AEC-42AD-9D89-9D22B7692A83}"/>
+    <hyperlink ref="D20" r:id="rId144" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4678+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{A40CA3A0-EFC6-4C97-832C-74A24CCDC6FF}"/>
+    <hyperlink ref="D19" r:id="rId145" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4677+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{78F5DB2E-49A2-451E-AC9D-70A254B63E14}"/>
+    <hyperlink ref="D18" r:id="rId146" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4478+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{A6F029A3-E574-4882-AB27-5DC3892BB0D1}"/>
+    <hyperlink ref="D17" r:id="rId147" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4477+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{DE81F827-A8A9-4CE5-94AC-82E5A9FCF4CB}"/>
+    <hyperlink ref="D16" r:id="rId148" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4206+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{E7964B2C-7A63-41C6-AD1A-E9F9212CE103}"/>
+    <hyperlink ref="D15" r:id="rId149" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+4140+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{4E046E7A-D71D-40B0-AB93-762BD7EB2892}"/>
+    <hyperlink ref="D14" r:id="rId150" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3873+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{CB920B08-B9D8-42FF-93E8-E115527B4A2D}"/>
+    <hyperlink ref="D13" r:id="rId151" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3872+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{5060CA80-D235-41FD-8A74-5BA0888DF912}"/>
+    <hyperlink ref="D12" r:id="rId152" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3608+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{BDD4902B-F0B4-4964-818E-A7AE70F194CC}"/>
+    <hyperlink ref="D11" r:id="rId153" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3575+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{91522E47-043D-498E-99A0-B240A929024E}"/>
+    <hyperlink ref="D10" r:id="rId154" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3246+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{FFC4ACC3-C5C2-4759-9B11-0CFF472A3E4A}"/>
+    <hyperlink ref="D9" r:id="rId155" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3245+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{9BF99F6C-DE1A-4A9A-9C88-B986A4A3ED2A}"/>
+    <hyperlink ref="D8" r:id="rId156" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+3213+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{E20A65AE-4C6A-4C48-BD56-2A4B8D844CC8}"/>
+    <hyperlink ref="D7" r:id="rId157" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2882+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{58F2D1D3-35F4-436B-8AF8-5E960B532FE6}"/>
+    <hyperlink ref="D6" r:id="rId158" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2619+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{3C745B55-B5E0-4CBA-89A8-AB62AAF2EAF7}"/>
+    <hyperlink ref="D5" r:id="rId159" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2618+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{5CE0A86F-B0A3-4097-A350-7085C39E75A6}"/>
+    <hyperlink ref="D4" r:id="rId160" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2157+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{68C6E5C8-234F-4FC1-B8A0-F309D420B769}"/>
+    <hyperlink ref="D3" r:id="rId161" display="https://xrspace.atlassian.net/issues/?jql=created+%3E%3D+2025-02-01+AND+created+%3C%3D+2026-12-31+AND+type+%3D+Bug+AND+project+%3D+SOVA+AND+Sprint+%3D+2156+AND+status+%3D+%22In+Progress+%2850+%7E+70%25%29%22" xr:uid="{09D6BEAB-506C-402E-ACDB-3F3690009EC6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId162"/>
@@ -16598,7 +16777,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC3F3FC-17EF-4D6A-9290-8FAFFC789915}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.5546875" customWidth="1"/>
@@ -17105,6 +17284,42 @@
       <c r="E28" s="14">
         <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
         <v>198</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="A29" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="14">
+        <v>100</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>98</v>
+      </c>
+      <c r="E29" s="14">
+        <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="A30" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" s="14">
+        <v>101</v>
+      </c>
+      <c r="C30" s="14">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14">
+        <v>98</v>
+      </c>
+      <c r="E30" s="14">
+        <f>SUM(Table25[[#This Row],[Done]:[TODO (P1)]])</f>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
